--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30249,6 +30249,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1300">
+      <c r="A1300" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1300" t="n">
+        <v>496</v>
+      </c>
+      <c r="C1300" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="D1300" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="G1300" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30272,6 +30272,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1301">
+      <c r="A1301" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1301" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1301" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="G1301" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30295,6 +30295,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1302">
+      <c r="A1302" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1302" t="n">
+        <v>3893</v>
+      </c>
+      <c r="C1302" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="G1302" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30318,6 +30318,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1303">
+      <c r="A1303" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1303" t="n">
+        <v>10750</v>
+      </c>
+      <c r="C1303" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="G1303" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30159,10 +30159,10 @@
     </row>
     <row r="1296">
       <c r="A1296" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1296" t="n">
-        <v>1934</v>
+        <v>760</v>
       </c>
       <c r="C1296" t="n">
         <v>3.44000005722046</v>
@@ -30171,7 +30171,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="E1296" t="n">
-        <v>3.40000009536743</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="F1296" t="n">
         <v>3.40000009536743</v>
@@ -30182,16 +30182,16 @@
     </row>
     <row r="1297">
       <c r="A1297" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1297" t="n">
-        <v>4312</v>
+        <v>1934</v>
       </c>
       <c r="C1297" t="n">
-        <v>3.4300000667572</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="D1297" t="n">
-        <v>3.33999991416931</v>
+        <v>3.40000009536743</v>
       </c>
       <c r="E1297" t="n">
         <v>3.40000009536743</v>
@@ -30205,22 +30205,22 @@
     </row>
     <row r="1298">
       <c r="A1298" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1298" t="n">
-        <v>4084</v>
+        <v>4312</v>
       </c>
       <c r="C1298" t="n">
-        <v>3.45000004768372</v>
+        <v>3.4300000667572</v>
       </c>
       <c r="D1298" t="n">
-        <v>3.38000011444092</v>
+        <v>3.33999991416931</v>
       </c>
       <c r="E1298" t="n">
-        <v>3.4300000667572</v>
+        <v>3.40000009536743</v>
       </c>
       <c r="F1298" t="n">
-        <v>3.45000004768372</v>
+        <v>3.40000009536743</v>
       </c>
       <c r="G1298" t="s">
         <v>7</v>
@@ -30228,22 +30228,22 @@
     </row>
     <row r="1299">
       <c r="A1299" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1299" t="n">
-        <v>8732</v>
+        <v>4084</v>
       </c>
       <c r="C1299" t="n">
         <v>3.45000004768372</v>
       </c>
       <c r="D1299" t="n">
-        <v>3.39000010490417</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="E1299" t="n">
-        <v>3.44000005722046</v>
+        <v>3.4300000667572</v>
       </c>
       <c r="F1299" t="n">
-        <v>3.44000005722046</v>
+        <v>3.45000004768372</v>
       </c>
       <c r="G1299" t="s">
         <v>7</v>
@@ -30251,22 +30251,22 @@
     </row>
     <row r="1300">
       <c r="A1300" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1300" t="n">
-        <v>496</v>
+        <v>8732</v>
       </c>
       <c r="C1300" t="n">
-        <v>3.4300000667572</v>
+        <v>3.45000004768372</v>
       </c>
       <c r="D1300" t="n">
-        <v>3.35999989509583</v>
+        <v>3.39000010490417</v>
       </c>
       <c r="E1300" t="n">
-        <v>3.4300000667572</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="F1300" t="n">
-        <v>3.42000007629395</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="G1300" t="s">
         <v>7</v>
@@ -30274,22 +30274,22 @@
     </row>
     <row r="1301">
       <c r="A1301" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1301" t="n">
-        <v>4</v>
+        <v>496</v>
       </c>
       <c r="C1301" t="n">
-        <v>3.35999989509583</v>
+        <v>3.4300000667572</v>
       </c>
       <c r="D1301" t="n">
         <v>3.35999989509583</v>
       </c>
       <c r="E1301" t="n">
-        <v>3.35999989509583</v>
+        <v>3.4300000667572</v>
       </c>
       <c r="F1301" t="n">
-        <v>3.35999989509583</v>
+        <v>3.42000007629395</v>
       </c>
       <c r="G1301" t="s">
         <v>7</v>
@@ -30297,22 +30297,22 @@
     </row>
     <row r="1302">
       <c r="A1302" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1302" t="n">
-        <v>3893</v>
+        <v>4</v>
       </c>
       <c r="C1302" t="n">
-        <v>3.44000005722046</v>
+        <v>3.35999989509583</v>
       </c>
       <c r="D1302" t="n">
-        <v>3.34999990463257</v>
+        <v>3.35999989509583</v>
       </c>
       <c r="E1302" t="n">
-        <v>3.34999990463257</v>
+        <v>3.35999989509583</v>
       </c>
       <c r="F1302" t="n">
-        <v>3.44000005722046</v>
+        <v>3.35999989509583</v>
       </c>
       <c r="G1302" t="s">
         <v>7</v>
@@ -30320,24 +30320,47 @@
     </row>
     <row r="1303">
       <c r="A1303" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1303" t="n">
-        <v>10750</v>
+        <v>3893</v>
       </c>
       <c r="C1303" t="n">
-        <v>3.4300000667572</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="D1303" t="n">
-        <v>3.4300000667572</v>
+        <v>3.34999990463257</v>
       </c>
       <c r="E1303" t="n">
-        <v>3.4300000667572</v>
+        <v>3.34999990463257</v>
       </c>
       <c r="F1303" t="n">
-        <v>3.4300000667572</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="G1303" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1304" t="n">
+        <v>8058</v>
+      </c>
+      <c r="C1304" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="G1304" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11975526809692</v>
+        <v>3.11975502967834</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.13789367675781</v>
+        <v>3.13789343833923</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G15" t="n">
-        <v>3.39182710647583</v>
+        <v>3.39182686805725</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>3.73645067214966</v>
+        <v>3.73645091056824</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75458860397339</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75458860397339</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G24" t="n">
-        <v>3.73645067214966</v>
+        <v>3.73645091056824</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.89515924453735</v>
+        <v>3.89515972137451</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876317024231</v>
+        <v>3.90876269340515</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726173400879</v>
+        <v>3.77726149559021</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993438720703</v>
+        <v>3.79993462562561</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365852355957</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G39" t="n">
-        <v>3.79086518287659</v>
+        <v>3.79086542129517</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633117675781</v>
+        <v>3.78633093833923</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>3.78179621696472</v>
+        <v>3.7817964553833</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75458860397339</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365852355957</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.80900359153748</v>
+        <v>3.80900287628174</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G55" t="n">
-        <v>3.65482950210571</v>
+        <v>3.65482974052429</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G56" t="n">
-        <v>3.65482950210571</v>
+        <v>3.65482974052429</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284770011902</v>
+        <v>3.72284746170044</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110584259033</v>
+        <v>3.69110608100891</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>3.75458860397339</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110584259033</v>
+        <v>3.69110608100891</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320809364319</v>
+        <v>3.57320785522461</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G83" t="n">
-        <v>3.54600119590759</v>
+        <v>3.54600095748901</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47344827651978</v>
+        <v>3.4734480381012</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>3.41449975967407</v>
+        <v>3.41449999809265</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996527671814</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996527671814</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008524894714</v>
+        <v>3.36008501052856</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>3.41449975967407</v>
+        <v>3.41449999809265</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077586174011</v>
+        <v>3.45077610015869</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G117" t="n">
-        <v>3.60041546821594</v>
+        <v>3.60041522979736</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287811279297</v>
+        <v>3.33287787437439</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>3.26486039161682</v>
+        <v>3.26486015319824</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32834339141846</v>
+        <v>3.32834362983704</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42810320854187</v>
+        <v>3.42810297012329</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.3963611125946</v>
+        <v>3.39636135101318</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G129" t="n">
-        <v>3.3963611125946</v>
+        <v>3.39636135101318</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G131" t="n">
-        <v>3.27392911911011</v>
+        <v>3.27392935752869</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>3.26486039161682</v>
+        <v>3.26486015319824</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404932975769</v>
+        <v>3.22404956817627</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>3.31927442550659</v>
+        <v>3.31927466392517</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.47344827651978</v>
+        <v>3.4734480381012</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G145" t="n">
-        <v>3.31927442550659</v>
+        <v>3.31927466392517</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G147" t="n">
-        <v>3.22858381271362</v>
+        <v>3.2285840511322</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.14696216583252</v>
+        <v>3.1469624042511</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510057449341</v>
+        <v>3.16510033607483</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756345748901</v>
+        <v>2.89756321907043</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>3.01546096801758</v>
+        <v>3.01546120643616</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278855323792</v>
+        <v>2.99278831481934</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615134239197</v>
+        <v>3.10615158081055</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266858100891</v>
+        <v>3.04266834259033</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G195" t="n">
-        <v>3.09254837036133</v>
+        <v>3.09254813194275</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G197" t="n">
-        <v>3.01546096801758</v>
+        <v>3.01546120643616</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G201" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.36461973190308</v>
+        <v>3.36461997032166</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765277862549</v>
+        <v>3.23765301704407</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>3.11975526809692</v>
+        <v>3.11975502967834</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.92930483818054</v>
+        <v>2.92930507659912</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G226" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>2.79326915740967</v>
+        <v>2.79326939582825</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G251" t="n">
-        <v>2.75245881080627</v>
+        <v>2.7524585723877</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G252" t="n">
-        <v>2.75245881080627</v>
+        <v>2.7524585723877</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456058502197</v>
+        <v>2.63456082344055</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.67537188529968</v>
+        <v>2.67537140846252</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.6300265789032</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G271" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>2.45317983627319</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.29900574684143</v>
+        <v>2.29900598526001</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.2309877872467</v>
+        <v>2.23098754882812</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.13576245307922</v>
+        <v>2.1357626914978</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.33074736595154</v>
+        <v>2.33074712753296</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>2.34435081481934</v>
+        <v>2.34435105323792</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33074736595154</v>
+        <v>2.33074712753296</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.43050694465637</v>
+        <v>2.43050718307495</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46678304672241</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46678304672241</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G322" t="n">
-        <v>2.46224880218506</v>
+        <v>2.46224856376648</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.39876532554626</v>
+        <v>2.39876508712769</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>2.43050694465637</v>
+        <v>2.43050718307495</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.2944712638855</v>
+        <v>2.29447102546692</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.30807495117188</v>
+        <v>2.3080747127533</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G337" t="n">
-        <v>2.29900574684143</v>
+        <v>2.29900598526001</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.32167816162109</v>
+        <v>2.32167792320251</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528208732605</v>
+        <v>2.33528184890747</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179861068726</v>
+        <v>2.27179837226868</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G352" t="n">
-        <v>2.45317983627319</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34888529777527</v>
+        <v>2.34888577461243</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G368" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41690349578857</v>
+        <v>2.41690325737</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.38969612121582</v>
+        <v>2.3896963596344</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933596611023</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.49852514266968</v>
+        <v>2.4985249042511</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933596611023</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933596611023</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933596611023</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57107734680176</v>
+        <v>2.57107758522034</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666283607483</v>
+        <v>2.51666307449341</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933596611023</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.6300265789032</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.6300265789032</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.6300265789032</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>2.6300265789032</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.46224880218506</v>
+        <v>2.46224856376648</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573204040527</v>
+        <v>2.52573227882385</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34888529777527</v>
+        <v>2.34888577461243</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G423" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>2.46678304672241</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G435" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G438" t="n">
-        <v>2.6300265789032</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G441" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.66630268096924</v>
+        <v>2.66630244255066</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G447" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -34328,6 +34328,32 @@
         <v>3.40000009536743</v>
       </c>
       <c r="H1306" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1307" t="n">
+        <v>2532</v>
+      </c>
+      <c r="C1307" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="H1307" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11975502967834</v>
+        <v>3.11975526809692</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1333589553833</v>
+        <v>3.13335871696472</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.56867337226868</v>
+        <v>3.56867361068726</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4008960723877</v>
+        <v>3.40089583396912</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924401283264</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924401283264</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458931922913</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458931922913</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876269340515</v>
+        <v>3.90876317024231</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726149559021</v>
+        <v>3.77726173400879</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993462562561</v>
+        <v>3.79993438720703</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377801895142</v>
+        <v>3.71377825737</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>3.56413888931274</v>
+        <v>3.5641393661499</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>3.56413888931274</v>
+        <v>3.5641393661499</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>3.6729679107666</v>
+        <v>3.67296743392944</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365852355957</v>
+        <v>3.76365804672241</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G39" t="n">
-        <v>3.79086542129517</v>
+        <v>3.79086518287659</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>3.7817964553833</v>
+        <v>3.78179621696472</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458931922913</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365852355957</v>
+        <v>3.76365804672241</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.80900287628174</v>
+        <v>3.8090033531189</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284746170044</v>
+        <v>3.72284722328186</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>3.69564008712769</v>
+        <v>3.69564032554626</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>3.68203687667847</v>
+        <v>3.68203663825989</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>3.6729679107666</v>
+        <v>3.67296743392944</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458931922913</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.68203687667847</v>
+        <v>3.68203663825989</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>3.63215708732605</v>
+        <v>3.63215684890747</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320785522461</v>
+        <v>3.57320809364319</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G85" t="n">
-        <v>3.50065565109253</v>
+        <v>3.50065541267395</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729214668274</v>
+        <v>3.38729238510132</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.45984506607056</v>
+        <v>3.45984482765198</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.4734480381012</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555052757263</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891403198242</v>
+        <v>3.46891379356384</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>3.42356872558594</v>
+        <v>3.42356896400452</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>3.41449999809265</v>
+        <v>3.41449975967407</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996503829956</v>
+        <v>3.40996479988098</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996503829956</v>
+        <v>3.40996479988098</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008501052856</v>
+        <v>3.36008524894714</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555052757263</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555052757263</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50065565109253</v>
+        <v>3.50065541267395</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>3.41449999809265</v>
+        <v>3.41449975967407</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077610015869</v>
+        <v>3.45077562332153</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42810297012329</v>
+        <v>3.42810320854187</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G131" t="n">
-        <v>3.27392935752869</v>
+        <v>3.27392911911011</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404956817627</v>
+        <v>3.22404932975769</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>3.31927466392517</v>
+        <v>3.31927442550659</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G137" t="n">
-        <v>3.3510160446167</v>
+        <v>3.35101580619812</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555052757263</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G141" t="n">
-        <v>3.5278627872467</v>
+        <v>3.52786302566528</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.4734480381012</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.75</v>
       </c>
       <c r="G143" t="n">
-        <v>3.4008960723877</v>
+        <v>3.40089583396912</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G145" t="n">
-        <v>3.31927466392517</v>
+        <v>3.31927442550659</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>3.09708261489868</v>
+        <v>3.0970823764801</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G147" t="n">
-        <v>3.2285840511322</v>
+        <v>3.22858381271362</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>3.25125646591187</v>
+        <v>3.25125670433044</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510033607483</v>
+        <v>3.16510057449341</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.97465038299561</v>
+        <v>2.97465062141418</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570115089417</v>
+        <v>2.91570162773132</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278831481934</v>
+        <v>2.99278855323792</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>3.09708261489868</v>
+        <v>3.0970823764801</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>3.21044588088989</v>
+        <v>3.21044564247131</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.37368869781494</v>
+        <v>3.37368893623352</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615158081055</v>
+        <v>3.10615181922913</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>3.11522054672241</v>
+        <v>3.11522078514099</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.91116714477539</v>
+        <v>2.91116690635681</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G179" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>2.97465038299561</v>
+        <v>2.97465062141418</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266834259033</v>
+        <v>3.04266858100891</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G189" t="n">
-        <v>2.99732327461243</v>
+        <v>2.99732303619385</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627155303955</v>
+        <v>3.05627179145813</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.06534099578857</v>
+        <v>3.06534123420715</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489080429077</v>
+        <v>2.87489104270935</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>2.95651245117188</v>
+        <v>2.9565122127533</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G207" t="n">
-        <v>2.92477035522461</v>
+        <v>2.92477059364319</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>3.00639200210571</v>
+        <v>3.00639224052429</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416977882385</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>3.11975502967834</v>
+        <v>3.11975526809692</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>3.11522054672241</v>
+        <v>3.11522078514099</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416977882385</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603137016296</v>
+        <v>3.15603160858154</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570115089417</v>
+        <v>2.91570162773132</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489080429077</v>
+        <v>2.87489104270935</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954549789429</v>
+        <v>2.82954525947571</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.88849425315857</v>
+        <v>2.88849401473999</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>2.77513122558594</v>
+        <v>2.77513098716736</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350957870483</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.67537140846252</v>
+        <v>2.6753716468811</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.5801465511322</v>
+        <v>2.58014631271362</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.59828448295593</v>
+        <v>2.59828472137451</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.53480100631714</v>
+        <v>2.53480124473572</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062715530396</v>
+        <v>2.38062691688538</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.35342001914978</v>
+        <v>2.35342025756836</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.28086757659912</v>
+        <v>2.28086805343628</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.29900598526001</v>
+        <v>2.29900574684143</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.23098754882812</v>
+        <v>2.23098802566528</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750454902649</v>
+        <v>2.16750431060791</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.33074712753296</v>
+        <v>2.33074736595154</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.22645306587219</v>
+        <v>2.22645330429077</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14029693603516</v>
+        <v>2.14029717445374</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33074712753296</v>
+        <v>2.33074736595154</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G305" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.43050718307495</v>
+        <v>2.43050694465637</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G314" t="n">
-        <v>2.48038673400879</v>
+        <v>2.48038649559021</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G316" t="n">
-        <v>2.50759387016296</v>
+        <v>2.50759410858154</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>2.53480100631714</v>
+        <v>2.53480124473572</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G322" t="n">
-        <v>2.46224856376648</v>
+        <v>2.46224880218506</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.39876508712769</v>
+        <v>2.39876532554626</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>2.43050718307495</v>
+        <v>2.43050694465637</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.35342001914978</v>
+        <v>2.35342025756836</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28540205955505</v>
+        <v>2.28540229797363</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G337" t="n">
-        <v>2.29900598526001</v>
+        <v>2.29900574684143</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.32167792320251</v>
+        <v>2.32167840003967</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528184890747</v>
+        <v>2.33528208732605</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993678092957</v>
+        <v>2.28993654251099</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005651473999</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G343" t="n">
-        <v>2.27633285522461</v>
+        <v>2.27633309364319</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>2.27633285522461</v>
+        <v>2.27633309364319</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179837226868</v>
+        <v>2.27179884910583</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005651473999</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34888577461243</v>
+        <v>2.34888529777527</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G370" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41690325737</v>
+        <v>2.41690349578857</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.3896963596344</v>
+        <v>2.38969588279724</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>2.56200838088989</v>
+        <v>2.56200861930847</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57107758522034</v>
+        <v>2.57107710838318</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666307449341</v>
+        <v>2.51666283607483</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G398" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.53480100631714</v>
+        <v>2.53480124473572</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840445518494</v>
+        <v>2.54840469360352</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840445518494</v>
+        <v>2.54840469360352</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281920433044</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G403" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281920433044</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281920433044</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G412" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.46224856376648</v>
+        <v>2.46224880218506</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573227882385</v>
+        <v>2.52573204040527</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34888577461243</v>
+        <v>2.34888529777527</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47131752967834</v>
+        <v>2.47131776809692</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G428" t="n">
-        <v>2.56200838088989</v>
+        <v>2.56200861930847</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G438" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G441" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281920433044</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G446" t="n">
-        <v>2.59374976158142</v>
+        <v>2.59375</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350957870483</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G455" t="n">
-        <v>2.82047653198242</v>
+        <v>2.82047629356384</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>2.81140732765198</v>
+        <v>2.8114070892334</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G461" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G462" t="n">
-        <v>2.74043488502502</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G463" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74043488502502</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G465" t="n">
-        <v>2.74043488502502</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>2.74966192245483</v>
+        <v>2.74966168403625</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G474" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G478" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G486" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61125612258911</v>
+        <v>2.61125588417053</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G489" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G490" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G494" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G497" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.74043488502502</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G499" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G511" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G513" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.74043488502502</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G531" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>2.74043488502502</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.74043488502502</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G559" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74966192245483</v>
+        <v>2.74966168403625</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.55589365959167</v>
+        <v>2.55589389801025</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G579" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G581" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G582" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.57434797286987</v>
+        <v>2.57434773445129</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.61125612258911</v>
+        <v>2.61125588417053</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G589" t="n">
-        <v>2.50975847244263</v>
+        <v>2.50975871086121</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G592" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G594" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G597" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>2.50975847244263</v>
+        <v>2.50975871086121</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G615" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>2.74966192245483</v>
+        <v>2.74966168403625</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>2.74966192245483</v>
+        <v>2.74966168403625</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797093391418</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797093391418</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>3.15565228462219</v>
+        <v>3.15565252304077</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>3.15565228462219</v>
+        <v>3.15565252304077</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797093391418</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>3.32173943519592</v>
+        <v>3.32173919677734</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>3.34019327163696</v>
+        <v>3.34019303321838</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G658" t="n">
-        <v>3.29405784606934</v>
+        <v>3.29405808448792</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>3.0633819103241</v>
+        <v>3.06338167190552</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>2.96188426017761</v>
+        <v>2.96188402175903</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.88806772232056</v>
+        <v>2.88806796073914</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G666" t="n">
-        <v>2.85115957260132</v>
+        <v>2.85115933418274</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>2.84193229675293</v>
+        <v>2.84193253517151</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G692" t="n">
-        <v>2.83270525932312</v>
+        <v>2.8327054977417</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>2.84193229675293</v>
+        <v>2.84193253517151</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>2.94342994689941</v>
+        <v>2.94343018531799</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>2.96188426017761</v>
+        <v>2.96188402175903</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.25</v>
       </c>
       <c r="G699" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.25</v>
       </c>
       <c r="G705" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.25</v>
       </c>
       <c r="G706" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G709" t="n">
-        <v>3.0633819103241</v>
+        <v>3.06338167190552</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.32173943519592</v>
+        <v>3.32173919677734</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>3.34019327163696</v>
+        <v>3.34019303321838</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G718" t="n">
-        <v>3.42463660240173</v>
+        <v>3.42463636398315</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G720" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G721" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>3.62167024612427</v>
+        <v>3.62167000770569</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G730" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G733" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G737" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>3.5372269153595</v>
+        <v>3.53722715377808</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.66858291625977</v>
+        <v>3.66858315467834</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G762" t="n">
-        <v>3.62167024612427</v>
+        <v>3.62167000770569</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G768" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G771" t="n">
-        <v>3.649817943573</v>
+        <v>3.64981818199158</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G779" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G791" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G795" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85623455047607</v>
+        <v>3.8562343120575</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88438177108765</v>
+        <v>3.88438200950623</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G802" t="n">
-        <v>3.88438177108765</v>
+        <v>3.88438200950623</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>3.96882486343384</v>
+        <v>3.96882510185242</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G811" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>4.10018062591553</v>
+        <v>4.10018110275269</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G826" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>4.3065972328186</v>
+        <v>4.30659770965576</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G838" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G850" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G865" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G869" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G881" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G883" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G885" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G886" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G890" t="n">
-        <v>3.66858291625977</v>
+        <v>3.66858315467834</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G891" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.25</v>
       </c>
       <c r="G900" t="n">
-        <v>3.98759031295776</v>
+        <v>3.98759055137634</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G901" t="n">
-        <v>3.9782075881958</v>
+        <v>3.97820734977722</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G904" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G914" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G915" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G919" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G921" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G923" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.85623455047607</v>
+        <v>3.8562343120575</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G926" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>4.10018062591553</v>
+        <v>4.10018110275269</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G929" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.25</v>
       </c>
       <c r="G930" t="n">
-        <v>3.98759031295776</v>
+        <v>3.98759055137634</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G935" t="n">
-        <v>3.96882486343384</v>
+        <v>3.96882510185242</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G936" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G946" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.14709377288818</v>
+        <v>4.14709424972534</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G958" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G962" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -34354,6 +34354,32 @@
         <v>3.39000010490417</v>
       </c>
       <c r="H1307" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1308" t="n">
+        <v>1523</v>
+      </c>
+      <c r="C1308" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="H1308" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161709785461</v>
+        <v>3.10161733627319</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.13335871696472</v>
+        <v>3.1333589553833</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>3.40089583396912</v>
+        <v>3.4008960723877</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75458931922913</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75458931922913</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876317024231</v>
+        <v>3.90876293182373</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726173400879</v>
+        <v>3.77726149559021</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993438720703</v>
+        <v>3.79993462562561</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>3.5641393661499</v>
+        <v>3.56413888931274</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>3.5641393661499</v>
+        <v>3.56413888931274</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>3.67296743392944</v>
+        <v>3.6729679107666</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365804672241</v>
+        <v>3.76365828514099</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G39" t="n">
-        <v>3.79086518287659</v>
+        <v>3.79086542129517</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>3.78179621696472</v>
+        <v>3.7817964553833</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75458931922913</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365804672241</v>
+        <v>3.76365828514099</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.8090033531189</v>
+        <v>3.80900311470032</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936398506165</v>
+        <v>3.65936374664307</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.7001748085022</v>
+        <v>3.70017504692078</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284722328186</v>
+        <v>3.72284770011902</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>3.69564032554626</v>
+        <v>3.69564008712769</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110584259033</v>
+        <v>3.69110608100891</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>3.67296743392944</v>
+        <v>3.6729679107666</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>3.75458931922913</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936398506165</v>
+        <v>3.65936374664307</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110584259033</v>
+        <v>3.69110608100891</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.7001748085022</v>
+        <v>3.70017504692078</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G85" t="n">
-        <v>3.50065541267395</v>
+        <v>3.50065565109253</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729238510132</v>
+        <v>3.38729214668274</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47798299789429</v>
+        <v>3.47798275947571</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.4462411403656</v>
+        <v>3.44624090194702</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.47798299789429</v>
+        <v>3.47798275947571</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.48251724243164</v>
+        <v>3.48251748085022</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>3.35555052757263</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>3.3238091468811</v>
+        <v>3.32380890846252</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531034469604</v>
+        <v>3.45531010627747</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891379356384</v>
+        <v>3.46891403198242</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>3.41449975967407</v>
+        <v>3.41449999809265</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996479988098</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996479988098</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008524894714</v>
+        <v>3.36008501052856</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>3.35555052757263</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35555052757263</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50065541267395</v>
+        <v>3.50065565109253</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48251724243164</v>
+        <v>3.48251748085022</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>3.41449975967407</v>
+        <v>3.41449999809265</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.4961211681366</v>
+        <v>3.49612092971802</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077562332153</v>
+        <v>3.45077586174011</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>3.55960440635681</v>
+        <v>3.55960464477539</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.4961211681366</v>
+        <v>3.49612092971802</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287787437439</v>
+        <v>3.33287811279297</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42810320854187</v>
+        <v>3.42810297012329</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951460838318</v>
+        <v>3.21951484680176</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30113649368286</v>
+        <v>3.30113625526428</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G137" t="n">
-        <v>3.35101580619812</v>
+        <v>3.3510160446167</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020545959473</v>
+        <v>3.31020522117615</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>3.35555052757263</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G141" t="n">
-        <v>3.52786302566528</v>
+        <v>3.5278627872467</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.75</v>
       </c>
       <c r="G143" t="n">
-        <v>3.40089583396912</v>
+        <v>3.4008960723877</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>3.30113649368286</v>
+        <v>3.30113625526428</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>3.0970823764801</v>
+        <v>3.09708261489868</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510057449341</v>
+        <v>3.16510033607483</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.97465062141418</v>
+        <v>2.97465038299561</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570162773132</v>
+        <v>2.91570138931274</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.96104669570923</v>
+        <v>2.96104693412781</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278855323792</v>
+        <v>2.99278831481934</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G165" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>3.0970823764801</v>
+        <v>3.09708261489868</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G173" t="n">
-        <v>3.1605658531189</v>
+        <v>3.16056561470032</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.91116690635681</v>
+        <v>2.91116714477539</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.02453017234802</v>
+        <v>3.02452993392944</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G179" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>2.97465062141418</v>
+        <v>2.97465038299561</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G182" t="n">
-        <v>2.97918486595154</v>
+        <v>2.97918510437012</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266858100891</v>
+        <v>3.04266810417175</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G189" t="n">
-        <v>2.99732303619385</v>
+        <v>2.99732327461243</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744300842285</v>
+        <v>2.94744324684143</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489104270935</v>
+        <v>2.87489056587219</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744300842285</v>
+        <v>2.94744324684143</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011590003967</v>
+        <v>2.97011613845825</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G207" t="n">
-        <v>2.92477059364319</v>
+        <v>2.92477035522461</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>3.00639224052429</v>
+        <v>3.00639200210571</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951460838318</v>
+        <v>3.21951484680176</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753280639648</v>
+        <v>3.28753304481506</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416977882385</v>
+        <v>3.17416954040527</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.1605658531189</v>
+        <v>3.16056561470032</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416977882385</v>
+        <v>3.17416954040527</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603160858154</v>
+        <v>3.15603137016296</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.92930507659912</v>
+        <v>2.9293053150177</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.97918486595154</v>
+        <v>2.97918510437012</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570162773132</v>
+        <v>2.91570138931274</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489104270935</v>
+        <v>2.87489056587219</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954525947571</v>
+        <v>2.82954549789429</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.78420042991638</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.88849401473999</v>
+        <v>2.88849425315857</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>2.79326939582825</v>
+        <v>2.79326915740967</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.78420042991638</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.78420042991638</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.83407998085022</v>
+        <v>2.8340802192688</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.78420042991638</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071671485901</v>
+        <v>2.72071647644043</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.69804406166077</v>
+        <v>2.69804430007935</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456082344055</v>
+        <v>2.63456058502197</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.6753716468811</v>
+        <v>2.67537140846252</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.59828472137451</v>
+        <v>2.59828448295593</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945569992065</v>
+        <v>2.48945546150208</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>2.45317959785461</v>
+        <v>2.45317935943604</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062691688538</v>
+        <v>2.38062739372253</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.35342025756836</v>
+        <v>2.3534197807312</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.28086805343628</v>
+        <v>2.28086757659912</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912571907043</v>
+        <v>2.24912595748901</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>2.38516163825989</v>
+        <v>2.38516187667847</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.23098802566528</v>
+        <v>2.2309877872467</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750431060791</v>
+        <v>2.16750454902649</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.1357626914978</v>
+        <v>2.13576245307922</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G305" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957591056824</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957591056824</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46678352355957</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G314" t="n">
-        <v>2.48038649559021</v>
+        <v>2.48038673400879</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G316" t="n">
-        <v>2.50759410858154</v>
+        <v>2.50759387016296</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46678352355957</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G322" t="n">
-        <v>2.46224880218506</v>
+        <v>2.46224856376648</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.35342025756836</v>
+        <v>2.3534197807312</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28540229797363</v>
+        <v>2.28540205955505</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.29447102546692</v>
+        <v>2.2944712638855</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.32167840003967</v>
+        <v>2.32167816162109</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528208732605</v>
+        <v>2.33528184890747</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005651473999</v>
+        <v>2.24005699157715</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912571907043</v>
+        <v>2.24912595748901</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G343" t="n">
-        <v>2.27633309364319</v>
+        <v>2.27633285522461</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>2.27633309364319</v>
+        <v>2.27633285522461</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>2.38516163825989</v>
+        <v>2.38516187667847</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179884910583</v>
+        <v>2.27179837226868</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G352" t="n">
-        <v>2.45317959785461</v>
+        <v>2.45317935943604</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>2.2445912361145</v>
+        <v>2.24459147453308</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>2.2445912361145</v>
+        <v>2.24459147453308</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005651473999</v>
+        <v>2.24005699157715</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34888529777527</v>
+        <v>2.34888553619385</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G370" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41690349578857</v>
+        <v>2.41690325737</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.40330004692078</v>
+        <v>2.4032998085022</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.38969588279724</v>
+        <v>2.3896963596344</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.40330004692078</v>
+        <v>2.4032998085022</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957591056824</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>2.56200861930847</v>
+        <v>2.56200838088989</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57107710838318</v>
+        <v>2.57107734680176</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666283607483</v>
+        <v>2.51666331291199</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G398" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.60281920433044</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.60281920433044</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>2.60281920433044</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G412" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.46224880218506</v>
+        <v>2.46224856376648</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573204040527</v>
+        <v>2.52573251724243</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>2.38516163825989</v>
+        <v>2.38516187667847</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34888529777527</v>
+        <v>2.34888553619385</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.875</v>
       </c>
       <c r="G424" t="n">
-        <v>2.60735368728638</v>
+        <v>2.6073534488678</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47131776809692</v>
+        <v>2.47131752967834</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G428" t="n">
-        <v>2.56200861930847</v>
+        <v>2.56200838088989</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>2.46678352355957</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957591056824</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G438" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G441" t="n">
-        <v>2.60281920433044</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188817024231</v>
+        <v>2.61188840866089</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>2.8114070892334</v>
+        <v>2.81140732765198</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G462" t="n">
-        <v>2.7404351234436</v>
+        <v>2.74043488502502</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G464" t="n">
-        <v>2.7404351234436</v>
+        <v>2.74043488502502</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G465" t="n">
-        <v>2.7404351234436</v>
+        <v>2.74043488502502</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3</v>
       </c>
       <c r="G466" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3</v>
       </c>
       <c r="G467" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>2.74966168403625</v>
+        <v>2.74966192245483</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3</v>
       </c>
       <c r="G469" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3</v>
       </c>
       <c r="G470" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G473" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G480" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.75</v>
       </c>
       <c r="G481" t="n">
-        <v>2.53743958473206</v>
+        <v>2.53743982315063</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G483" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.75</v>
       </c>
       <c r="G484" t="n">
-        <v>2.53743958473206</v>
+        <v>2.53743982315063</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61125588417053</v>
+        <v>2.61125612258911</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.7404351234436</v>
+        <v>2.74043488502502</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G506" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.7404351234436</v>
+        <v>2.74043488502502</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G538" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G541" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3</v>
       </c>
       <c r="G549" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>2.7404351234436</v>
+        <v>2.74043488502502</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G554" t="n">
-        <v>2.86961364746094</v>
+        <v>2.86961340904236</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.7404351234436</v>
+        <v>2.74043488502502</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734303474426</v>
+        <v>2.77734327316284</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79579710960388</v>
+        <v>2.79579734802246</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74966168403625</v>
+        <v>2.74966192245483</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.55589389801025</v>
+        <v>2.55589365959167</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41748809814453</v>
+        <v>2.41748785972595</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G580" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.61125588417053</v>
+        <v>2.61125612258911</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>2.41748809814453</v>
+        <v>2.41748785972595</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G611" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734303474426</v>
+        <v>2.77734327316284</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>2.74966168403625</v>
+        <v>2.74966192245483</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>2.74966168403625</v>
+        <v>2.74966192245483</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>3.12797093391418</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.12797093391418</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>3.15565252304077</v>
+        <v>3.15565228462219</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>3.15565252304077</v>
+        <v>3.15565228462219</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>3.19256067276001</v>
+        <v>3.19256043434143</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12797093391418</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G651" t="n">
-        <v>3.17410635948181</v>
+        <v>3.17410659790039</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.19256067276001</v>
+        <v>3.19256043434143</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>3.25714993476868</v>
+        <v>3.2571496963501</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G658" t="n">
-        <v>3.29405808448792</v>
+        <v>3.29405784606934</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>3.10951685905457</v>
+        <v>3.10951662063599</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G666" t="n">
-        <v>2.85115933418274</v>
+        <v>2.85115957260132</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3</v>
       </c>
       <c r="G667" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G669" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G673" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.03570032119751</v>
+        <v>3.03570055961609</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05415463447571</v>
+        <v>3.05415439605713</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>2.84193253517151</v>
+        <v>2.84193229675293</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>2.84193253517151</v>
+        <v>2.84193229675293</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.86961364746094</v>
+        <v>2.86961340904236</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G704" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G708" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>3.03570032119751</v>
+        <v>3.03570055961609</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>3.17410635948181</v>
+        <v>3.17410659790039</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -34380,6 +34380,32 @@
         <v>3.42000007629395</v>
       </c>
       <c r="H1308" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1309" t="n">
+        <v>1667</v>
+      </c>
+      <c r="C1309" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="H1309" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11975526809692</v>
+        <v>3.1197555065155</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161733627319</v>
+        <v>3.10161709785461</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1333589553833</v>
+        <v>3.13335871696472</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G15" t="n">
-        <v>3.39182686805725</v>
+        <v>3.39182662963867</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924377441406</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924377441406</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272748947144</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876293182373</v>
+        <v>3.90876317024231</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726149559021</v>
+        <v>3.77726173400879</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272748947144</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993462562561</v>
+        <v>3.79993438720703</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G30" t="n">
-        <v>3.6865713596344</v>
+        <v>3.68657112121582</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377825737</v>
+        <v>3.71377849578857</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>3.56413888931274</v>
+        <v>3.56413912773132</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>3.56413888931274</v>
+        <v>3.56413912773132</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>3.6729679107666</v>
+        <v>3.67296767234802</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633093833923</v>
+        <v>3.78633069992065</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272748947144</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>3.6865713596344</v>
+        <v>3.68657112121582</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.70017504692078</v>
+        <v>3.7001748085022</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284770011902</v>
+        <v>3.72284746170044</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>3.68203663825989</v>
+        <v>3.68203687667847</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>3.6729679107666</v>
+        <v>3.67296767234802</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.68203663825989</v>
+        <v>3.68203687667847</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.70017504692078</v>
+        <v>3.7001748085022</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320809364319</v>
+        <v>3.57320785522461</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G83" t="n">
-        <v>3.54600095748901</v>
+        <v>3.54600119590759</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47798275947571</v>
+        <v>3.47798299789429</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.44624090194702</v>
+        <v>3.4462411403656</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.46437931060791</v>
+        <v>3.46437907218933</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.47798275947571</v>
+        <v>3.47798299789429</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47344827651978</v>
+        <v>3.47344851493835</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.48251748085022</v>
+        <v>3.48251724243164</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>3.32380890846252</v>
+        <v>3.3238091468811</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531010627747</v>
+        <v>3.45531034469604</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>3.41449999809265</v>
+        <v>3.41449975967407</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48251748085022</v>
+        <v>3.48251724243164</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>3.41449999809265</v>
+        <v>3.41449975967407</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077586174011</v>
+        <v>3.45077562332153</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>3.55507016181946</v>
+        <v>3.55506992340088</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G122" t="n">
-        <v>3.46437931060791</v>
+        <v>3.46437907218933</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.39636135101318</v>
+        <v>3.39636158943176</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G129" t="n">
-        <v>3.39636135101318</v>
+        <v>3.39636158943176</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404932975769</v>
+        <v>3.22404909133911</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020522117615</v>
+        <v>3.31020545959473</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>3.55507016181946</v>
+        <v>3.55506992340088</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.47344827651978</v>
+        <v>3.47344851493835</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>3.09708261489868</v>
+        <v>3.0970823764801</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G147" t="n">
-        <v>3.22858381271362</v>
+        <v>3.2285840511322</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.1469624042511</v>
+        <v>3.14696216583252</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510033607483</v>
+        <v>3.16510057449341</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756321907043</v>
+        <v>2.89756345748901</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906489372253</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>3.09708261489868</v>
+        <v>3.0970823764801</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>3.21044564247131</v>
+        <v>3.21044611930847</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.37368893623352</v>
+        <v>3.37368869781494</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>3.11522078514099</v>
+        <v>3.11522054672241</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G173" t="n">
-        <v>3.16056561470032</v>
+        <v>3.1605658531189</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.91116714477539</v>
+        <v>2.91116690635681</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906489372253</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.02452993392944</v>
+        <v>3.02453017234802</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G179" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906489372253</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G182" t="n">
-        <v>2.97918510437012</v>
+        <v>2.97918486595154</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266810417175</v>
+        <v>3.04266834259033</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G189" t="n">
-        <v>2.99732327461243</v>
+        <v>2.99732303619385</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627179145813</v>
+        <v>3.05627155303955</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489056587219</v>
+        <v>2.87489080429077</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>3.00639200210571</v>
+        <v>3.00639224052429</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765301704407</v>
+        <v>3.23765277862549</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416977882385</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>3.11975526809692</v>
+        <v>3.1197555065155</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>3.11522078514099</v>
+        <v>3.11522054672241</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.16056561470032</v>
+        <v>3.1605658531189</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416977882385</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603137016296</v>
+        <v>3.15603160858154</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.9293053150177</v>
+        <v>2.92930507659912</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>2.93837404251099</v>
+        <v>2.93837428092957</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.97918510437012</v>
+        <v>2.97918486595154</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.86128711700439</v>
+        <v>2.86128735542297</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489056587219</v>
+        <v>2.87489080429077</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954549789429</v>
+        <v>2.82954525947571</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.88849425315857</v>
+        <v>2.88849401473999</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.8340802192688</v>
+        <v>2.83407998085022</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G251" t="n">
-        <v>2.7524585723877</v>
+        <v>2.75245833396912</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G252" t="n">
-        <v>2.7524585723877</v>
+        <v>2.75245833396912</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350957870483</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.69804430007935</v>
+        <v>2.69804406166077</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.7161819934845</v>
+        <v>2.71618223190308</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G263" t="n">
-        <v>2.63909530639648</v>
+        <v>2.63909554481506</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63909530639648</v>
+        <v>2.63909554481506</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456058502197</v>
+        <v>2.63456082344055</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G266" t="n">
-        <v>2.63909530639648</v>
+        <v>2.63909554481506</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.58014631271362</v>
+        <v>2.5801465511322</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.55293941497803</v>
+        <v>2.55293917655945</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945546150208</v>
+        <v>2.48945569992065</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>2.45317935943604</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>2.45771408081055</v>
+        <v>2.45771431922913</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342001914978</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.28086757659912</v>
+        <v>2.2808678150177</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.13576245307922</v>
+        <v>2.13576292991638</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>2.34435105323792</v>
+        <v>2.34435081481934</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.44864511489868</v>
+        <v>2.44864535331726</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G305" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G314" t="n">
-        <v>2.48038673400879</v>
+        <v>2.48038649559021</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G322" t="n">
-        <v>2.46224856376648</v>
+        <v>2.4622483253479</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342001914978</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.2944712638855</v>
+        <v>2.29447102546692</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.32167816162109</v>
+        <v>2.32167840003967</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528184890747</v>
+        <v>2.33528208732605</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993654251099</v>
+        <v>2.28993678092957</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179837226868</v>
+        <v>2.27179861068726</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G352" t="n">
-        <v>2.45317935943604</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.44864511489868</v>
+        <v>2.44864535331726</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>2.45771408081055</v>
+        <v>2.45771431922913</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G370" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.3896963596344</v>
+        <v>2.38969612121582</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44864511489868</v>
+        <v>2.44864535331726</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>2.55293941497803</v>
+        <v>2.55293917655945</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G398" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G403" t="n">
-        <v>2.7161819934845</v>
+        <v>2.71618223190308</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G412" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.46224856376648</v>
+        <v>2.4622483253479</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>2.44864511489868</v>
+        <v>2.44864535331726</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573251724243</v>
+        <v>2.52573227882385</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47131752967834</v>
+        <v>2.47131776809692</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G438" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188840866089</v>
+        <v>2.61188817024231</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350957870483</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>2.81140732765198</v>
+        <v>2.8114070892334</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -34406,6 +34406,32 @@
         <v>3.39000010490417</v>
       </c>
       <c r="H1309" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1310" t="n">
+        <v>3887</v>
+      </c>
+      <c r="C1310" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="H1310" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161733627319</v>
+        <v>3.10161709785461</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4008960723877</v>
+        <v>3.40089631080627</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>3.73645091056824</v>
+        <v>3.73645067214966</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G24" t="n">
-        <v>3.73645091056824</v>
+        <v>3.73645067214966</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876293182373</v>
+        <v>3.90876317024231</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993462562561</v>
+        <v>3.79993438720703</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G30" t="n">
-        <v>3.68657112121582</v>
+        <v>3.6865713596344</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>3.67296767234802</v>
+        <v>3.6729679107666</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365852355957</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633093833923</v>
+        <v>3.78633117675781</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>3.66389846801758</v>
+        <v>3.66389870643616</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>3.68657112121582</v>
+        <v>3.6865713596344</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365852355957</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.80900311470032</v>
+        <v>3.80900359153748</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.66389846801758</v>
+        <v>3.66389870643616</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G55" t="n">
-        <v>3.65482974052429</v>
+        <v>3.65482950210571</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G56" t="n">
-        <v>3.65482974052429</v>
+        <v>3.65482950210571</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762212753296</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284746170044</v>
+        <v>3.72284770011902</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>3.67296767234802</v>
+        <v>3.6729679107666</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762212753296</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762212753296</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762212753296</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320809364319</v>
+        <v>3.57320785522461</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G85" t="n">
-        <v>3.50065565109253</v>
+        <v>3.50065541267395</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729214668274</v>
+        <v>3.38729238510132</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47798299789429</v>
+        <v>3.47798323631287</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.44624090194702</v>
+        <v>3.4462411403656</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.47798299789429</v>
+        <v>3.47798323631287</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47344851493835</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>3.41449999809265</v>
+        <v>3.41449952125549</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996479988098</v>
+        <v>3.40996527671814</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996479988098</v>
+        <v>3.40996527671814</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008501052856</v>
+        <v>3.36008524894714</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50065565109253</v>
+        <v>3.50065541267395</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>3.41449999809265</v>
+        <v>3.41449952125549</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077586174011</v>
+        <v>3.45077610015869</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>3.50972461700439</v>
+        <v>3.50972437858582</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G128" t="n">
-        <v>3.39636135101318</v>
+        <v>3.3963611125946</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G129" t="n">
-        <v>3.39636135101318</v>
+        <v>3.3963611125946</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404932975769</v>
+        <v>3.22404956817627</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30113625526428</v>
+        <v>3.30113649368286</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.47344851493835</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.75</v>
       </c>
       <c r="G143" t="n">
-        <v>3.4008960723877</v>
+        <v>3.40089631080627</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>3.30113625526428</v>
+        <v>3.30113649368286</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>3.0970823764801</v>
+        <v>3.09708261489868</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G148" t="n">
-        <v>3.11068606376648</v>
+        <v>3.11068630218506</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.1469624042511</v>
+        <v>3.14696264266968</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.97465014457703</v>
+        <v>2.97465038299561</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092672348022</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278831481934</v>
+        <v>2.99278855323792</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906489372253</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>3.04720282554626</v>
+        <v>3.04720258712769</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G165" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092672348022</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G166" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>3.0970823764801</v>
+        <v>3.09708261489868</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.37368869781494</v>
+        <v>3.37368893623352</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092672348022</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906489372253</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G179" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906489372253</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>2.97465014457703</v>
+        <v>2.97465038299561</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G182" t="n">
-        <v>2.97918510437012</v>
+        <v>2.97918486595154</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266834259033</v>
+        <v>3.04266858100891</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092672348022</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>3.0517373085022</v>
+        <v>3.05173707008362</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G201" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011613845825</v>
+        <v>2.97011590003967</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>3.00639224052429</v>
+        <v>3.00639200210571</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G209" t="n">
-        <v>3.11068606376648</v>
+        <v>3.11068630218506</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.36461997032166</v>
+        <v>3.3646194934845</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765301704407</v>
+        <v>3.23765277862549</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416977882385</v>
+        <v>3.17416954040527</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416977882385</v>
+        <v>3.17416954040527</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.92930507659912</v>
+        <v>2.92930483818054</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>2.93837404251099</v>
+        <v>2.93837428092957</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.97918510437012</v>
+        <v>2.97918486595154</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G226" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.86128735542297</v>
+        <v>2.86128711700439</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954525947571</v>
+        <v>2.82954549789429</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.04720282554626</v>
+        <v>3.04720258712769</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G233" t="n">
-        <v>3.04720282554626</v>
+        <v>3.04720258712769</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="n">
-        <v>3.04720282554626</v>
+        <v>3.04720258712769</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>2.83861470222473</v>
+        <v>2.83861446380615</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>2.77513098716736</v>
+        <v>2.77513122558594</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.83407998085022</v>
+        <v>2.8340802192688</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G251" t="n">
-        <v>2.7524585723877</v>
+        <v>2.75245881080627</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G252" t="n">
-        <v>2.7524585723877</v>
+        <v>2.75245881080627</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350934028625</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071647644043</v>
+        <v>2.72071671485901</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.69804406166077</v>
+        <v>2.69804430007935</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G263" t="n">
-        <v>2.63909530639648</v>
+        <v>2.63909506797791</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G264" t="n">
-        <v>2.63909530639648</v>
+        <v>2.63909506797791</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G266" t="n">
-        <v>2.63909530639648</v>
+        <v>2.63909506797791</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.67537140846252</v>
+        <v>2.6753716468811</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.5801465511322</v>
+        <v>2.58014631271362</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945569992065</v>
+        <v>2.48945593833923</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062739372253</v>
+        <v>2.38062691688538</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.5</v>
       </c>
       <c r="G284" t="n">
-        <v>2.26726388931274</v>
+        <v>2.26726412773132</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.5</v>
       </c>
       <c r="G285" t="n">
-        <v>2.26726388931274</v>
+        <v>2.26726412773132</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>2.38516163825989</v>
+        <v>2.38516211509705</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>2.11309003829956</v>
+        <v>2.11308979988098</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14029717445374</v>
+        <v>2.14029693603516</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.18564248085022</v>
+        <v>2.1856427192688</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.5</v>
       </c>
       <c r="G298" t="n">
-        <v>2.26726388931274</v>
+        <v>2.26726412773132</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.5</v>
       </c>
       <c r="G299" t="n">
-        <v>2.26726388931274</v>
+        <v>2.26726412773132</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.5</v>
       </c>
       <c r="G300" t="n">
-        <v>2.26726388931274</v>
+        <v>2.26726412773132</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G319" t="n">
-        <v>2.5574734210968</v>
+        <v>2.55747365951538</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G322" t="n">
-        <v>2.46224856376648</v>
+        <v>2.46224880218506</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528184890747</v>
+        <v>2.33528208732605</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993654251099</v>
+        <v>2.28993678092957</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005699157715</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.5</v>
       </c>
       <c r="G344" t="n">
-        <v>2.26726388931274</v>
+        <v>2.26726412773132</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>2.38516163825989</v>
+        <v>2.38516211509705</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G350" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>2.24459147453308</v>
+        <v>2.24459099769592</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>2.24459147453308</v>
+        <v>2.24459099769592</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005699157715</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>2.5</v>
       </c>
       <c r="G363" t="n">
-        <v>2.26726388931274</v>
+        <v>2.26726412773132</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>2.75</v>
       </c>
       <c r="G364" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>2.37609267234802</v>
+        <v>2.37609243392944</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34888529777527</v>
+        <v>2.34888505935669</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>2.37609267234802</v>
+        <v>2.37609243392944</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>2.37609267234802</v>
+        <v>2.37609243392944</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.4985249042511</v>
+        <v>2.49852514266968</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>2.56200861930847</v>
+        <v>2.56200838088989</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G394" t="n">
-        <v>2.4849214553833</v>
+        <v>2.48492121696472</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57107734680176</v>
+        <v>2.57107758522034</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G403" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.46224856376648</v>
+        <v>2.46224880218506</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573251724243</v>
+        <v>2.52573204040527</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>2.37609267234802</v>
+        <v>2.37609243392944</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>2.38516163825989</v>
+        <v>2.38516211509705</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34888529777527</v>
+        <v>2.34888505935669</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.75</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G423" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.875</v>
       </c>
       <c r="G424" t="n">
-        <v>2.6073534488678</v>
+        <v>2.60735368728638</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G428" t="n">
-        <v>2.56200861930847</v>
+        <v>2.56200838088989</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.75</v>
       </c>
       <c r="G432" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G435" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>2.5574734210968</v>
+        <v>2.55747365951538</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188817024231</v>
+        <v>2.61188793182373</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G447" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350934028625</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G462" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G465" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3</v>
       </c>
       <c r="G466" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3</v>
       </c>
       <c r="G467" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3</v>
       </c>
       <c r="G469" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3</v>
       </c>
       <c r="G470" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G473" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.75</v>
       </c>
       <c r="G481" t="n">
-        <v>2.53743982315063</v>
+        <v>2.53743958473206</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.75</v>
       </c>
       <c r="G484" t="n">
-        <v>2.53743982315063</v>
+        <v>2.53743958473206</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G486" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G489" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G490" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G494" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G499" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G501" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G504" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G512" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3</v>
       </c>
       <c r="G549" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79579734802246</v>
+        <v>2.79579710960388</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G579" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G581" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.57434773445129</v>
+        <v>2.57434797286987</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G594" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G597" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G607" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G611" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G627" t="n">
-        <v>2.93420314788818</v>
+        <v>2.9342029094696</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G651" t="n">
-        <v>3.17410659790039</v>
+        <v>3.17410635948181</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>3.2571496963501</v>
+        <v>3.25714993476868</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>3.34019303321838</v>
+        <v>3.34019327163696</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>3.10951662063599</v>
+        <v>3.10951685905457</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>3.06338167190552</v>
+        <v>3.0633819103241</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>2.96188402175903</v>
+        <v>2.96188426017761</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.88806796073914</v>
+        <v>2.88806772232056</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3</v>
       </c>
       <c r="G667" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.86038637161255</v>
+        <v>2.86038661003113</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05415439605713</v>
+        <v>3.05415463447571</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G689" t="n">
-        <v>2.86038637161255</v>
+        <v>2.86038661003113</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G692" t="n">
-        <v>2.8327054977417</v>
+        <v>2.83270525932312</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>2.94343018531799</v>
+        <v>2.94342994689941</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>2.96188402175903</v>
+        <v>2.96188426017761</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>2.86038637161255</v>
+        <v>2.86038661003113</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G703" t="n">
-        <v>2.86038637161255</v>
+        <v>2.86038661003113</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G709" t="n">
-        <v>3.06338167190552</v>
+        <v>3.0633819103241</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>3.17410659790039</v>
+        <v>3.17410635948181</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>3.34019303321838</v>
+        <v>3.34019327163696</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -34484,6 +34484,32 @@
         <v>3.55999994277954</v>
       </c>
       <c r="H1312" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1313" t="n">
+        <v>19132</v>
+      </c>
+      <c r="C1313" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>3.66000008583069</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>3.66000008583069</v>
+      </c>
+      <c r="H1313" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30633,8 +30633,31 @@
       <c r="E1316" t="n">
         <v>3.61999988555908</v>
       </c>
-      <c r="F1316"/>
+      <c r="F1316" t="n">
+        <v>3.64000010490417</v>
+      </c>
       <c r="G1316" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1317" t="n">
+        <v>11971</v>
+      </c>
+      <c r="C1317" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="F1317"/>
+      <c r="G1317" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30656,8 +30656,31 @@
       <c r="E1317" t="n">
         <v>3.65000009536743</v>
       </c>
-      <c r="F1317"/>
+      <c r="F1317" t="n">
+        <v>3.57999992370605</v>
+      </c>
       <c r="G1317" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1318" t="n">
+        <v>6354</v>
+      </c>
+      <c r="C1318" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>3.58999991416931</v>
+      </c>
+      <c r="F1318"/>
+      <c r="G1318" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30671,7 +30671,7 @@
         <v>6354</v>
       </c>
       <c r="C1318" t="n">
-        <v>3.61999988555908</v>
+        <v>3.64000010490417</v>
       </c>
       <c r="D1318" t="n">
         <v>3.52999997138977</v>
@@ -30679,8 +30679,31 @@
       <c r="E1318" t="n">
         <v>3.58999991416931</v>
       </c>
-      <c r="F1318"/>
+      <c r="F1318" t="n">
+        <v>3.64000010490417</v>
+      </c>
       <c r="G1318" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1319" t="n">
+        <v>4141</v>
+      </c>
+      <c r="C1319" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F1319"/>
+      <c r="G1319" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30702,8 +30702,31 @@
       <c r="E1319" t="n">
         <v>3.64000010490417</v>
       </c>
-      <c r="F1319"/>
+      <c r="F1319" t="n">
+        <v>3.65000009536743</v>
+      </c>
       <c r="G1319" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1320" t="n">
+        <v>15279</v>
+      </c>
+      <c r="C1320" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="F1320"/>
+      <c r="G1320" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -30732,6 +30732,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1321">
+      <c r="A1321" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1321" t="n">
+        <v>24186</v>
+      </c>
+      <c r="C1321" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>3.65000009536743</v>
+      </c>
+      <c r="G1321" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11975526809692</v>
+        <v>3.11975502967834</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>3.13789367675781</v>
+        <v>3.13789343833923</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161709785461</v>
+        <v>3.10161733627319</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.13335871696472</v>
+        <v>3.1333589553833</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876269340515</v>
+        <v>3.90876293182373</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726173400879</v>
+        <v>3.77726149559021</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993438720703</v>
+        <v>3.79993462562561</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377801895142</v>
+        <v>3.71377825737</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G39" t="n">
-        <v>3.79086518287659</v>
+        <v>3.79086565971375</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633069992065</v>
+        <v>3.78633117675781</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>3.78179621696472</v>
+        <v>3.7817964553833</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738170623779</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738170623779</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.80900311470032</v>
+        <v>3.80900287628174</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284770011902</v>
+        <v>3.72284746170044</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.66843295097351</v>
+        <v>3.66843318939209</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320833206177</v>
+        <v>3.57320785522461</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.45984506607056</v>
+        <v>3.45984482765198</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.48251724243164</v>
+        <v>3.48251748085022</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891379356384</v>
+        <v>3.46891403198242</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996527671814</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996527671814</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008548736572</v>
+        <v>3.36008501052856</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48251724243164</v>
+        <v>3.48251748085022</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G108" t="n">
-        <v>3.48705220222473</v>
+        <v>3.48705196380615</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.4961211681366</v>
+        <v>3.49612092971802</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>3.55960440635681</v>
+        <v>3.55960464477539</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.4961211681366</v>
+        <v>3.49612092971802</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287787437439</v>
+        <v>3.33287811279297</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>3.26486015319824</v>
+        <v>3.26485991477966</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32834339141846</v>
+        <v>3.32834386825562</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42810320854187</v>
+        <v>3.42810297012329</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G131" t="n">
-        <v>3.27392935752869</v>
+        <v>3.27392911911011</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>3.26486015319824</v>
+        <v>3.26485991477966</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404956817627</v>
+        <v>3.22404932975769</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30113649368286</v>
+        <v>3.30113625526428</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G137" t="n">
-        <v>3.35101628303528</v>
+        <v>3.3510160446167</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020545959473</v>
+        <v>3.31020522117615</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>3.30113649368286</v>
+        <v>3.30113625526428</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G147" t="n">
-        <v>3.2285840511322</v>
+        <v>3.22858381271362</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>3.25125646591187</v>
+        <v>3.25125670433044</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G153" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756345748901</v>
+        <v>2.89756321907043</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.96104669570923</v>
+        <v>2.96104693412781</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278855323792</v>
+        <v>2.99278831481934</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.37368869781494</v>
+        <v>3.37368893623352</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615134239197</v>
+        <v>3.10615181922913</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G179" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266834259033</v>
+        <v>3.04266810417175</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G189" t="n">
-        <v>2.99732327461243</v>
+        <v>2.99732303619385</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627155303955</v>
+        <v>3.05627179145813</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.06534099578857</v>
+        <v>3.06534123420715</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G201" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011566162109</v>
+        <v>2.97011613845825</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765277862549</v>
+        <v>3.23765301704407</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753280639648</v>
+        <v>3.28753304481506</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416977882385</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>3.11975526809692</v>
+        <v>3.11975502967834</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416977882385</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>2.93837428092957</v>
+        <v>2.93837404251099</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035608291626</v>
+        <v>2.87035632133484</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G226" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.86128735542297</v>
+        <v>2.86128711700439</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954525947571</v>
+        <v>2.82954549789429</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>2.79326915740967</v>
+        <v>2.79326939582825</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>2.77513122558594</v>
+        <v>2.77513098716736</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G246" t="n">
-        <v>2.84768390655518</v>
+        <v>2.84768342971802</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.83407998085022</v>
+        <v>2.8340802192688</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071695327759</v>
+        <v>2.72071671485901</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456082344055</v>
+        <v>2.63456058502197</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.6753716468811</v>
+        <v>2.67537140846252</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G271" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.5801465511322</v>
+        <v>2.58014631271362</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>2.45771384239197</v>
+        <v>2.45771431922913</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062691688538</v>
+        <v>2.38062739372253</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.35342001914978</v>
+        <v>2.3534197807312</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G287" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750431060791</v>
+        <v>2.16750454902649</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.33074712753296</v>
+        <v>2.33074736595154</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>2.34435081481934</v>
+        <v>2.34435105323792</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.22645306587219</v>
+        <v>2.22645330429077</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14029693603516</v>
+        <v>2.14029717445374</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.18564248085022</v>
+        <v>2.1856427192688</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33074712753296</v>
+        <v>2.33074736595154</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>2.35795474052429</v>
+        <v>2.35795426368713</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46678304672241</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46678304672241</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.39876532554626</v>
+        <v>2.39876508712769</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.35342001914978</v>
+        <v>2.3534197807312</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.29447102546692</v>
+        <v>2.2944712638855</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.30807495117188</v>
+        <v>2.3080747127533</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528208732605</v>
+        <v>2.33528184890747</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G347" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179861068726</v>
+        <v>2.27179837226868</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.35795474052429</v>
+        <v>2.35795426368713</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>2.24459099769592</v>
+        <v>2.2445912361145</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>2.24459099769592</v>
+        <v>2.2445912361145</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>2.45771384239197</v>
+        <v>2.45771431922913</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G368" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G372" t="n">
-        <v>2.41690325737</v>
+        <v>2.41690349578857</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.40330004692078</v>
+        <v>2.4032998085022</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.38969612121582</v>
+        <v>2.3896963596344</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.40330004692078</v>
+        <v>2.4032998085022</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.49852514266968</v>
+        <v>2.49852466583252</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666307449341</v>
+        <v>2.51666331291199</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281920433044</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281920433044</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281920433044</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573204040527</v>
+        <v>2.52573251724243</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>2.38516187667847</v>
+        <v>2.38516163825989</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G423" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.875</v>
       </c>
       <c r="G424" t="n">
-        <v>2.6073534488678</v>
+        <v>2.60735368728638</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47131776809692</v>
+        <v>2.47131752967834</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>2.46678304672241</v>
+        <v>2.46678328514099</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G435" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G441" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281920433044</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188817024231</v>
+        <v>2.61188840866089</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G446" t="n">
-        <v>2.59374976158142</v>
+        <v>2.59375</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G447" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>2.81140732765198</v>
+        <v>2.8114070892334</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G461" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G462" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G465" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3</v>
       </c>
       <c r="G466" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3</v>
       </c>
       <c r="G467" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3</v>
       </c>
       <c r="G469" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3</v>
       </c>
       <c r="G470" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G474" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G477" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G478" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G479" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G480" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G482" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G483" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G494" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G497" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G499" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G501" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G504" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G506" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G511" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G512" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G513" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G538" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G541" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3</v>
       </c>
       <c r="G549" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.74043488502502</v>
+        <v>2.74043464660645</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734303474426</v>
+        <v>2.77734327316284</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.55589389801025</v>
+        <v>2.55589365959167</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41748809814453</v>
+        <v>2.41748785972595</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G580" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G582" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G583" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.57434773445129</v>
+        <v>2.57434797286987</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G589" t="n">
-        <v>2.50975847244263</v>
+        <v>2.50975871086121</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G592" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>2.41748809814453</v>
+        <v>2.41748785972595</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.59280204772949</v>
+        <v>2.59280180931091</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G605" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>2.50975847244263</v>
+        <v>2.50975871086121</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G607" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734303474426</v>
+        <v>2.77734327316284</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G627" t="n">
-        <v>2.93420314788818</v>
+        <v>2.9342029094696</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G629" t="n">
-        <v>3.07260847091675</v>
+        <v>3.07260870933533</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>3.12797141075134</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.12797141075134</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>3.19256067276001</v>
+        <v>3.19256043434143</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G647" t="n">
-        <v>2.97111105918884</v>
+        <v>2.97111129760742</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>3.07260847091675</v>
+        <v>3.07260870933533</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12797141075134</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.19256067276001</v>
+        <v>3.19256043434143</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3</v>
       </c>
       <c r="G667" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G670" t="n">
-        <v>3.00801920890808</v>
+        <v>3.00801944732666</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G676" t="n">
-        <v>2.87884044647217</v>
+        <v>2.87884068489075</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.86038637161255</v>
+        <v>2.86038661003113</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>3.01724624633789</v>
+        <v>3.01724648475647</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>3.00801920890808</v>
+        <v>3.00801944732666</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>3.01724624633789</v>
+        <v>3.01724648475647</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>3.01724624633789</v>
+        <v>3.01724648475647</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G689" t="n">
-        <v>2.86038637161255</v>
+        <v>2.86038661003113</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G692" t="n">
-        <v>2.8327054977417</v>
+        <v>2.83270525932312</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.25</v>
       </c>
       <c r="G699" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>2.86038637161255</v>
+        <v>2.86038661003113</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G703" t="n">
-        <v>2.86038637161255</v>
+        <v>2.86038661003113</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.25</v>
       </c>
       <c r="G705" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>3.25</v>
       </c>
       <c r="G706" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G718" t="n">
-        <v>3.42463660240173</v>
+        <v>3.42463636398315</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G720" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G721" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>3.62167024612427</v>
+        <v>3.62167000770569</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G730" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G733" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G737" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>3.5372269153595</v>
+        <v>3.53722715377808</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.66858291625977</v>
+        <v>3.66858315467834</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G762" t="n">
-        <v>3.62167024612427</v>
+        <v>3.62167000770569</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G768" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G771" t="n">
-        <v>3.649817943573</v>
+        <v>3.64981818199158</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G779" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G791" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G795" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85623455047607</v>
+        <v>3.8562343120575</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88438177108765</v>
+        <v>3.88438200950623</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G802" t="n">
-        <v>3.88438177108765</v>
+        <v>3.88438200950623</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>3.96882486343384</v>
+        <v>3.96882510185242</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G811" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>4.10018062591553</v>
+        <v>4.10018110275269</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G826" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>4.3065972328186</v>
+        <v>4.30659770965576</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G838" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G850" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G865" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G869" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G881" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G883" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G885" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G886" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G890" t="n">
-        <v>3.66858291625977</v>
+        <v>3.66858315467834</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G891" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.25</v>
       </c>
       <c r="G900" t="n">
-        <v>3.98759031295776</v>
+        <v>3.98759055137634</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G901" t="n">
-        <v>3.9782075881958</v>
+        <v>3.97820734977722</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G904" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G914" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G915" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G919" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G921" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G923" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.85623455047607</v>
+        <v>3.8562343120575</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G926" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>4.10018062591553</v>
+        <v>4.10018110275269</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G929" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.25</v>
       </c>
       <c r="G930" t="n">
-        <v>3.98759031295776</v>
+        <v>3.98759055137634</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G935" t="n">
-        <v>3.96882486343384</v>
+        <v>3.96882510185242</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G936" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G946" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.14709377288818</v>
+        <v>4.14709424972534</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G958" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G962" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -34770,6 +34770,32 @@
         <v>3.60999989509583</v>
       </c>
       <c r="H1323" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1324" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C1324" t="n">
+        <v>3.63000011444092</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>3.63000011444092</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="H1324" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11975502967834</v>
+        <v>3.11975526809692</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161733627319</v>
+        <v>3.10161709785461</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1333589553833</v>
+        <v>3.13335871696472</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.56867337226868</v>
+        <v>3.56867361068726</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4008960723877</v>
+        <v>3.40089583396912</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924401283264</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924401283264</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>3.73645067214966</v>
+        <v>3.73645091056824</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458931922913</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458931922913</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G24" t="n">
-        <v>3.73645067214966</v>
+        <v>3.73645091056824</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876293182373</v>
+        <v>3.90876317024231</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726149559021</v>
+        <v>3.77726173400879</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993462562561</v>
+        <v>3.79993438720703</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G30" t="n">
-        <v>3.68657112121582</v>
+        <v>3.6865713596344</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>3.56413912773132</v>
+        <v>3.5641393661499</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>3.56413912773132</v>
+        <v>3.5641393661499</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>3.6729679107666</v>
+        <v>3.67296743392944</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365804672241</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G39" t="n">
-        <v>3.79086565971375</v>
+        <v>3.79086518287659</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633117675781</v>
+        <v>3.78633093833923</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>3.7817964553833</v>
+        <v>3.78179621696472</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738170623779</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738170623779</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>3.68657112121582</v>
+        <v>3.6865713596344</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458931922913</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365804672241</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.80900287628174</v>
+        <v>3.8090033531189</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284746170044</v>
+        <v>3.72284722328186</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>3.69564008712769</v>
+        <v>3.69564032554626</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>3.6729679107666</v>
+        <v>3.67296743392944</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458931922913</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>3.63215708732605</v>
+        <v>3.63215684890747</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320785522461</v>
+        <v>3.57320809364319</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G85" t="n">
-        <v>3.50065565109253</v>
+        <v>3.50065541267395</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729214668274</v>
+        <v>3.38729238510132</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.48251748085022</v>
+        <v>3.48251724243164</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555052757263</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531010627747</v>
+        <v>3.45531034469604</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891403198242</v>
+        <v>3.46891379356384</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>3.42356872558594</v>
+        <v>3.42356896400452</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996503829956</v>
+        <v>3.40996479988098</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996503829956</v>
+        <v>3.40996479988098</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008501052856</v>
+        <v>3.36008524894714</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555052757263</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555052757263</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50065565109253</v>
+        <v>3.50065541267395</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48251748085022</v>
+        <v>3.48251724243164</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.49612092971802</v>
+        <v>3.4961211681366</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077586174011</v>
+        <v>3.45077562332153</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>3.55960464477539</v>
+        <v>3.55960440635681</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.49612092971802</v>
+        <v>3.4961211681366</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287811279297</v>
+        <v>3.33287787437439</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>3.26485991477966</v>
+        <v>3.26486015319824</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32834386825562</v>
+        <v>3.32834362983704</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G126" t="n">
-        <v>3.42810297012329</v>
+        <v>3.42810320854187</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>3.26485991477966</v>
+        <v>3.26486015319824</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30113625526428</v>
+        <v>3.30113649368286</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G137" t="n">
-        <v>3.3510160446167</v>
+        <v>3.35101580619812</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020522117615</v>
+        <v>3.31020545959473</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555052757263</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G141" t="n">
-        <v>3.5278627872467</v>
+        <v>3.52786302566528</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.75</v>
       </c>
       <c r="G143" t="n">
-        <v>3.4008960723877</v>
+        <v>3.40089583396912</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>3.30113625526428</v>
+        <v>3.30113649368286</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>3.09708261489868</v>
+        <v>3.0970823764801</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510033607483</v>
+        <v>3.16510057449341</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.97465038299561</v>
+        <v>2.97465062141418</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570162773132</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.96104693412781</v>
+        <v>2.96104669570923</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278831481934</v>
+        <v>2.99278855323792</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>3.09708261489868</v>
+        <v>3.0970823764801</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>3.21044588088989</v>
+        <v>3.21044564247131</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>3.11522054672241</v>
+        <v>3.11522078514099</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.91116714477539</v>
+        <v>2.91116690635681</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>2.97465038299561</v>
+        <v>2.97465062141418</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266810417175</v>
+        <v>3.04266858100891</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489080429077</v>
+        <v>2.87489104270935</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011613845825</v>
+        <v>2.97011590003967</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G207" t="n">
-        <v>2.92477035522461</v>
+        <v>2.92477059364319</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>3.00639200210571</v>
+        <v>3.00639224052429</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753304481506</v>
+        <v>3.28753280639648</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>3.11975502967834</v>
+        <v>3.11975526809692</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>3.11522054672241</v>
+        <v>3.11522078514099</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603137016296</v>
+        <v>3.15603160858154</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035632133484</v>
+        <v>2.87035608291626</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570162773132</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489080429077</v>
+        <v>2.87489104270935</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954549789429</v>
+        <v>2.82954525947571</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>2.88849425315857</v>
+        <v>2.88849401473999</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G246" t="n">
-        <v>2.84768342971802</v>
+        <v>2.8476836681366</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.8340802192688</v>
+        <v>2.83407998085022</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350957870483</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456058502197</v>
+        <v>2.63456082344055</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.67537140846252</v>
+        <v>2.6753716468811</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.59828448295593</v>
+        <v>2.59828472137451</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>2.45771431922913</v>
+        <v>2.45771408081055</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062739372253</v>
+        <v>2.38062691688538</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342025756836</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.28086757659912</v>
+        <v>2.28086805343628</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G288" t="n">
-        <v>2.29900598526001</v>
+        <v>2.29900574684143</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.2309877872467</v>
+        <v>2.23098802566528</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750454902649</v>
+        <v>2.16750431060791</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.1856427192688</v>
+        <v>2.18564248085022</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>2.35795426368713</v>
+        <v>2.35795450210571</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G305" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G314" t="n">
-        <v>2.48038673400879</v>
+        <v>2.48038649559021</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G316" t="n">
-        <v>2.50759387016296</v>
+        <v>2.50759410858154</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G321" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G322" t="n">
-        <v>2.46224856376648</v>
+        <v>2.46224880218506</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.39876508712769</v>
+        <v>2.39876532554626</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342025756836</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G333" t="n">
-        <v>2.28540205955505</v>
+        <v>2.28540229797363</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.2944712638855</v>
+        <v>2.29447102546692</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G337" t="n">
-        <v>2.29900598526001</v>
+        <v>2.29900574684143</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.32167816162109</v>
+        <v>2.32167840003967</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528184890747</v>
+        <v>2.33528208732605</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993678092957</v>
+        <v>2.28993654251099</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005651473999</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G343" t="n">
-        <v>2.27633285522461</v>
+        <v>2.27633309364319</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>2.27633285522461</v>
+        <v>2.27633309364319</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179837226868</v>
+        <v>2.27179884910583</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.41236901283264</v>
+        <v>2.41236925125122</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.35795426368713</v>
+        <v>2.35795450210571</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005651473999</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>2.45771431922913</v>
+        <v>2.45771408081055</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34888553619385</v>
+        <v>2.34888529777527</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G370" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.4032998085022</v>
+        <v>2.40330004692078</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.3896963596344</v>
+        <v>2.38969588279724</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.4032998085022</v>
+        <v>2.40330004692078</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.49852466583252</v>
+        <v>2.4985249042511</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>2.56200838088989</v>
+        <v>2.56200861930847</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57107758522034</v>
+        <v>2.57107710838318</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666331291199</v>
+        <v>2.51666283607483</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G398" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840445518494</v>
+        <v>2.54840469360352</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840445518494</v>
+        <v>2.54840469360352</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G403" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G412" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.46224856376648</v>
+        <v>2.46224880218506</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573251724243</v>
+        <v>2.52573204040527</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34888553619385</v>
+        <v>2.34888529777527</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47131752967834</v>
+        <v>2.47131776809692</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G428" t="n">
-        <v>2.56200838088989</v>
+        <v>2.56200861930847</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G430" t="n">
-        <v>2.46678328514099</v>
+        <v>2.46678352355957</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G438" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188840866089</v>
+        <v>2.61188817024231</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350957870483</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G462" t="n">
-        <v>2.74043464660645</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74043464660645</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G465" t="n">
-        <v>2.74043464660645</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>2.74966192245483</v>
+        <v>2.74966168403625</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G480" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G483" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G486" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61125612258911</v>
+        <v>2.61125588417053</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G489" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G490" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G494" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G496" t="n">
-        <v>2.59280180931091</v>
+        <v>2.59280204772949</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G498" t="n">
-        <v>2.74043464660645</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G499" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G501" t="n">
-        <v>2.59280180931091</v>
+        <v>2.59280204772949</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G502" t="n">
-        <v>2.59280180931091</v>
+        <v>2.59280204772949</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G503" t="n">
-        <v>2.59280180931091</v>
+        <v>2.59280204772949</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G504" t="n">
-        <v>2.59280180931091</v>
+        <v>2.59280204772949</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G506" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G512" t="n">
-        <v>2.59280180931091</v>
+        <v>2.59280204772949</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.74043464660645</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G538" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G541" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>2.74043464660645</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G554" t="n">
-        <v>2.86961340904236</v>
+        <v>2.86961364746094</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G557" t="n">
-        <v>2.74043464660645</v>
+        <v>2.7404351234436</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734327316284</v>
+        <v>2.77734303474426</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>2.74966192245483</v>
+        <v>2.74966168403625</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.55589365959167</v>
+        <v>2.55589389801025</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41748785972595</v>
+        <v>2.41748809814453</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G579" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G580" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G581" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.57434797286987</v>
+        <v>2.57434773445129</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.61125612258911</v>
+        <v>2.61125588417053</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G594" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>2.41748785972595</v>
+        <v>2.41748809814453</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G597" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G602" t="n">
-        <v>2.59280180931091</v>
+        <v>2.59280204772949</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G607" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734327316284</v>
+        <v>2.77734303474426</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G625" t="n">
-        <v>2.74966192245483</v>
+        <v>2.74966168403625</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G626" t="n">
-        <v>2.74966192245483</v>
+        <v>2.74966168403625</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G627" t="n">
-        <v>2.9342029094696</v>
+        <v>2.93420314788818</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797093391418</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797093391418</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>3.15565228462219</v>
+        <v>3.15565252304077</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>3.15565228462219</v>
+        <v>3.15565252304077</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>3.19256043434143</v>
+        <v>3.19256067276001</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797093391418</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.19256043434143</v>
+        <v>3.19256067276001</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>3.34019327163696</v>
+        <v>3.34019303321838</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G658" t="n">
-        <v>3.29405784606934</v>
+        <v>3.29405808448792</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>3.0633819103241</v>
+        <v>3.06338167190552</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>2.96188426017761</v>
+        <v>2.96188402175903</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.88806772232056</v>
+        <v>2.88806796073914</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G666" t="n">
-        <v>2.85115957260132</v>
+        <v>2.85115933418274</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G669" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G673" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G678" t="n">
-        <v>2.86038661003113</v>
+        <v>2.86038637161255</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.03570055961609</v>
+        <v>3.03570032119751</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G689" t="n">
-        <v>2.86038661003113</v>
+        <v>2.86038637161255</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G691" t="n">
-        <v>2.84193229675293</v>
+        <v>2.84193253517151</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G692" t="n">
-        <v>2.83270525932312</v>
+        <v>2.8327054977417</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>2.84193229675293</v>
+        <v>2.84193253517151</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>2.94342994689941</v>
+        <v>2.94343018531799</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>2.96188426017761</v>
+        <v>2.96188402175903</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.86961340904236</v>
+        <v>2.86961364746094</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G702" t="n">
-        <v>2.86038661003113</v>
+        <v>2.86038637161255</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G703" t="n">
-        <v>2.86038661003113</v>
+        <v>2.86038637161255</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G704" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G708" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G709" t="n">
-        <v>3.0633819103241</v>
+        <v>3.06338167190552</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>3.03570055961609</v>
+        <v>3.03570032119751</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>3.34019327163696</v>
+        <v>3.34019303321838</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -34796,6 +34796,32 @@
         <v>3.5699999332428</v>
       </c>
       <c r="H1324" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1325" t="n">
+        <v>1682</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="H1325" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0834789276123</v>
+        <v>3.08347916603088</v>
       </c>
       <c r="H2" t="n">
         <v>561784</v>
@@ -601,7 +601,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H8" t="n">
         <v>720993</v>
@@ -630,7 +630,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.56867337226868</v>
+        <v>3.5686731338501</v>
       </c>
       <c r="H9" t="n">
         <v>292968</v>
@@ -775,7 +775,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903376579285</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H14" t="n">
         <v>18667</v>
@@ -804,7 +804,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G15" t="n">
-        <v>3.39182686805725</v>
+        <v>3.39182662963867</v>
       </c>
       <c r="H15" t="n">
         <v>33287</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903376579285</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H16" t="n">
         <v>44813</v>
@@ -862,7 +862,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H17" t="n">
         <v>150547</v>
@@ -891,7 +891,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H18" t="n">
         <v>290894</v>
@@ -949,7 +949,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>3.73645067214966</v>
+        <v>3.73645091056824</v>
       </c>
       <c r="H20" t="n">
         <v>32664</v>
@@ -978,7 +978,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H21" t="n">
         <v>33033</v>
@@ -1007,7 +1007,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H22" t="n">
         <v>16624</v>
@@ -1036,7 +1036,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831297874451</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H23" t="n">
         <v>29141</v>
@@ -1065,7 +1065,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G24" t="n">
-        <v>3.73645067214966</v>
+        <v>3.73645091056824</v>
       </c>
       <c r="H24" t="n">
         <v>33920</v>
@@ -1094,7 +1094,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.89515972137451</v>
+        <v>3.89515924453735</v>
       </c>
       <c r="H25" t="n">
         <v>186140</v>
@@ -1152,7 +1152,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726173400879</v>
+        <v>3.77726149559021</v>
       </c>
       <c r="H27" t="n">
         <v>75595</v>
@@ -1210,7 +1210,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993438720703</v>
+        <v>3.79993486404419</v>
       </c>
       <c r="H29" t="n">
         <v>38465</v>
@@ -1268,7 +1268,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377801895142</v>
+        <v>3.71377825737</v>
       </c>
       <c r="H31" t="n">
         <v>31484</v>
@@ -1326,7 +1326,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H33" t="n">
         <v>18869</v>
@@ -1471,7 +1471,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365804672241</v>
+        <v>3.76365828514099</v>
       </c>
       <c r="H38" t="n">
         <v>28609</v>
@@ -1500,7 +1500,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G39" t="n">
-        <v>3.79086565971375</v>
+        <v>3.79086542129517</v>
       </c>
       <c r="H39" t="n">
         <v>88203</v>
@@ -1587,7 +1587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H42" t="n">
         <v>23606</v>
@@ -1616,7 +1616,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H43" t="n">
         <v>10910</v>
@@ -1674,7 +1674,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H45" t="n">
         <v>2007</v>
@@ -1703,7 +1703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H46" t="n">
         <v>6914</v>
@@ -1732,7 +1732,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>3.66389870643616</v>
+        <v>3.66389846801758</v>
       </c>
       <c r="H47" t="n">
         <v>10524</v>
@@ -1790,7 +1790,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H49" t="n">
         <v>16797</v>
@@ -1819,7 +1819,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365804672241</v>
+        <v>3.76365828514099</v>
       </c>
       <c r="H50" t="n">
         <v>9599</v>
@@ -1848,7 +1848,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.8090033531189</v>
+        <v>3.80900311470032</v>
       </c>
       <c r="H51" t="n">
         <v>25429</v>
@@ -1877,7 +1877,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H52" t="n">
         <v>919</v>
@@ -1906,7 +1906,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H53" t="n">
         <v>5908</v>
@@ -1935,7 +1935,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.66389870643616</v>
+        <v>3.66389846801758</v>
       </c>
       <c r="H54" t="n">
         <v>34891</v>
@@ -1964,7 +1964,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G55" t="n">
-        <v>3.65482974052429</v>
+        <v>3.65482950210571</v>
       </c>
       <c r="H55" t="n">
         <v>11562</v>
@@ -1993,7 +1993,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G56" t="n">
-        <v>3.65482974052429</v>
+        <v>3.65482950210571</v>
       </c>
       <c r="H56" t="n">
         <v>8142</v>
@@ -2022,7 +2022,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762212753296</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H57" t="n">
         <v>18537</v>
@@ -2051,7 +2051,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H58" t="n">
         <v>4003</v>
@@ -2080,7 +2080,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H59" t="n">
         <v>6637</v>
@@ -2109,7 +2109,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936398506165</v>
+        <v>3.65936374664307</v>
       </c>
       <c r="H60" t="n">
         <v>5790</v>
@@ -2138,7 +2138,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H61" t="n">
         <v>93456</v>
@@ -2196,7 +2196,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284770011902</v>
+        <v>3.72284746170044</v>
       </c>
       <c r="H63" t="n">
         <v>20100</v>
@@ -2283,7 +2283,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G66" t="n">
-        <v>3.66843295097351</v>
+        <v>3.66843318939209</v>
       </c>
       <c r="H66" t="n">
         <v>11194</v>
@@ -2312,7 +2312,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110584259033</v>
+        <v>3.69110608100891</v>
       </c>
       <c r="H67" t="n">
         <v>3242</v>
@@ -2370,7 +2370,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H69" t="n">
         <v>16753</v>
@@ -2457,7 +2457,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936398506165</v>
+        <v>3.65936374664307</v>
       </c>
       <c r="H72" t="n">
         <v>6928</v>
@@ -2486,7 +2486,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110584259033</v>
+        <v>3.69110608100891</v>
       </c>
       <c r="H73" t="n">
         <v>6007</v>
@@ -2515,7 +2515,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>3.63215684890747</v>
+        <v>3.63215708732605</v>
       </c>
       <c r="H74" t="n">
         <v>9636</v>
@@ -2544,7 +2544,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762212753296</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H75" t="n">
         <v>10828</v>
@@ -2573,7 +2573,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762212753296</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H76" t="n">
         <v>9217</v>
@@ -2602,7 +2602,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H77" t="n">
         <v>10457</v>
@@ -2660,7 +2660,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H79" t="n">
         <v>16654</v>
@@ -2689,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762212753296</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H80" t="n">
         <v>1294</v>
@@ -2747,7 +2747,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320809364319</v>
+        <v>3.57320785522461</v>
       </c>
       <c r="H82" t="n">
         <v>5877</v>
@@ -2776,7 +2776,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G83" t="n">
-        <v>3.54600071907043</v>
+        <v>3.54600095748901</v>
       </c>
       <c r="H83" t="n">
         <v>3337</v>
@@ -2805,7 +2805,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H84" t="n">
         <v>21297</v>
@@ -2863,7 +2863,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729238510132</v>
+        <v>3.38729214668274</v>
       </c>
       <c r="H86" t="n">
         <v>4796</v>
@@ -2892,7 +2892,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.45984482765198</v>
+        <v>3.45984506607056</v>
       </c>
       <c r="H87" t="n">
         <v>56731</v>
@@ -2921,7 +2921,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47798323631287</v>
+        <v>3.47798299789429</v>
       </c>
       <c r="H88" t="n">
         <v>5844</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.44624137878418</v>
+        <v>3.4462411403656</v>
       </c>
       <c r="H89" t="n">
         <v>5063</v>
@@ -3008,7 +3008,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.47798323631287</v>
+        <v>3.47798299789429</v>
       </c>
       <c r="H91" t="n">
         <v>7413</v>
@@ -3037,7 +3037,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47344851493835</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H92" t="n">
         <v>2793</v>
@@ -3095,7 +3095,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903376579285</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H94" t="n">
         <v>14502</v>
@@ -3124,7 +3124,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>3.35555052757263</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H95" t="n">
         <v>19856</v>
@@ -3153,7 +3153,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>3.32380890846252</v>
+        <v>3.3238091468811</v>
       </c>
       <c r="H96" t="n">
         <v>1326</v>
@@ -3182,7 +3182,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531010627747</v>
+        <v>3.45531058311462</v>
       </c>
       <c r="H97" t="n">
         <v>13724</v>
@@ -3211,7 +3211,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891379356384</v>
+        <v>3.46891403198242</v>
       </c>
       <c r="H98" t="n">
         <v>2853</v>
@@ -3385,7 +3385,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>3.35555052757263</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H104" t="n">
         <v>6856</v>
@@ -3414,7 +3414,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35555052757263</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H105" t="n">
         <v>4111</v>
@@ -3559,7 +3559,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H110" t="n">
         <v>33451</v>
@@ -3617,7 +3617,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.49612092971802</v>
+        <v>3.4961211681366</v>
       </c>
       <c r="H112" t="n">
         <v>28788</v>
@@ -3762,7 +3762,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G117" t="n">
-        <v>3.60041522979736</v>
+        <v>3.60041546821594</v>
       </c>
       <c r="H117" t="n">
         <v>3317</v>
@@ -3791,7 +3791,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831297874451</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H118" t="n">
         <v>29715</v>
@@ -3878,7 +3878,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.49612092971802</v>
+        <v>3.4961211681366</v>
       </c>
       <c r="H121" t="n">
         <v>6937</v>
@@ -3936,7 +3936,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287811279297</v>
+        <v>3.33287787437439</v>
       </c>
       <c r="H123" t="n">
         <v>13328</v>
@@ -3965,7 +3965,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>3.26486015319824</v>
+        <v>3.26485991477966</v>
       </c>
       <c r="H124" t="n">
         <v>17450</v>
@@ -3994,7 +3994,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32834362983704</v>
+        <v>3.32834339141846</v>
       </c>
       <c r="H125" t="n">
         <v>9558</v>
@@ -4139,7 +4139,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H130" t="n">
         <v>2361</v>
@@ -4197,7 +4197,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>3.26486015319824</v>
+        <v>3.26485991477966</v>
       </c>
       <c r="H132" t="n">
         <v>3010</v>
@@ -4255,7 +4255,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951460838318</v>
+        <v>3.21951484680176</v>
       </c>
       <c r="H134" t="n">
         <v>60461</v>
@@ -4313,7 +4313,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>3.31927442550659</v>
+        <v>3.31927466392517</v>
       </c>
       <c r="H136" t="n">
         <v>21037</v>
@@ -4371,7 +4371,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020569801331</v>
+        <v>3.31020545959473</v>
       </c>
       <c r="H138" t="n">
         <v>2087</v>
@@ -4400,7 +4400,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>3.35555052757263</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H139" t="n">
         <v>353762</v>
@@ -4487,7 +4487,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.47344851493835</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H142" t="n">
         <v>1980</v>
@@ -4574,7 +4574,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G145" t="n">
-        <v>3.31927442550659</v>
+        <v>3.31927466392517</v>
       </c>
       <c r="H145" t="n">
         <v>2079</v>
@@ -4603,7 +4603,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>3.09708285331726</v>
+        <v>3.09708261489868</v>
       </c>
       <c r="H146" t="n">
         <v>29237</v>
@@ -4806,7 +4806,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G153" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H153" t="n">
         <v>14357</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H156" t="n">
         <v>10379</v>
@@ -4922,7 +4922,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756345748901</v>
+        <v>2.89756321907043</v>
       </c>
       <c r="H157" t="n">
         <v>4634</v>
@@ -4951,7 +4951,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.96104693412781</v>
+        <v>2.96104669570923</v>
       </c>
       <c r="H158" t="n">
         <v>1286</v>
@@ -4980,7 +4980,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>2.95197796821594</v>
+        <v>2.95197772979736</v>
       </c>
       <c r="H159" t="n">
         <v>3731</v>
@@ -5096,7 +5096,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H163" t="n">
         <v>1018</v>
@@ -5125,7 +5125,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G164" t="n">
-        <v>3.04720258712769</v>
+        <v>3.04720282554626</v>
       </c>
       <c r="H164" t="n">
         <v>3360</v>
@@ -5183,7 +5183,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G166" t="n">
-        <v>3.0834789276123</v>
+        <v>3.08347916603088</v>
       </c>
       <c r="H166" t="n">
         <v>6067</v>
@@ -5212,7 +5212,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G167" t="n">
-        <v>3.09708285331726</v>
+        <v>3.09708261489868</v>
       </c>
       <c r="H167" t="n">
         <v>10498</v>
@@ -5270,7 +5270,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.3736891746521</v>
+        <v>3.37368869781494</v>
       </c>
       <c r="H169" t="n">
         <v>87762</v>
@@ -5386,7 +5386,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G173" t="n">
-        <v>3.16056609153748</v>
+        <v>3.1605658531189</v>
       </c>
       <c r="H173" t="n">
         <v>546</v>
@@ -5415,7 +5415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.0834789276123</v>
+        <v>3.08347916603088</v>
       </c>
       <c r="H174" t="n">
         <v>4116</v>
@@ -5473,7 +5473,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.91116714477539</v>
+        <v>2.91116690635681</v>
       </c>
       <c r="H176" t="n">
         <v>13401</v>
@@ -5502,7 +5502,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H177" t="n">
         <v>9793</v>
@@ -5531,7 +5531,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.02453017234802</v>
+        <v>3.02452993392944</v>
       </c>
       <c r="H178" t="n">
         <v>1198</v>
@@ -5589,7 +5589,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H180" t="n">
         <v>998</v>
@@ -5676,7 +5676,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.03813362121582</v>
+        <v>3.0381338596344</v>
       </c>
       <c r="H183" t="n">
         <v>788</v>
@@ -5705,7 +5705,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266810417175</v>
+        <v>3.04266834259033</v>
       </c>
       <c r="H184" t="n">
         <v>656</v>
@@ -5734,7 +5734,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.03813362121582</v>
+        <v>3.0381338596344</v>
       </c>
       <c r="H185" t="n">
         <v>3316</v>
@@ -5821,7 +5821,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G188" t="n">
-        <v>3.03813362121582</v>
+        <v>3.0381338596344</v>
       </c>
       <c r="H188" t="n">
         <v>26816</v>
@@ -5850,7 +5850,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G189" t="n">
-        <v>2.99732327461243</v>
+        <v>2.99732303619385</v>
       </c>
       <c r="H189" t="n">
         <v>14092</v>
@@ -5908,7 +5908,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.0834789276123</v>
+        <v>3.08347916603088</v>
       </c>
       <c r="H191" t="n">
         <v>12796</v>
@@ -5966,7 +5966,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>3.03813362121582</v>
+        <v>3.0381338596344</v>
       </c>
       <c r="H193" t="n">
         <v>2404</v>
@@ -6111,7 +6111,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H198" t="n">
         <v>8621</v>
@@ -6140,7 +6140,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H199" t="n">
         <v>6598</v>
@@ -6227,7 +6227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.03813362121582</v>
+        <v>3.0381338596344</v>
       </c>
       <c r="H202" t="n">
         <v>6893</v>
@@ -6314,7 +6314,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011566162109</v>
+        <v>2.97011590003967</v>
       </c>
       <c r="H205" t="n">
         <v>4097</v>
@@ -6459,7 +6459,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951460838318</v>
+        <v>3.21951484680176</v>
       </c>
       <c r="H210" t="n">
         <v>21001</v>
@@ -6517,7 +6517,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.36461973190308</v>
+        <v>3.36461997032166</v>
       </c>
       <c r="H212" t="n">
         <v>17177</v>
@@ -6546,7 +6546,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765301704407</v>
+        <v>3.23765277862549</v>
       </c>
       <c r="H213" t="n">
         <v>4683</v>
@@ -6604,7 +6604,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416977882385</v>
+        <v>3.17416954040527</v>
       </c>
       <c r="H215" t="n">
         <v>6340</v>
@@ -6691,7 +6691,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.16056609153748</v>
+        <v>3.1605658531189</v>
       </c>
       <c r="H218" t="n">
         <v>4799</v>
@@ -6720,7 +6720,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416977882385</v>
+        <v>3.17416954040527</v>
       </c>
       <c r="H219" t="n">
         <v>8838</v>
@@ -6749,7 +6749,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603137016296</v>
+        <v>3.15603160858154</v>
       </c>
       <c r="H220" t="n">
         <v>16930</v>
@@ -6778,7 +6778,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.92930507659912</v>
+        <v>2.9293053150177</v>
       </c>
       <c r="H221" t="n">
         <v>10002</v>
@@ -6981,7 +6981,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H228" t="n">
         <v>593</v>
@@ -7039,7 +7039,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954549789429</v>
+        <v>2.82954525947571</v>
       </c>
       <c r="H230" t="n">
         <v>4733</v>
@@ -7097,7 +7097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.04720258712769</v>
+        <v>3.04720282554626</v>
       </c>
       <c r="H232" t="n">
         <v>111</v>
@@ -7126,7 +7126,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G233" t="n">
-        <v>3.04720258712769</v>
+        <v>3.04720282554626</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G234" t="n">
-        <v>3.04720258712769</v>
+        <v>3.04720282554626</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G235" t="n">
-        <v>2.83861446380615</v>
+        <v>2.83861470222473</v>
       </c>
       <c r="H235" t="n">
         <v>18000</v>
@@ -7213,7 +7213,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H236" t="n">
         <v>11979</v>
@@ -7271,7 +7271,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H238" t="n">
         <v>16491</v>
@@ -7300,7 +7300,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H239" t="n">
         <v>10412</v>
@@ -7416,7 +7416,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>2.77513098716736</v>
+        <v>2.77513122558594</v>
       </c>
       <c r="H243" t="n">
         <v>3305</v>
@@ -7474,7 +7474,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>2.68444085121155</v>
+        <v>2.68444061279297</v>
       </c>
       <c r="H245" t="n">
         <v>28119</v>
@@ -7503,7 +7503,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G246" t="n">
-        <v>2.84768390655518</v>
+        <v>2.84768342971802</v>
       </c>
       <c r="H246" t="n">
         <v>8994</v>
@@ -7532,7 +7532,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H247" t="n">
         <v>5286</v>
@@ -7561,7 +7561,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H248" t="n">
         <v>1003</v>
@@ -7648,7 +7648,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G251" t="n">
-        <v>2.7524585723877</v>
+        <v>2.75245881080627</v>
       </c>
       <c r="H251" t="n">
         <v>1377</v>
@@ -7677,7 +7677,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G252" t="n">
-        <v>2.7524585723877</v>
+        <v>2.75245881080627</v>
       </c>
       <c r="H252" t="n">
         <v>336</v>
@@ -7764,7 +7764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H255" t="n">
         <v>18878</v>
@@ -7793,7 +7793,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H256" t="n">
         <v>2600</v>
@@ -7851,7 +7851,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071695327759</v>
+        <v>2.72071671485901</v>
       </c>
       <c r="H258" t="n">
         <v>1704</v>
@@ -7909,7 +7909,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>2.68444085121155</v>
+        <v>2.68444061279297</v>
       </c>
       <c r="H260" t="n">
         <v>6213</v>
@@ -7938,7 +7938,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H261" t="n">
         <v>2757</v>
@@ -7967,7 +7967,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H262" t="n">
         <v>5847</v>
@@ -8141,7 +8141,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H268" t="n">
         <v>6031</v>
@@ -8170,7 +8170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H269" t="n">
         <v>1163</v>
@@ -8228,7 +8228,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G271" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H271" t="n">
         <v>23246</v>
@@ -8257,7 +8257,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.5801465511322</v>
+        <v>2.58014631271362</v>
       </c>
       <c r="H272" t="n">
         <v>7178</v>
@@ -8286,7 +8286,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.59828472137451</v>
+        <v>2.59828448295593</v>
       </c>
       <c r="H273" t="n">
         <v>1912</v>
@@ -8315,7 +8315,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.55293941497803</v>
+        <v>2.55293917655945</v>
       </c>
       <c r="H274" t="n">
         <v>1083</v>
@@ -8373,7 +8373,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H276" t="n">
         <v>8540</v>
@@ -8431,7 +8431,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>2.45317983627319</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H278" t="n">
         <v>2892</v>
@@ -8460,7 +8460,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G279" t="n">
-        <v>2.45771384239197</v>
+        <v>2.45771408081055</v>
       </c>
       <c r="H279" t="n">
         <v>2775</v>
@@ -8489,7 +8489,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062715530396</v>
+        <v>2.38062739372253</v>
       </c>
       <c r="H280" t="n">
         <v>7350</v>
@@ -8518,7 +8518,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342001914978</v>
       </c>
       <c r="H281" t="n">
         <v>44116</v>
@@ -8576,7 +8576,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.2808678150177</v>
+        <v>2.28086757659912</v>
       </c>
       <c r="H283" t="n">
         <v>2655</v>
@@ -8663,7 +8663,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912571907043</v>
+        <v>2.24912595748901</v>
       </c>
       <c r="H286" t="n">
         <v>3503</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750431060791</v>
+        <v>2.16750454902649</v>
       </c>
       <c r="H290" t="n">
         <v>7059</v>
@@ -8808,7 +8808,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>2.11308979988098</v>
+        <v>2.11309003829956</v>
       </c>
       <c r="H291" t="n">
         <v>2789</v>
@@ -8837,7 +8837,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.13576292991638</v>
+        <v>2.1357626914978</v>
       </c>
       <c r="H292" t="n">
         <v>9540</v>
@@ -8953,7 +8953,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14029717445374</v>
+        <v>2.14029693603516</v>
       </c>
       <c r="H296" t="n">
         <v>8430</v>
@@ -8982,7 +8982,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.18564248085022</v>
+        <v>2.18564224243164</v>
       </c>
       <c r="H297" t="n">
         <v>16353</v>
@@ -9156,7 +9156,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H303" t="n">
         <v>8916</v>
@@ -9185,7 +9185,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H304" t="n">
         <v>9153</v>
@@ -9330,7 +9330,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H309" t="n">
         <v>7036</v>
@@ -9359,7 +9359,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H311" t="n">
         <v>5875</v>
@@ -9475,7 +9475,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G314" t="n">
-        <v>2.48038649559021</v>
+        <v>2.48038673400879</v>
       </c>
       <c r="H314" t="n">
         <v>4439</v>
@@ -9504,7 +9504,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H315" t="n">
         <v>2887</v>
@@ -9533,7 +9533,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G316" t="n">
-        <v>2.50759387016296</v>
+        <v>2.50759410858154</v>
       </c>
       <c r="H316" t="n">
         <v>2151</v>
@@ -9591,7 +9591,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H318" t="n">
         <v>3432</v>
@@ -9736,7 +9736,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236877441406</v>
       </c>
       <c r="H323" t="n">
         <v>923</v>
@@ -9765,7 +9765,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236877441406</v>
       </c>
       <c r="H324" t="n">
         <v>500</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423060417175</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H326" t="n">
         <v>10875</v>
@@ -9939,7 +9939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.36702346801758</v>
+        <v>2.367023229599</v>
       </c>
       <c r="H330" t="n">
         <v>7415</v>
@@ -9968,7 +9968,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342001914978</v>
       </c>
       <c r="H331" t="n">
         <v>12852</v>
@@ -10113,7 +10113,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.30807518959045</v>
+        <v>2.3080747127533</v>
       </c>
       <c r="H336" t="n">
         <v>989</v>
@@ -10171,7 +10171,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.32167840003967</v>
+        <v>2.32167816162109</v>
       </c>
       <c r="H338" t="n">
         <v>5855</v>
@@ -10229,7 +10229,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993654251099</v>
+        <v>2.28993678092957</v>
       </c>
       <c r="H340" t="n">
         <v>31736</v>
@@ -10258,7 +10258,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H341" t="n">
         <v>4266</v>
@@ -10287,7 +10287,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912571907043</v>
+        <v>2.24912595748901</v>
       </c>
       <c r="H342" t="n">
         <v>12825</v>
@@ -10316,7 +10316,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G343" t="n">
-        <v>2.27633309364319</v>
+        <v>2.27633285522461</v>
       </c>
       <c r="H343" t="n">
         <v>5900</v>
@@ -10374,7 +10374,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>2.27633309364319</v>
+        <v>2.27633285522461</v>
       </c>
       <c r="H345" t="n">
         <v>8557</v>
@@ -10461,7 +10461,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423060417175</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H348" t="n">
         <v>518</v>
@@ -10548,7 +10548,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179861068726</v>
+        <v>2.27179837226868</v>
       </c>
       <c r="H351" t="n">
         <v>4619</v>
@@ -10577,7 +10577,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G352" t="n">
-        <v>2.45317983627319</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H352" t="n">
         <v>4007</v>
@@ -10635,7 +10635,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.41236925125122</v>
+        <v>2.41236877441406</v>
       </c>
       <c r="H354" t="n">
         <v>2737</v>
@@ -10664,7 +10664,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G355" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H355" t="n">
         <v>4472</v>
@@ -10693,7 +10693,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G356" t="n">
-        <v>2.36702346801758</v>
+        <v>2.367023229599</v>
       </c>
       <c r="H356" t="n">
         <v>153</v>
@@ -10780,7 +10780,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G359" t="n">
-        <v>2.19017696380615</v>
+        <v>2.19017672538757</v>
       </c>
       <c r="H359" t="n">
         <v>9087</v>
@@ -10867,7 +10867,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H362" t="n">
         <v>1115</v>
@@ -10925,7 +10925,7 @@
         <v>2.75</v>
       </c>
       <c r="G364" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H364" t="n">
         <v>5478</v>
@@ -10954,7 +10954,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>2.45771384239197</v>
+        <v>2.45771408081055</v>
       </c>
       <c r="H365" t="n">
         <v>3245</v>
@@ -10983,7 +10983,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G366" t="n">
-        <v>2.37609243392944</v>
+        <v>2.37609267234802</v>
       </c>
       <c r="H366" t="n">
         <v>6489</v>
@@ -11041,7 +11041,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G368" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H368" t="n">
         <v>2162</v>
@@ -11070,7 +11070,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H369" t="n">
         <v>1383</v>
@@ -11128,7 +11128,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>2.37609243392944</v>
+        <v>2.37609267234802</v>
       </c>
       <c r="H371" t="n">
         <v>15244</v>
@@ -11186,7 +11186,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.4032998085022</v>
+        <v>2.40330004692078</v>
       </c>
       <c r="H373" t="n">
         <v>26801</v>
@@ -11215,7 +11215,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.38969612121582</v>
+        <v>2.3896963596344</v>
       </c>
       <c r="H374" t="n">
         <v>7617</v>
@@ -11244,7 +11244,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.4032998085022</v>
+        <v>2.40330004692078</v>
       </c>
       <c r="H375" t="n">
         <v>8213</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H376" t="n">
         <v>7974</v>
@@ -11302,7 +11302,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H377" t="n">
         <v>85081</v>
@@ -11331,7 +11331,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>2.37609243392944</v>
+        <v>2.37609267234802</v>
       </c>
       <c r="H378" t="n">
         <v>4460</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H379" t="n">
         <v>125340</v>
@@ -11389,7 +11389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H380" t="n">
         <v>15968</v>
@@ -11418,7 +11418,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.4985249042511</v>
+        <v>2.49852514266968</v>
       </c>
       <c r="H381" t="n">
         <v>3626</v>
@@ -11476,7 +11476,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>2.56200814247131</v>
+        <v>2.56200838088989</v>
       </c>
       <c r="H383" t="n">
         <v>1921</v>
@@ -11505,7 +11505,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>2.55293941497803</v>
+        <v>2.55293917655945</v>
       </c>
       <c r="H384" t="n">
         <v>7902</v>
@@ -11563,7 +11563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H386" t="n">
         <v>6461</v>
@@ -11592,7 +11592,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H387" t="n">
         <v>400</v>
@@ -11650,7 +11650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H389" t="n">
         <v>5695</v>
@@ -11679,7 +11679,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H390" t="n">
         <v>3704</v>
@@ -11737,7 +11737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H392" t="n">
         <v>8970</v>
@@ -11853,7 +11853,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666331291199</v>
+        <v>2.51666307449341</v>
       </c>
       <c r="H396" t="n">
         <v>67390</v>
@@ -11882,7 +11882,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H397" t="n">
         <v>6517</v>
@@ -11969,7 +11969,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H400" t="n">
         <v>6772</v>
@@ -11998,7 +11998,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H401" t="n">
         <v>25644</v>
@@ -12056,7 +12056,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G403" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H403" t="n">
         <v>27202</v>
@@ -12085,7 +12085,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095761299133</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H404" t="n">
         <v>20579</v>
@@ -12114,7 +12114,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H405" t="n">
         <v>5957</v>
@@ -12143,7 +12143,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H406" t="n">
         <v>4040</v>
@@ -12172,7 +12172,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H407" t="n">
         <v>10856</v>
@@ -12201,7 +12201,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H408" t="n">
         <v>3770</v>
@@ -12230,7 +12230,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095761299133</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H409" t="n">
         <v>3350</v>
@@ -12375,7 +12375,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>2.44864535331726</v>
+        <v>2.44864511489868</v>
       </c>
       <c r="H414" t="n">
         <v>11291</v>
@@ -12404,7 +12404,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573204040527</v>
+        <v>2.52573227882385</v>
       </c>
       <c r="H415" t="n">
         <v>8421</v>
@@ -12462,7 +12462,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G417" t="n">
-        <v>2.37609243392944</v>
+        <v>2.37609267234802</v>
       </c>
       <c r="H417" t="n">
         <v>3055</v>
@@ -12520,7 +12520,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G419" t="n">
-        <v>2.36702346801758</v>
+        <v>2.367023229599</v>
       </c>
       <c r="H419" t="n">
         <v>3581</v>
@@ -12578,7 +12578,7 @@
         <v>2.75</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H421" t="n">
         <v>5517</v>
@@ -12607,7 +12607,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H422" t="n">
         <v>7693</v>
@@ -12694,7 +12694,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47131776809692</v>
+        <v>2.47131752967834</v>
       </c>
       <c r="H425" t="n">
         <v>642</v>
@@ -12723,7 +12723,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H426" t="n">
         <v>2034</v>
@@ -12752,7 +12752,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H427" t="n">
         <v>4867</v>
@@ -12781,7 +12781,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G428" t="n">
-        <v>2.56200814247131</v>
+        <v>2.56200838088989</v>
       </c>
       <c r="H428" t="n">
         <v>30098</v>
@@ -12868,7 +12868,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H431" t="n">
         <v>2176</v>
@@ -12897,7 +12897,7 @@
         <v>2.75</v>
       </c>
       <c r="G432" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H432" t="n">
         <v>6692</v>
@@ -13042,7 +13042,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H437" t="n">
         <v>4459</v>
@@ -13071,7 +13071,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G438" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H438" t="n">
         <v>7550</v>
@@ -13129,7 +13129,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H440" t="n">
         <v>1970</v>
@@ -13187,7 +13187,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.66630220413208</v>
+        <v>2.66630244255066</v>
       </c>
       <c r="H442" t="n">
         <v>3157</v>
@@ -13216,7 +13216,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H443" t="n">
         <v>905</v>
@@ -13245,7 +13245,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095761299133</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H444" t="n">
         <v>305</v>
@@ -13390,7 +13390,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095761299133</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H449" t="n">
         <v>5650</v>
@@ -13419,7 +13419,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G450" t="n">
-        <v>2.68444085121155</v>
+        <v>2.68444061279297</v>
       </c>
       <c r="H450" t="n">
         <v>7407</v>
@@ -13564,7 +13564,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G455" t="n">
-        <v>2.82047629356384</v>
+        <v>2.82047653198242</v>
       </c>
       <c r="H455" t="n">
         <v>22810</v>
@@ -13622,7 +13622,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H457" t="n">
         <v>267</v>
@@ -13651,7 +13651,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>2.8114070892334</v>
+        <v>2.81140732765198</v>
       </c>
       <c r="H458" t="n">
         <v>2064</v>
@@ -13680,7 +13680,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>2.68444085121155</v>
+        <v>2.68444061279297</v>
       </c>
       <c r="H459" t="n">
         <v>11631</v>
@@ -13709,7 +13709,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H460" t="n">
         <v>4577</v>
@@ -14144,7 +14144,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H475" t="n">
         <v>7912</v>
@@ -14202,7 +14202,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G477" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H477" t="n">
         <v>29506</v>
@@ -14260,7 +14260,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G479" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H479" t="n">
         <v>58941</v>
@@ -14347,7 +14347,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G482" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H482" t="n">
         <v>7670</v>
@@ -14434,7 +14434,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H485" t="n">
         <v>2516</v>
@@ -14492,7 +14492,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61125588417053</v>
+        <v>2.61125612258911</v>
       </c>
       <c r="H487" t="n">
         <v>126942</v>
@@ -14550,7 +14550,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G489" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H489" t="n">
         <v>1637</v>
@@ -14579,7 +14579,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G490" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H490" t="n">
         <v>62146</v>
@@ -14637,7 +14637,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H492" t="n">
         <v>9831</v>
@@ -14666,7 +14666,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G497" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H497" t="n">
         <v>1143</v>
@@ -14869,7 +14869,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H500" t="n">
         <v>5010</v>
@@ -15275,7 +15275,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G514" t="n">
-        <v>2.66661882400513</v>
+        <v>2.66661858558655</v>
       </c>
       <c r="H514" t="n">
         <v>3133</v>
@@ -15304,7 +15304,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G515" t="n">
-        <v>2.66661882400513</v>
+        <v>2.66661858558655</v>
       </c>
       <c r="H515" t="n">
         <v>1609</v>
@@ -15362,7 +15362,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H517" t="n">
         <v>1132</v>
@@ -15391,7 +15391,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H518" t="n">
         <v>1263</v>
@@ -15449,7 +15449,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H520" t="n">
         <v>236</v>
@@ -15478,7 +15478,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H521" t="n">
         <v>2000</v>
@@ -16203,7 +16203,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120808601379</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H546" t="n">
         <v>23578</v>
@@ -16232,7 +16232,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120808601379</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H547" t="n">
         <v>4925</v>
@@ -16377,7 +16377,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120808601379</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H552" t="n">
         <v>22273</v>
@@ -16609,7 +16609,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734279632568</v>
+        <v>2.77734303474426</v>
       </c>
       <c r="H560" t="n">
         <v>6973</v>
@@ -16638,7 +16638,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79579734802246</v>
+        <v>2.79579710960388</v>
       </c>
       <c r="H561" t="n">
         <v>2786</v>
@@ -16696,7 +16696,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120808601379</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H563" t="n">
         <v>1740</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H568" t="n">
         <v>4278</v>
@@ -16957,7 +16957,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41748785972595</v>
+        <v>2.41748809814453</v>
       </c>
       <c r="H572" t="n">
         <v>1200</v>
@@ -17102,7 +17102,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>2.66661882400513</v>
+        <v>2.66661858558655</v>
       </c>
       <c r="H577" t="n">
         <v>1902</v>
@@ -17131,7 +17131,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H578" t="n">
         <v>8794</v>
@@ -17160,7 +17160,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G579" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H579" t="n">
         <v>17262</v>
@@ -17276,7 +17276,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G583" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H583" t="n">
         <v>2004</v>
@@ -17392,7 +17392,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.61125588417053</v>
+        <v>2.61125612258911</v>
       </c>
       <c r="H587" t="n">
         <v>2540</v>
@@ -17421,7 +17421,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H588" t="n">
         <v>3050</v>
@@ -17537,7 +17537,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G592" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H592" t="n">
         <v>2322</v>
@@ -17566,7 +17566,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H593" t="n">
         <v>12355</v>
@@ -17595,7 +17595,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G594" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H594" t="n">
         <v>4823</v>
@@ -17624,7 +17624,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H595" t="n">
         <v>7592</v>
@@ -17653,7 +17653,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>2.41748785972595</v>
+        <v>2.41748809814453</v>
       </c>
       <c r="H596" t="n">
         <v>13053</v>
@@ -17682,7 +17682,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G597" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H597" t="n">
         <v>20130</v>
@@ -17798,7 +17798,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H601" t="n">
         <v>1618</v>
@@ -17914,7 +17914,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G605" t="n">
-        <v>2.58357501029968</v>
+        <v>2.5835747718811</v>
       </c>
       <c r="H605" t="n">
         <v>985</v>
@@ -17972,7 +17972,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G607" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H607" t="n">
         <v>5192</v>
@@ -18001,7 +18001,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H608" t="n">
         <v>2394</v>
@@ -18175,7 +18175,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H614" t="n">
         <v>1453</v>
@@ -18291,7 +18291,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584562301636</v>
       </c>
       <c r="H618" t="n">
         <v>5256</v>
@@ -18349,7 +18349,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734279632568</v>
+        <v>2.77734303474426</v>
       </c>
       <c r="H620" t="n">
         <v>10213</v>
@@ -18610,7 +18610,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G629" t="n">
-        <v>3.07260870933533</v>
+        <v>3.07260847091675</v>
       </c>
       <c r="H629" t="n">
         <v>16167</v>
@@ -18639,7 +18639,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797141075134</v>
       </c>
       <c r="H630" t="n">
         <v>13699</v>
@@ -18668,7 +18668,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H631" t="n">
         <v>57880</v>
@@ -18697,7 +18697,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797141075134</v>
       </c>
       <c r="H632" t="n">
         <v>4540</v>
@@ -18755,7 +18755,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>3.15565252304077</v>
+        <v>3.15565228462219</v>
       </c>
       <c r="H634" t="n">
         <v>2023</v>
@@ -18813,7 +18813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H636" t="n">
         <v>1875</v>
@@ -18871,7 +18871,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>3.15565252304077</v>
+        <v>3.15565228462219</v>
       </c>
       <c r="H638" t="n">
         <v>17794</v>
@@ -19161,7 +19161,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>3.07260870933533</v>
+        <v>3.07260847091675</v>
       </c>
       <c r="H648" t="n">
         <v>31675</v>
@@ -19219,7 +19219,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12797117233276</v>
+        <v>3.12797141075134</v>
       </c>
       <c r="H650" t="n">
         <v>81888</v>
@@ -19277,7 +19277,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H652" t="n">
         <v>8899</v>
@@ -19393,7 +19393,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>3.34019303321838</v>
+        <v>3.34019327163696</v>
       </c>
       <c r="H656" t="n">
         <v>11889</v>
@@ -19422,7 +19422,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>3.43246412277222</v>
+        <v>3.43246388435364</v>
       </c>
       <c r="H657" t="n">
         <v>69496</v>
@@ -19451,7 +19451,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G658" t="n">
-        <v>3.29405808448792</v>
+        <v>3.29405784606934</v>
       </c>
       <c r="H658" t="n">
         <v>44455</v>
@@ -19509,7 +19509,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H660" t="n">
         <v>3302</v>
@@ -19567,7 +19567,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>3.06338167190552</v>
+        <v>3.0633819103241</v>
       </c>
       <c r="H662" t="n">
         <v>6848</v>
@@ -19683,7 +19683,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G666" t="n">
-        <v>2.85115933418274</v>
+        <v>2.85115957260132</v>
       </c>
       <c r="H666" t="n">
         <v>3592</v>
@@ -19770,7 +19770,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G669" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H669" t="n">
         <v>2510</v>
@@ -19799,7 +19799,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G670" t="n">
-        <v>3.00801944732666</v>
+        <v>3.00801920890808</v>
       </c>
       <c r="H670" t="n">
         <v>4150</v>
@@ -19886,7 +19886,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G673" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H673" t="n">
         <v>229</v>
@@ -19944,7 +19944,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>2.92497587203979</v>
+        <v>2.92497611045837</v>
       </c>
       <c r="H675" t="n">
         <v>12549</v>
@@ -19973,7 +19973,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G676" t="n">
-        <v>2.87884068489075</v>
+        <v>2.87884044647217</v>
       </c>
       <c r="H676" t="n">
         <v>530</v>
@@ -20118,7 +20118,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>3.01724648475647</v>
+        <v>3.01724624633789</v>
       </c>
       <c r="H681" t="n">
         <v>5416</v>
@@ -20147,7 +20147,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>3.00801944732666</v>
+        <v>3.00801920890808</v>
       </c>
       <c r="H682" t="n">
         <v>3265</v>
@@ -20176,7 +20176,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>3.01724648475647</v>
+        <v>3.01724624633789</v>
       </c>
       <c r="H683" t="n">
         <v>6747</v>
@@ -20263,7 +20263,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>3.01724648475647</v>
+        <v>3.01724624633789</v>
       </c>
       <c r="H686" t="n">
         <v>3184</v>
@@ -20495,7 +20495,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>2.94343018531799</v>
+        <v>2.94342994689941</v>
       </c>
       <c r="H694" t="n">
         <v>2567</v>
@@ -20785,7 +20785,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G704" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H704" t="n">
         <v>7911</v>
@@ -20901,7 +20901,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G708" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H708" t="n">
         <v>10802</v>
@@ -20930,7 +20930,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G709" t="n">
-        <v>3.06338167190552</v>
+        <v>3.0633819103241</v>
       </c>
       <c r="H709" t="n">
         <v>10942</v>
@@ -21046,7 +21046,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>3.34019303321838</v>
+        <v>3.34019327163696</v>
       </c>
       <c r="H713" t="n">
         <v>29644</v>
@@ -38800,6 +38800,64 @@
         <v>1682</v>
       </c>
       <c r="I1325" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1326" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>3.47000002861023</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H1326" t="n">
+        <v>2699</v>
+      </c>
+      <c r="I1326" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1327" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="H1327" t="n">
+        <v>1350</v>
+      </c>
+      <c r="I1327" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161733627319</v>
+        <v>3.10161709785461</v>
       </c>
       <c r="H5" t="n">
         <v>23147</v>
@@ -601,7 +601,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H8" t="n">
         <v>720993</v>
@@ -804,7 +804,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G15" t="n">
-        <v>3.39182662963867</v>
+        <v>3.39182686805725</v>
       </c>
       <c r="H15" t="n">
         <v>33287</v>
@@ -862,7 +862,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924377441406</v>
       </c>
       <c r="H17" t="n">
         <v>150547</v>
@@ -891,7 +891,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924377441406</v>
       </c>
       <c r="H18" t="n">
         <v>290894</v>
@@ -1036,7 +1036,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831274032593</v>
+        <v>3.71831321716309</v>
       </c>
       <c r="H23" t="n">
         <v>29141</v>
@@ -1094,7 +1094,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.89515924453735</v>
+        <v>3.89515972137451</v>
       </c>
       <c r="H25" t="n">
         <v>186140</v>
@@ -1152,7 +1152,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726149559021</v>
+        <v>3.77726197242737</v>
       </c>
       <c r="H27" t="n">
         <v>75595</v>
@@ -1210,7 +1210,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993486404419</v>
+        <v>3.79993438720703</v>
       </c>
       <c r="H29" t="n">
         <v>38465</v>
@@ -1239,7 +1239,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G30" t="n">
-        <v>3.6865713596344</v>
+        <v>3.68657112121582</v>
       </c>
       <c r="H30" t="n">
         <v>57117</v>
@@ -1268,7 +1268,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377825737</v>
+        <v>3.71377801895142</v>
       </c>
       <c r="H31" t="n">
         <v>31484</v>
@@ -1326,7 +1326,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H33" t="n">
         <v>18869</v>
@@ -1384,7 +1384,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>3.56413888931274</v>
+        <v>3.56413912773132</v>
       </c>
       <c r="H35" t="n">
         <v>54741</v>
@@ -1413,7 +1413,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>3.56413888931274</v>
+        <v>3.56413912773132</v>
       </c>
       <c r="H36" t="n">
         <v>13961</v>
@@ -1529,7 +1529,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633093833923</v>
+        <v>3.78633069992065</v>
       </c>
       <c r="H40" t="n">
         <v>4635</v>
@@ -1587,7 +1587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H42" t="n">
         <v>23606</v>
@@ -1616,7 +1616,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H43" t="n">
         <v>10910</v>
@@ -1674,7 +1674,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H45" t="n">
         <v>2007</v>
@@ -1703,7 +1703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H46" t="n">
         <v>6914</v>
@@ -1761,7 +1761,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>3.6865713596344</v>
+        <v>3.68657112121582</v>
       </c>
       <c r="H48" t="n">
         <v>2180</v>
@@ -1877,7 +1877,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H52" t="n">
         <v>919</v>
@@ -1906,7 +1906,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H53" t="n">
         <v>5908</v>
@@ -2051,7 +2051,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H58" t="n">
         <v>4003</v>
@@ -2080,7 +2080,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H59" t="n">
         <v>6637</v>
@@ -2109,7 +2109,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H60" t="n">
         <v>5790</v>
@@ -2138,7 +2138,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H61" t="n">
         <v>93456</v>
@@ -2167,7 +2167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.7001748085022</v>
+        <v>3.70017457008362</v>
       </c>
       <c r="H62" t="n">
         <v>8191</v>
@@ -2225,7 +2225,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>3.69564008712769</v>
+        <v>3.69564032554626</v>
       </c>
       <c r="H64" t="n">
         <v>5559</v>
@@ -2457,7 +2457,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H72" t="n">
         <v>6928</v>
@@ -2602,7 +2602,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H77" t="n">
         <v>10457</v>
@@ -2631,7 +2631,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.7001748085022</v>
+        <v>3.70017457008362</v>
       </c>
       <c r="H78" t="n">
         <v>36913</v>
@@ -2660,7 +2660,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H79" t="n">
         <v>16654</v>
@@ -2718,7 +2718,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H81" t="n">
         <v>14163</v>
@@ -2747,7 +2747,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320785522461</v>
+        <v>3.57320809364319</v>
       </c>
       <c r="H82" t="n">
         <v>5877</v>
@@ -2776,7 +2776,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G83" t="n">
-        <v>3.54600095748901</v>
+        <v>3.54600071907043</v>
       </c>
       <c r="H83" t="n">
         <v>3337</v>
@@ -2805,7 +2805,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H84" t="n">
         <v>21297</v>
@@ -2863,7 +2863,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729214668274</v>
+        <v>3.38729238510132</v>
       </c>
       <c r="H86" t="n">
         <v>4796</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.4462411403656</v>
+        <v>3.44624137878418</v>
       </c>
       <c r="H89" t="n">
         <v>5063</v>
@@ -3037,7 +3037,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47344827651978</v>
+        <v>3.47344851493835</v>
       </c>
       <c r="H92" t="n">
         <v>2793</v>
@@ -3182,7 +3182,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531058311462</v>
+        <v>3.45531034469604</v>
       </c>
       <c r="H97" t="n">
         <v>13724</v>
@@ -3211,7 +3211,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891403198242</v>
+        <v>3.46891379356384</v>
       </c>
       <c r="H98" t="n">
         <v>2853</v>
@@ -3559,7 +3559,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H110" t="n">
         <v>33451</v>
@@ -3588,7 +3588,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H111" t="n">
         <v>13196</v>
@@ -3646,7 +3646,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077586174011</v>
+        <v>3.45077610015869</v>
       </c>
       <c r="H113" t="n">
         <v>3151</v>
@@ -3733,7 +3733,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H116" t="n">
         <v>1006</v>
@@ -3791,7 +3791,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831274032593</v>
+        <v>3.71831321716309</v>
       </c>
       <c r="H118" t="n">
         <v>29715</v>
@@ -3820,7 +3820,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H119" t="n">
         <v>35244</v>
@@ -4139,7 +4139,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H130" t="n">
         <v>2361</v>
@@ -4168,7 +4168,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G131" t="n">
-        <v>3.27392911911011</v>
+        <v>3.27392935752869</v>
       </c>
       <c r="H131" t="n">
         <v>8662</v>
@@ -4255,7 +4255,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H134" t="n">
         <v>60461</v>
@@ -4371,7 +4371,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020545959473</v>
+        <v>3.31020569801331</v>
       </c>
       <c r="H138" t="n">
         <v>2087</v>
@@ -4487,7 +4487,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.47344827651978</v>
+        <v>3.47344851493835</v>
       </c>
       <c r="H142" t="n">
         <v>1980</v>
@@ -4690,7 +4690,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.1469624042511</v>
+        <v>3.14696264266968</v>
       </c>
       <c r="H149" t="n">
         <v>11513</v>
@@ -4719,7 +4719,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>3.25125646591187</v>
+        <v>3.25125670433044</v>
       </c>
       <c r="H150" t="n">
         <v>5307</v>
@@ -4777,7 +4777,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.97465038299561</v>
+        <v>2.97465014457703</v>
       </c>
       <c r="H152" t="n">
         <v>14806</v>
@@ -4806,7 +4806,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G153" t="n">
-        <v>2.92023611068726</v>
+        <v>2.92023587226868</v>
       </c>
       <c r="H153" t="n">
         <v>14357</v>
@@ -4835,7 +4835,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H154" t="n">
         <v>1770</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H156" t="n">
         <v>10379</v>
@@ -4922,7 +4922,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756321907043</v>
+        <v>2.89756345748901</v>
       </c>
       <c r="H157" t="n">
         <v>4634</v>
@@ -5096,7 +5096,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H163" t="n">
         <v>1018</v>
@@ -5241,7 +5241,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>3.21044564247131</v>
+        <v>3.21044588088989</v>
       </c>
       <c r="H168" t="n">
         <v>11151</v>
@@ -5328,7 +5328,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615158081055</v>
+        <v>3.10615134239197</v>
       </c>
       <c r="H171" t="n">
         <v>59616</v>
@@ -5473,7 +5473,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.91116690635681</v>
+        <v>2.91116714477539</v>
       </c>
       <c r="H176" t="n">
         <v>13401</v>
@@ -5502,7 +5502,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H177" t="n">
         <v>9793</v>
@@ -5531,7 +5531,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.02452993392944</v>
+        <v>3.02453017234802</v>
       </c>
       <c r="H178" t="n">
         <v>1198</v>
@@ -5589,7 +5589,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H180" t="n">
         <v>998</v>
@@ -5618,7 +5618,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>2.97465038299561</v>
+        <v>2.97465014457703</v>
       </c>
       <c r="H181" t="n">
         <v>3283</v>
@@ -5705,7 +5705,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266834259033</v>
+        <v>3.04266810417175</v>
       </c>
       <c r="H184" t="n">
         <v>656</v>
@@ -5937,7 +5937,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627179145813</v>
+        <v>3.05627155303955</v>
       </c>
       <c r="H192" t="n">
         <v>9528</v>
@@ -6053,7 +6053,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744348526001</v>
       </c>
       <c r="H196" t="n">
         <v>9781</v>
@@ -6111,7 +6111,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>2.92023611068726</v>
+        <v>2.92023587226868</v>
       </c>
       <c r="H198" t="n">
         <v>8621</v>
@@ -6140,7 +6140,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>2.92023611068726</v>
+        <v>2.92023587226868</v>
       </c>
       <c r="H199" t="n">
         <v>6598</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744348526001</v>
       </c>
       <c r="H204" t="n">
         <v>41187</v>
@@ -6459,7 +6459,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H210" t="n">
         <v>21001</v>
@@ -6575,7 +6575,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753280639648</v>
+        <v>3.28753256797791</v>
       </c>
       <c r="H214" t="n">
         <v>1310</v>
@@ -6749,7 +6749,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603160858154</v>
+        <v>3.15603137016296</v>
       </c>
       <c r="H220" t="n">
         <v>16930</v>
@@ -6778,7 +6778,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.9293053150177</v>
+        <v>2.92930507659912</v>
       </c>
       <c r="H221" t="n">
         <v>10002</v>
@@ -6865,7 +6865,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035608291626</v>
+        <v>2.87035584449768</v>
       </c>
       <c r="H224" t="n">
         <v>4992</v>
@@ -6894,7 +6894,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H225" t="n">
         <v>3170</v>
@@ -6981,7 +6981,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H228" t="n">
         <v>593</v>
@@ -7213,7 +7213,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H236" t="n">
         <v>11979</v>
@@ -7271,7 +7271,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H238" t="n">
         <v>16491</v>
@@ -7300,7 +7300,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H239" t="n">
         <v>10412</v>
@@ -7445,7 +7445,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H244" t="n">
         <v>4956</v>
@@ -7503,7 +7503,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G246" t="n">
-        <v>2.84768342971802</v>
+        <v>2.8476836681366</v>
       </c>
       <c r="H246" t="n">
         <v>8994</v>
@@ -7532,7 +7532,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H247" t="n">
         <v>5286</v>
@@ -7561,7 +7561,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H248" t="n">
         <v>1003</v>
@@ -7648,7 +7648,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G251" t="n">
-        <v>2.75245881080627</v>
+        <v>2.7524585723877</v>
       </c>
       <c r="H251" t="n">
         <v>1377</v>
@@ -7677,7 +7677,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G252" t="n">
-        <v>2.75245881080627</v>
+        <v>2.7524585723877</v>
       </c>
       <c r="H252" t="n">
         <v>336</v>
@@ -7764,7 +7764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H255" t="n">
         <v>18878</v>
@@ -7793,7 +7793,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H256" t="n">
         <v>2600</v>
@@ -7822,7 +7822,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350957870483</v>
+        <v>2.69350934028625</v>
       </c>
       <c r="H257" t="n">
         <v>8062</v>
@@ -7851,7 +7851,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071671485901</v>
+        <v>2.72071695327759</v>
       </c>
       <c r="H258" t="n">
         <v>1704</v>
@@ -8170,7 +8170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H269" t="n">
         <v>1163</v>
@@ -8286,7 +8286,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.59828448295593</v>
+        <v>2.59828472137451</v>
       </c>
       <c r="H273" t="n">
         <v>1912</v>
@@ -8373,7 +8373,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H276" t="n">
         <v>8540</v>
@@ -8402,7 +8402,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945569992065</v>
+        <v>2.48945593833923</v>
       </c>
       <c r="H277" t="n">
         <v>995</v>
@@ -8489,7 +8489,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062739372253</v>
+        <v>2.38062715530396</v>
       </c>
       <c r="H280" t="n">
         <v>7350</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750454902649</v>
+        <v>2.16750431060791</v>
       </c>
       <c r="H290" t="n">
         <v>7059</v>
@@ -8866,7 +8866,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.33074736595154</v>
+        <v>2.33074712753296</v>
       </c>
       <c r="H293" t="n">
         <v>4108</v>
@@ -8895,7 +8895,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>2.34435105323792</v>
+        <v>2.34435081481934</v>
       </c>
       <c r="H294" t="n">
         <v>591</v>
@@ -8982,7 +8982,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.18564224243164</v>
+        <v>2.18564248085022</v>
       </c>
       <c r="H297" t="n">
         <v>16353</v>
@@ -9098,7 +9098,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33074736595154</v>
+        <v>2.33074712753296</v>
       </c>
       <c r="H301" t="n">
         <v>9820</v>
@@ -9127,7 +9127,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>2.35795450210571</v>
+        <v>2.35795474052429</v>
       </c>
       <c r="H302" t="n">
         <v>5211</v>
@@ -9301,7 +9301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H308" t="n">
         <v>371</v>
@@ -9330,7 +9330,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H309" t="n">
         <v>7036</v>
@@ -9359,7 +9359,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H311" t="n">
         <v>5875</v>
@@ -9533,7 +9533,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G316" t="n">
-        <v>2.50759410858154</v>
+        <v>2.50759387016296</v>
       </c>
       <c r="H316" t="n">
         <v>2151</v>
@@ -9591,7 +9591,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H318" t="n">
         <v>3432</v>
@@ -9620,7 +9620,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G319" t="n">
-        <v>2.55747365951538</v>
+        <v>2.5574734210968</v>
       </c>
       <c r="H319" t="n">
         <v>2553</v>
@@ -9794,7 +9794,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.39876532554626</v>
+        <v>2.39876556396484</v>
       </c>
       <c r="H325" t="n">
         <v>2044</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H326" t="n">
         <v>10875</v>
@@ -9881,7 +9881,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H328" t="n">
         <v>9578</v>
@@ -9910,7 +9910,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H329" t="n">
         <v>4763</v>
@@ -9997,7 +9997,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.31260919570923</v>
+        <v>2.31260943412781</v>
       </c>
       <c r="H332" t="n">
         <v>4605</v>
@@ -10084,7 +10084,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G335" t="n">
-        <v>2.31260919570923</v>
+        <v>2.31260943412781</v>
       </c>
       <c r="H335" t="n">
         <v>4870</v>
@@ -10113,7 +10113,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.3080747127533</v>
+        <v>2.30807495117188</v>
       </c>
       <c r="H336" t="n">
         <v>989</v>
@@ -10403,7 +10403,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>2.31260919570923</v>
+        <v>2.31260943412781</v>
       </c>
       <c r="H346" t="n">
         <v>2050</v>
@@ -10461,7 +10461,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H348" t="n">
         <v>518</v>
@@ -10606,7 +10606,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>2.36248898506165</v>
+        <v>2.36248922348022</v>
       </c>
       <c r="H353" t="n">
         <v>4548</v>
@@ -10722,7 +10722,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.35795450210571</v>
+        <v>2.35795474052429</v>
       </c>
       <c r="H357" t="n">
         <v>1884</v>
@@ -10925,7 +10925,7 @@
         <v>2.75</v>
       </c>
       <c r="G364" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H364" t="n">
         <v>5478</v>
@@ -11215,7 +11215,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.3896963596344</v>
+        <v>2.38969612121582</v>
       </c>
       <c r="H374" t="n">
         <v>7617</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H376" t="n">
         <v>7974</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H379" t="n">
         <v>125340</v>
@@ -11389,7 +11389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H380" t="n">
         <v>15968</v>
@@ -11563,7 +11563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H386" t="n">
         <v>6461</v>
@@ -11592,7 +11592,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H387" t="n">
         <v>400</v>
@@ -11650,7 +11650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H389" t="n">
         <v>5695</v>
@@ -11679,7 +11679,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H390" t="n">
         <v>3704</v>
@@ -11737,7 +11737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H392" t="n">
         <v>8970</v>
@@ -11882,7 +11882,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H397" t="n">
         <v>6517</v>
@@ -11969,7 +11969,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840445518494</v>
+        <v>2.54840469360352</v>
       </c>
       <c r="H400" t="n">
         <v>6772</v>
@@ -11998,7 +11998,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840445518494</v>
+        <v>2.54840469360352</v>
       </c>
       <c r="H401" t="n">
         <v>25644</v>
@@ -12085,7 +12085,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095761299133</v>
       </c>
       <c r="H404" t="n">
         <v>20579</v>
@@ -12230,7 +12230,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095761299133</v>
       </c>
       <c r="H409" t="n">
         <v>3350</v>
@@ -12578,7 +12578,7 @@
         <v>2.75</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H421" t="n">
         <v>5517</v>
@@ -12607,7 +12607,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H422" t="n">
         <v>7693</v>
@@ -12723,7 +12723,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H426" t="n">
         <v>2034</v>
@@ -12752,7 +12752,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H427" t="n">
         <v>4867</v>
@@ -12868,7 +12868,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H431" t="n">
         <v>2176</v>
@@ -12897,7 +12897,7 @@
         <v>2.75</v>
       </c>
       <c r="G432" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H432" t="n">
         <v>6692</v>
@@ -13013,7 +13013,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>2.55747365951538</v>
+        <v>2.5574734210968</v>
       </c>
       <c r="H436" t="n">
         <v>4951</v>
@@ -13042,7 +13042,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H437" t="n">
         <v>4459</v>
@@ -13129,7 +13129,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H440" t="n">
         <v>1970</v>
@@ -13187,7 +13187,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.66630244255066</v>
+        <v>2.66630268096924</v>
       </c>
       <c r="H442" t="n">
         <v>3157</v>
@@ -13216,7 +13216,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H443" t="n">
         <v>905</v>
@@ -13245,7 +13245,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095761299133</v>
       </c>
       <c r="H444" t="n">
         <v>305</v>
@@ -13361,7 +13361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350957870483</v>
+        <v>2.69350934028625</v>
       </c>
       <c r="H448" t="n">
         <v>14662</v>
@@ -13390,7 +13390,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095761299133</v>
       </c>
       <c r="H449" t="n">
         <v>5650</v>
@@ -13448,7 +13448,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H451" t="n">
         <v>17368</v>
@@ -13506,7 +13506,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H453" t="n">
         <v>1381</v>
@@ -13622,7 +13622,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H457" t="n">
         <v>267</v>
@@ -38858,6 +38858,35 @@
         <v>1350</v>
       </c>
       <c r="I1327" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1328" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E1328" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="H1328" t="n">
+        <v>4910</v>
+      </c>
+      <c r="I1328" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161709785461</v>
+        <v>3.10161733627319</v>
       </c>
       <c r="H5" t="n">
         <v>23147</v>
@@ -543,7 +543,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.13335871696472</v>
+        <v>3.1333589553833</v>
       </c>
       <c r="H6" t="n">
         <v>30898</v>
@@ -630,7 +630,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5686731338501</v>
+        <v>3.56867361068726</v>
       </c>
       <c r="H9" t="n">
         <v>292968</v>
@@ -775,7 +775,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H14" t="n">
         <v>18667</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H16" t="n">
         <v>44813</v>
@@ -862,7 +862,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924377441406</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H17" t="n">
         <v>150547</v>
@@ -891,7 +891,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924377441406</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H18" t="n">
         <v>290894</v>
@@ -920,7 +920,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H19" t="n">
         <v>61034</v>
@@ -1036,7 +1036,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H23" t="n">
         <v>29141</v>
@@ -1123,7 +1123,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876317024231</v>
+        <v>3.90876293182373</v>
       </c>
       <c r="H26" t="n">
         <v>85789</v>
@@ -1152,7 +1152,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726197242737</v>
+        <v>3.77726149559021</v>
       </c>
       <c r="H27" t="n">
         <v>75595</v>
@@ -1181,7 +1181,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H28" t="n">
         <v>90036</v>
@@ -1210,7 +1210,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993438720703</v>
+        <v>3.79993462562561</v>
       </c>
       <c r="H29" t="n">
         <v>38465</v>
@@ -1239,7 +1239,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G30" t="n">
-        <v>3.68657112121582</v>
+        <v>3.6865713596344</v>
       </c>
       <c r="H30" t="n">
         <v>57117</v>
@@ -1268,7 +1268,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377801895142</v>
+        <v>3.71377825737</v>
       </c>
       <c r="H31" t="n">
         <v>31484</v>
@@ -1297,7 +1297,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H32" t="n">
         <v>14654</v>
@@ -1355,7 +1355,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H34" t="n">
         <v>5781</v>
@@ -1384,7 +1384,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>3.56413912773132</v>
+        <v>3.56413888931274</v>
       </c>
       <c r="H35" t="n">
         <v>54741</v>
@@ -1413,7 +1413,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>3.56413912773132</v>
+        <v>3.56413888931274</v>
       </c>
       <c r="H36" t="n">
         <v>13961</v>
@@ -1529,7 +1529,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633069992065</v>
+        <v>3.78633093833923</v>
       </c>
       <c r="H40" t="n">
         <v>4635</v>
@@ -1587,7 +1587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74552011489868</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H42" t="n">
         <v>23606</v>
@@ -1616,7 +1616,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.74552011489868</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H43" t="n">
         <v>10910</v>
@@ -1645,7 +1645,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H44" t="n">
         <v>34605</v>
@@ -1674,7 +1674,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H45" t="n">
         <v>2007</v>
@@ -1703,7 +1703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H46" t="n">
         <v>6914</v>
@@ -1761,7 +1761,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>3.68657112121582</v>
+        <v>3.6865713596344</v>
       </c>
       <c r="H48" t="n">
         <v>2180</v>
@@ -1877,7 +1877,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.74552011489868</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H52" t="n">
         <v>919</v>
@@ -1906,7 +1906,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.74552011489868</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H53" t="n">
         <v>5908</v>
@@ -1964,7 +1964,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G55" t="n">
-        <v>3.65482950210571</v>
+        <v>3.65482974052429</v>
       </c>
       <c r="H55" t="n">
         <v>11562</v>
@@ -1993,7 +1993,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G56" t="n">
-        <v>3.65482950210571</v>
+        <v>3.65482974052429</v>
       </c>
       <c r="H56" t="n">
         <v>8142</v>
@@ -2051,7 +2051,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H58" t="n">
         <v>4003</v>
@@ -2080,7 +2080,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H59" t="n">
         <v>6637</v>
@@ -2109,7 +2109,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936398506165</v>
+        <v>3.65936374664307</v>
       </c>
       <c r="H60" t="n">
         <v>5790</v>
@@ -2167,7 +2167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.70017457008362</v>
+        <v>3.70017504692078</v>
       </c>
       <c r="H62" t="n">
         <v>8191</v>
@@ -2196,7 +2196,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284746170044</v>
+        <v>3.72284770011902</v>
       </c>
       <c r="H63" t="n">
         <v>20100</v>
@@ -2225,7 +2225,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>3.69564032554626</v>
+        <v>3.69564008712769</v>
       </c>
       <c r="H64" t="n">
         <v>5559</v>
@@ -2399,7 +2399,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H70" t="n">
         <v>15982</v>
@@ -2457,7 +2457,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936398506165</v>
+        <v>3.65936374664307</v>
       </c>
       <c r="H72" t="n">
         <v>6928</v>
@@ -2515,7 +2515,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G74" t="n">
-        <v>3.63215708732605</v>
+        <v>3.63215684890747</v>
       </c>
       <c r="H74" t="n">
         <v>9636</v>
@@ -2602,7 +2602,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H77" t="n">
         <v>10457</v>
@@ -2631,7 +2631,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.70017457008362</v>
+        <v>3.70017504692078</v>
       </c>
       <c r="H78" t="n">
         <v>36913</v>
@@ -2660,7 +2660,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H79" t="n">
         <v>16654</v>
@@ -2718,7 +2718,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H81" t="n">
         <v>14163</v>
@@ -2776,7 +2776,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G83" t="n">
-        <v>3.54600071907043</v>
+        <v>3.54600095748901</v>
       </c>
       <c r="H83" t="n">
         <v>3337</v>
@@ -2805,7 +2805,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H84" t="n">
         <v>21297</v>
@@ -2863,7 +2863,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729238510132</v>
+        <v>3.38729214668274</v>
       </c>
       <c r="H86" t="n">
         <v>4796</v>
@@ -2892,7 +2892,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.45984506607056</v>
+        <v>3.45984482765198</v>
       </c>
       <c r="H87" t="n">
         <v>56731</v>
@@ -2921,7 +2921,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47798299789429</v>
+        <v>3.47798275947571</v>
       </c>
       <c r="H88" t="n">
         <v>5844</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.44624137878418</v>
+        <v>3.44624090194702</v>
       </c>
       <c r="H89" t="n">
         <v>5063</v>
@@ -3008,7 +3008,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.47798299789429</v>
+        <v>3.47798275947571</v>
       </c>
       <c r="H91" t="n">
         <v>7413</v>
@@ -3037,7 +3037,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47344851493835</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H92" t="n">
         <v>2793</v>
@@ -3066,7 +3066,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.48251724243164</v>
+        <v>3.48251748085022</v>
       </c>
       <c r="H93" t="n">
         <v>7085</v>
@@ -3095,7 +3095,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H94" t="n">
         <v>14502</v>
@@ -3153,7 +3153,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>3.3238091468811</v>
+        <v>3.32380890846252</v>
       </c>
       <c r="H96" t="n">
         <v>1326</v>
@@ -3182,7 +3182,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531034469604</v>
+        <v>3.45531010627747</v>
       </c>
       <c r="H97" t="n">
         <v>13724</v>
@@ -3211,7 +3211,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891379356384</v>
+        <v>3.46891403198242</v>
       </c>
       <c r="H98" t="n">
         <v>2853</v>
@@ -3240,7 +3240,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>3.42356872558594</v>
+        <v>3.42356896400452</v>
       </c>
       <c r="H99" t="n">
         <v>4056</v>
@@ -3269,7 +3269,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>3.41449975967407</v>
+        <v>3.41449999809265</v>
       </c>
       <c r="H100" t="n">
         <v>2072</v>
@@ -3298,7 +3298,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996527671814</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H101" t="n">
         <v>3157</v>
@@ -3327,7 +3327,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996527671814</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H102" t="n">
         <v>340</v>
@@ -3356,7 +3356,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008524894714</v>
+        <v>3.36008501052856</v>
       </c>
       <c r="H103" t="n">
         <v>13842</v>
@@ -3472,7 +3472,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48251724243164</v>
+        <v>3.48251748085022</v>
       </c>
       <c r="H107" t="n">
         <v>5104</v>
@@ -3530,7 +3530,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>3.41449975967407</v>
+        <v>3.41449999809265</v>
       </c>
       <c r="H109" t="n">
         <v>6279</v>
@@ -3559,7 +3559,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H110" t="n">
         <v>33451</v>
@@ -3588,7 +3588,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H111" t="n">
         <v>13196</v>
@@ -3617,7 +3617,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.4961211681366</v>
+        <v>3.49612092971802</v>
       </c>
       <c r="H112" t="n">
         <v>28788</v>
@@ -3646,7 +3646,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077610015869</v>
+        <v>3.45077586174011</v>
       </c>
       <c r="H113" t="n">
         <v>3151</v>
@@ -3675,7 +3675,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>3.55960440635681</v>
+        <v>3.55960464477539</v>
       </c>
       <c r="H114" t="n">
         <v>4027</v>
@@ -3704,7 +3704,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H115" t="n">
         <v>8785</v>
@@ -3733,7 +3733,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H116" t="n">
         <v>1006</v>
@@ -3762,7 +3762,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G117" t="n">
-        <v>3.60041546821594</v>
+        <v>3.60041522979736</v>
       </c>
       <c r="H117" t="n">
         <v>3317</v>
@@ -3791,7 +3791,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H118" t="n">
         <v>29715</v>
@@ -3820,7 +3820,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H119" t="n">
         <v>35244</v>
@@ -3878,7 +3878,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.4961211681366</v>
+        <v>3.49612092971802</v>
       </c>
       <c r="H121" t="n">
         <v>6937</v>
@@ -3936,7 +3936,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287787437439</v>
+        <v>3.33287811279297</v>
       </c>
       <c r="H123" t="n">
         <v>13328</v>
@@ -3965,7 +3965,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>3.26485991477966</v>
+        <v>3.26486015319824</v>
       </c>
       <c r="H124" t="n">
         <v>17450</v>
@@ -3994,7 +3994,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32834339141846</v>
+        <v>3.32834362983704</v>
       </c>
       <c r="H125" t="n">
         <v>9558</v>
@@ -4052,7 +4052,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H127" t="n">
         <v>3094</v>
@@ -4139,7 +4139,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H130" t="n">
         <v>2361</v>
@@ -4168,7 +4168,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G131" t="n">
-        <v>3.27392935752869</v>
+        <v>3.27392911911011</v>
       </c>
       <c r="H131" t="n">
         <v>8662</v>
@@ -4197,7 +4197,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>3.26485991477966</v>
+        <v>3.26486015319824</v>
       </c>
       <c r="H132" t="n">
         <v>3010</v>
@@ -4226,7 +4226,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404956817627</v>
+        <v>3.22404932975769</v>
       </c>
       <c r="H133" t="n">
         <v>4602</v>
@@ -4255,7 +4255,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951460838318</v>
+        <v>3.21951484680176</v>
       </c>
       <c r="H134" t="n">
         <v>60461</v>
@@ -4284,7 +4284,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30113649368286</v>
+        <v>3.30113625526428</v>
       </c>
       <c r="H135" t="n">
         <v>17559</v>
@@ -4313,7 +4313,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>3.31927466392517</v>
+        <v>3.31927442550659</v>
       </c>
       <c r="H136" t="n">
         <v>21037</v>
@@ -4371,7 +4371,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020569801331</v>
+        <v>3.31020522117615</v>
       </c>
       <c r="H138" t="n">
         <v>2087</v>
@@ -4429,7 +4429,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H140" t="n">
         <v>17360</v>
@@ -4487,7 +4487,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.47344851493835</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H142" t="n">
         <v>1980</v>
@@ -4545,7 +4545,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>3.30113649368286</v>
+        <v>3.30113625526428</v>
       </c>
       <c r="H144" t="n">
         <v>9061</v>
@@ -4574,7 +4574,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G145" t="n">
-        <v>3.31927466392517</v>
+        <v>3.31927442550659</v>
       </c>
       <c r="H145" t="n">
         <v>2079</v>
@@ -4632,7 +4632,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G147" t="n">
-        <v>3.2285840511322</v>
+        <v>3.22858381271362</v>
       </c>
       <c r="H147" t="n">
         <v>5516</v>
@@ -4690,7 +4690,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.14696264266968</v>
+        <v>3.1469624042511</v>
       </c>
       <c r="H149" t="n">
         <v>11513</v>
@@ -4748,7 +4748,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510057449341</v>
+        <v>3.16510033607483</v>
       </c>
       <c r="H151" t="n">
         <v>218</v>
@@ -4777,7 +4777,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.97465014457703</v>
+        <v>2.97465038299561</v>
       </c>
       <c r="H152" t="n">
         <v>14806</v>
@@ -4806,7 +4806,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G153" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H153" t="n">
         <v>14357</v>
@@ -4835,7 +4835,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570115089417</v>
+        <v>2.91570138931274</v>
       </c>
       <c r="H154" t="n">
         <v>1770</v>
@@ -4864,7 +4864,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H155" t="n">
         <v>5951</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H156" t="n">
         <v>10379</v>
@@ -4922,7 +4922,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756345748901</v>
+        <v>2.89756321907043</v>
       </c>
       <c r="H157" t="n">
         <v>4634</v>
@@ -4951,7 +4951,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.96104669570923</v>
+        <v>2.96104693412781</v>
       </c>
       <c r="H158" t="n">
         <v>1286</v>
@@ -5038,7 +5038,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278855323792</v>
+        <v>2.99278831481934</v>
       </c>
       <c r="H161" t="n">
         <v>12598</v>
@@ -5154,7 +5154,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G165" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H165" t="n">
         <v>3774</v>
@@ -5241,7 +5241,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>3.21044588088989</v>
+        <v>3.21044564247131</v>
       </c>
       <c r="H168" t="n">
         <v>11151</v>
@@ -5270,7 +5270,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.37368869781494</v>
+        <v>3.37368893623352</v>
       </c>
       <c r="H169" t="n">
         <v>87762</v>
@@ -5328,7 +5328,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615134239197</v>
+        <v>3.10615181922913</v>
       </c>
       <c r="H171" t="n">
         <v>59616</v>
@@ -5357,7 +5357,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>3.11522054672241</v>
+        <v>3.11522078514099</v>
       </c>
       <c r="H172" t="n">
         <v>8398</v>
@@ -5386,7 +5386,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G173" t="n">
-        <v>3.1605658531189</v>
+        <v>3.16056561470032</v>
       </c>
       <c r="H173" t="n">
         <v>546</v>
@@ -5444,7 +5444,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H175" t="n">
         <v>7513</v>
@@ -5531,7 +5531,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.02453017234802</v>
+        <v>3.02452993392944</v>
       </c>
       <c r="H178" t="n">
         <v>1198</v>
@@ -5618,7 +5618,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>2.97465014457703</v>
+        <v>2.97465038299561</v>
       </c>
       <c r="H181" t="n">
         <v>3283</v>
@@ -5647,7 +5647,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G182" t="n">
-        <v>2.97918486595154</v>
+        <v>2.97918510437012</v>
       </c>
       <c r="H182" t="n">
         <v>7488</v>
@@ -5676,7 +5676,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>3.0381338596344</v>
+        <v>3.03813362121582</v>
       </c>
       <c r="H183" t="n">
         <v>788</v>
@@ -5734,7 +5734,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.0381338596344</v>
+        <v>3.03813362121582</v>
       </c>
       <c r="H185" t="n">
         <v>3316</v>
@@ -5763,7 +5763,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H186" t="n">
         <v>3889</v>
@@ -5821,7 +5821,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G188" t="n">
-        <v>3.0381338596344</v>
+        <v>3.03813362121582</v>
       </c>
       <c r="H188" t="n">
         <v>26816</v>
@@ -5850,7 +5850,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G189" t="n">
-        <v>2.99732303619385</v>
+        <v>2.99732327461243</v>
       </c>
       <c r="H189" t="n">
         <v>14092</v>
@@ -5937,7 +5937,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627155303955</v>
+        <v>3.05627179145813</v>
       </c>
       <c r="H192" t="n">
         <v>9528</v>
@@ -5966,7 +5966,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>3.0381338596344</v>
+        <v>3.03813362121582</v>
       </c>
       <c r="H193" t="n">
         <v>2404</v>
@@ -5995,7 +5995,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.06534099578857</v>
+        <v>3.06534123420715</v>
       </c>
       <c r="H194" t="n">
         <v>924</v>
@@ -6053,7 +6053,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744348526001</v>
+        <v>2.94744324684143</v>
       </c>
       <c r="H196" t="n">
         <v>9781</v>
@@ -6111,7 +6111,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H198" t="n">
         <v>8621</v>
@@ -6140,7 +6140,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H199" t="n">
         <v>6598</v>
@@ -6169,7 +6169,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489080429077</v>
+        <v>2.87489056587219</v>
       </c>
       <c r="H200" t="n">
         <v>7430</v>
@@ -6227,7 +6227,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.0381338596344</v>
+        <v>3.03813362121582</v>
       </c>
       <c r="H202" t="n">
         <v>6893</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744348526001</v>
+        <v>2.94744324684143</v>
       </c>
       <c r="H204" t="n">
         <v>41187</v>
@@ -6314,7 +6314,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011590003967</v>
+        <v>2.97011613845825</v>
       </c>
       <c r="H205" t="n">
         <v>4097</v>
@@ -6372,7 +6372,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G207" t="n">
-        <v>2.92477059364319</v>
+        <v>2.92477035522461</v>
       </c>
       <c r="H207" t="n">
         <v>1550</v>
@@ -6459,7 +6459,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951460838318</v>
+        <v>3.21951484680176</v>
       </c>
       <c r="H210" t="n">
         <v>21001</v>
@@ -6488,7 +6488,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H211" t="n">
         <v>53801</v>
@@ -6546,7 +6546,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765277862549</v>
+        <v>3.23765301704407</v>
       </c>
       <c r="H213" t="n">
         <v>4683</v>
@@ -6575,7 +6575,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753256797791</v>
+        <v>3.28753304481506</v>
       </c>
       <c r="H214" t="n">
         <v>1310</v>
@@ -6662,7 +6662,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>3.11522054672241</v>
+        <v>3.11522078514099</v>
       </c>
       <c r="H217" t="n">
         <v>1846</v>
@@ -6691,7 +6691,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.1605658531189</v>
+        <v>3.16056561470032</v>
       </c>
       <c r="H218" t="n">
         <v>4799</v>
@@ -6778,7 +6778,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.92930507659912</v>
+        <v>2.9293053150177</v>
       </c>
       <c r="H221" t="n">
         <v>10002</v>
@@ -6836,7 +6836,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.97918486595154</v>
+        <v>2.97918510437012</v>
       </c>
       <c r="H223" t="n">
         <v>3005</v>
@@ -6865,7 +6865,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035584449768</v>
+        <v>2.87035608291626</v>
       </c>
       <c r="H224" t="n">
         <v>4992</v>
@@ -6894,7 +6894,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570115089417</v>
+        <v>2.91570138931274</v>
       </c>
       <c r="H225" t="n">
         <v>3170</v>
@@ -6952,7 +6952,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.86128735542297</v>
+        <v>2.86128711700439</v>
       </c>
       <c r="H227" t="n">
         <v>62</v>
@@ -6981,7 +6981,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H228" t="n">
         <v>593</v>
@@ -7010,7 +7010,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489080429077</v>
+        <v>2.87489056587219</v>
       </c>
       <c r="H229" t="n">
         <v>389</v>
@@ -7039,7 +7039,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954525947571</v>
+        <v>2.82954549789429</v>
       </c>
       <c r="H230" t="n">
         <v>4733</v>
@@ -7213,7 +7213,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H236" t="n">
         <v>11979</v>
@@ -7271,7 +7271,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H238" t="n">
         <v>16491</v>
@@ -7416,7 +7416,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>2.77513122558594</v>
+        <v>2.77513098716736</v>
       </c>
       <c r="H243" t="n">
         <v>3305</v>
@@ -7445,7 +7445,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H244" t="n">
         <v>4956</v>
@@ -7590,7 +7590,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.83407998085022</v>
+        <v>2.8340802192688</v>
       </c>
       <c r="H249" t="n">
         <v>625</v>
@@ -7764,7 +7764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H255" t="n">
         <v>18878</v>
@@ -7822,7 +7822,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350934028625</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H257" t="n">
         <v>8062</v>
@@ -7851,7 +7851,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071695327759</v>
+        <v>2.72071647644043</v>
       </c>
       <c r="H258" t="n">
         <v>1704</v>
@@ -7880,7 +7880,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.69804406166077</v>
+        <v>2.69804430007935</v>
       </c>
       <c r="H259" t="n">
         <v>16864</v>
@@ -7967,7 +7967,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H262" t="n">
         <v>5847</v>
@@ -8054,7 +8054,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456082344055</v>
+        <v>2.63456058502197</v>
       </c>
       <c r="H265" t="n">
         <v>9259</v>
@@ -8112,7 +8112,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.6753716468811</v>
+        <v>2.67537140846252</v>
       </c>
       <c r="H267" t="n">
         <v>735</v>
@@ -8170,7 +8170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H269" t="n">
         <v>1163</v>
@@ -8228,7 +8228,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G271" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H271" t="n">
         <v>23246</v>
@@ -8286,7 +8286,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.59828472137451</v>
+        <v>2.59828448295593</v>
       </c>
       <c r="H273" t="n">
         <v>1912</v>
@@ -8315,7 +8315,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H274" t="n">
         <v>1083</v>
@@ -8373,7 +8373,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H276" t="n">
         <v>8540</v>
@@ -8402,7 +8402,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945593833923</v>
+        <v>2.48945546150208</v>
       </c>
       <c r="H277" t="n">
         <v>995</v>
@@ -8431,7 +8431,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>2.45317959785461</v>
+        <v>2.45317935943604</v>
       </c>
       <c r="H278" t="n">
         <v>2892</v>
@@ -8489,7 +8489,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062715530396</v>
+        <v>2.38062739372253</v>
       </c>
       <c r="H280" t="n">
         <v>7350</v>
@@ -8518,7 +8518,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.35342001914978</v>
+        <v>2.3534197807312</v>
       </c>
       <c r="H281" t="n">
         <v>44116</v>
@@ -8605,7 +8605,7 @@
         <v>2.5</v>
       </c>
       <c r="G284" t="n">
-        <v>2.26726412773132</v>
+        <v>2.26726388931274</v>
       </c>
       <c r="H284" t="n">
         <v>15525</v>
@@ -8634,7 +8634,7 @@
         <v>2.5</v>
       </c>
       <c r="G285" t="n">
-        <v>2.26726412773132</v>
+        <v>2.26726388931274</v>
       </c>
       <c r="H285" t="n">
         <v>8032</v>
@@ -8750,7 +8750,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.23098754882812</v>
+        <v>2.2309877872467</v>
       </c>
       <c r="H289" t="n">
         <v>9243</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750431060791</v>
+        <v>2.16750454902649</v>
       </c>
       <c r="H290" t="n">
         <v>7059</v>
@@ -8837,7 +8837,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.1357626914978</v>
+        <v>2.13576245307922</v>
       </c>
       <c r="H292" t="n">
         <v>9540</v>
@@ -8866,7 +8866,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.33074712753296</v>
+        <v>2.33074736595154</v>
       </c>
       <c r="H293" t="n">
         <v>4108</v>
@@ -8895,7 +8895,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>2.34435081481934</v>
+        <v>2.34435105323792</v>
       </c>
       <c r="H294" t="n">
         <v>591</v>
@@ -8924,7 +8924,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.22645306587219</v>
+        <v>2.22645330429077</v>
       </c>
       <c r="H295" t="n">
         <v>7856</v>
@@ -8953,7 +8953,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G296" t="n">
-        <v>2.14029693603516</v>
+        <v>2.14029717445374</v>
       </c>
       <c r="H296" t="n">
         <v>8430</v>
@@ -9011,7 +9011,7 @@
         <v>2.5</v>
       </c>
       <c r="G298" t="n">
-        <v>2.26726412773132</v>
+        <v>2.26726388931274</v>
       </c>
       <c r="H298" t="n">
         <v>4970</v>
@@ -9040,7 +9040,7 @@
         <v>2.5</v>
       </c>
       <c r="G299" t="n">
-        <v>2.26726412773132</v>
+        <v>2.26726388931274</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>2.5</v>
       </c>
       <c r="G300" t="n">
-        <v>2.26726412773132</v>
+        <v>2.26726388931274</v>
       </c>
       <c r="H300" t="n">
         <v>6868</v>
@@ -9098,7 +9098,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33074712753296</v>
+        <v>2.33074736595154</v>
       </c>
       <c r="H301" t="n">
         <v>9820</v>
@@ -9127,7 +9127,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>2.35795474052429</v>
+        <v>2.35795450210571</v>
       </c>
       <c r="H302" t="n">
         <v>5211</v>
@@ -9156,7 +9156,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H303" t="n">
         <v>8916</v>
@@ -9301,7 +9301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H308" t="n">
         <v>371</v>
@@ -9504,7 +9504,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H315" t="n">
         <v>2887</v>
@@ -9591,7 +9591,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H318" t="n">
         <v>3432</v>
@@ -9620,7 +9620,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G319" t="n">
-        <v>2.5574734210968</v>
+        <v>2.55747365951538</v>
       </c>
       <c r="H319" t="n">
         <v>2553</v>
@@ -9736,7 +9736,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G323" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H323" t="n">
         <v>923</v>
@@ -9765,7 +9765,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H324" t="n">
         <v>500</v>
@@ -9794,7 +9794,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.39876556396484</v>
+        <v>2.39876532554626</v>
       </c>
       <c r="H325" t="n">
         <v>2044</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H326" t="n">
         <v>10875</v>
@@ -9881,7 +9881,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H328" t="n">
         <v>9578</v>
@@ -9910,7 +9910,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H329" t="n">
         <v>4763</v>
@@ -9939,7 +9939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.367023229599</v>
+        <v>2.36702346801758</v>
       </c>
       <c r="H330" t="n">
         <v>7415</v>
@@ -9968,7 +9968,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.35342001914978</v>
+        <v>2.3534197807312</v>
       </c>
       <c r="H331" t="n">
         <v>12852</v>
@@ -9997,7 +9997,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.31260943412781</v>
+        <v>2.31260919570923</v>
       </c>
       <c r="H332" t="n">
         <v>4605</v>
@@ -10055,7 +10055,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.29447102546692</v>
+        <v>2.2944712638855</v>
       </c>
       <c r="H334" t="n">
         <v>2916</v>
@@ -10084,7 +10084,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G335" t="n">
-        <v>2.31260943412781</v>
+        <v>2.31260919570923</v>
       </c>
       <c r="H335" t="n">
         <v>4870</v>
@@ -10113,7 +10113,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.30807495117188</v>
+        <v>2.3080747127533</v>
       </c>
       <c r="H336" t="n">
         <v>989</v>
@@ -10200,7 +10200,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528208732605</v>
+        <v>2.33528184890747</v>
       </c>
       <c r="H339" t="n">
         <v>4539</v>
@@ -10229,7 +10229,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993678092957</v>
+        <v>2.28993654251099</v>
       </c>
       <c r="H340" t="n">
         <v>31736</v>
@@ -10258,7 +10258,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005699157715</v>
       </c>
       <c r="H341" t="n">
         <v>4266</v>
@@ -10345,7 +10345,7 @@
         <v>2.5</v>
       </c>
       <c r="G344" t="n">
-        <v>2.26726412773132</v>
+        <v>2.26726388931274</v>
       </c>
       <c r="H344" t="n">
         <v>4053</v>
@@ -10403,7 +10403,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>2.31260943412781</v>
+        <v>2.31260919570923</v>
       </c>
       <c r="H346" t="n">
         <v>2050</v>
@@ -10461,7 +10461,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H348" t="n">
         <v>518</v>
@@ -10577,7 +10577,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G352" t="n">
-        <v>2.45317959785461</v>
+        <v>2.45317935943604</v>
       </c>
       <c r="H352" t="n">
         <v>4007</v>
@@ -10635,7 +10635,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G354" t="n">
-        <v>2.41236877441406</v>
+        <v>2.41236901283264</v>
       </c>
       <c r="H354" t="n">
         <v>2737</v>
@@ -10693,7 +10693,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G356" t="n">
-        <v>2.367023229599</v>
+        <v>2.36702346801758</v>
       </c>
       <c r="H356" t="n">
         <v>153</v>
@@ -10722,7 +10722,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.35795474052429</v>
+        <v>2.35795450210571</v>
       </c>
       <c r="H357" t="n">
         <v>1884</v>
@@ -10780,7 +10780,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G359" t="n">
-        <v>2.19017672538757</v>
+        <v>2.19017696380615</v>
       </c>
       <c r="H359" t="n">
         <v>9087</v>
@@ -10809,7 +10809,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>2.2445912361145</v>
+        <v>2.24459147453308</v>
       </c>
       <c r="H360" t="n">
         <v>1525</v>
@@ -10838,7 +10838,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>2.2445912361145</v>
+        <v>2.24459147453308</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005699157715</v>
       </c>
       <c r="H362" t="n">
         <v>1115</v>
@@ -10896,7 +10896,7 @@
         <v>2.5</v>
       </c>
       <c r="G363" t="n">
-        <v>2.26726412773132</v>
+        <v>2.26726388931274</v>
       </c>
       <c r="H363" t="n">
         <v>2366</v>
@@ -10925,7 +10925,7 @@
         <v>2.75</v>
       </c>
       <c r="G364" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H364" t="n">
         <v>5478</v>
@@ -11041,7 +11041,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G368" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H368" t="n">
         <v>2162</v>
@@ -11070,7 +11070,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H369" t="n">
         <v>1383</v>
@@ -11186,7 +11186,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.40330004692078</v>
+        <v>2.4032998085022</v>
       </c>
       <c r="H373" t="n">
         <v>26801</v>
@@ -11215,7 +11215,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.38969612121582</v>
+        <v>2.3896963596344</v>
       </c>
       <c r="H374" t="n">
         <v>7617</v>
@@ -11244,7 +11244,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.40330004692078</v>
+        <v>2.4032998085022</v>
       </c>
       <c r="H375" t="n">
         <v>8213</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H379" t="n">
         <v>125340</v>
@@ -11389,7 +11389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H380" t="n">
         <v>15968</v>
@@ -11418,7 +11418,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.49852514266968</v>
+        <v>2.4985249042511</v>
       </c>
       <c r="H381" t="n">
         <v>3626</v>
@@ -11447,7 +11447,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H382" t="n">
         <v>4545</v>
@@ -11505,7 +11505,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H384" t="n">
         <v>7902</v>
@@ -11592,7 +11592,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H387" t="n">
         <v>400</v>
@@ -11621,7 +11621,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H388" t="n">
         <v>9739</v>
@@ -11650,7 +11650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H389" t="n">
         <v>5695</v>
@@ -11679,7 +11679,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H390" t="n">
         <v>3704</v>
@@ -11737,7 +11737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H392" t="n">
         <v>8970</v>
@@ -11824,7 +11824,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>2.57107758522034</v>
+        <v>2.57107734680176</v>
       </c>
       <c r="H395" t="n">
         <v>11919</v>
@@ -11853,7 +11853,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666307449341</v>
+        <v>2.51666331291199</v>
       </c>
       <c r="H396" t="n">
         <v>67390</v>
@@ -11882,7 +11882,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H397" t="n">
         <v>6517</v>
@@ -12027,7 +12027,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H402" t="n">
         <v>27847</v>
@@ -12085,7 +12085,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095761299133</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H404" t="n">
         <v>20579</v>
@@ -12230,7 +12230,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095761299133</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H409" t="n">
         <v>3350</v>
@@ -12259,7 +12259,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H410" t="n">
         <v>4500</v>
@@ -12288,7 +12288,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H411" t="n">
         <v>2860</v>
@@ -12404,7 +12404,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573227882385</v>
+        <v>2.52573251724243</v>
       </c>
       <c r="H415" t="n">
         <v>8421</v>
@@ -12520,7 +12520,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G419" t="n">
-        <v>2.367023229599</v>
+        <v>2.36702346801758</v>
       </c>
       <c r="H419" t="n">
         <v>3581</v>
@@ -12578,7 +12578,7 @@
         <v>2.75</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H421" t="n">
         <v>5517</v>
@@ -12607,7 +12607,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H422" t="n">
         <v>7693</v>
@@ -12636,7 +12636,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G423" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H423" t="n">
         <v>7526</v>
@@ -12723,7 +12723,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H426" t="n">
         <v>2034</v>
@@ -12897,7 +12897,7 @@
         <v>2.75</v>
       </c>
       <c r="G432" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H432" t="n">
         <v>6692</v>
@@ -12984,7 +12984,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G435" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H435" t="n">
         <v>2214</v>
@@ -13013,7 +13013,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>2.5574734210968</v>
+        <v>2.55747365951538</v>
       </c>
       <c r="H436" t="n">
         <v>4951</v>
@@ -13129,7 +13129,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H440" t="n">
         <v>1970</v>
@@ -13158,7 +13158,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G441" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H441" t="n">
         <v>16239</v>
@@ -13187,7 +13187,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.66630268096924</v>
+        <v>2.66630244255066</v>
       </c>
       <c r="H442" t="n">
         <v>3157</v>
@@ -13216,7 +13216,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H443" t="n">
         <v>905</v>
@@ -13245,7 +13245,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095761299133</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H444" t="n">
         <v>305</v>
@@ -13274,7 +13274,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188817024231</v>
+        <v>2.61188840866089</v>
       </c>
       <c r="H445" t="n">
         <v>5437</v>
@@ -13303,7 +13303,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G446" t="n">
-        <v>2.59374976158142</v>
+        <v>2.59375</v>
       </c>
       <c r="H446" t="n">
         <v>2456</v>
@@ -13332,7 +13332,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G447" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H447" t="n">
         <v>1026</v>
@@ -13361,7 +13361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350934028625</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H448" t="n">
         <v>14662</v>
@@ -13390,7 +13390,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095761299133</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H449" t="n">
         <v>5650</v>
@@ -13448,7 +13448,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H451" t="n">
         <v>17368</v>
@@ -13506,7 +13506,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H453" t="n">
         <v>1381</v>
@@ -13564,7 +13564,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G455" t="n">
-        <v>2.82047653198242</v>
+        <v>2.82047629356384</v>
       </c>
       <c r="H455" t="n">
         <v>22810</v>
@@ -13622,7 +13622,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H457" t="n">
         <v>267</v>
@@ -13709,7 +13709,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H460" t="n">
         <v>4577</v>
@@ -13738,7 +13738,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G461" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H461" t="n">
         <v>1854</v>
@@ -13883,7 +13883,7 @@
         <v>3</v>
       </c>
       <c r="G466" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H466" t="n">
         <v>2400</v>
@@ -13912,7 +13912,7 @@
         <v>3</v>
       </c>
       <c r="G467" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H467" t="n">
         <v>897</v>
@@ -13970,7 +13970,7 @@
         <v>3</v>
       </c>
       <c r="G469" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H469" t="n">
         <v>598</v>
@@ -13999,7 +13999,7 @@
         <v>3</v>
       </c>
       <c r="G470" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G473" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H473" t="n">
         <v>7200</v>
@@ -14115,7 +14115,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G474" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H474" t="n">
         <v>468</v>
@@ -14144,7 +14144,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G475" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H475" t="n">
         <v>7912</v>
@@ -14202,7 +14202,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G477" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H477" t="n">
         <v>29506</v>
@@ -14231,7 +14231,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G478" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H478" t="n">
         <v>21409</v>
@@ -14260,7 +14260,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G479" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H479" t="n">
         <v>58941</v>
@@ -14289,7 +14289,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G480" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H480" t="n">
         <v>6941</v>
@@ -14318,7 +14318,7 @@
         <v>2.75</v>
       </c>
       <c r="G481" t="n">
-        <v>2.53743958473206</v>
+        <v>2.53743982315063</v>
       </c>
       <c r="H481" t="n">
         <v>5639</v>
@@ -14347,7 +14347,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G482" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H482" t="n">
         <v>7670</v>
@@ -14376,7 +14376,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G483" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H483" t="n">
         <v>869</v>
@@ -14405,7 +14405,7 @@
         <v>2.75</v>
       </c>
       <c r="G484" t="n">
-        <v>2.53743958473206</v>
+        <v>2.53743982315063</v>
       </c>
       <c r="H484" t="n">
         <v>1915</v>
@@ -14463,7 +14463,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G486" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H486" t="n">
         <v>1200</v>
@@ -14550,7 +14550,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G489" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H489" t="n">
         <v>1637</v>
@@ -14579,7 +14579,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G490" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H490" t="n">
         <v>62146</v>
@@ -14637,7 +14637,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H492" t="n">
         <v>9831</v>
@@ -14666,7 +14666,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H495" t="n">
         <v>367</v>
@@ -14782,7 +14782,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G497" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H497" t="n">
         <v>1143</v>
@@ -14869,7 +14869,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H500" t="n">
         <v>5010</v>
@@ -15014,7 +15014,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H505" t="n">
         <v>2168</v>
@@ -15043,7 +15043,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G506" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H506" t="n">
         <v>516</v>
@@ -15072,7 +15072,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H507" t="n">
         <v>4213</v>
@@ -15101,7 +15101,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H508" t="n">
         <v>1909</v>
@@ -15130,7 +15130,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H509" t="n">
         <v>2208</v>
@@ -15159,7 +15159,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H510" t="n">
         <v>2337</v>
@@ -15188,7 +15188,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G511" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H511" t="n">
         <v>123</v>
@@ -15246,7 +15246,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G513" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H513" t="n">
         <v>2999</v>
@@ -15333,7 +15333,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H516" t="n">
         <v>9199</v>
@@ -15362,7 +15362,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H517" t="n">
         <v>1132</v>
@@ -15391,7 +15391,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H518" t="n">
         <v>1263</v>
@@ -15420,7 +15420,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H519" t="n">
         <v>107</v>
@@ -15449,7 +15449,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G520" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H520" t="n">
         <v>236</v>
@@ -15478,7 +15478,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H521" t="n">
         <v>2000</v>
@@ -15536,7 +15536,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H523" t="n">
         <v>3940</v>
@@ -15565,7 +15565,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H524" t="n">
         <v>5586</v>
@@ -15797,7 +15797,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H532" t="n">
         <v>420</v>
@@ -15826,7 +15826,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H533" t="n">
         <v>8008</v>
@@ -15855,7 +15855,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H534" t="n">
         <v>1274</v>
@@ -15884,7 +15884,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G538" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H538" t="n">
         <v>908</v>
@@ -16029,7 +16029,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H540" t="n">
         <v>14503</v>
@@ -16058,7 +16058,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G541" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H541" t="n">
         <v>300</v>
@@ -16145,7 +16145,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H544" t="n">
         <v>5816</v>
@@ -16290,7 +16290,7 @@
         <v>3</v>
       </c>
       <c r="G549" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H549" t="n">
         <v>2815</v>
@@ -16551,7 +16551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H558" t="n">
         <v>8956</v>
@@ -16609,7 +16609,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734303474426</v>
+        <v>2.77734327316284</v>
       </c>
       <c r="H560" t="n">
         <v>6973</v>
@@ -16638,7 +16638,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79579710960388</v>
+        <v>2.79579734802246</v>
       </c>
       <c r="H561" t="n">
         <v>2786</v>
@@ -16667,7 +16667,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H562" t="n">
         <v>6763</v>
@@ -16754,7 +16754,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H565" t="n">
         <v>27</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H568" t="n">
         <v>4278</v>
@@ -16870,7 +16870,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.55589389801025</v>
+        <v>2.55589365959167</v>
       </c>
       <c r="H569" t="n">
         <v>3153</v>
@@ -16928,7 +16928,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H571" t="n">
         <v>13431</v>
@@ -16957,7 +16957,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41748809814453</v>
+        <v>2.41748785972595</v>
       </c>
       <c r="H572" t="n">
         <v>1200</v>
@@ -17044,7 +17044,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H575" t="n">
         <v>838</v>
@@ -17073,7 +17073,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H576" t="n">
         <v>24569</v>
@@ -17131,7 +17131,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H578" t="n">
         <v>8794</v>
@@ -17160,7 +17160,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G579" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H579" t="n">
         <v>17262</v>
@@ -17189,7 +17189,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G580" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H580" t="n">
         <v>596</v>
@@ -17218,7 +17218,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G581" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H581" t="n">
         <v>3015</v>
@@ -17247,7 +17247,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G582" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17276,7 +17276,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G583" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H583" t="n">
         <v>2004</v>
@@ -17334,7 +17334,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H585" t="n">
         <v>1960</v>
@@ -17363,7 +17363,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H586" t="n">
         <v>2846</v>
@@ -17421,7 +17421,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H588" t="n">
         <v>3050</v>
@@ -17450,7 +17450,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G589" t="n">
-        <v>2.50975847244263</v>
+        <v>2.50975871086121</v>
       </c>
       <c r="H589" t="n">
         <v>6124</v>
@@ -17508,7 +17508,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H591" t="n">
         <v>2840</v>
@@ -17537,7 +17537,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G592" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H592" t="n">
         <v>2322</v>
@@ -17566,7 +17566,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H593" t="n">
         <v>12355</v>
@@ -17595,7 +17595,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G594" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H594" t="n">
         <v>4823</v>
@@ -17624,7 +17624,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H595" t="n">
         <v>7592</v>
@@ -17653,7 +17653,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>2.41748809814453</v>
+        <v>2.41748785972595</v>
       </c>
       <c r="H596" t="n">
         <v>13053</v>
@@ -17682,7 +17682,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G597" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H597" t="n">
         <v>20130</v>
@@ -17769,7 +17769,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H600" t="n">
         <v>1222</v>
@@ -17798,7 +17798,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H601" t="n">
         <v>1618</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H603" t="n">
         <v>2226</v>
@@ -17885,7 +17885,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H604" t="n">
         <v>50</v>
@@ -17914,7 +17914,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G605" t="n">
-        <v>2.5835747718811</v>
+        <v>2.58357501029968</v>
       </c>
       <c r="H605" t="n">
         <v>985</v>
@@ -17943,7 +17943,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>2.50975847244263</v>
+        <v>2.50975871086121</v>
       </c>
       <c r="H606" t="n">
         <v>5678</v>
@@ -18030,7 +18030,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H609" t="n">
         <v>7373</v>
@@ -18059,7 +18059,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H610" t="n">
         <v>1755</v>
@@ -18088,7 +18088,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G611" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H611" t="n">
         <v>3646</v>
@@ -18117,7 +18117,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H612" t="n">
         <v>1353</v>
@@ -18146,7 +18146,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H613" t="n">
         <v>3521</v>
@@ -18175,7 +18175,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H614" t="n">
         <v>1453</v>
@@ -18233,7 +18233,7 @@
         <v>3</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H616" t="n">
         <v>31723</v>
@@ -18291,7 +18291,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67584562301636</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H618" t="n">
         <v>5256</v>
@@ -18349,7 +18349,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734303474426</v>
+        <v>2.77734327316284</v>
       </c>
       <c r="H620" t="n">
         <v>10213</v>
@@ -18610,7 +18610,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G629" t="n">
-        <v>3.07260847091675</v>
+        <v>3.07260870933533</v>
       </c>
       <c r="H629" t="n">
         <v>16167</v>
@@ -18639,7 +18639,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G630" t="n">
-        <v>3.12797141075134</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H630" t="n">
         <v>13699</v>
@@ -18697,7 +18697,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.12797141075134</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H632" t="n">
         <v>4540</v>
@@ -18726,7 +18726,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H633" t="n">
         <v>2929</v>
@@ -18784,7 +18784,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H635" t="n">
         <v>15459</v>
@@ -18900,7 +18900,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>3.19256067276001</v>
+        <v>3.19256043434143</v>
       </c>
       <c r="H639" t="n">
         <v>121971</v>
@@ -19045,7 +19045,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H644" t="n">
         <v>1108</v>
@@ -19132,7 +19132,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G647" t="n">
-        <v>2.97111105918884</v>
+        <v>2.97111129760742</v>
       </c>
       <c r="H647" t="n">
         <v>1164</v>
@@ -19161,7 +19161,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>3.07260847091675</v>
+        <v>3.07260870933533</v>
       </c>
       <c r="H648" t="n">
         <v>31675</v>
@@ -19219,7 +19219,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G650" t="n">
-        <v>3.12797141075134</v>
+        <v>3.12797117233276</v>
       </c>
       <c r="H650" t="n">
         <v>81888</v>
@@ -19248,7 +19248,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G651" t="n">
-        <v>3.17410635948181</v>
+        <v>3.17410659790039</v>
       </c>
       <c r="H651" t="n">
         <v>7106</v>
@@ -19306,7 +19306,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.19256067276001</v>
+        <v>3.19256043434143</v>
       </c>
       <c r="H653" t="n">
         <v>17275</v>
@@ -19335,7 +19335,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>3.25714993476868</v>
+        <v>3.2571496963501</v>
       </c>
       <c r="H654" t="n">
         <v>1756</v>
@@ -19393,7 +19393,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>3.34019327163696</v>
+        <v>3.34019303321838</v>
       </c>
       <c r="H656" t="n">
         <v>11889</v>
@@ -19538,7 +19538,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>3.10951685905457</v>
+        <v>3.10951662063599</v>
       </c>
       <c r="H661" t="n">
         <v>7980</v>
@@ -19567,7 +19567,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>3.0633819103241</v>
+        <v>3.06338167190552</v>
       </c>
       <c r="H662" t="n">
         <v>6848</v>
@@ -19596,7 +19596,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>2.96188426017761</v>
+        <v>2.96188402175903</v>
       </c>
       <c r="H663" t="n">
         <v>19629</v>
@@ -19625,7 +19625,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H664" t="n">
         <v>78917</v>
@@ -19654,7 +19654,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.88806772232056</v>
+        <v>2.88806796073914</v>
       </c>
       <c r="H665" t="n">
         <v>1731</v>
@@ -19712,7 +19712,7 @@
         <v>3</v>
       </c>
       <c r="G667" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H667" t="n">
         <v>3857</v>
@@ -19741,7 +19741,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H668" t="n">
         <v>18109</v>
@@ -19799,7 +19799,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G670" t="n">
-        <v>3.00801920890808</v>
+        <v>3.00801944732666</v>
       </c>
       <c r="H670" t="n">
         <v>4150</v>
@@ -19828,7 +19828,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H671" t="n">
         <v>3776</v>
@@ -19973,7 +19973,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G676" t="n">
-        <v>2.87884044647217</v>
+        <v>2.87884068489075</v>
       </c>
       <c r="H676" t="n">
         <v>530</v>
@@ -20002,7 +20002,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H677" t="n">
         <v>213</v>
@@ -20060,7 +20060,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H679" t="n">
         <v>14622</v>
@@ -20118,7 +20118,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>3.01724624633789</v>
+        <v>3.01724648475647</v>
       </c>
       <c r="H681" t="n">
         <v>5416</v>
@@ -20147,7 +20147,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G682" t="n">
-        <v>3.00801920890808</v>
+        <v>3.00801944732666</v>
       </c>
       <c r="H682" t="n">
         <v>3265</v>
@@ -20176,7 +20176,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>3.01724624633789</v>
+        <v>3.01724648475647</v>
       </c>
       <c r="H683" t="n">
         <v>6747</v>
@@ -20234,7 +20234,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05415463447571</v>
+        <v>3.05415439605713</v>
       </c>
       <c r="H685" t="n">
         <v>1682</v>
@@ -20263,7 +20263,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>3.01724624633789</v>
+        <v>3.01724648475647</v>
       </c>
       <c r="H686" t="n">
         <v>3184</v>
@@ -20379,7 +20379,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H690" t="n">
         <v>20373</v>
@@ -20495,7 +20495,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>2.94342994689941</v>
+        <v>2.94343018531799</v>
       </c>
       <c r="H694" t="n">
         <v>2567</v>
@@ -20582,7 +20582,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>2.96188426017761</v>
+        <v>2.96188402175903</v>
       </c>
       <c r="H697" t="n">
         <v>422</v>
@@ -20611,7 +20611,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H698" t="n">
         <v>581</v>
@@ -20640,7 +20640,7 @@
         <v>3.25</v>
       </c>
       <c r="G699" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H699" t="n">
         <v>620</v>
@@ -20814,7 +20814,7 @@
         <v>3.25</v>
       </c>
       <c r="G705" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H705" t="n">
         <v>46785</v>
@@ -20843,7 +20843,7 @@
         <v>3.25</v>
       </c>
       <c r="G706" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H706" t="n">
         <v>3156</v>
@@ -20872,7 +20872,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H707" t="n">
         <v>553</v>
@@ -20930,7 +20930,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G709" t="n">
-        <v>3.0633819103241</v>
+        <v>3.06338167190552</v>
       </c>
       <c r="H709" t="n">
         <v>10942</v>
@@ -20988,7 +20988,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>3.17410635948181</v>
+        <v>3.17410659790039</v>
       </c>
       <c r="H711" t="n">
         <v>37895</v>
@@ -21046,7 +21046,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>3.34019327163696</v>
+        <v>3.34019303321838</v>
       </c>
       <c r="H713" t="n">
         <v>29644</v>
@@ -21191,7 +21191,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G718" t="n">
-        <v>3.42463660240173</v>
+        <v>3.42463636398315</v>
       </c>
       <c r="H718" t="n">
         <v>19996</v>
@@ -21249,7 +21249,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G720" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H720" t="n">
         <v>26821</v>
@@ -21278,7 +21278,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G721" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H721" t="n">
         <v>22556</v>
@@ -21423,7 +21423,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H726" t="n">
         <v>2271</v>
@@ -21481,7 +21481,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H728" t="n">
         <v>10721</v>
@@ -21510,7 +21510,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>3.62167024612427</v>
+        <v>3.62167000770569</v>
       </c>
       <c r="H729" t="n">
         <v>4368</v>
@@ -21539,7 +21539,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G730" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H730" t="n">
         <v>12120</v>
@@ -21568,7 +21568,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H731" t="n">
         <v>10096</v>
@@ -21626,7 +21626,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G733" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H733" t="n">
         <v>8164</v>
@@ -21742,7 +21742,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G737" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H737" t="n">
         <v>2069</v>
@@ -21887,7 +21887,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>3.5372269153595</v>
+        <v>3.53722715377808</v>
       </c>
       <c r="H742" t="n">
         <v>32</v>
@@ -22177,7 +22177,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H752" t="n">
         <v>1100</v>
@@ -22206,7 +22206,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H753" t="n">
         <v>4824</v>
@@ -22235,7 +22235,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H754" t="n">
         <v>15245</v>
@@ -22322,7 +22322,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.66858291625977</v>
+        <v>3.66858315467834</v>
       </c>
       <c r="H757" t="n">
         <v>8377</v>
@@ -22467,7 +22467,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G762" t="n">
-        <v>3.62167024612427</v>
+        <v>3.62167000770569</v>
       </c>
       <c r="H762" t="n">
         <v>7020</v>
@@ -22612,7 +22612,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H767" t="n">
         <v>18904</v>
@@ -22641,7 +22641,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G768" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H768" t="n">
         <v>7062</v>
@@ -22728,7 +22728,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G771" t="n">
-        <v>3.649817943573</v>
+        <v>3.64981818199158</v>
       </c>
       <c r="H771" t="n">
         <v>1791</v>
@@ -22960,7 +22960,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G779" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H779" t="n">
         <v>1305</v>
@@ -23105,7 +23105,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H784" t="n">
         <v>297</v>
@@ -23134,7 +23134,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H788" t="n">
         <v>372</v>
@@ -23308,7 +23308,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G791" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H791" t="n">
         <v>2121</v>
@@ -23395,7 +23395,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H794" t="n">
         <v>18360</v>
@@ -23424,7 +23424,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G795" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H795" t="n">
         <v>5078</v>
@@ -23511,7 +23511,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H798" t="n">
         <v>12843</v>
@@ -23569,7 +23569,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85623455047607</v>
+        <v>3.8562343120575</v>
       </c>
       <c r="H800" t="n">
         <v>1776</v>
@@ -23598,7 +23598,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88438177108765</v>
+        <v>3.88438200950623</v>
       </c>
       <c r="H801" t="n">
         <v>4253</v>
@@ -23627,7 +23627,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G802" t="n">
-        <v>3.88438177108765</v>
+        <v>3.88438200950623</v>
       </c>
       <c r="H802" t="n">
         <v>2408</v>
@@ -23685,7 +23685,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>3.96882486343384</v>
+        <v>3.96882510185242</v>
       </c>
       <c r="H804" t="n">
         <v>11913</v>
@@ -23743,7 +23743,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H806" t="n">
         <v>41169</v>
@@ -23888,7 +23888,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G811" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H811" t="n">
         <v>17935</v>
@@ -23917,7 +23917,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>4.10018062591553</v>
+        <v>4.10018110275269</v>
       </c>
       <c r="H812" t="n">
         <v>12249</v>
@@ -23946,7 +23946,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H813" t="n">
         <v>3381</v>
@@ -24236,7 +24236,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H823" t="n">
         <v>41614</v>
@@ -24294,7 +24294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H825" t="n">
         <v>2822</v>
@@ -24323,7 +24323,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G826" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H826" t="n">
         <v>4126</v>
@@ -24410,7 +24410,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H829" t="n">
         <v>5363</v>
@@ -24439,7 +24439,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>4.3065972328186</v>
+        <v>4.30659770965576</v>
       </c>
       <c r="H830" t="n">
         <v>13944</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H831" t="n">
         <v>8663</v>
@@ -24526,7 +24526,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H833" t="n">
         <v>15658</v>
@@ -24613,7 +24613,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H836" t="n">
         <v>10141</v>
@@ -24671,7 +24671,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G838" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H838" t="n">
         <v>2963</v>
@@ -24700,7 +24700,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H839" t="n">
         <v>15833</v>
@@ -24758,7 +24758,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H841" t="n">
         <v>3553</v>
@@ -24787,7 +24787,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H842" t="n">
         <v>5470</v>
@@ -24874,7 +24874,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H845" t="n">
         <v>3484</v>
@@ -25019,7 +25019,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G850" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H850" t="n">
         <v>3030</v>
@@ -25106,7 +25106,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H853" t="n">
         <v>2333</v>
@@ -25164,7 +25164,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H855" t="n">
         <v>12319</v>
@@ -25280,7 +25280,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H859" t="n">
         <v>7062</v>
@@ -25338,7 +25338,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H861" t="n">
         <v>9293</v>
@@ -25454,7 +25454,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G865" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H865" t="n">
         <v>808</v>
@@ -25512,7 +25512,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H867" t="n">
         <v>611</v>
@@ -25570,7 +25570,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G869" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H869" t="n">
         <v>13902</v>
@@ -25657,7 +25657,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H872" t="n">
         <v>570</v>
@@ -25802,7 +25802,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H877" t="n">
         <v>5546</v>
@@ -25918,7 +25918,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G881" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H881" t="n">
         <v>10744</v>
@@ -25976,7 +25976,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G883" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H883" t="n">
         <v>50</v>
@@ -26005,7 +26005,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H884" t="n">
         <v>2574</v>
@@ -26034,7 +26034,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G885" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H885" t="n">
         <v>3925</v>
@@ -26063,7 +26063,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G886" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H886" t="n">
         <v>1154</v>
@@ -26092,7 +26092,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H887" t="n">
         <v>6727</v>
@@ -26179,7 +26179,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G890" t="n">
-        <v>3.66858291625977</v>
+        <v>3.66858315467834</v>
       </c>
       <c r="H890" t="n">
         <v>6569</v>
@@ -26208,7 +26208,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G891" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H891" t="n">
         <v>1081</v>
@@ -26295,7 +26295,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H894" t="n">
         <v>1455</v>
@@ -26353,7 +26353,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H896" t="n">
         <v>4606</v>
@@ -26440,7 +26440,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H899" t="n">
         <v>4331</v>
@@ -26469,7 +26469,7 @@
         <v>4.25</v>
       </c>
       <c r="G900" t="n">
-        <v>3.98759031295776</v>
+        <v>3.98759055137634</v>
       </c>
       <c r="H900" t="n">
         <v>477</v>
@@ -26498,7 +26498,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G901" t="n">
-        <v>3.9782075881958</v>
+        <v>3.97820734977722</v>
       </c>
       <c r="H901" t="n">
         <v>160</v>
@@ -26556,7 +26556,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H903" t="n">
         <v>7451</v>
@@ -26585,7 +26585,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G904" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -26643,7 +26643,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H906" t="n">
         <v>7171</v>
@@ -26846,7 +26846,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H913" t="n">
         <v>5572</v>
@@ -26875,7 +26875,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G914" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H914" t="n">
         <v>2431</v>
@@ -26904,7 +26904,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G915" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H915" t="n">
         <v>694</v>
@@ -26933,7 +26933,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H916" t="n">
         <v>6079</v>
@@ -26962,7 +26962,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H917" t="n">
         <v>1682</v>
@@ -27020,7 +27020,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G919" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H919" t="n">
         <v>172</v>
@@ -27078,7 +27078,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G921" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H921" t="n">
         <v>3356</v>
@@ -27136,7 +27136,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G923" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H923" t="n">
         <v>10267</v>
@@ -27165,7 +27165,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H924" t="n">
         <v>2845</v>
@@ -27194,7 +27194,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.85623455047607</v>
+        <v>3.8562343120575</v>
       </c>
       <c r="H925" t="n">
         <v>6744</v>
@@ -27223,7 +27223,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G926" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H926" t="n">
         <v>81918</v>
@@ -27252,7 +27252,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H927" t="n">
         <v>16501</v>
@@ -27281,7 +27281,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>4.10018062591553</v>
+        <v>4.10018110275269</v>
       </c>
       <c r="H928" t="n">
         <v>19219</v>
@@ -27310,7 +27310,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G929" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H929" t="n">
         <v>7657</v>
@@ -27339,7 +27339,7 @@
         <v>4.25</v>
       </c>
       <c r="G930" t="n">
-        <v>3.98759031295776</v>
+        <v>3.98759055137634</v>
       </c>
       <c r="H930" t="n">
         <v>18877</v>
@@ -27397,7 +27397,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H932" t="n">
         <v>12772</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H934" t="n">
         <v>1187</v>
@@ -27484,7 +27484,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G935" t="n">
-        <v>3.96882486343384</v>
+        <v>3.96882510185242</v>
       </c>
       <c r="H935" t="n">
         <v>193</v>
@@ -27513,7 +27513,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G936" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H936" t="n">
         <v>1816</v>
@@ -27687,7 +27687,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H942" t="n">
         <v>4920</v>
@@ -27774,7 +27774,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H945" t="n">
         <v>1416</v>
@@ -27803,7 +27803,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G946" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H946" t="n">
         <v>5443</v>
@@ -27832,7 +27832,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H947" t="n">
         <v>1999</v>
@@ -27948,7 +27948,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H951" t="n">
         <v>2435</v>
@@ -28093,7 +28093,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H956" t="n">
         <v>2077</v>
@@ -28122,7 +28122,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.14709377288818</v>
+        <v>4.14709424972534</v>
       </c>
       <c r="H957" t="n">
         <v>2834</v>
@@ -28151,7 +28151,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G958" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H958" t="n">
         <v>1651</v>
@@ -28267,7 +28267,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G962" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H962" t="n">
         <v>1164</v>
@@ -38887,6 +38887,35 @@
         <v>4910</v>
       </c>
       <c r="I1328" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1329" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1329" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="E1329" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="H1329" t="n">
+        <v>471</v>
+      </c>
+      <c r="I1329" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -38919,6 +38919,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1330">
+      <c r="A1330" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1330" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1330" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="D1330" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E1330" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="H1330" t="n">
+        <v>6583</v>
+      </c>
+      <c r="I1330" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H2" t="n">
         <v>561784</v>
@@ -456,7 +456,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11975526809692</v>
+        <v>3.11975502967834</v>
       </c>
       <c r="H3" t="n">
         <v>105419</v>
@@ -514,7 +514,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161733627319</v>
+        <v>3.10161709785461</v>
       </c>
       <c r="H5" t="n">
         <v>23147</v>
@@ -572,7 +572,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>3.29206728935242</v>
+        <v>3.292067527771</v>
       </c>
       <c r="H7" t="n">
         <v>292211</v>
@@ -601,7 +601,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H8" t="n">
         <v>720993</v>
@@ -630,7 +630,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.56867361068726</v>
+        <v>3.56867337226868</v>
       </c>
       <c r="H9" t="n">
         <v>292968</v>
@@ -659,7 +659,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H10" t="n">
         <v>160329</v>
@@ -688,7 +688,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H11" t="n">
         <v>65268</v>
@@ -717,7 +717,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H12" t="n">
         <v>34000</v>
@@ -775,7 +775,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H14" t="n">
         <v>18667</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H16" t="n">
         <v>44813</v>
@@ -862,7 +862,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924401283264</v>
       </c>
       <c r="H17" t="n">
         <v>150547</v>
@@ -891,7 +891,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924401283264</v>
       </c>
       <c r="H18" t="n">
         <v>290894</v>
@@ -1036,7 +1036,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831274032593</v>
+        <v>3.71831321716309</v>
       </c>
       <c r="H23" t="n">
         <v>29141</v>
@@ -1094,7 +1094,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.89515972137451</v>
+        <v>3.89515924453735</v>
       </c>
       <c r="H25" t="n">
         <v>186140</v>
@@ -1123,7 +1123,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876293182373</v>
+        <v>3.90876317024231</v>
       </c>
       <c r="H26" t="n">
         <v>85789</v>
@@ -1210,7 +1210,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993462562561</v>
+        <v>3.79993414878845</v>
       </c>
       <c r="H29" t="n">
         <v>38465</v>
@@ -1268,7 +1268,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377825737</v>
+        <v>3.71377801895142</v>
       </c>
       <c r="H31" t="n">
         <v>31484</v>
@@ -1297,7 +1297,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H32" t="n">
         <v>14654</v>
@@ -1326,7 +1326,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H33" t="n">
         <v>18869</v>
@@ -1355,7 +1355,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H34" t="n">
         <v>5781</v>
@@ -1471,7 +1471,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365852355957</v>
       </c>
       <c r="H38" t="n">
         <v>28609</v>
@@ -1587,7 +1587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H42" t="n">
         <v>23606</v>
@@ -1616,7 +1616,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H43" t="n">
         <v>10910</v>
@@ -1674,7 +1674,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H45" t="n">
         <v>2007</v>
@@ -1703,7 +1703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H46" t="n">
         <v>6914</v>
@@ -1819,7 +1819,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365852355957</v>
       </c>
       <c r="H50" t="n">
         <v>9599</v>
@@ -1848,7 +1848,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.80900311470032</v>
+        <v>3.8090033531189</v>
       </c>
       <c r="H51" t="n">
         <v>25429</v>
@@ -1877,7 +1877,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H52" t="n">
         <v>919</v>
@@ -1906,7 +1906,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H53" t="n">
         <v>5908</v>
@@ -2022,7 +2022,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H57" t="n">
         <v>18537</v>
@@ -2051,7 +2051,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H58" t="n">
         <v>4003</v>
@@ -2080,7 +2080,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H59" t="n">
         <v>6637</v>
@@ -2109,7 +2109,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H60" t="n">
         <v>5790</v>
@@ -2138,7 +2138,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H61" t="n">
         <v>93456</v>
@@ -2167,7 +2167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.70017504692078</v>
+        <v>3.7001748085022</v>
       </c>
       <c r="H62" t="n">
         <v>8191</v>
@@ -2196,7 +2196,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284770011902</v>
+        <v>3.72284746170044</v>
       </c>
       <c r="H63" t="n">
         <v>20100</v>
@@ -2254,7 +2254,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>3.68203663825989</v>
+        <v>3.68203687667847</v>
       </c>
       <c r="H65" t="n">
         <v>13936</v>
@@ -2312,7 +2312,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H67" t="n">
         <v>3242</v>
@@ -2399,7 +2399,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H70" t="n">
         <v>15982</v>
@@ -2428,7 +2428,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.68203663825989</v>
+        <v>3.68203687667847</v>
       </c>
       <c r="H71" t="n">
         <v>9106</v>
@@ -2457,7 +2457,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H72" t="n">
         <v>6928</v>
@@ -2486,7 +2486,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H73" t="n">
         <v>6007</v>
@@ -2544,7 +2544,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H75" t="n">
         <v>10828</v>
@@ -2573,7 +2573,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H76" t="n">
         <v>9217</v>
@@ -2602,7 +2602,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H77" t="n">
         <v>10457</v>
@@ -2631,7 +2631,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.70017504692078</v>
+        <v>3.7001748085022</v>
       </c>
       <c r="H78" t="n">
         <v>36913</v>
@@ -2660,7 +2660,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H79" t="n">
         <v>16654</v>
@@ -2689,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H80" t="n">
         <v>1294</v>
@@ -2718,7 +2718,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H81" t="n">
         <v>14163</v>
@@ -2747,7 +2747,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320809364319</v>
+        <v>3.57320785522461</v>
       </c>
       <c r="H82" t="n">
         <v>5877</v>
@@ -2863,7 +2863,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729214668274</v>
+        <v>3.38729190826416</v>
       </c>
       <c r="H86" t="n">
         <v>4796</v>
@@ -2892,7 +2892,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.45984482765198</v>
+        <v>3.45984506607056</v>
       </c>
       <c r="H87" t="n">
         <v>56731</v>
@@ -2921,7 +2921,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47798275947571</v>
+        <v>3.47798299789429</v>
       </c>
       <c r="H88" t="n">
         <v>5844</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.44624090194702</v>
+        <v>3.44624137878418</v>
       </c>
       <c r="H89" t="n">
         <v>5063</v>
@@ -3008,7 +3008,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.47798275947571</v>
+        <v>3.47798299789429</v>
       </c>
       <c r="H91" t="n">
         <v>7413</v>
@@ -3066,7 +3066,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.48251748085022</v>
+        <v>3.48251724243164</v>
       </c>
       <c r="H93" t="n">
         <v>7085</v>
@@ -3095,7 +3095,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H94" t="n">
         <v>14502</v>
@@ -3124,7 +3124,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555100440979</v>
       </c>
       <c r="H95" t="n">
         <v>19856</v>
@@ -3153,7 +3153,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>3.32380890846252</v>
+        <v>3.3238091468811</v>
       </c>
       <c r="H96" t="n">
         <v>1326</v>
@@ -3182,7 +3182,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531010627747</v>
+        <v>3.45531034469604</v>
       </c>
       <c r="H97" t="n">
         <v>13724</v>
@@ -3240,7 +3240,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>3.42356896400452</v>
+        <v>3.42356872558594</v>
       </c>
       <c r="H99" t="n">
         <v>4056</v>
@@ -3298,7 +3298,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996503829956</v>
+        <v>3.40996527671814</v>
       </c>
       <c r="H101" t="n">
         <v>3157</v>
@@ -3327,7 +3327,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996503829956</v>
+        <v>3.40996527671814</v>
       </c>
       <c r="H102" t="n">
         <v>340</v>
@@ -3385,7 +3385,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555100440979</v>
       </c>
       <c r="H104" t="n">
         <v>6856</v>
@@ -3414,7 +3414,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555100440979</v>
       </c>
       <c r="H105" t="n">
         <v>4111</v>
@@ -3472,7 +3472,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48251748085022</v>
+        <v>3.48251724243164</v>
       </c>
       <c r="H107" t="n">
         <v>5104</v>
@@ -3559,7 +3559,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H110" t="n">
         <v>33451</v>
@@ -3588,7 +3588,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H111" t="n">
         <v>13196</v>
@@ -3617,7 +3617,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.49612092971802</v>
+        <v>3.4961211681366</v>
       </c>
       <c r="H112" t="n">
         <v>28788</v>
@@ -3675,7 +3675,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>3.55960464477539</v>
+        <v>3.55960440635681</v>
       </c>
       <c r="H114" t="n">
         <v>4027</v>
@@ -3704,7 +3704,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>3.55507016181946</v>
+        <v>3.55506992340088</v>
       </c>
       <c r="H115" t="n">
         <v>8785</v>
@@ -3733,7 +3733,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H116" t="n">
         <v>1006</v>
@@ -3791,7 +3791,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831274032593</v>
+        <v>3.71831321716309</v>
       </c>
       <c r="H118" t="n">
         <v>29715</v>
@@ -3820,7 +3820,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H119" t="n">
         <v>35244</v>
@@ -3849,7 +3849,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>3.50972461700439</v>
+        <v>3.50972437858582</v>
       </c>
       <c r="H120" t="n">
         <v>9381</v>
@@ -3878,7 +3878,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.49612092971802</v>
+        <v>3.4961211681366</v>
       </c>
       <c r="H121" t="n">
         <v>6937</v>
@@ -3936,7 +3936,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287811279297</v>
+        <v>3.33287787437439</v>
       </c>
       <c r="H123" t="n">
         <v>13328</v>
@@ -3994,7 +3994,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32834362983704</v>
+        <v>3.32834339141846</v>
       </c>
       <c r="H125" t="n">
         <v>9558</v>
@@ -4052,7 +4052,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H127" t="n">
         <v>3094</v>
@@ -4226,7 +4226,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404932975769</v>
+        <v>3.22404956817627</v>
       </c>
       <c r="H133" t="n">
         <v>4602</v>
@@ -4284,7 +4284,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30113625526428</v>
+        <v>3.30113649368286</v>
       </c>
       <c r="H135" t="n">
         <v>17559</v>
@@ -4313,7 +4313,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>3.31927442550659</v>
+        <v>3.31927466392517</v>
       </c>
       <c r="H136" t="n">
         <v>21037</v>
@@ -4371,7 +4371,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020522117615</v>
+        <v>3.31020569801331</v>
       </c>
       <c r="H138" t="n">
         <v>2087</v>
@@ -4400,7 +4400,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555100440979</v>
       </c>
       <c r="H139" t="n">
         <v>353762</v>
@@ -4429,7 +4429,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>3.55507016181946</v>
+        <v>3.55506992340088</v>
       </c>
       <c r="H140" t="n">
         <v>17360</v>
@@ -4545,7 +4545,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>3.30113625526428</v>
+        <v>3.30113649368286</v>
       </c>
       <c r="H144" t="n">
         <v>9061</v>
@@ -4574,7 +4574,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G145" t="n">
-        <v>3.31927442550659</v>
+        <v>3.31927466392517</v>
       </c>
       <c r="H145" t="n">
         <v>2079</v>
@@ -4632,7 +4632,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G147" t="n">
-        <v>3.22858381271362</v>
+        <v>3.2285840511322</v>
       </c>
       <c r="H147" t="n">
         <v>5516</v>
@@ -4690,7 +4690,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.1469624042511</v>
+        <v>3.14696216583252</v>
       </c>
       <c r="H149" t="n">
         <v>11513</v>
@@ -4719,7 +4719,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>3.25125670433044</v>
+        <v>3.25125646591187</v>
       </c>
       <c r="H150" t="n">
         <v>5307</v>
@@ -4748,7 +4748,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510033607483</v>
+        <v>3.16510057449341</v>
       </c>
       <c r="H151" t="n">
         <v>218</v>
@@ -4835,7 +4835,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H154" t="n">
         <v>1770</v>
@@ -4864,7 +4864,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092648506165</v>
       </c>
       <c r="H155" t="n">
         <v>5951</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H156" t="n">
         <v>10379</v>
@@ -4922,7 +4922,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756321907043</v>
+        <v>2.89756345748901</v>
       </c>
       <c r="H157" t="n">
         <v>4634</v>
@@ -4951,7 +4951,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.96104693412781</v>
+        <v>2.96104669570923</v>
       </c>
       <c r="H158" t="n">
         <v>1286</v>
@@ -5096,7 +5096,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H163" t="n">
         <v>1018</v>
@@ -5154,7 +5154,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G165" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092648506165</v>
       </c>
       <c r="H165" t="n">
         <v>3774</v>
@@ -5183,7 +5183,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G166" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H166" t="n">
         <v>6067</v>
@@ -5241,7 +5241,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>3.21044564247131</v>
+        <v>3.21044588088989</v>
       </c>
       <c r="H168" t="n">
         <v>11151</v>
@@ -5270,7 +5270,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.37368893623352</v>
+        <v>3.37368869781494</v>
       </c>
       <c r="H169" t="n">
         <v>87762</v>
@@ -5328,7 +5328,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615181922913</v>
+        <v>3.10615158081055</v>
       </c>
       <c r="H171" t="n">
         <v>59616</v>
@@ -5357,7 +5357,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>3.11522078514099</v>
+        <v>3.11522054672241</v>
       </c>
       <c r="H172" t="n">
         <v>8398</v>
@@ -5386,7 +5386,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G173" t="n">
-        <v>3.16056561470032</v>
+        <v>3.1605658531189</v>
       </c>
       <c r="H173" t="n">
         <v>546</v>
@@ -5415,7 +5415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H174" t="n">
         <v>4116</v>
@@ -5444,7 +5444,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092648506165</v>
       </c>
       <c r="H175" t="n">
         <v>7513</v>
@@ -5502,7 +5502,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H177" t="n">
         <v>9793</v>
@@ -5531,7 +5531,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.02452993392944</v>
+        <v>3.02453017234802</v>
       </c>
       <c r="H178" t="n">
         <v>1198</v>
@@ -5589,7 +5589,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H180" t="n">
         <v>998</v>
@@ -5705,7 +5705,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266810417175</v>
+        <v>3.04266858100891</v>
       </c>
       <c r="H184" t="n">
         <v>656</v>
@@ -5763,7 +5763,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092648506165</v>
       </c>
       <c r="H186" t="n">
         <v>3889</v>
@@ -5908,7 +5908,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H191" t="n">
         <v>12796</v>
@@ -5937,7 +5937,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627179145813</v>
+        <v>3.05627155303955</v>
       </c>
       <c r="H192" t="n">
         <v>9528</v>
@@ -5995,7 +5995,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.06534123420715</v>
+        <v>3.06534099578857</v>
       </c>
       <c r="H194" t="n">
         <v>924</v>
@@ -6169,7 +6169,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489056587219</v>
+        <v>2.87489080429077</v>
       </c>
       <c r="H200" t="n">
         <v>7430</v>
@@ -6198,7 +6198,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G201" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H201" t="n">
         <v>7306</v>
@@ -6256,7 +6256,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>2.9565122127533</v>
+        <v>2.95651245117188</v>
       </c>
       <c r="H203" t="n">
         <v>1563</v>
@@ -6314,7 +6314,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011613845825</v>
+        <v>2.97011566162109</v>
       </c>
       <c r="H205" t="n">
         <v>4097</v>
@@ -6488,7 +6488,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H211" t="n">
         <v>53801</v>
@@ -6517,7 +6517,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.36461997032166</v>
+        <v>3.36461973190308</v>
       </c>
       <c r="H212" t="n">
         <v>17177</v>
@@ -6546,7 +6546,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765301704407</v>
+        <v>3.23765277862549</v>
       </c>
       <c r="H213" t="n">
         <v>4683</v>
@@ -6575,7 +6575,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753304481506</v>
+        <v>3.28753280639648</v>
       </c>
       <c r="H214" t="n">
         <v>1310</v>
@@ -6604,7 +6604,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416930198669</v>
       </c>
       <c r="H215" t="n">
         <v>6340</v>
@@ -6633,7 +6633,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>3.11975526809692</v>
+        <v>3.11975502967834</v>
       </c>
       <c r="H216" t="n">
         <v>5488</v>
@@ -6662,7 +6662,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>3.11522078514099</v>
+        <v>3.11522054672241</v>
       </c>
       <c r="H217" t="n">
         <v>1846</v>
@@ -6691,7 +6691,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.16056561470032</v>
+        <v>3.1605658531189</v>
       </c>
       <c r="H218" t="n">
         <v>4799</v>
@@ -6720,7 +6720,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416930198669</v>
       </c>
       <c r="H219" t="n">
         <v>8838</v>
@@ -6778,7 +6778,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.9293053150177</v>
+        <v>2.92930507659912</v>
       </c>
       <c r="H221" t="n">
         <v>10002</v>
@@ -6865,7 +6865,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035608291626</v>
+        <v>2.87035584449768</v>
       </c>
       <c r="H224" t="n">
         <v>4992</v>
@@ -6894,7 +6894,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H225" t="n">
         <v>3170</v>
@@ -6923,7 +6923,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G226" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H226" t="n">
         <v>8814</v>
@@ -6981,7 +6981,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H228" t="n">
         <v>593</v>
@@ -7010,7 +7010,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489056587219</v>
+        <v>2.87489080429077</v>
       </c>
       <c r="H229" t="n">
         <v>389</v>
@@ -7068,7 +7068,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H231" t="n">
         <v>1012</v>
@@ -7213,7 +7213,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H236" t="n">
         <v>11979</v>
@@ -7242,7 +7242,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H237" t="n">
         <v>3487</v>
@@ -7271,7 +7271,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H238" t="n">
         <v>16491</v>
@@ -7300,7 +7300,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H239" t="n">
         <v>10412</v>
@@ -7329,7 +7329,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H240" t="n">
         <v>17990</v>
@@ -7416,7 +7416,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>2.77513098716736</v>
+        <v>2.77513122558594</v>
       </c>
       <c r="H243" t="n">
         <v>3305</v>
@@ -7445,7 +7445,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H244" t="n">
         <v>4956</v>
@@ -7532,7 +7532,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H247" t="n">
         <v>5286</v>
@@ -7561,7 +7561,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H248" t="n">
         <v>1003</v>
@@ -7590,7 +7590,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.8340802192688</v>
+        <v>2.83407998085022</v>
       </c>
       <c r="H249" t="n">
         <v>625</v>
@@ -7619,7 +7619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H250" t="n">
         <v>11443</v>
@@ -7706,7 +7706,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H253" t="n">
         <v>1884</v>
@@ -7735,7 +7735,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H254" t="n">
         <v>1758</v>
@@ -7764,7 +7764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H255" t="n">
         <v>18878</v>
@@ -7793,7 +7793,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H256" t="n">
         <v>2600</v>
@@ -7822,7 +7822,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350934028625</v>
       </c>
       <c r="H257" t="n">
         <v>8062</v>
@@ -7851,7 +7851,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071647644043</v>
+        <v>2.72071671485901</v>
       </c>
       <c r="H258" t="n">
         <v>1704</v>
@@ -7880,7 +7880,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.69804430007935</v>
+        <v>2.69804406166077</v>
       </c>
       <c r="H259" t="n">
         <v>16864</v>
@@ -7938,7 +7938,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.7161819934845</v>
+        <v>2.71618223190308</v>
       </c>
       <c r="H261" t="n">
         <v>2757</v>
@@ -7967,7 +7967,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H262" t="n">
         <v>5847</v>
@@ -8054,7 +8054,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456058502197</v>
+        <v>2.63456082344055</v>
       </c>
       <c r="H265" t="n">
         <v>9259</v>
@@ -8112,7 +8112,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.67537140846252</v>
+        <v>2.6753716468811</v>
       </c>
       <c r="H267" t="n">
         <v>735</v>
@@ -8170,7 +8170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H269" t="n">
         <v>1163</v>
@@ -8199,7 +8199,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H270" t="n">
         <v>9817</v>
@@ -8228,7 +8228,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G271" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H271" t="n">
         <v>23246</v>
@@ -8257,7 +8257,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.58014631271362</v>
+        <v>2.5801465511322</v>
       </c>
       <c r="H272" t="n">
         <v>7178</v>
@@ -8402,7 +8402,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945546150208</v>
+        <v>2.48945569992065</v>
       </c>
       <c r="H277" t="n">
         <v>995</v>
@@ -8431,7 +8431,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>2.45317935943604</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H278" t="n">
         <v>2892</v>
@@ -8489,7 +8489,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062739372253</v>
+        <v>2.38062715530396</v>
       </c>
       <c r="H280" t="n">
         <v>7350</v>
@@ -8518,7 +8518,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342025756836</v>
       </c>
       <c r="H281" t="n">
         <v>44116</v>
@@ -8547,7 +8547,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H282" t="n">
         <v>4891</v>
@@ -8663,7 +8663,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H286" t="n">
         <v>3503</v>
@@ -8808,7 +8808,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>2.11309003829956</v>
+        <v>2.11308979988098</v>
       </c>
       <c r="H291" t="n">
         <v>2789</v>
@@ -8837,7 +8837,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.13576245307922</v>
+        <v>2.1357626914978</v>
       </c>
       <c r="H292" t="n">
         <v>9540</v>
@@ -8866,7 +8866,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.33074736595154</v>
+        <v>2.33074712753296</v>
       </c>
       <c r="H293" t="n">
         <v>4108</v>
@@ -8924,7 +8924,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.22645330429077</v>
+        <v>2.22645306587219</v>
       </c>
       <c r="H295" t="n">
         <v>7856</v>
@@ -9098,7 +9098,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33074736595154</v>
+        <v>2.33074712753296</v>
       </c>
       <c r="H301" t="n">
         <v>9820</v>
@@ -9156,7 +9156,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H303" t="n">
         <v>8916</v>
@@ -9272,7 +9272,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.43050694465637</v>
+        <v>2.43050718307495</v>
       </c>
       <c r="H307" t="n">
         <v>5406</v>
@@ -9301,7 +9301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H308" t="n">
         <v>371</v>
@@ -9330,7 +9330,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H309" t="n">
         <v>7036</v>
@@ -9359,7 +9359,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G314" t="n">
-        <v>2.48038673400879</v>
+        <v>2.48038649559021</v>
       </c>
       <c r="H314" t="n">
         <v>4439</v>
@@ -9504,7 +9504,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H315" t="n">
         <v>2887</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H326" t="n">
         <v>10875</v>
@@ -9852,7 +9852,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>2.43050694465637</v>
+        <v>2.43050718307495</v>
       </c>
       <c r="H327" t="n">
         <v>902</v>
@@ -9881,7 +9881,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H328" t="n">
         <v>9578</v>
@@ -9910,7 +9910,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H329" t="n">
         <v>4763</v>
@@ -9968,7 +9968,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342025756836</v>
       </c>
       <c r="H331" t="n">
         <v>12852</v>
@@ -10055,7 +10055,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.2944712638855</v>
+        <v>2.29447102546692</v>
       </c>
       <c r="H334" t="n">
         <v>2916</v>
@@ -10113,7 +10113,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.3080747127533</v>
+        <v>2.30807495117188</v>
       </c>
       <c r="H336" t="n">
         <v>989</v>
@@ -10229,7 +10229,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993654251099</v>
+        <v>2.28993678092957</v>
       </c>
       <c r="H340" t="n">
         <v>31736</v>
@@ -10258,7 +10258,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H341" t="n">
         <v>4266</v>
@@ -10287,7 +10287,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H342" t="n">
         <v>12825</v>
@@ -10461,7 +10461,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H348" t="n">
         <v>518</v>
@@ -10490,7 +10490,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H349" t="n">
         <v>5793</v>
@@ -10519,7 +10519,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G350" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H350" t="n">
         <v>68</v>
@@ -10548,7 +10548,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179837226868</v>
+        <v>2.27179861068726</v>
       </c>
       <c r="H351" t="n">
         <v>4619</v>
@@ -10577,7 +10577,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G352" t="n">
-        <v>2.45317935943604</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H352" t="n">
         <v>4007</v>
@@ -10751,7 +10751,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G358" t="n">
-        <v>2.26272940635681</v>
+        <v>2.26272964477539</v>
       </c>
       <c r="H358" t="n">
         <v>5565</v>
@@ -10809,7 +10809,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>2.24459147453308</v>
+        <v>2.2445912361145</v>
       </c>
       <c r="H360" t="n">
         <v>1525</v>
@@ -10838,7 +10838,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>2.24459147453308</v>
+        <v>2.2445912361145</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H362" t="n">
         <v>1115</v>
@@ -11041,7 +11041,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G368" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H368" t="n">
         <v>2162</v>
@@ -11070,7 +11070,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H369" t="n">
         <v>1383</v>
@@ -11186,7 +11186,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.4032998085022</v>
+        <v>2.40330004692078</v>
       </c>
       <c r="H373" t="n">
         <v>26801</v>
@@ -11215,7 +11215,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.3896963596344</v>
+        <v>2.38969612121582</v>
       </c>
       <c r="H374" t="n">
         <v>7617</v>
@@ -11244,7 +11244,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.4032998085022</v>
+        <v>2.40330004692078</v>
       </c>
       <c r="H375" t="n">
         <v>8213</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H376" t="n">
         <v>7974</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H379" t="n">
         <v>125340</v>
@@ -11389,7 +11389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H380" t="n">
         <v>15968</v>
@@ -11418,7 +11418,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.4985249042511</v>
+        <v>2.49852514266968</v>
       </c>
       <c r="H381" t="n">
         <v>3626</v>
@@ -11447,7 +11447,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H382" t="n">
         <v>4545</v>
@@ -11476,7 +11476,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>2.56200838088989</v>
+        <v>2.56200861930847</v>
       </c>
       <c r="H383" t="n">
         <v>1921</v>
@@ -11592,7 +11592,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H387" t="n">
         <v>400</v>
@@ -11621,7 +11621,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H388" t="n">
         <v>9739</v>
@@ -11650,7 +11650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H389" t="n">
         <v>5695</v>
@@ -11679,7 +11679,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H390" t="n">
         <v>3704</v>
@@ -11737,7 +11737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H392" t="n">
         <v>8970</v>
@@ -11766,7 +11766,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H393" t="n">
         <v>258</v>
@@ -11853,7 +11853,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666331291199</v>
+        <v>2.51666283607483</v>
       </c>
       <c r="H396" t="n">
         <v>67390</v>
@@ -11882,7 +11882,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H397" t="n">
         <v>6517</v>
@@ -11969,7 +11969,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H400" t="n">
         <v>6772</v>
@@ -11998,7 +11998,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H401" t="n">
         <v>25644</v>
@@ -12027,7 +12027,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281872749329</v>
       </c>
       <c r="H402" t="n">
         <v>27847</v>
@@ -12056,7 +12056,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G403" t="n">
-        <v>2.7161819934845</v>
+        <v>2.71618223190308</v>
       </c>
       <c r="H403" t="n">
         <v>27202</v>
@@ -12085,7 +12085,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H404" t="n">
         <v>20579</v>
@@ -12230,7 +12230,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H409" t="n">
         <v>3350</v>
@@ -12259,7 +12259,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281872749329</v>
       </c>
       <c r="H410" t="n">
         <v>4500</v>
@@ -12288,7 +12288,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281872749329</v>
       </c>
       <c r="H411" t="n">
         <v>2860</v>
@@ -12404,7 +12404,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573251724243</v>
+        <v>2.52573204040527</v>
       </c>
       <c r="H415" t="n">
         <v>8421</v>
@@ -12433,7 +12433,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H416" t="n">
         <v>1088</v>
@@ -12607,7 +12607,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H422" t="n">
         <v>7693</v>
@@ -12636,7 +12636,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G423" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H423" t="n">
         <v>7526</v>
@@ -12665,7 +12665,7 @@
         <v>2.875</v>
       </c>
       <c r="G424" t="n">
-        <v>2.6073534488678</v>
+        <v>2.60735368728638</v>
       </c>
       <c r="H424" t="n">
         <v>1280</v>
@@ -12781,7 +12781,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G428" t="n">
-        <v>2.56200838088989</v>
+        <v>2.56200861930847</v>
       </c>
       <c r="H428" t="n">
         <v>30098</v>
@@ -12868,7 +12868,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H431" t="n">
         <v>2176</v>
@@ -12955,7 +12955,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H434" t="n">
         <v>10353</v>
@@ -12984,7 +12984,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G435" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H435" t="n">
         <v>2214</v>
@@ -13158,7 +13158,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G441" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281872749329</v>
       </c>
       <c r="H441" t="n">
         <v>16239</v>
@@ -13216,7 +13216,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H443" t="n">
         <v>905</v>
@@ -13245,7 +13245,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H444" t="n">
         <v>305</v>
@@ -13274,7 +13274,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188840866089</v>
+        <v>2.61188817024231</v>
       </c>
       <c r="H445" t="n">
         <v>5437</v>
@@ -13303,7 +13303,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G446" t="n">
-        <v>2.59375</v>
+        <v>2.59374976158142</v>
       </c>
       <c r="H446" t="n">
         <v>2456</v>
@@ -13332,7 +13332,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G447" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H447" t="n">
         <v>1026</v>
@@ -13361,7 +13361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350934028625</v>
       </c>
       <c r="H448" t="n">
         <v>14662</v>
@@ -13390,7 +13390,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H449" t="n">
         <v>5650</v>
@@ -13448,7 +13448,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H451" t="n">
         <v>17368</v>
@@ -13477,7 +13477,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H452" t="n">
         <v>9599</v>
@@ -13506,7 +13506,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H453" t="n">
         <v>1381</v>
@@ -13535,7 +13535,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H454" t="n">
         <v>642</v>
@@ -13564,7 +13564,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G455" t="n">
-        <v>2.82047629356384</v>
+        <v>2.82047653198242</v>
       </c>
       <c r="H455" t="n">
         <v>22810</v>
@@ -13593,7 +13593,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H456" t="n">
         <v>17281</v>
@@ -13622,7 +13622,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H457" t="n">
         <v>267</v>
@@ -13709,7 +13709,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H460" t="n">
         <v>4577</v>
@@ -13738,7 +13738,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G461" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H461" t="n">
         <v>1854</v>
@@ -13796,7 +13796,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G463" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H463" t="n">
         <v>1249</v>
@@ -13883,7 +13883,7 @@
         <v>3</v>
       </c>
       <c r="G466" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H466" t="n">
         <v>2400</v>
@@ -13912,7 +13912,7 @@
         <v>3</v>
       </c>
       <c r="G467" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H467" t="n">
         <v>897</v>
@@ -13970,7 +13970,7 @@
         <v>3</v>
       </c>
       <c r="G469" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H469" t="n">
         <v>598</v>
@@ -13999,7 +13999,7 @@
         <v>3</v>
       </c>
       <c r="G470" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H471" t="n">
         <v>6971</v>
@@ -14057,7 +14057,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H472" t="n">
         <v>15161</v>
@@ -14086,7 +14086,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G473" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H473" t="n">
         <v>7200</v>
@@ -14115,7 +14115,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G474" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H474" t="n">
         <v>468</v>
@@ -14231,7 +14231,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G478" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H478" t="n">
         <v>21409</v>
@@ -14289,7 +14289,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G480" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H480" t="n">
         <v>6941</v>
@@ -14318,7 +14318,7 @@
         <v>2.75</v>
       </c>
       <c r="G481" t="n">
-        <v>2.53743982315063</v>
+        <v>2.53743958473206</v>
       </c>
       <c r="H481" t="n">
         <v>5639</v>
@@ -14376,7 +14376,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G483" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H483" t="n">
         <v>869</v>
@@ -14405,7 +14405,7 @@
         <v>2.75</v>
       </c>
       <c r="G484" t="n">
-        <v>2.53743982315063</v>
+        <v>2.53743958473206</v>
       </c>
       <c r="H484" t="n">
         <v>1915</v>
@@ -14463,7 +14463,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G486" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H486" t="n">
         <v>1200</v>
@@ -14521,7 +14521,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H488" t="n">
         <v>4646</v>
@@ -14550,7 +14550,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G489" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H489" t="n">
         <v>1637</v>
@@ -14579,7 +14579,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G490" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H490" t="n">
         <v>62146</v>
@@ -14608,7 +14608,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H491" t="n">
         <v>146750</v>
@@ -14637,7 +14637,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H492" t="n">
         <v>9831</v>
@@ -14666,7 +14666,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G494" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H494" t="n">
         <v>4238</v>
@@ -14724,7 +14724,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H495" t="n">
         <v>367</v>
@@ -14782,7 +14782,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G497" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H497" t="n">
         <v>1143</v>
@@ -14840,7 +14840,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G499" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H499" t="n">
         <v>146</v>
@@ -14869,7 +14869,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H500" t="n">
         <v>5010</v>
@@ -15014,7 +15014,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H505" t="n">
         <v>2168</v>
@@ -15043,7 +15043,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G506" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H506" t="n">
         <v>516</v>
@@ -15072,7 +15072,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H507" t="n">
         <v>4213</v>
@@ -15101,7 +15101,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H508" t="n">
         <v>1909</v>
@@ -15130,7 +15130,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H509" t="n">
         <v>2208</v>
@@ -15159,7 +15159,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H510" t="n">
         <v>2337</v>
@@ -15188,7 +15188,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G511" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H511" t="n">
         <v>123</v>
@@ -15246,7 +15246,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G513" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H513" t="n">
         <v>2999</v>
@@ -15333,7 +15333,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H516" t="n">
         <v>9199</v>
@@ -15420,7 +15420,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H519" t="n">
         <v>107</v>
@@ -15478,7 +15478,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H521" t="n">
         <v>2000</v>
@@ -15507,7 +15507,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H522" t="n">
         <v>3105</v>
@@ -15536,7 +15536,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H523" t="n">
         <v>3940</v>
@@ -15565,7 +15565,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H524" t="n">
         <v>5586</v>
@@ -15594,7 +15594,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H525" t="n">
         <v>256</v>
@@ -15623,7 +15623,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H526" t="n">
         <v>2296</v>
@@ -15681,7 +15681,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H528" t="n">
         <v>165</v>
@@ -15710,7 +15710,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H529" t="n">
         <v>352</v>
@@ -15739,7 +15739,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H530" t="n">
         <v>1618</v>
@@ -15768,7 +15768,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G531" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H531" t="n">
         <v>5250</v>
@@ -15797,7 +15797,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H532" t="n">
         <v>420</v>
@@ -15826,7 +15826,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H533" t="n">
         <v>8008</v>
@@ -15855,7 +15855,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H534" t="n">
         <v>1274</v>
@@ -15884,7 +15884,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H536" t="n">
         <v>553</v>
@@ -15942,7 +15942,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G538" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H538" t="n">
         <v>908</v>
@@ -16029,7 +16029,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H540" t="n">
         <v>14503</v>
@@ -16058,7 +16058,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G541" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H541" t="n">
         <v>300</v>
@@ -16116,7 +16116,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H543" t="n">
         <v>50</v>
@@ -16145,7 +16145,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H544" t="n">
         <v>5816</v>
@@ -16203,7 +16203,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H546" t="n">
         <v>23578</v>
@@ -16232,7 +16232,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H547" t="n">
         <v>4925</v>
@@ -16290,7 +16290,7 @@
         <v>3</v>
       </c>
       <c r="G549" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H549" t="n">
         <v>2815</v>
@@ -16348,7 +16348,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H551" t="n">
         <v>1945</v>
@@ -16377,7 +16377,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H552" t="n">
         <v>22273</v>
@@ -16435,7 +16435,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G554" t="n">
-        <v>2.86961340904236</v>
+        <v>2.86961364746094</v>
       </c>
       <c r="H554" t="n">
         <v>10116</v>
@@ -16551,7 +16551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H558" t="n">
         <v>8956</v>
@@ -16580,7 +16580,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G559" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H559" t="n">
         <v>5192</v>
@@ -16609,7 +16609,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734327316284</v>
+        <v>2.77734303474426</v>
       </c>
       <c r="H560" t="n">
         <v>6973</v>
@@ -16638,7 +16638,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79579734802246</v>
+        <v>2.79579710960388</v>
       </c>
       <c r="H561" t="n">
         <v>2786</v>
@@ -16667,7 +16667,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H562" t="n">
         <v>6763</v>
@@ -16696,7 +16696,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H563" t="n">
         <v>1740</v>
@@ -16725,7 +16725,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H564" t="n">
         <v>33572</v>
@@ -16754,7 +16754,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H565" t="n">
         <v>27</v>
@@ -16783,7 +16783,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H566" t="n">
         <v>2877</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H568" t="n">
         <v>4278</v>
@@ -16928,7 +16928,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43594217300415</v>
+        <v>2.43594193458557</v>
       </c>
       <c r="H571" t="n">
         <v>13431</v>
@@ -16957,7 +16957,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41748785972595</v>
+        <v>2.41748809814453</v>
       </c>
       <c r="H572" t="n">
         <v>1200</v>
@@ -17044,7 +17044,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43594217300415</v>
+        <v>2.43594193458557</v>
       </c>
       <c r="H575" t="n">
         <v>838</v>
@@ -17073,7 +17073,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43594217300415</v>
+        <v>2.43594193458557</v>
       </c>
       <c r="H576" t="n">
         <v>24569</v>
@@ -17131,7 +17131,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H578" t="n">
         <v>8794</v>
@@ -17160,7 +17160,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G579" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H579" t="n">
         <v>17262</v>
@@ -17189,7 +17189,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G580" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H580" t="n">
         <v>596</v>
@@ -17218,7 +17218,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G581" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H581" t="n">
         <v>3015</v>
@@ -17247,7 +17247,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G582" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17305,7 +17305,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.57434773445129</v>
+        <v>2.57434797286987</v>
       </c>
       <c r="H584" t="n">
         <v>8917</v>
@@ -17334,7 +17334,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H585" t="n">
         <v>1960</v>
@@ -17363,7 +17363,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H586" t="n">
         <v>2846</v>
@@ -17450,7 +17450,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G589" t="n">
-        <v>2.50975871086121</v>
+        <v>2.50975847244263</v>
       </c>
       <c r="H589" t="n">
         <v>6124</v>
@@ -17508,7 +17508,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H591" t="n">
         <v>2840</v>
@@ -17537,7 +17537,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G592" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H592" t="n">
         <v>2322</v>
@@ -17566,7 +17566,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H593" t="n">
         <v>12355</v>
@@ -17595,7 +17595,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G594" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H594" t="n">
         <v>4823</v>
@@ -17624,7 +17624,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H595" t="n">
         <v>7592</v>
@@ -17653,7 +17653,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>2.41748785972595</v>
+        <v>2.41748809814453</v>
       </c>
       <c r="H596" t="n">
         <v>13053</v>
@@ -17682,7 +17682,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G597" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H597" t="n">
         <v>20130</v>
@@ -17769,7 +17769,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H600" t="n">
         <v>1222</v>
@@ -17798,7 +17798,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H601" t="n">
         <v>1618</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H603" t="n">
         <v>2226</v>
@@ -17885,7 +17885,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H604" t="n">
         <v>50</v>
@@ -17943,7 +17943,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>2.50975871086121</v>
+        <v>2.50975847244263</v>
       </c>
       <c r="H606" t="n">
         <v>5678</v>
@@ -18030,7 +18030,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H609" t="n">
         <v>7373</v>
@@ -18059,7 +18059,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H610" t="n">
         <v>1755</v>
@@ -18088,7 +18088,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G611" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H611" t="n">
         <v>3646</v>
@@ -18117,7 +18117,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H612" t="n">
         <v>1353</v>
@@ -18146,7 +18146,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H613" t="n">
         <v>3521</v>
@@ -18175,7 +18175,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H614" t="n">
         <v>1453</v>
@@ -18204,7 +18204,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G615" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H615" t="n">
         <v>12525</v>
@@ -18233,7 +18233,7 @@
         <v>3</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H616" t="n">
         <v>31723</v>
@@ -18291,7 +18291,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H618" t="n">
         <v>5256</v>
@@ -18320,7 +18320,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H619" t="n">
         <v>345</v>
@@ -18349,7 +18349,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734327316284</v>
+        <v>2.77734303474426</v>
       </c>
       <c r="H620" t="n">
         <v>10213</v>
@@ -18407,7 +18407,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H622" t="n">
         <v>2229</v>
@@ -18465,7 +18465,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H624" t="n">
         <v>87</v>
@@ -18726,7 +18726,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.11874437332153</v>
+        <v>3.11874413490295</v>
       </c>
       <c r="H633" t="n">
         <v>2929</v>
@@ -18784,7 +18784,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>3.11874437332153</v>
+        <v>3.11874413490295</v>
       </c>
       <c r="H635" t="n">
         <v>15459</v>
@@ -18900,7 +18900,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>3.19256043434143</v>
+        <v>3.19256067276001</v>
       </c>
       <c r="H639" t="n">
         <v>121971</v>
@@ -19045,7 +19045,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.11874437332153</v>
+        <v>3.11874413490295</v>
       </c>
       <c r="H644" t="n">
         <v>1108</v>
@@ -19248,7 +19248,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G651" t="n">
-        <v>3.17410659790039</v>
+        <v>3.17410635948181</v>
       </c>
       <c r="H651" t="n">
         <v>7106</v>
@@ -19306,7 +19306,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.19256043434143</v>
+        <v>3.19256067276001</v>
       </c>
       <c r="H653" t="n">
         <v>17275</v>
@@ -19335,7 +19335,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>3.2571496963501</v>
+        <v>3.25714993476868</v>
       </c>
       <c r="H654" t="n">
         <v>1756</v>
@@ -19364,7 +19364,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>3.32173919677734</v>
+        <v>3.32173943519592</v>
       </c>
       <c r="H655" t="n">
         <v>35366</v>
@@ -19393,7 +19393,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>3.34019303321838</v>
+        <v>3.34019327163696</v>
       </c>
       <c r="H656" t="n">
         <v>11889</v>
@@ -19538,7 +19538,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>3.10951662063599</v>
+        <v>3.10951685905457</v>
       </c>
       <c r="H661" t="n">
         <v>7980</v>
@@ -19567,7 +19567,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>3.06338167190552</v>
+        <v>3.0633819103241</v>
       </c>
       <c r="H662" t="n">
         <v>6848</v>
@@ -19596,7 +19596,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>2.96188402175903</v>
+        <v>2.96188426017761</v>
       </c>
       <c r="H663" t="n">
         <v>19629</v>
@@ -19625,7 +19625,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>2.90652203559875</v>
+        <v>2.90652179718018</v>
       </c>
       <c r="H664" t="n">
         <v>78917</v>
@@ -19654,7 +19654,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.88806796073914</v>
+        <v>2.88806772232056</v>
       </c>
       <c r="H665" t="n">
         <v>1731</v>
@@ -19712,7 +19712,7 @@
         <v>3</v>
       </c>
       <c r="G667" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H667" t="n">
         <v>3857</v>
@@ -19770,7 +19770,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G669" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H669" t="n">
         <v>2510</v>
@@ -19828,7 +19828,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.90652203559875</v>
+        <v>2.90652179718018</v>
       </c>
       <c r="H671" t="n">
         <v>3776</v>
@@ -19886,7 +19886,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G673" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H673" t="n">
         <v>229</v>
@@ -20002,7 +20002,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.90652203559875</v>
+        <v>2.90652179718018</v>
       </c>
       <c r="H677" t="n">
         <v>213</v>
@@ -20060,7 +20060,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.11874437332153</v>
+        <v>3.11874413490295</v>
       </c>
       <c r="H679" t="n">
         <v>14622</v>
@@ -20089,7 +20089,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.03570055961609</v>
+        <v>3.03570032119751</v>
       </c>
       <c r="H680" t="n">
         <v>6809</v>
@@ -20234,7 +20234,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05415439605713</v>
+        <v>3.05415463447571</v>
       </c>
       <c r="H685" t="n">
         <v>1682</v>
@@ -20379,7 +20379,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>2.90652203559875</v>
+        <v>2.90652179718018</v>
       </c>
       <c r="H690" t="n">
         <v>20373</v>
@@ -20437,7 +20437,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G692" t="n">
-        <v>2.8327054977417</v>
+        <v>2.83270525932312</v>
       </c>
       <c r="H692" t="n">
         <v>5417</v>
@@ -20495,7 +20495,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>2.94343018531799</v>
+        <v>2.94342994689941</v>
       </c>
       <c r="H694" t="n">
         <v>2567</v>
@@ -20582,7 +20582,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>2.96188402175903</v>
+        <v>2.96188426017761</v>
       </c>
       <c r="H697" t="n">
         <v>422</v>
@@ -20640,7 +20640,7 @@
         <v>3.25</v>
       </c>
       <c r="G699" t="n">
-        <v>2.99879217147827</v>
+        <v>2.99879240989685</v>
       </c>
       <c r="H699" t="n">
         <v>620</v>
@@ -20698,7 +20698,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.86961340904236</v>
+        <v>2.86961364746094</v>
       </c>
       <c r="H701" t="n">
         <v>2172</v>
@@ -20785,7 +20785,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G704" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H704" t="n">
         <v>7911</v>
@@ -20814,7 +20814,7 @@
         <v>3.25</v>
       </c>
       <c r="G705" t="n">
-        <v>2.99879217147827</v>
+        <v>2.99879240989685</v>
       </c>
       <c r="H705" t="n">
         <v>46785</v>
@@ -20843,7 +20843,7 @@
         <v>3.25</v>
       </c>
       <c r="G706" t="n">
-        <v>2.99879217147827</v>
+        <v>2.99879240989685</v>
       </c>
       <c r="H706" t="n">
         <v>3156</v>
@@ -20901,7 +20901,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G708" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H708" t="n">
         <v>10802</v>
@@ -20930,7 +20930,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G709" t="n">
-        <v>3.06338167190552</v>
+        <v>3.0633819103241</v>
       </c>
       <c r="H709" t="n">
         <v>10942</v>
@@ -20959,7 +20959,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>3.03570055961609</v>
+        <v>3.03570032119751</v>
       </c>
       <c r="H710" t="n">
         <v>132393</v>
@@ -20988,7 +20988,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>3.17410659790039</v>
+        <v>3.17410635948181</v>
       </c>
       <c r="H711" t="n">
         <v>37895</v>
@@ -21017,7 +21017,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.32173919677734</v>
+        <v>3.32173943519592</v>
       </c>
       <c r="H712" t="n">
         <v>125810</v>
@@ -21046,7 +21046,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>3.34019303321838</v>
+        <v>3.34019327163696</v>
       </c>
       <c r="H713" t="n">
         <v>29644</v>
@@ -21191,7 +21191,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G718" t="n">
-        <v>3.42463636398315</v>
+        <v>3.42463660240173</v>
       </c>
       <c r="H718" t="n">
         <v>19996</v>
@@ -21249,7 +21249,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G720" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H720" t="n">
         <v>26821</v>
@@ -21278,7 +21278,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G721" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H721" t="n">
         <v>22556</v>
@@ -21423,7 +21423,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>3.68734836578369</v>
+        <v>3.68734812736511</v>
       </c>
       <c r="H726" t="n">
         <v>2271</v>
@@ -21481,7 +21481,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H728" t="n">
         <v>10721</v>
@@ -21510,7 +21510,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>3.62167000770569</v>
+        <v>3.62167024612427</v>
       </c>
       <c r="H729" t="n">
         <v>4368</v>
@@ -21539,7 +21539,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G730" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H730" t="n">
         <v>12120</v>
@@ -21568,7 +21568,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H731" t="n">
         <v>10096</v>
@@ -21626,7 +21626,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G733" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H733" t="n">
         <v>8164</v>
@@ -21742,7 +21742,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G737" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H737" t="n">
         <v>2069</v>
@@ -21887,7 +21887,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>3.53722715377808</v>
+        <v>3.5372269153595</v>
       </c>
       <c r="H742" t="n">
         <v>32</v>
@@ -22177,7 +22177,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H752" t="n">
         <v>1100</v>
@@ -22206,7 +22206,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H753" t="n">
         <v>4824</v>
@@ -22235,7 +22235,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H754" t="n">
         <v>15245</v>
@@ -22322,7 +22322,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.66858315467834</v>
+        <v>3.66858291625977</v>
       </c>
       <c r="H757" t="n">
         <v>8377</v>
@@ -22467,7 +22467,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G762" t="n">
-        <v>3.62167000770569</v>
+        <v>3.62167024612427</v>
       </c>
       <c r="H762" t="n">
         <v>7020</v>
@@ -22612,7 +22612,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H767" t="n">
         <v>18904</v>
@@ -22641,7 +22641,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G768" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H768" t="n">
         <v>7062</v>
@@ -22728,7 +22728,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G771" t="n">
-        <v>3.64981818199158</v>
+        <v>3.649817943573</v>
       </c>
       <c r="H771" t="n">
         <v>1791</v>
@@ -22960,7 +22960,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G779" t="n">
-        <v>3.68734836578369</v>
+        <v>3.68734812736511</v>
       </c>
       <c r="H779" t="n">
         <v>1305</v>
@@ -23105,7 +23105,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H784" t="n">
         <v>297</v>
@@ -23134,7 +23134,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H788" t="n">
         <v>372</v>
@@ -23308,7 +23308,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G791" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H791" t="n">
         <v>2121</v>
@@ -23395,7 +23395,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H794" t="n">
         <v>18360</v>
@@ -23424,7 +23424,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G795" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H795" t="n">
         <v>5078</v>
@@ -23511,7 +23511,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H798" t="n">
         <v>12843</v>
@@ -23569,7 +23569,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G800" t="n">
-        <v>3.8562343120575</v>
+        <v>3.85623455047607</v>
       </c>
       <c r="H800" t="n">
         <v>1776</v>
@@ -23598,7 +23598,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88438200950623</v>
+        <v>3.88438177108765</v>
       </c>
       <c r="H801" t="n">
         <v>4253</v>
@@ -23627,7 +23627,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G802" t="n">
-        <v>3.88438200950623</v>
+        <v>3.88438177108765</v>
       </c>
       <c r="H802" t="n">
         <v>2408</v>
@@ -23685,7 +23685,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>3.96882510185242</v>
+        <v>3.96882486343384</v>
       </c>
       <c r="H804" t="n">
         <v>11913</v>
@@ -23743,7 +23743,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H806" t="n">
         <v>41169</v>
@@ -23888,7 +23888,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G811" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H811" t="n">
         <v>17935</v>
@@ -23917,7 +23917,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>4.10018110275269</v>
+        <v>4.10018062591553</v>
       </c>
       <c r="H812" t="n">
         <v>12249</v>
@@ -23946,7 +23946,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H813" t="n">
         <v>3381</v>
@@ -24236,7 +24236,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H823" t="n">
         <v>41614</v>
@@ -24294,7 +24294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>4.16585874557495</v>
+        <v>4.16585922241211</v>
       </c>
       <c r="H825" t="n">
         <v>2822</v>
@@ -24323,7 +24323,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G826" t="n">
-        <v>4.15647602081299</v>
+        <v>4.15647649765015</v>
       </c>
       <c r="H826" t="n">
         <v>4126</v>
@@ -24410,7 +24410,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.99697303771973</v>
+        <v>3.99697279930115</v>
       </c>
       <c r="H829" t="n">
         <v>5363</v>
@@ -24439,7 +24439,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>4.30659770965576</v>
+        <v>4.3065972328186</v>
       </c>
       <c r="H830" t="n">
         <v>13944</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H831" t="n">
         <v>8663</v>
@@ -24526,7 +24526,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H833" t="n">
         <v>15658</v>
@@ -24613,7 +24613,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H836" t="n">
         <v>10141</v>
@@ -24671,7 +24671,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G838" t="n">
-        <v>3.68734836578369</v>
+        <v>3.68734812736511</v>
       </c>
       <c r="H838" t="n">
         <v>2963</v>
@@ -24700,7 +24700,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H839" t="n">
         <v>15833</v>
@@ -24758,7 +24758,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.86561679840088</v>
+        <v>3.8656165599823</v>
       </c>
       <c r="H841" t="n">
         <v>3553</v>
@@ -24787,7 +24787,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H842" t="n">
         <v>5470</v>
@@ -24874,7 +24874,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.92191219329834</v>
+        <v>3.92191243171692</v>
       </c>
       <c r="H845" t="n">
         <v>3484</v>
@@ -25019,7 +25019,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G850" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H850" t="n">
         <v>3030</v>
@@ -25106,7 +25106,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H853" t="n">
         <v>2333</v>
@@ -25164,7 +25164,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.81870412826538</v>
+        <v>3.81870436668396</v>
       </c>
       <c r="H855" t="n">
         <v>12319</v>
@@ -25280,7 +25280,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H859" t="n">
         <v>7062</v>
@@ -25338,7 +25338,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H861" t="n">
         <v>9293</v>
@@ -25454,7 +25454,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G865" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H865" t="n">
         <v>808</v>
@@ -25512,7 +25512,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H867" t="n">
         <v>611</v>
@@ -25570,7 +25570,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G869" t="n">
-        <v>3.92191219329834</v>
+        <v>3.92191243171692</v>
       </c>
       <c r="H869" t="n">
         <v>13902</v>
@@ -25657,7 +25657,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.92191219329834</v>
+        <v>3.92191243171692</v>
       </c>
       <c r="H872" t="n">
         <v>570</v>
@@ -25802,7 +25802,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H877" t="n">
         <v>5546</v>
@@ -25918,7 +25918,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G881" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H881" t="n">
         <v>10744</v>
@@ -25976,7 +25976,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G883" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H883" t="n">
         <v>50</v>
@@ -26005,7 +26005,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H884" t="n">
         <v>2574</v>
@@ -26034,7 +26034,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G885" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H885" t="n">
         <v>3925</v>
@@ -26063,7 +26063,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G886" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H886" t="n">
         <v>1154</v>
@@ -26092,7 +26092,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H887" t="n">
         <v>6727</v>
@@ -26179,7 +26179,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G890" t="n">
-        <v>3.66858315467834</v>
+        <v>3.66858291625977</v>
       </c>
       <c r="H890" t="n">
         <v>6569</v>
@@ -26208,7 +26208,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G891" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H891" t="n">
         <v>1081</v>
@@ -26295,7 +26295,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H894" t="n">
         <v>1455</v>
@@ -26353,7 +26353,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H896" t="n">
         <v>4606</v>
@@ -26440,7 +26440,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99697303771973</v>
+        <v>3.99697279930115</v>
       </c>
       <c r="H899" t="n">
         <v>4331</v>
@@ -26469,7 +26469,7 @@
         <v>4.25</v>
       </c>
       <c r="G900" t="n">
-        <v>3.98759055137634</v>
+        <v>3.98759031295776</v>
       </c>
       <c r="H900" t="n">
         <v>477</v>
@@ -26498,7 +26498,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G901" t="n">
-        <v>3.97820734977722</v>
+        <v>3.9782075881958</v>
       </c>
       <c r="H901" t="n">
         <v>160</v>
@@ -26556,7 +26556,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>3.86561679840088</v>
+        <v>3.8656165599823</v>
       </c>
       <c r="H903" t="n">
         <v>7451</v>
@@ -26585,7 +26585,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G904" t="n">
-        <v>3.86561679840088</v>
+        <v>3.8656165599823</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -26643,7 +26643,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H906" t="n">
         <v>7171</v>
@@ -26846,7 +26846,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H913" t="n">
         <v>5572</v>
@@ -26875,7 +26875,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G914" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H914" t="n">
         <v>2431</v>
@@ -26904,7 +26904,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G915" t="n">
-        <v>3.81870412826538</v>
+        <v>3.81870436668396</v>
       </c>
       <c r="H915" t="n">
         <v>694</v>
@@ -26933,7 +26933,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81870412826538</v>
+        <v>3.81870436668396</v>
       </c>
       <c r="H916" t="n">
         <v>6079</v>
@@ -26962,7 +26962,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H917" t="n">
         <v>1682</v>
@@ -27020,7 +27020,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G919" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H919" t="n">
         <v>172</v>
@@ -27078,7 +27078,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G921" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H921" t="n">
         <v>3356</v>
@@ -27136,7 +27136,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G923" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H923" t="n">
         <v>10267</v>
@@ -27165,7 +27165,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H924" t="n">
         <v>2845</v>
@@ -27194,7 +27194,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.8562343120575</v>
+        <v>3.85623455047607</v>
       </c>
       <c r="H925" t="n">
         <v>6744</v>
@@ -27223,7 +27223,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G926" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H926" t="n">
         <v>81918</v>
@@ -27252,7 +27252,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H927" t="n">
         <v>16501</v>
@@ -27281,7 +27281,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>4.10018110275269</v>
+        <v>4.10018062591553</v>
       </c>
       <c r="H928" t="n">
         <v>19219</v>
@@ -27310,7 +27310,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G929" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H929" t="n">
         <v>7657</v>
@@ -27339,7 +27339,7 @@
         <v>4.25</v>
       </c>
       <c r="G930" t="n">
-        <v>3.98759055137634</v>
+        <v>3.98759031295776</v>
       </c>
       <c r="H930" t="n">
         <v>18877</v>
@@ -27397,7 +27397,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H932" t="n">
         <v>12772</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.92191219329834</v>
+        <v>3.92191243171692</v>
       </c>
       <c r="H934" t="n">
         <v>1187</v>
@@ -27484,7 +27484,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G935" t="n">
-        <v>3.96882510185242</v>
+        <v>3.96882486343384</v>
       </c>
       <c r="H935" t="n">
         <v>193</v>
@@ -27513,7 +27513,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G936" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H936" t="n">
         <v>1816</v>
@@ -27687,7 +27687,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>3.99697303771973</v>
+        <v>3.99697279930115</v>
       </c>
       <c r="H942" t="n">
         <v>4920</v>
@@ -27774,7 +27774,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H945" t="n">
         <v>1416</v>
@@ -27803,7 +27803,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G946" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H946" t="n">
         <v>5443</v>
@@ -27832,7 +27832,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H947" t="n">
         <v>1999</v>
@@ -27948,7 +27948,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>4.16585874557495</v>
+        <v>4.16585922241211</v>
       </c>
       <c r="H951" t="n">
         <v>2435</v>
@@ -28093,7 +28093,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.16585874557495</v>
+        <v>4.16585922241211</v>
       </c>
       <c r="H956" t="n">
         <v>2077</v>
@@ -28122,7 +28122,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.14709424972534</v>
+        <v>4.14709377288818</v>
       </c>
       <c r="H957" t="n">
         <v>2834</v>
@@ -28151,7 +28151,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G958" t="n">
-        <v>4.15647602081299</v>
+        <v>4.15647649765015</v>
       </c>
       <c r="H958" t="n">
         <v>1651</v>
@@ -28267,7 +28267,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G962" t="n">
-        <v>4.15647602081299</v>
+        <v>4.15647649765015</v>
       </c>
       <c r="H962" t="n">
         <v>1164</v>
@@ -38945,6 +38945,35 @@
         <v>6583</v>
       </c>
       <c r="I1330" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1331" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1331" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="E1331" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="H1331" t="n">
+        <v>10821</v>
+      </c>
+      <c r="I1331" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0834789276123</v>
+        <v>3.08347916603088</v>
       </c>
       <c r="H2" t="n">
         <v>561784</v>
@@ -456,7 +456,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11975502967834</v>
+        <v>3.11975526809692</v>
       </c>
       <c r="H3" t="n">
         <v>105419</v>
@@ -514,7 +514,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161709785461</v>
+        <v>3.10161733627319</v>
       </c>
       <c r="H5" t="n">
         <v>23147</v>
@@ -572,7 +572,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>3.292067527771</v>
+        <v>3.29206728935242</v>
       </c>
       <c r="H7" t="n">
         <v>292211</v>
@@ -601,7 +601,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H8" t="n">
         <v>720993</v>
@@ -630,7 +630,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.56867337226868</v>
+        <v>3.56867361068726</v>
       </c>
       <c r="H9" t="n">
         <v>292968</v>
@@ -659,7 +659,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H10" t="n">
         <v>160329</v>
@@ -688,7 +688,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H11" t="n">
         <v>65268</v>
@@ -717,7 +717,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>3.44170689582825</v>
+        <v>3.44170665740967</v>
       </c>
       <c r="H12" t="n">
         <v>34000</v>
@@ -775,7 +775,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H14" t="n">
         <v>18667</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H16" t="n">
         <v>44813</v>
@@ -862,7 +862,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H17" t="n">
         <v>150547</v>
@@ -891,7 +891,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924401283264</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H18" t="n">
         <v>290894</v>
@@ -1036,7 +1036,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H23" t="n">
         <v>29141</v>
@@ -1094,7 +1094,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.89515924453735</v>
+        <v>3.89515972137451</v>
       </c>
       <c r="H25" t="n">
         <v>186140</v>
@@ -1123,7 +1123,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876317024231</v>
+        <v>3.90876293182373</v>
       </c>
       <c r="H26" t="n">
         <v>85789</v>
@@ -1210,7 +1210,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993414878845</v>
+        <v>3.79993462562561</v>
       </c>
       <c r="H29" t="n">
         <v>38465</v>
@@ -1268,7 +1268,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377801895142</v>
+        <v>3.71377825737</v>
       </c>
       <c r="H31" t="n">
         <v>31484</v>
@@ -1297,7 +1297,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H32" t="n">
         <v>14654</v>
@@ -1326,7 +1326,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H33" t="n">
         <v>18869</v>
@@ -1355,7 +1355,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H34" t="n">
         <v>5781</v>
@@ -1471,7 +1471,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365852355957</v>
+        <v>3.76365828514099</v>
       </c>
       <c r="H38" t="n">
         <v>28609</v>
@@ -1587,7 +1587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H42" t="n">
         <v>23606</v>
@@ -1616,7 +1616,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H43" t="n">
         <v>10910</v>
@@ -1674,7 +1674,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H45" t="n">
         <v>2007</v>
@@ -1703,7 +1703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H46" t="n">
         <v>6914</v>
@@ -1819,7 +1819,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365852355957</v>
+        <v>3.76365828514099</v>
       </c>
       <c r="H50" t="n">
         <v>9599</v>
@@ -1848,7 +1848,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.8090033531189</v>
+        <v>3.80900311470032</v>
       </c>
       <c r="H51" t="n">
         <v>25429</v>
@@ -1877,7 +1877,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H52" t="n">
         <v>919</v>
@@ -1906,7 +1906,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.74552035331726</v>
+        <v>3.7455198764801</v>
       </c>
       <c r="H53" t="n">
         <v>5908</v>
@@ -2022,7 +2022,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H57" t="n">
         <v>18537</v>
@@ -2051,7 +2051,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H58" t="n">
         <v>4003</v>
@@ -2080,7 +2080,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H59" t="n">
         <v>6637</v>
@@ -2109,7 +2109,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936398506165</v>
+        <v>3.65936374664307</v>
       </c>
       <c r="H60" t="n">
         <v>5790</v>
@@ -2138,7 +2138,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>3.64576077461243</v>
+        <v>3.64576053619385</v>
       </c>
       <c r="H61" t="n">
         <v>93456</v>
@@ -2167,7 +2167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.7001748085022</v>
+        <v>3.70017504692078</v>
       </c>
       <c r="H62" t="n">
         <v>8191</v>
@@ -2196,7 +2196,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284746170044</v>
+        <v>3.72284770011902</v>
       </c>
       <c r="H63" t="n">
         <v>20100</v>
@@ -2254,7 +2254,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>3.68203687667847</v>
+        <v>3.68203663825989</v>
       </c>
       <c r="H65" t="n">
         <v>13936</v>
@@ -2312,7 +2312,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110584259033</v>
+        <v>3.69110608100891</v>
       </c>
       <c r="H67" t="n">
         <v>3242</v>
@@ -2399,7 +2399,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>3.70470929145813</v>
+        <v>3.70470952987671</v>
       </c>
       <c r="H70" t="n">
         <v>15982</v>
@@ -2428,7 +2428,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.68203687667847</v>
+        <v>3.68203663825989</v>
       </c>
       <c r="H71" t="n">
         <v>9106</v>
@@ -2457,7 +2457,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936398506165</v>
+        <v>3.65936374664307</v>
       </c>
       <c r="H72" t="n">
         <v>6928</v>
@@ -2486,7 +2486,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110584259033</v>
+        <v>3.69110608100891</v>
       </c>
       <c r="H73" t="n">
         <v>6007</v>
@@ -2544,7 +2544,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H75" t="n">
         <v>10828</v>
@@ -2573,7 +2573,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H76" t="n">
         <v>9217</v>
@@ -2602,7 +2602,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H77" t="n">
         <v>10457</v>
@@ -2631,7 +2631,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.7001748085022</v>
+        <v>3.70017504692078</v>
       </c>
       <c r="H78" t="n">
         <v>36913</v>
@@ -2660,7 +2660,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H79" t="n">
         <v>16654</v>
@@ -2689,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762260437012</v>
+        <v>3.62762236595154</v>
       </c>
       <c r="H80" t="n">
         <v>1294</v>
@@ -2718,7 +2718,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H81" t="n">
         <v>14163</v>
@@ -2747,7 +2747,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320785522461</v>
+        <v>3.57320809364319</v>
       </c>
       <c r="H82" t="n">
         <v>5877</v>
@@ -2863,7 +2863,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729190826416</v>
+        <v>3.38729214668274</v>
       </c>
       <c r="H86" t="n">
         <v>4796</v>
@@ -2892,7 +2892,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.45984506607056</v>
+        <v>3.45984482765198</v>
       </c>
       <c r="H87" t="n">
         <v>56731</v>
@@ -2921,7 +2921,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47798299789429</v>
+        <v>3.47798275947571</v>
       </c>
       <c r="H88" t="n">
         <v>5844</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.44624137878418</v>
+        <v>3.44624090194702</v>
       </c>
       <c r="H89" t="n">
         <v>5063</v>
@@ -3008,7 +3008,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.47798299789429</v>
+        <v>3.47798275947571</v>
       </c>
       <c r="H91" t="n">
         <v>7413</v>
@@ -3066,7 +3066,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.48251724243164</v>
+        <v>3.48251748085022</v>
       </c>
       <c r="H93" t="n">
         <v>7085</v>
@@ -3095,7 +3095,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H94" t="n">
         <v>14502</v>
@@ -3124,7 +3124,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>3.35555100440979</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H95" t="n">
         <v>19856</v>
@@ -3153,7 +3153,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>3.3238091468811</v>
+        <v>3.32380890846252</v>
       </c>
       <c r="H96" t="n">
         <v>1326</v>
@@ -3182,7 +3182,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531034469604</v>
+        <v>3.45531010627747</v>
       </c>
       <c r="H97" t="n">
         <v>13724</v>
@@ -3240,7 +3240,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>3.42356872558594</v>
+        <v>3.42356896400452</v>
       </c>
       <c r="H99" t="n">
         <v>4056</v>
@@ -3298,7 +3298,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996527671814</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H101" t="n">
         <v>3157</v>
@@ -3327,7 +3327,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996527671814</v>
+        <v>3.40996503829956</v>
       </c>
       <c r="H102" t="n">
         <v>340</v>
@@ -3385,7 +3385,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>3.35555100440979</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H104" t="n">
         <v>6856</v>
@@ -3414,7 +3414,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35555100440979</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H105" t="n">
         <v>4111</v>
@@ -3472,7 +3472,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48251724243164</v>
+        <v>3.48251748085022</v>
       </c>
       <c r="H107" t="n">
         <v>5104</v>
@@ -3559,7 +3559,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948419570923</v>
+        <v>3.60948395729065</v>
       </c>
       <c r="H110" t="n">
         <v>33451</v>
@@ -3588,7 +3588,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H111" t="n">
         <v>13196</v>
@@ -3617,7 +3617,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.4961211681366</v>
+        <v>3.49612092971802</v>
       </c>
       <c r="H112" t="n">
         <v>28788</v>
@@ -3675,7 +3675,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>3.55960440635681</v>
+        <v>3.55960464477539</v>
       </c>
       <c r="H114" t="n">
         <v>4027</v>
@@ -3704,7 +3704,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H115" t="n">
         <v>8785</v>
@@ -3733,7 +3733,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H116" t="n">
         <v>1006</v>
@@ -3791,7 +3791,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H118" t="n">
         <v>29715</v>
@@ -3820,7 +3820,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>3.58227705955505</v>
+        <v>3.58227729797363</v>
       </c>
       <c r="H119" t="n">
         <v>35244</v>
@@ -3849,7 +3849,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>3.50972437858582</v>
+        <v>3.50972461700439</v>
       </c>
       <c r="H120" t="n">
         <v>9381</v>
@@ -3878,7 +3878,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.4961211681366</v>
+        <v>3.49612092971802</v>
       </c>
       <c r="H121" t="n">
         <v>6937</v>
@@ -3936,7 +3936,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287787437439</v>
+        <v>3.33287811279297</v>
       </c>
       <c r="H123" t="n">
         <v>13328</v>
@@ -3994,7 +3994,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32834339141846</v>
+        <v>3.32834362983704</v>
       </c>
       <c r="H125" t="n">
         <v>9558</v>
@@ -4052,7 +4052,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H127" t="n">
         <v>3094</v>
@@ -4226,7 +4226,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404956817627</v>
+        <v>3.22404932975769</v>
       </c>
       <c r="H133" t="n">
         <v>4602</v>
@@ -4284,7 +4284,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30113649368286</v>
+        <v>3.30113625526428</v>
       </c>
       <c r="H135" t="n">
         <v>17559</v>
@@ -4313,7 +4313,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>3.31927466392517</v>
+        <v>3.31927442550659</v>
       </c>
       <c r="H136" t="n">
         <v>21037</v>
@@ -4371,7 +4371,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020569801331</v>
+        <v>3.31020522117615</v>
       </c>
       <c r="H138" t="n">
         <v>2087</v>
@@ -4400,7 +4400,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>3.35555100440979</v>
+        <v>3.35555076599121</v>
       </c>
       <c r="H139" t="n">
         <v>353762</v>
@@ -4429,7 +4429,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>3.55506992340088</v>
+        <v>3.55507016181946</v>
       </c>
       <c r="H140" t="n">
         <v>17360</v>
@@ -4545,7 +4545,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>3.30113649368286</v>
+        <v>3.30113625526428</v>
       </c>
       <c r="H144" t="n">
         <v>9061</v>
@@ -4574,7 +4574,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G145" t="n">
-        <v>3.31927466392517</v>
+        <v>3.31927442550659</v>
       </c>
       <c r="H145" t="n">
         <v>2079</v>
@@ -4632,7 +4632,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G147" t="n">
-        <v>3.2285840511322</v>
+        <v>3.22858381271362</v>
       </c>
       <c r="H147" t="n">
         <v>5516</v>
@@ -4690,7 +4690,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.14696216583252</v>
+        <v>3.1469624042511</v>
       </c>
       <c r="H149" t="n">
         <v>11513</v>
@@ -4719,7 +4719,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>3.25125646591187</v>
+        <v>3.25125670433044</v>
       </c>
       <c r="H150" t="n">
         <v>5307</v>
@@ -4748,7 +4748,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510057449341</v>
+        <v>3.16510033607483</v>
       </c>
       <c r="H151" t="n">
         <v>218</v>
@@ -4835,7 +4835,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570115089417</v>
+        <v>2.91570138931274</v>
       </c>
       <c r="H154" t="n">
         <v>1770</v>
@@ -4864,7 +4864,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H155" t="n">
         <v>5951</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H156" t="n">
         <v>10379</v>
@@ -4922,7 +4922,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756345748901</v>
+        <v>2.89756321907043</v>
       </c>
       <c r="H157" t="n">
         <v>4634</v>
@@ -4951,7 +4951,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.96104669570923</v>
+        <v>2.96104693412781</v>
       </c>
       <c r="H158" t="n">
         <v>1286</v>
@@ -5096,7 +5096,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H163" t="n">
         <v>1018</v>
@@ -5154,7 +5154,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G165" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H165" t="n">
         <v>3774</v>
@@ -5183,7 +5183,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G166" t="n">
-        <v>3.0834789276123</v>
+        <v>3.08347916603088</v>
       </c>
       <c r="H166" t="n">
         <v>6067</v>
@@ -5241,7 +5241,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>3.21044588088989</v>
+        <v>3.21044564247131</v>
       </c>
       <c r="H168" t="n">
         <v>11151</v>
@@ -5270,7 +5270,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.37368869781494</v>
+        <v>3.37368893623352</v>
       </c>
       <c r="H169" t="n">
         <v>87762</v>
@@ -5328,7 +5328,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615158081055</v>
+        <v>3.10615181922913</v>
       </c>
       <c r="H171" t="n">
         <v>59616</v>
@@ -5357,7 +5357,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>3.11522054672241</v>
+        <v>3.11522078514099</v>
       </c>
       <c r="H172" t="n">
         <v>8398</v>
@@ -5386,7 +5386,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G173" t="n">
-        <v>3.1605658531189</v>
+        <v>3.16056561470032</v>
       </c>
       <c r="H173" t="n">
         <v>546</v>
@@ -5415,7 +5415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.0834789276123</v>
+        <v>3.08347916603088</v>
       </c>
       <c r="H174" t="n">
         <v>4116</v>
@@ -5444,7 +5444,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H175" t="n">
         <v>7513</v>
@@ -5502,7 +5502,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H177" t="n">
         <v>9793</v>
@@ -5531,7 +5531,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.02453017234802</v>
+        <v>3.02452993392944</v>
       </c>
       <c r="H178" t="n">
         <v>1198</v>
@@ -5589,7 +5589,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906441688538</v>
+        <v>3.02906465530396</v>
       </c>
       <c r="H180" t="n">
         <v>998</v>
@@ -5705,7 +5705,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266858100891</v>
+        <v>3.04266810417175</v>
       </c>
       <c r="H184" t="n">
         <v>656</v>
@@ -5763,7 +5763,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01092648506165</v>
+        <v>3.01092624664307</v>
       </c>
       <c r="H186" t="n">
         <v>3889</v>
@@ -5908,7 +5908,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.0834789276123</v>
+        <v>3.08347916603088</v>
       </c>
       <c r="H191" t="n">
         <v>12796</v>
@@ -5937,7 +5937,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627155303955</v>
+        <v>3.05627179145813</v>
       </c>
       <c r="H192" t="n">
         <v>9528</v>
@@ -5995,7 +5995,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.06534099578857</v>
+        <v>3.06534123420715</v>
       </c>
       <c r="H194" t="n">
         <v>924</v>
@@ -6169,7 +6169,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489080429077</v>
+        <v>2.87489056587219</v>
       </c>
       <c r="H200" t="n">
         <v>7430</v>
@@ -6198,7 +6198,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G201" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H201" t="n">
         <v>7306</v>
@@ -6256,7 +6256,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>2.95651245117188</v>
+        <v>2.9565122127533</v>
       </c>
       <c r="H203" t="n">
         <v>1563</v>
@@ -6314,7 +6314,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011566162109</v>
+        <v>2.97011613845825</v>
       </c>
       <c r="H205" t="n">
         <v>4097</v>
@@ -6488,7 +6488,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648180007935</v>
+        <v>3.34648156166077</v>
       </c>
       <c r="H211" t="n">
         <v>53801</v>
@@ -6517,7 +6517,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.36461973190308</v>
+        <v>3.36461997032166</v>
       </c>
       <c r="H212" t="n">
         <v>17177</v>
@@ -6546,7 +6546,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765277862549</v>
+        <v>3.23765301704407</v>
       </c>
       <c r="H213" t="n">
         <v>4683</v>
@@ -6575,7 +6575,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753280639648</v>
+        <v>3.28753304481506</v>
       </c>
       <c r="H214" t="n">
         <v>1310</v>
@@ -6604,7 +6604,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416930198669</v>
+        <v>3.17416954040527</v>
       </c>
       <c r="H215" t="n">
         <v>6340</v>
@@ -6633,7 +6633,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>3.11975502967834</v>
+        <v>3.11975526809692</v>
       </c>
       <c r="H216" t="n">
         <v>5488</v>
@@ -6662,7 +6662,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>3.11522054672241</v>
+        <v>3.11522078514099</v>
       </c>
       <c r="H217" t="n">
         <v>1846</v>
@@ -6691,7 +6691,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.1605658531189</v>
+        <v>3.16056561470032</v>
       </c>
       <c r="H218" t="n">
         <v>4799</v>
@@ -6720,7 +6720,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416930198669</v>
+        <v>3.17416954040527</v>
       </c>
       <c r="H219" t="n">
         <v>8838</v>
@@ -6778,7 +6778,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.92930507659912</v>
+        <v>2.9293053150177</v>
       </c>
       <c r="H221" t="n">
         <v>10002</v>
@@ -6865,7 +6865,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035584449768</v>
+        <v>2.87035608291626</v>
       </c>
       <c r="H224" t="n">
         <v>4992</v>
@@ -6894,7 +6894,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570115089417</v>
+        <v>2.91570138931274</v>
       </c>
       <c r="H225" t="n">
         <v>3170</v>
@@ -6923,7 +6923,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G226" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H226" t="n">
         <v>8814</v>
@@ -6981,7 +6981,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H228" t="n">
         <v>593</v>
@@ -7010,7 +7010,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489080429077</v>
+        <v>2.87489056587219</v>
       </c>
       <c r="H229" t="n">
         <v>389</v>
@@ -7068,7 +7068,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H231" t="n">
         <v>1012</v>
@@ -7213,7 +7213,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675287246704</v>
+        <v>2.85675239562988</v>
       </c>
       <c r="H236" t="n">
         <v>11979</v>
@@ -7242,7 +7242,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H237" t="n">
         <v>3487</v>
@@ -7271,7 +7271,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H238" t="n">
         <v>16491</v>
@@ -7300,7 +7300,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H239" t="n">
         <v>10412</v>
@@ -7329,7 +7329,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.88395977020264</v>
+        <v>2.88396000862122</v>
       </c>
       <c r="H240" t="n">
         <v>17990</v>
@@ -7416,7 +7416,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>2.77513122558594</v>
+        <v>2.77513098716736</v>
       </c>
       <c r="H243" t="n">
         <v>3305</v>
@@ -7445,7 +7445,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H244" t="n">
         <v>4956</v>
@@ -7532,7 +7532,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H247" t="n">
         <v>5286</v>
@@ -7561,7 +7561,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H248" t="n">
         <v>1003</v>
@@ -7590,7 +7590,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.83407998085022</v>
+        <v>2.8340802192688</v>
       </c>
       <c r="H249" t="n">
         <v>625</v>
@@ -7619,7 +7619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H250" t="n">
         <v>11443</v>
@@ -7706,7 +7706,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H253" t="n">
         <v>1884</v>
@@ -7735,7 +7735,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>2.7025785446167</v>
+        <v>2.70257878303528</v>
       </c>
       <c r="H254" t="n">
         <v>1758</v>
@@ -7764,7 +7764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H255" t="n">
         <v>18878</v>
@@ -7793,7 +7793,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.78419995307922</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H256" t="n">
         <v>2600</v>
@@ -7822,7 +7822,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350934028625</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H257" t="n">
         <v>8062</v>
@@ -7851,7 +7851,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071671485901</v>
+        <v>2.72071647644043</v>
       </c>
       <c r="H258" t="n">
         <v>1704</v>
@@ -7880,7 +7880,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.69804406166077</v>
+        <v>2.69804430007935</v>
       </c>
       <c r="H259" t="n">
         <v>16864</v>
@@ -7938,7 +7938,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H261" t="n">
         <v>2757</v>
@@ -7967,7 +7967,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H262" t="n">
         <v>5847</v>
@@ -8054,7 +8054,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456082344055</v>
+        <v>2.63456058502197</v>
       </c>
       <c r="H265" t="n">
         <v>9259</v>
@@ -8112,7 +8112,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.6753716468811</v>
+        <v>2.67537140846252</v>
       </c>
       <c r="H267" t="n">
         <v>735</v>
@@ -8170,7 +8170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H269" t="n">
         <v>1163</v>
@@ -8199,7 +8199,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H270" t="n">
         <v>9817</v>
@@ -8228,7 +8228,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G271" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H271" t="n">
         <v>23246</v>
@@ -8257,7 +8257,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.5801465511322</v>
+        <v>2.58014631271362</v>
       </c>
       <c r="H272" t="n">
         <v>7178</v>
@@ -8402,7 +8402,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945569992065</v>
+        <v>2.48945546150208</v>
       </c>
       <c r="H277" t="n">
         <v>995</v>
@@ -8431,7 +8431,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>2.45317959785461</v>
+        <v>2.45317935943604</v>
       </c>
       <c r="H278" t="n">
         <v>2892</v>
@@ -8489,7 +8489,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062715530396</v>
+        <v>2.38062739372253</v>
       </c>
       <c r="H280" t="n">
         <v>7350</v>
@@ -8518,7 +8518,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.35342025756836</v>
+        <v>2.3534197807312</v>
       </c>
       <c r="H281" t="n">
         <v>44116</v>
@@ -8547,7 +8547,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32621264457703</v>
+        <v>2.32621288299561</v>
       </c>
       <c r="H282" t="n">
         <v>4891</v>
@@ -8663,7 +8663,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912571907043</v>
+        <v>2.24912595748901</v>
       </c>
       <c r="H286" t="n">
         <v>3503</v>
@@ -8808,7 +8808,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>2.11308979988098</v>
+        <v>2.11309003829956</v>
       </c>
       <c r="H291" t="n">
         <v>2789</v>
@@ -8837,7 +8837,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.1357626914978</v>
+        <v>2.13576245307922</v>
       </c>
       <c r="H292" t="n">
         <v>9540</v>
@@ -8866,7 +8866,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.33074712753296</v>
+        <v>2.33074736595154</v>
       </c>
       <c r="H293" t="n">
         <v>4108</v>
@@ -8924,7 +8924,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.22645306587219</v>
+        <v>2.22645330429077</v>
       </c>
       <c r="H295" t="n">
         <v>7856</v>
@@ -9098,7 +9098,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33074712753296</v>
+        <v>2.33074736595154</v>
       </c>
       <c r="H301" t="n">
         <v>9820</v>
@@ -9156,7 +9156,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H303" t="n">
         <v>8916</v>
@@ -9272,7 +9272,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.43050718307495</v>
+        <v>2.43050694465637</v>
       </c>
       <c r="H307" t="n">
         <v>5406</v>
@@ -9301,7 +9301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H308" t="n">
         <v>371</v>
@@ -9330,7 +9330,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H309" t="n">
         <v>7036</v>
@@ -9359,7 +9359,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G314" t="n">
-        <v>2.48038649559021</v>
+        <v>2.48038673400879</v>
       </c>
       <c r="H314" t="n">
         <v>4439</v>
@@ -9504,7 +9504,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H315" t="n">
         <v>2887</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H326" t="n">
         <v>10875</v>
@@ -9852,7 +9852,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>2.43050718307495</v>
+        <v>2.43050694465637</v>
       </c>
       <c r="H327" t="n">
         <v>902</v>
@@ -9881,7 +9881,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H328" t="n">
         <v>9578</v>
@@ -9910,7 +9910,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143797874451</v>
+        <v>2.42143774032593</v>
       </c>
       <c r="H329" t="n">
         <v>4763</v>
@@ -9968,7 +9968,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.35342025756836</v>
+        <v>2.3534197807312</v>
       </c>
       <c r="H331" t="n">
         <v>12852</v>
@@ -10055,7 +10055,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.29447102546692</v>
+        <v>2.2944712638855</v>
       </c>
       <c r="H334" t="n">
         <v>2916</v>
@@ -10113,7 +10113,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.30807495117188</v>
+        <v>2.3080747127533</v>
       </c>
       <c r="H336" t="n">
         <v>989</v>
@@ -10229,7 +10229,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993678092957</v>
+        <v>2.28993654251099</v>
       </c>
       <c r="H340" t="n">
         <v>31736</v>
@@ -10258,7 +10258,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005699157715</v>
       </c>
       <c r="H341" t="n">
         <v>4266</v>
@@ -10287,7 +10287,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912571907043</v>
+        <v>2.24912595748901</v>
       </c>
       <c r="H342" t="n">
         <v>12825</v>
@@ -10461,7 +10461,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H348" t="n">
         <v>518</v>
@@ -10490,7 +10490,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>2.32621264457703</v>
+        <v>2.32621288299561</v>
       </c>
       <c r="H349" t="n">
         <v>5793</v>
@@ -10519,7 +10519,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G350" t="n">
-        <v>2.32621264457703</v>
+        <v>2.32621288299561</v>
       </c>
       <c r="H350" t="n">
         <v>68</v>
@@ -10548,7 +10548,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179861068726</v>
+        <v>2.27179837226868</v>
       </c>
       <c r="H351" t="n">
         <v>4619</v>
@@ -10577,7 +10577,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G352" t="n">
-        <v>2.45317959785461</v>
+        <v>2.45317935943604</v>
       </c>
       <c r="H352" t="n">
         <v>4007</v>
@@ -10751,7 +10751,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G358" t="n">
-        <v>2.26272964477539</v>
+        <v>2.26272940635681</v>
       </c>
       <c r="H358" t="n">
         <v>5565</v>
@@ -10809,7 +10809,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>2.2445912361145</v>
+        <v>2.24459147453308</v>
       </c>
       <c r="H360" t="n">
         <v>1525</v>
@@ -10838,7 +10838,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>2.2445912361145</v>
+        <v>2.24459147453308</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005675315857</v>
+        <v>2.24005699157715</v>
       </c>
       <c r="H362" t="n">
         <v>1115</v>
@@ -11041,7 +11041,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G368" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H368" t="n">
         <v>2162</v>
@@ -11070,7 +11070,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>2.44411063194275</v>
+        <v>2.44411039352417</v>
       </c>
       <c r="H369" t="n">
         <v>1383</v>
@@ -11186,7 +11186,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.40330004692078</v>
+        <v>2.4032998085022</v>
       </c>
       <c r="H373" t="n">
         <v>26801</v>
@@ -11215,7 +11215,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.38969612121582</v>
+        <v>2.3896963596344</v>
       </c>
       <c r="H374" t="n">
         <v>7617</v>
@@ -11244,7 +11244,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.40330004692078</v>
+        <v>2.4032998085022</v>
       </c>
       <c r="H375" t="n">
         <v>8213</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H376" t="n">
         <v>7974</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H379" t="n">
         <v>125340</v>
@@ -11389,7 +11389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H380" t="n">
         <v>15968</v>
@@ -11418,7 +11418,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.49852514266968</v>
+        <v>2.4985249042511</v>
       </c>
       <c r="H381" t="n">
         <v>3626</v>
@@ -11447,7 +11447,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H382" t="n">
         <v>4545</v>
@@ -11476,7 +11476,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>2.56200861930847</v>
+        <v>2.56200838088989</v>
       </c>
       <c r="H383" t="n">
         <v>1921</v>
@@ -11592,7 +11592,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H387" t="n">
         <v>400</v>
@@ -11621,7 +11621,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H388" t="n">
         <v>9739</v>
@@ -11650,7 +11650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H389" t="n">
         <v>5695</v>
@@ -11679,7 +11679,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H390" t="n">
         <v>3704</v>
@@ -11737,7 +11737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H392" t="n">
         <v>8970</v>
@@ -11766,7 +11766,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H393" t="n">
         <v>258</v>
@@ -11853,7 +11853,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666283607483</v>
+        <v>2.51666331291199</v>
       </c>
       <c r="H396" t="n">
         <v>67390</v>
@@ -11882,7 +11882,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H397" t="n">
         <v>6517</v>
@@ -11969,7 +11969,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840445518494</v>
+        <v>2.54840469360352</v>
       </c>
       <c r="H400" t="n">
         <v>6772</v>
@@ -11998,7 +11998,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840445518494</v>
+        <v>2.54840469360352</v>
       </c>
       <c r="H401" t="n">
         <v>25644</v>
@@ -12027,7 +12027,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H402" t="n">
         <v>27847</v>
@@ -12056,7 +12056,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G403" t="n">
-        <v>2.71618223190308</v>
+        <v>2.7161819934845</v>
       </c>
       <c r="H403" t="n">
         <v>27202</v>
@@ -12085,7 +12085,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H404" t="n">
         <v>20579</v>
@@ -12230,7 +12230,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H409" t="n">
         <v>3350</v>
@@ -12259,7 +12259,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H410" t="n">
         <v>4500</v>
@@ -12288,7 +12288,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H411" t="n">
         <v>2860</v>
@@ -12404,7 +12404,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573204040527</v>
+        <v>2.52573251724243</v>
       </c>
       <c r="H415" t="n">
         <v>8421</v>
@@ -12433,7 +12433,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H416" t="n">
         <v>1088</v>
@@ -12607,7 +12607,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H422" t="n">
         <v>7693</v>
@@ -12636,7 +12636,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G423" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H423" t="n">
         <v>7526</v>
@@ -12665,7 +12665,7 @@
         <v>2.875</v>
       </c>
       <c r="G424" t="n">
-        <v>2.60735368728638</v>
+        <v>2.6073534488678</v>
       </c>
       <c r="H424" t="n">
         <v>1280</v>
@@ -12781,7 +12781,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G428" t="n">
-        <v>2.56200861930847</v>
+        <v>2.56200838088989</v>
       </c>
       <c r="H428" t="n">
         <v>30098</v>
@@ -12868,7 +12868,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.4395763874054</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H431" t="n">
         <v>2176</v>
@@ -12955,7 +12955,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.5121283531189</v>
+        <v>2.51212859153748</v>
       </c>
       <c r="H434" t="n">
         <v>10353</v>
@@ -12984,7 +12984,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G435" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H435" t="n">
         <v>2214</v>
@@ -13158,7 +13158,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G441" t="n">
-        <v>2.60281872749329</v>
+        <v>2.60281896591187</v>
       </c>
       <c r="H441" t="n">
         <v>16239</v>
@@ -13216,7 +13216,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H443" t="n">
         <v>905</v>
@@ -13245,7 +13245,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H444" t="n">
         <v>305</v>
@@ -13274,7 +13274,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188817024231</v>
+        <v>2.61188840866089</v>
       </c>
       <c r="H445" t="n">
         <v>5437</v>
@@ -13303,7 +13303,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G446" t="n">
-        <v>2.59374976158142</v>
+        <v>2.59375</v>
       </c>
       <c r="H446" t="n">
         <v>2456</v>
@@ -13332,7 +13332,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G447" t="n">
-        <v>2.57561182975769</v>
+        <v>2.57561159133911</v>
       </c>
       <c r="H447" t="n">
         <v>1026</v>
@@ -13361,7 +13361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350934028625</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H448" t="n">
         <v>14662</v>
@@ -13390,7 +13390,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H449" t="n">
         <v>5650</v>
@@ -13448,7 +13448,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H451" t="n">
         <v>17368</v>
@@ -13477,7 +13477,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H452" t="n">
         <v>9599</v>
@@ -13506,7 +13506,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H453" t="n">
         <v>1381</v>
@@ -13535,7 +13535,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H454" t="n">
         <v>642</v>
@@ -13564,7 +13564,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G455" t="n">
-        <v>2.82047653198242</v>
+        <v>2.82047629356384</v>
       </c>
       <c r="H455" t="n">
         <v>22810</v>
@@ -13593,7 +13593,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.76606225967407</v>
+        <v>2.76606202125549</v>
       </c>
       <c r="H456" t="n">
         <v>17281</v>
@@ -13622,7 +13622,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164774894714</v>
+        <v>2.71164751052856</v>
       </c>
       <c r="H457" t="n">
         <v>267</v>
@@ -13709,7 +13709,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816451072693</v>
       </c>
       <c r="H460" t="n">
         <v>4577</v>
@@ -13738,7 +13738,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G461" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H461" t="n">
         <v>1854</v>
@@ -13796,7 +13796,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G463" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H463" t="n">
         <v>1249</v>
@@ -13883,7 +13883,7 @@
         <v>3</v>
       </c>
       <c r="G466" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H466" t="n">
         <v>2400</v>
@@ -13912,7 +13912,7 @@
         <v>3</v>
       </c>
       <c r="G467" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H467" t="n">
         <v>897</v>
@@ -13970,7 +13970,7 @@
         <v>3</v>
       </c>
       <c r="G469" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H469" t="n">
         <v>598</v>
@@ -13999,7 +13999,7 @@
         <v>3</v>
       </c>
       <c r="G470" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H471" t="n">
         <v>6971</v>
@@ -14057,7 +14057,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H472" t="n">
         <v>15161</v>
@@ -14086,7 +14086,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G473" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H473" t="n">
         <v>7200</v>
@@ -14115,7 +14115,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G474" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H474" t="n">
         <v>468</v>
@@ -14231,7 +14231,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G478" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H478" t="n">
         <v>21409</v>
@@ -14289,7 +14289,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G480" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H480" t="n">
         <v>6941</v>
@@ -14318,7 +14318,7 @@
         <v>2.75</v>
       </c>
       <c r="G481" t="n">
-        <v>2.53743958473206</v>
+        <v>2.53743982315063</v>
       </c>
       <c r="H481" t="n">
         <v>5639</v>
@@ -14376,7 +14376,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G483" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H483" t="n">
         <v>869</v>
@@ -14405,7 +14405,7 @@
         <v>2.75</v>
       </c>
       <c r="G484" t="n">
-        <v>2.53743958473206</v>
+        <v>2.53743982315063</v>
       </c>
       <c r="H484" t="n">
         <v>1915</v>
@@ -14463,7 +14463,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G486" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H486" t="n">
         <v>1200</v>
@@ -14521,7 +14521,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H488" t="n">
         <v>4646</v>
@@ -14550,7 +14550,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G489" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H489" t="n">
         <v>1637</v>
@@ -14579,7 +14579,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G490" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H490" t="n">
         <v>62146</v>
@@ -14608,7 +14608,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H491" t="n">
         <v>146750</v>
@@ -14637,7 +14637,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H492" t="n">
         <v>9831</v>
@@ -14666,7 +14666,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G494" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H494" t="n">
         <v>4238</v>
@@ -14724,7 +14724,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H495" t="n">
         <v>367</v>
@@ -14782,7 +14782,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G497" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H497" t="n">
         <v>1143</v>
@@ -14840,7 +14840,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G499" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H499" t="n">
         <v>146</v>
@@ -14869,7 +14869,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H500" t="n">
         <v>5010</v>
@@ -15014,7 +15014,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H505" t="n">
         <v>2168</v>
@@ -15043,7 +15043,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G506" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H506" t="n">
         <v>516</v>
@@ -15072,7 +15072,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H507" t="n">
         <v>4213</v>
@@ -15101,7 +15101,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H508" t="n">
         <v>1909</v>
@@ -15130,7 +15130,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H509" t="n">
         <v>2208</v>
@@ -15159,7 +15159,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H510" t="n">
         <v>2337</v>
@@ -15188,7 +15188,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G511" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H511" t="n">
         <v>123</v>
@@ -15246,7 +15246,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G513" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H513" t="n">
         <v>2999</v>
@@ -15333,7 +15333,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H516" t="n">
         <v>9199</v>
@@ -15420,7 +15420,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H519" t="n">
         <v>107</v>
@@ -15478,7 +15478,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H521" t="n">
         <v>2000</v>
@@ -15507,7 +15507,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H522" t="n">
         <v>3105</v>
@@ -15536,7 +15536,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H523" t="n">
         <v>3940</v>
@@ -15565,7 +15565,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H524" t="n">
         <v>5586</v>
@@ -15594,7 +15594,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H525" t="n">
         <v>256</v>
@@ -15623,7 +15623,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H526" t="n">
         <v>2296</v>
@@ -15681,7 +15681,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H528" t="n">
         <v>165</v>
@@ -15710,7 +15710,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H529" t="n">
         <v>352</v>
@@ -15739,7 +15739,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H530" t="n">
         <v>1618</v>
@@ -15768,7 +15768,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G531" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H531" t="n">
         <v>5250</v>
@@ -15797,7 +15797,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H532" t="n">
         <v>420</v>
@@ -15826,7 +15826,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H533" t="n">
         <v>8008</v>
@@ -15855,7 +15855,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H534" t="n">
         <v>1274</v>
@@ -15884,7 +15884,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H536" t="n">
         <v>553</v>
@@ -15942,7 +15942,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G538" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H538" t="n">
         <v>908</v>
@@ -16029,7 +16029,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H540" t="n">
         <v>14503</v>
@@ -16058,7 +16058,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G541" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H541" t="n">
         <v>300</v>
@@ -16116,7 +16116,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H543" t="n">
         <v>50</v>
@@ -16145,7 +16145,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H544" t="n">
         <v>5816</v>
@@ -16203,7 +16203,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H546" t="n">
         <v>23578</v>
@@ -16232,7 +16232,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H547" t="n">
         <v>4925</v>
@@ -16290,7 +16290,7 @@
         <v>3</v>
       </c>
       <c r="G549" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H549" t="n">
         <v>2815</v>
@@ -16348,7 +16348,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H551" t="n">
         <v>1945</v>
@@ -16377,7 +16377,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H552" t="n">
         <v>22273</v>
@@ -16435,7 +16435,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G554" t="n">
-        <v>2.86961364746094</v>
+        <v>2.86961340904236</v>
       </c>
       <c r="H554" t="n">
         <v>10116</v>
@@ -16551,7 +16551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H558" t="n">
         <v>8956</v>
@@ -16580,7 +16580,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G559" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H559" t="n">
         <v>5192</v>
@@ -16609,7 +16609,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734303474426</v>
+        <v>2.77734327316284</v>
       </c>
       <c r="H560" t="n">
         <v>6973</v>
@@ -16638,7 +16638,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79579710960388</v>
+        <v>2.79579734802246</v>
       </c>
       <c r="H561" t="n">
         <v>2786</v>
@@ -16667,7 +16667,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H562" t="n">
         <v>6763</v>
@@ -16696,7 +16696,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120760917664</v>
+        <v>2.73120784759521</v>
       </c>
       <c r="H563" t="n">
         <v>1740</v>
@@ -16725,7 +16725,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>2.7127537727356</v>
+        <v>2.71275353431702</v>
       </c>
       <c r="H564" t="n">
         <v>33572</v>
@@ -16754,7 +16754,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H565" t="n">
         <v>27</v>
@@ -16783,7 +16783,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H566" t="n">
         <v>2877</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H568" t="n">
         <v>4278</v>
@@ -16928,7 +16928,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H571" t="n">
         <v>13431</v>
@@ -16957,7 +16957,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41748809814453</v>
+        <v>2.41748785972595</v>
       </c>
       <c r="H572" t="n">
         <v>1200</v>
@@ -17044,7 +17044,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H575" t="n">
         <v>838</v>
@@ -17073,7 +17073,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43594193458557</v>
+        <v>2.43594217300415</v>
       </c>
       <c r="H576" t="n">
         <v>24569</v>
@@ -17131,7 +17131,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H578" t="n">
         <v>8794</v>
@@ -17160,7 +17160,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G579" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H579" t="n">
         <v>17262</v>
@@ -17189,7 +17189,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G580" t="n">
-        <v>2.63893699645996</v>
+        <v>2.63893723487854</v>
       </c>
       <c r="H580" t="n">
         <v>596</v>
@@ -17218,7 +17218,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G581" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H581" t="n">
         <v>3015</v>
@@ -17247,7 +17247,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G582" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17305,7 +17305,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.57434797286987</v>
+        <v>2.57434773445129</v>
       </c>
       <c r="H584" t="n">
         <v>8917</v>
@@ -17334,7 +17334,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H585" t="n">
         <v>1960</v>
@@ -17363,7 +17363,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H586" t="n">
         <v>2846</v>
@@ -17450,7 +17450,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G589" t="n">
-        <v>2.50975847244263</v>
+        <v>2.50975871086121</v>
       </c>
       <c r="H589" t="n">
         <v>6124</v>
@@ -17508,7 +17508,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65739154815674</v>
+        <v>2.65739130973816</v>
       </c>
       <c r="H591" t="n">
         <v>2840</v>
@@ -17537,7 +17537,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G592" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H592" t="n">
         <v>2322</v>
@@ -17566,7 +17566,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H593" t="n">
         <v>12355</v>
@@ -17595,7 +17595,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G594" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H594" t="n">
         <v>4823</v>
@@ -17624,7 +17624,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H595" t="n">
         <v>7592</v>
@@ -17653,7 +17653,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>2.41748809814453</v>
+        <v>2.41748785972595</v>
       </c>
       <c r="H596" t="n">
         <v>13053</v>
@@ -17682,7 +17682,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G597" t="n">
-        <v>2.45439624786377</v>
+        <v>2.45439648628235</v>
       </c>
       <c r="H597" t="n">
         <v>20130</v>
@@ -17769,7 +17769,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.52821278572083</v>
+        <v>2.52821254730225</v>
       </c>
       <c r="H600" t="n">
         <v>1222</v>
@@ -17798,7 +17798,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.56512069702148</v>
+        <v>2.56512093544006</v>
       </c>
       <c r="H601" t="n">
         <v>1618</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H603" t="n">
         <v>2226</v>
@@ -17885,7 +17885,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.62048316001892</v>
+        <v>2.62048292160034</v>
       </c>
       <c r="H604" t="n">
         <v>50</v>
@@ -17943,7 +17943,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>2.50975847244263</v>
+        <v>2.50975871086121</v>
       </c>
       <c r="H606" t="n">
         <v>5678</v>
@@ -18030,7 +18030,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H609" t="n">
         <v>7373</v>
@@ -18059,7 +18059,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H610" t="n">
         <v>1755</v>
@@ -18088,7 +18088,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G611" t="n">
-        <v>2.62971019744873</v>
+        <v>2.62970995903015</v>
       </c>
       <c r="H611" t="n">
         <v>3646</v>
@@ -18117,7 +18117,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H612" t="n">
         <v>1353</v>
@@ -18146,7 +18146,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>2.64816403388977</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H613" t="n">
         <v>3521</v>
@@ -18175,7 +18175,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H614" t="n">
         <v>1453</v>
@@ -18204,7 +18204,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G615" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H615" t="n">
         <v>12525</v>
@@ -18233,7 +18233,7 @@
         <v>3</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H616" t="n">
         <v>31723</v>
@@ -18291,7 +18291,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67584586143494</v>
+        <v>2.67584538459778</v>
       </c>
       <c r="H618" t="n">
         <v>5256</v>
@@ -18320,7 +18320,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.72198104858398</v>
+        <v>2.72198081016541</v>
       </c>
       <c r="H619" t="n">
         <v>345</v>
@@ -18349,7 +18349,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734303474426</v>
+        <v>2.77734327316284</v>
       </c>
       <c r="H620" t="n">
         <v>10213</v>
@@ -18407,7 +18407,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>2.6942994594574</v>
+        <v>2.69429969787598</v>
       </c>
       <c r="H622" t="n">
         <v>2229</v>
@@ -18465,7 +18465,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>2.68507242202759</v>
+        <v>2.68507266044617</v>
       </c>
       <c r="H624" t="n">
         <v>87</v>
@@ -18726,7 +18726,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H633" t="n">
         <v>2929</v>
@@ -18784,7 +18784,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H635" t="n">
         <v>15459</v>
@@ -18900,7 +18900,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>3.19256067276001</v>
+        <v>3.19256043434143</v>
       </c>
       <c r="H639" t="n">
         <v>121971</v>
@@ -19045,7 +19045,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H644" t="n">
         <v>1108</v>
@@ -19248,7 +19248,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G651" t="n">
-        <v>3.17410635948181</v>
+        <v>3.17410659790039</v>
       </c>
       <c r="H651" t="n">
         <v>7106</v>
@@ -19306,7 +19306,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.19256067276001</v>
+        <v>3.19256043434143</v>
       </c>
       <c r="H653" t="n">
         <v>17275</v>
@@ -19335,7 +19335,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>3.25714993476868</v>
+        <v>3.2571496963501</v>
       </c>
       <c r="H654" t="n">
         <v>1756</v>
@@ -19364,7 +19364,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>3.32173943519592</v>
+        <v>3.32173919677734</v>
       </c>
       <c r="H655" t="n">
         <v>35366</v>
@@ -19393,7 +19393,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>3.34019327163696</v>
+        <v>3.34019303321838</v>
       </c>
       <c r="H656" t="n">
         <v>11889</v>
@@ -19538,7 +19538,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>3.10951685905457</v>
+        <v>3.10951662063599</v>
       </c>
       <c r="H661" t="n">
         <v>7980</v>
@@ -19567,7 +19567,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>3.0633819103241</v>
+        <v>3.06338167190552</v>
       </c>
       <c r="H662" t="n">
         <v>6848</v>
@@ -19596,7 +19596,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>2.96188426017761</v>
+        <v>2.96188402175903</v>
       </c>
       <c r="H663" t="n">
         <v>19629</v>
@@ -19625,7 +19625,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H664" t="n">
         <v>78917</v>
@@ -19654,7 +19654,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.88806772232056</v>
+        <v>2.88806796073914</v>
       </c>
       <c r="H665" t="n">
         <v>1731</v>
@@ -19712,7 +19712,7 @@
         <v>3</v>
       </c>
       <c r="G667" t="n">
-        <v>2.76811599731445</v>
+        <v>2.76811575889587</v>
       </c>
       <c r="H667" t="n">
         <v>3857</v>
@@ -19770,7 +19770,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G669" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H669" t="n">
         <v>2510</v>
@@ -19828,7 +19828,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H671" t="n">
         <v>3776</v>
@@ -19886,7 +19886,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G673" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H673" t="n">
         <v>229</v>
@@ -20002,7 +20002,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H677" t="n">
         <v>213</v>
@@ -20060,7 +20060,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.11874413490295</v>
+        <v>3.11874437332153</v>
       </c>
       <c r="H679" t="n">
         <v>14622</v>
@@ -20089,7 +20089,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.03570032119751</v>
+        <v>3.03570055961609</v>
       </c>
       <c r="H680" t="n">
         <v>6809</v>
@@ -20234,7 +20234,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05415463447571</v>
+        <v>3.05415439605713</v>
       </c>
       <c r="H685" t="n">
         <v>1682</v>
@@ -20379,7 +20379,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>2.90652179718018</v>
+        <v>2.90652203559875</v>
       </c>
       <c r="H690" t="n">
         <v>20373</v>
@@ -20437,7 +20437,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G692" t="n">
-        <v>2.83270525932312</v>
+        <v>2.8327054977417</v>
       </c>
       <c r="H692" t="n">
         <v>5417</v>
@@ -20495,7 +20495,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>2.94342994689941</v>
+        <v>2.94343018531799</v>
       </c>
       <c r="H694" t="n">
         <v>2567</v>
@@ -20582,7 +20582,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>2.96188426017761</v>
+        <v>2.96188402175903</v>
       </c>
       <c r="H697" t="n">
         <v>422</v>
@@ -20640,7 +20640,7 @@
         <v>3.25</v>
       </c>
       <c r="G699" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H699" t="n">
         <v>620</v>
@@ -20698,7 +20698,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.86961364746094</v>
+        <v>2.86961340904236</v>
       </c>
       <c r="H701" t="n">
         <v>2172</v>
@@ -20785,7 +20785,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G704" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H704" t="n">
         <v>7911</v>
@@ -20814,7 +20814,7 @@
         <v>3.25</v>
       </c>
       <c r="G705" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H705" t="n">
         <v>46785</v>
@@ -20843,7 +20843,7 @@
         <v>3.25</v>
       </c>
       <c r="G706" t="n">
-        <v>2.99879240989685</v>
+        <v>2.99879217147827</v>
       </c>
       <c r="H706" t="n">
         <v>3156</v>
@@ -20901,7 +20901,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G708" t="n">
-        <v>2.98956513404846</v>
+        <v>2.98956537246704</v>
       </c>
       <c r="H708" t="n">
         <v>10802</v>
@@ -20930,7 +20930,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G709" t="n">
-        <v>3.0633819103241</v>
+        <v>3.06338167190552</v>
       </c>
       <c r="H709" t="n">
         <v>10942</v>
@@ -20959,7 +20959,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>3.03570032119751</v>
+        <v>3.03570055961609</v>
       </c>
       <c r="H710" t="n">
         <v>132393</v>
@@ -20988,7 +20988,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>3.17410635948181</v>
+        <v>3.17410659790039</v>
       </c>
       <c r="H711" t="n">
         <v>37895</v>
@@ -21017,7 +21017,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.32173943519592</v>
+        <v>3.32173919677734</v>
       </c>
       <c r="H712" t="n">
         <v>125810</v>
@@ -21046,7 +21046,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>3.34019327163696</v>
+        <v>3.34019303321838</v>
       </c>
       <c r="H713" t="n">
         <v>29644</v>
@@ -21191,7 +21191,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G718" t="n">
-        <v>3.42463660240173</v>
+        <v>3.42463636398315</v>
       </c>
       <c r="H718" t="n">
         <v>19996</v>
@@ -21249,7 +21249,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G720" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H720" t="n">
         <v>26821</v>
@@ -21278,7 +21278,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G721" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H721" t="n">
         <v>22556</v>
@@ -21423,7 +21423,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H726" t="n">
         <v>2271</v>
@@ -21481,7 +21481,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H728" t="n">
         <v>10721</v>
@@ -21510,7 +21510,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>3.62167024612427</v>
+        <v>3.62167000770569</v>
       </c>
       <c r="H729" t="n">
         <v>4368</v>
@@ -21539,7 +21539,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G730" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H730" t="n">
         <v>12120</v>
@@ -21568,7 +21568,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H731" t="n">
         <v>10096</v>
@@ -21626,7 +21626,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G733" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H733" t="n">
         <v>8164</v>
@@ -21742,7 +21742,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G737" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H737" t="n">
         <v>2069</v>
@@ -21887,7 +21887,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>3.5372269153595</v>
+        <v>3.53722715377808</v>
       </c>
       <c r="H742" t="n">
         <v>32</v>
@@ -22177,7 +22177,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H752" t="n">
         <v>1100</v>
@@ -22206,7 +22206,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H753" t="n">
         <v>4824</v>
@@ -22235,7 +22235,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H754" t="n">
         <v>15245</v>
@@ -22322,7 +22322,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.66858291625977</v>
+        <v>3.66858315467834</v>
       </c>
       <c r="H757" t="n">
         <v>8377</v>
@@ -22467,7 +22467,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G762" t="n">
-        <v>3.62167024612427</v>
+        <v>3.62167000770569</v>
       </c>
       <c r="H762" t="n">
         <v>7020</v>
@@ -22612,7 +22612,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H767" t="n">
         <v>18904</v>
@@ -22641,7 +22641,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G768" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H768" t="n">
         <v>7062</v>
@@ -22728,7 +22728,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G771" t="n">
-        <v>3.649817943573</v>
+        <v>3.64981818199158</v>
       </c>
       <c r="H771" t="n">
         <v>1791</v>
@@ -22960,7 +22960,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G779" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H779" t="n">
         <v>1305</v>
@@ -23105,7 +23105,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H784" t="n">
         <v>297</v>
@@ -23134,7 +23134,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H788" t="n">
         <v>372</v>
@@ -23308,7 +23308,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G791" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H791" t="n">
         <v>2121</v>
@@ -23395,7 +23395,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H794" t="n">
         <v>18360</v>
@@ -23424,7 +23424,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G795" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H795" t="n">
         <v>5078</v>
@@ -23511,7 +23511,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H798" t="n">
         <v>12843</v>
@@ -23569,7 +23569,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G800" t="n">
-        <v>3.85623455047607</v>
+        <v>3.8562343120575</v>
       </c>
       <c r="H800" t="n">
         <v>1776</v>
@@ -23598,7 +23598,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88438177108765</v>
+        <v>3.88438200950623</v>
       </c>
       <c r="H801" t="n">
         <v>4253</v>
@@ -23627,7 +23627,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G802" t="n">
-        <v>3.88438177108765</v>
+        <v>3.88438200950623</v>
       </c>
       <c r="H802" t="n">
         <v>2408</v>
@@ -23685,7 +23685,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>3.96882486343384</v>
+        <v>3.96882510185242</v>
       </c>
       <c r="H804" t="n">
         <v>11913</v>
@@ -23743,7 +23743,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H806" t="n">
         <v>41169</v>
@@ -23888,7 +23888,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G811" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H811" t="n">
         <v>17935</v>
@@ -23917,7 +23917,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>4.10018062591553</v>
+        <v>4.10018110275269</v>
       </c>
       <c r="H812" t="n">
         <v>12249</v>
@@ -23946,7 +23946,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H813" t="n">
         <v>3381</v>
@@ -24236,7 +24236,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H823" t="n">
         <v>41614</v>
@@ -24294,7 +24294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H825" t="n">
         <v>2822</v>
@@ -24323,7 +24323,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G826" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H826" t="n">
         <v>4126</v>
@@ -24410,7 +24410,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H829" t="n">
         <v>5363</v>
@@ -24439,7 +24439,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>4.3065972328186</v>
+        <v>4.30659770965576</v>
       </c>
       <c r="H830" t="n">
         <v>13944</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H831" t="n">
         <v>8663</v>
@@ -24526,7 +24526,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H833" t="n">
         <v>15658</v>
@@ -24613,7 +24613,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H836" t="n">
         <v>10141</v>
@@ -24671,7 +24671,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G838" t="n">
-        <v>3.68734812736511</v>
+        <v>3.68734836578369</v>
       </c>
       <c r="H838" t="n">
         <v>2963</v>
@@ -24700,7 +24700,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H839" t="n">
         <v>15833</v>
@@ -24758,7 +24758,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H841" t="n">
         <v>3553</v>
@@ -24787,7 +24787,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H842" t="n">
         <v>5470</v>
@@ -24874,7 +24874,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H845" t="n">
         <v>3484</v>
@@ -25019,7 +25019,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G850" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H850" t="n">
         <v>3030</v>
@@ -25106,7 +25106,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H853" t="n">
         <v>2333</v>
@@ -25164,7 +25164,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H855" t="n">
         <v>12319</v>
@@ -25280,7 +25280,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H859" t="n">
         <v>7062</v>
@@ -25338,7 +25338,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H861" t="n">
         <v>9293</v>
@@ -25454,7 +25454,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G865" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H865" t="n">
         <v>808</v>
@@ -25512,7 +25512,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H867" t="n">
         <v>611</v>
@@ -25570,7 +25570,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G869" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H869" t="n">
         <v>13902</v>
@@ -25657,7 +25657,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H872" t="n">
         <v>570</v>
@@ -25802,7 +25802,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H877" t="n">
         <v>5546</v>
@@ -25918,7 +25918,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G881" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H881" t="n">
         <v>10744</v>
@@ -25976,7 +25976,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G883" t="n">
-        <v>3.74364352226257</v>
+        <v>3.74364376068115</v>
       </c>
       <c r="H883" t="n">
         <v>50</v>
@@ -26005,7 +26005,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H884" t="n">
         <v>2574</v>
@@ -26034,7 +26034,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G885" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H885" t="n">
         <v>3925</v>
@@ -26063,7 +26063,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G886" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H886" t="n">
         <v>1154</v>
@@ -26092,7 +26092,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>3.56537485122681</v>
+        <v>3.56537461280823</v>
       </c>
       <c r="H887" t="n">
         <v>6727</v>
@@ -26179,7 +26179,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G890" t="n">
-        <v>3.66858291625977</v>
+        <v>3.66858315467834</v>
       </c>
       <c r="H890" t="n">
         <v>6569</v>
@@ -26208,7 +26208,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G891" t="n">
-        <v>3.65920066833496</v>
+        <v>3.65920042991638</v>
       </c>
       <c r="H891" t="n">
         <v>1081</v>
@@ -26295,7 +26295,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>3.60290479660034</v>
+        <v>3.60290503501892</v>
       </c>
       <c r="H894" t="n">
         <v>1455</v>
@@ -26353,7 +26353,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H896" t="n">
         <v>4606</v>
@@ -26440,7 +26440,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H899" t="n">
         <v>4331</v>
@@ -26469,7 +26469,7 @@
         <v>4.25</v>
       </c>
       <c r="G900" t="n">
-        <v>3.98759031295776</v>
+        <v>3.98759055137634</v>
       </c>
       <c r="H900" t="n">
         <v>477</v>
@@ -26498,7 +26498,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G901" t="n">
-        <v>3.9782075881958</v>
+        <v>3.97820734977722</v>
       </c>
       <c r="H901" t="n">
         <v>160</v>
@@ -26556,7 +26556,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H903" t="n">
         <v>7451</v>
@@ -26585,7 +26585,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G904" t="n">
-        <v>3.8656165599823</v>
+        <v>3.86561679840088</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -26643,7 +26643,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H906" t="n">
         <v>7171</v>
@@ -26846,7 +26846,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84685182571411</v>
+        <v>3.84685158729553</v>
       </c>
       <c r="H913" t="n">
         <v>5572</v>
@@ -26875,7 +26875,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G914" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H914" t="n">
         <v>2431</v>
@@ -26904,7 +26904,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G915" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H915" t="n">
         <v>694</v>
@@ -26933,7 +26933,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81870436668396</v>
+        <v>3.81870412826538</v>
       </c>
       <c r="H916" t="n">
         <v>6079</v>
@@ -26962,7 +26962,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H917" t="n">
         <v>1682</v>
@@ -27020,7 +27020,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G919" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H919" t="n">
         <v>172</v>
@@ -27078,7 +27078,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G921" t="n">
-        <v>3.7624089717865</v>
+        <v>3.76240873336792</v>
       </c>
       <c r="H921" t="n">
         <v>3356</v>
@@ -27136,7 +27136,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G923" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H923" t="n">
         <v>10267</v>
@@ -27165,7 +27165,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>3.79993915557861</v>
+        <v>3.79993891716003</v>
       </c>
       <c r="H924" t="n">
         <v>2845</v>
@@ -27194,7 +27194,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.85623455047607</v>
+        <v>3.8562343120575</v>
       </c>
       <c r="H925" t="n">
         <v>6744</v>
@@ -27223,7 +27223,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G926" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H926" t="n">
         <v>81918</v>
@@ -27252,7 +27252,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H927" t="n">
         <v>16501</v>
@@ -27281,7 +27281,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>4.10018062591553</v>
+        <v>4.10018110275269</v>
       </c>
       <c r="H928" t="n">
         <v>19219</v>
@@ -27310,7 +27310,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G929" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H929" t="n">
         <v>7657</v>
@@ -27339,7 +27339,7 @@
         <v>4.25</v>
       </c>
       <c r="G930" t="n">
-        <v>3.98759031295776</v>
+        <v>3.98759055137634</v>
       </c>
       <c r="H930" t="n">
         <v>18877</v>
@@ -27397,7 +27397,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>4.08141613006592</v>
+        <v>4.08141565322876</v>
       </c>
       <c r="H932" t="n">
         <v>12772</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.92191243171692</v>
+        <v>3.92191219329834</v>
       </c>
       <c r="H934" t="n">
         <v>1187</v>
@@ -27484,7 +27484,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G935" t="n">
-        <v>3.96882486343384</v>
+        <v>3.96882510185242</v>
       </c>
       <c r="H935" t="n">
         <v>193</v>
@@ -27513,7 +27513,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G936" t="n">
-        <v>3.87499976158142</v>
+        <v>3.87499952316284</v>
       </c>
       <c r="H936" t="n">
         <v>1816</v>
@@ -27687,7 +27687,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>3.99697279930115</v>
+        <v>3.99697303771973</v>
       </c>
       <c r="H942" t="n">
         <v>4920</v>
@@ -27774,7 +27774,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H945" t="n">
         <v>1416</v>
@@ -27803,7 +27803,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G946" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H946" t="n">
         <v>5443</v>
@@ -27832,7 +27832,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>4.13771104812622</v>
+        <v>4.13771152496338</v>
       </c>
       <c r="H947" t="n">
         <v>1999</v>
@@ -27948,7 +27948,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H951" t="n">
         <v>2435</v>
@@ -28093,7 +28093,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.16585922241211</v>
+        <v>4.16585874557495</v>
       </c>
       <c r="H956" t="n">
         <v>2077</v>
@@ -28122,7 +28122,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.14709377288818</v>
+        <v>4.14709424972534</v>
       </c>
       <c r="H957" t="n">
         <v>2834</v>
@@ -28151,7 +28151,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G958" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H958" t="n">
         <v>1651</v>
@@ -28267,7 +28267,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G962" t="n">
-        <v>4.15647649765015</v>
+        <v>4.15647602081299</v>
       </c>
       <c r="H962" t="n">
         <v>1164</v>
@@ -38974,6 +38974,35 @@
         <v>10821</v>
       </c>
       <c r="I1331" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1332" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="H1332" t="n">
+        <v>2759</v>
+      </c>
+      <c r="I1332" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161733627319</v>
+        <v>3.10161709785461</v>
       </c>
       <c r="H5" t="n">
         <v>23147</v>
@@ -543,7 +543,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1333589553833</v>
+        <v>3.13335871696472</v>
       </c>
       <c r="H6" t="n">
         <v>30898</v>
@@ -630,7 +630,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G9" t="n">
-        <v>3.56867361068726</v>
+        <v>3.56867337226868</v>
       </c>
       <c r="H9" t="n">
         <v>292968</v>
@@ -775,7 +775,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H14" t="n">
         <v>18667</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H16" t="n">
         <v>44813</v>
@@ -862,7 +862,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924377441406</v>
       </c>
       <c r="H17" t="n">
         <v>150547</v>
@@ -891,7 +891,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924377441406</v>
       </c>
       <c r="H18" t="n">
         <v>290894</v>
@@ -920,7 +920,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H19" t="n">
         <v>61034</v>
@@ -978,7 +978,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458908081055</v>
       </c>
       <c r="H21" t="n">
         <v>33033</v>
@@ -1007,7 +1007,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458908081055</v>
       </c>
       <c r="H22" t="n">
         <v>16624</v>
@@ -1036,7 +1036,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831274032593</v>
+        <v>3.71831321716309</v>
       </c>
       <c r="H23" t="n">
         <v>29141</v>
@@ -1094,7 +1094,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.89515972137451</v>
+        <v>3.89515995979309</v>
       </c>
       <c r="H25" t="n">
         <v>186140</v>
@@ -1123,7 +1123,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>3.90876293182373</v>
+        <v>3.90876317024231</v>
       </c>
       <c r="H26" t="n">
         <v>85789</v>
@@ -1152,7 +1152,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726149559021</v>
+        <v>3.77726197242737</v>
       </c>
       <c r="H27" t="n">
         <v>75595</v>
@@ -1181,7 +1181,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H28" t="n">
         <v>90036</v>
@@ -1210,7 +1210,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993462562561</v>
+        <v>3.79993438720703</v>
       </c>
       <c r="H29" t="n">
         <v>38465</v>
@@ -1239,7 +1239,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G30" t="n">
-        <v>3.6865713596344</v>
+        <v>3.68657112121582</v>
       </c>
       <c r="H30" t="n">
         <v>57117</v>
@@ -1268,7 +1268,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G31" t="n">
-        <v>3.71377825737</v>
+        <v>3.71377801895142</v>
       </c>
       <c r="H31" t="n">
         <v>31484</v>
@@ -1384,7 +1384,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>3.56413888931274</v>
+        <v>3.56413912773132</v>
       </c>
       <c r="H35" t="n">
         <v>54741</v>
@@ -1413,7 +1413,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>3.56413888931274</v>
+        <v>3.56413912773132</v>
       </c>
       <c r="H36" t="n">
         <v>13961</v>
@@ -1442,7 +1442,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>3.6729679107666</v>
+        <v>3.67296767234802</v>
       </c>
       <c r="H37" t="n">
         <v>85205</v>
@@ -1471,7 +1471,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365804672241</v>
       </c>
       <c r="H38" t="n">
         <v>28609</v>
@@ -1529,7 +1529,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633093833923</v>
+        <v>3.78633069992065</v>
       </c>
       <c r="H40" t="n">
         <v>4635</v>
@@ -1558,7 +1558,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>3.7817964553833</v>
+        <v>3.78179621696472</v>
       </c>
       <c r="H41" t="n">
         <v>19462</v>
@@ -1587,7 +1587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H42" t="n">
         <v>23606</v>
@@ -1616,7 +1616,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H43" t="n">
         <v>10910</v>
@@ -1645,7 +1645,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272725105286</v>
+        <v>3.77272701263428</v>
       </c>
       <c r="H44" t="n">
         <v>34605</v>
@@ -1674,7 +1674,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H45" t="n">
         <v>2007</v>
@@ -1703,7 +1703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H46" t="n">
         <v>6914</v>
@@ -1761,7 +1761,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>3.6865713596344</v>
+        <v>3.68657112121582</v>
       </c>
       <c r="H48" t="n">
         <v>2180</v>
@@ -1790,7 +1790,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458908081055</v>
       </c>
       <c r="H49" t="n">
         <v>16797</v>
@@ -1819,7 +1819,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365828514099</v>
+        <v>3.76365804672241</v>
       </c>
       <c r="H50" t="n">
         <v>9599</v>
@@ -1848,7 +1848,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G51" t="n">
-        <v>3.80900311470032</v>
+        <v>3.8090033531189</v>
       </c>
       <c r="H51" t="n">
         <v>25429</v>
@@ -1877,7 +1877,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H52" t="n">
         <v>919</v>
@@ -1906,7 +1906,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.7455198764801</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H53" t="n">
         <v>5908</v>
@@ -2051,7 +2051,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H58" t="n">
         <v>4003</v>
@@ -2080,7 +2080,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H59" t="n">
         <v>6637</v>
@@ -2109,7 +2109,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G60" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H60" t="n">
         <v>5790</v>
@@ -2167,7 +2167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.70017504692078</v>
+        <v>3.7001748085022</v>
       </c>
       <c r="H62" t="n">
         <v>8191</v>
@@ -2196,7 +2196,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>3.72284770011902</v>
+        <v>3.72284746170044</v>
       </c>
       <c r="H63" t="n">
         <v>20100</v>
@@ -2225,7 +2225,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>3.69564008712769</v>
+        <v>3.69564032554626</v>
       </c>
       <c r="H64" t="n">
         <v>5559</v>
@@ -2341,7 +2341,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>3.6729679107666</v>
+        <v>3.67296767234802</v>
       </c>
       <c r="H68" t="n">
         <v>56808</v>
@@ -2370,7 +2370,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>3.75458884239197</v>
+        <v>3.75458908081055</v>
       </c>
       <c r="H69" t="n">
         <v>16753</v>
@@ -2457,7 +2457,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>3.65936374664307</v>
+        <v>3.65936398506165</v>
       </c>
       <c r="H72" t="n">
         <v>6928</v>
@@ -2602,7 +2602,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H77" t="n">
         <v>10457</v>
@@ -2631,7 +2631,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.70017504692078</v>
+        <v>3.7001748085022</v>
       </c>
       <c r="H78" t="n">
         <v>36913</v>
@@ -2660,7 +2660,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H79" t="n">
         <v>16654</v>
@@ -2718,7 +2718,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227682113647</v>
       </c>
       <c r="H81" t="n">
         <v>14163</v>
@@ -2776,7 +2776,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G83" t="n">
-        <v>3.54600095748901</v>
+        <v>3.54600071907043</v>
       </c>
       <c r="H83" t="n">
         <v>3337</v>
@@ -2805,7 +2805,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H84" t="n">
         <v>21297</v>
@@ -2834,7 +2834,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G85" t="n">
-        <v>3.50065565109253</v>
+        <v>3.50065541267395</v>
       </c>
       <c r="H85" t="n">
         <v>6702</v>
@@ -2863,7 +2863,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729214668274</v>
+        <v>3.38729238510132</v>
       </c>
       <c r="H86" t="n">
         <v>4796</v>
@@ -2892,7 +2892,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G87" t="n">
-        <v>3.45984482765198</v>
+        <v>3.45984506607056</v>
       </c>
       <c r="H87" t="n">
         <v>56731</v>
@@ -2921,7 +2921,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G88" t="n">
-        <v>3.47798275947571</v>
+        <v>3.47798299789429</v>
       </c>
       <c r="H88" t="n">
         <v>5844</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.44624090194702</v>
+        <v>3.44624137878418</v>
       </c>
       <c r="H89" t="n">
         <v>5063</v>
@@ -3008,7 +3008,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.47798275947571</v>
+        <v>3.47798299789429</v>
       </c>
       <c r="H91" t="n">
         <v>7413</v>
@@ -3037,7 +3037,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47344827651978</v>
+        <v>3.47344851493835</v>
       </c>
       <c r="H92" t="n">
         <v>2793</v>
@@ -3066,7 +3066,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G93" t="n">
-        <v>3.48251748085022</v>
+        <v>3.48251724243164</v>
       </c>
       <c r="H93" t="n">
         <v>7085</v>
@@ -3095,7 +3095,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H94" t="n">
         <v>14502</v>
@@ -3153,7 +3153,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G96" t="n">
-        <v>3.32380890846252</v>
+        <v>3.3238091468811</v>
       </c>
       <c r="H96" t="n">
         <v>1326</v>
@@ -3182,7 +3182,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531010627747</v>
+        <v>3.45531034469604</v>
       </c>
       <c r="H97" t="n">
         <v>13724</v>
@@ -3211,7 +3211,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891403198242</v>
+        <v>3.46891379356384</v>
       </c>
       <c r="H98" t="n">
         <v>2853</v>
@@ -3269,7 +3269,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>3.41449999809265</v>
+        <v>3.41449975967407</v>
       </c>
       <c r="H100" t="n">
         <v>2072</v>
@@ -3356,7 +3356,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008501052856</v>
+        <v>3.36008524894714</v>
       </c>
       <c r="H103" t="n">
         <v>13842</v>
@@ -3443,7 +3443,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50065565109253</v>
+        <v>3.50065541267395</v>
       </c>
       <c r="H106" t="n">
         <v>14793</v>
@@ -3472,7 +3472,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G107" t="n">
-        <v>3.48251748085022</v>
+        <v>3.48251724243164</v>
       </c>
       <c r="H107" t="n">
         <v>5104</v>
@@ -3530,7 +3530,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>3.41449999809265</v>
+        <v>3.41449975967407</v>
       </c>
       <c r="H109" t="n">
         <v>6279</v>
@@ -3559,7 +3559,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948395729065</v>
+        <v>3.60948443412781</v>
       </c>
       <c r="H110" t="n">
         <v>33451</v>
@@ -3588,7 +3588,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227682113647</v>
       </c>
       <c r="H111" t="n">
         <v>13196</v>
@@ -3617,7 +3617,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.49612092971802</v>
+        <v>3.4961211681366</v>
       </c>
       <c r="H112" t="n">
         <v>28788</v>
@@ -3675,7 +3675,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G114" t="n">
-        <v>3.55960464477539</v>
+        <v>3.55960440635681</v>
       </c>
       <c r="H114" t="n">
         <v>4027</v>
@@ -3733,7 +3733,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227682113647</v>
       </c>
       <c r="H116" t="n">
         <v>1006</v>
@@ -3791,7 +3791,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831274032593</v>
+        <v>3.71831321716309</v>
       </c>
       <c r="H118" t="n">
         <v>29715</v>
@@ -3820,7 +3820,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>3.58227729797363</v>
+        <v>3.58227682113647</v>
       </c>
       <c r="H119" t="n">
         <v>35244</v>
@@ -3878,7 +3878,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>3.49612092971802</v>
+        <v>3.4961211681366</v>
       </c>
       <c r="H121" t="n">
         <v>6937</v>
@@ -3936,7 +3936,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G123" t="n">
-        <v>3.33287811279297</v>
+        <v>3.33287787437439</v>
       </c>
       <c r="H123" t="n">
         <v>13328</v>
@@ -3965,7 +3965,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>3.26486015319824</v>
+        <v>3.26485991477966</v>
       </c>
       <c r="H124" t="n">
         <v>17450</v>
@@ -4052,7 +4052,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G127" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H127" t="n">
         <v>3094</v>
@@ -4139,7 +4139,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543079376221</v>
+        <v>3.40543055534363</v>
       </c>
       <c r="H130" t="n">
         <v>2361</v>
@@ -4168,7 +4168,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G131" t="n">
-        <v>3.27392911911011</v>
+        <v>3.27392935752869</v>
       </c>
       <c r="H131" t="n">
         <v>8662</v>
@@ -4197,7 +4197,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>3.26486015319824</v>
+        <v>3.26485991477966</v>
       </c>
       <c r="H132" t="n">
         <v>3010</v>
@@ -4226,7 +4226,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G133" t="n">
-        <v>3.22404932975769</v>
+        <v>3.22404956817627</v>
       </c>
       <c r="H133" t="n">
         <v>4602</v>
@@ -4255,7 +4255,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H134" t="n">
         <v>60461</v>
@@ -4371,7 +4371,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020522117615</v>
+        <v>3.31020569801331</v>
       </c>
       <c r="H138" t="n">
         <v>2087</v>
@@ -4487,7 +4487,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.47344827651978</v>
+        <v>3.47344851493835</v>
       </c>
       <c r="H142" t="n">
         <v>1980</v>
@@ -4690,7 +4690,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.1469624042511</v>
+        <v>3.14696264266968</v>
       </c>
       <c r="H149" t="n">
         <v>11513</v>
@@ -4748,7 +4748,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G151" t="n">
-        <v>3.16510033607483</v>
+        <v>3.16510057449341</v>
       </c>
       <c r="H151" t="n">
         <v>218</v>
@@ -4806,7 +4806,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G153" t="n">
-        <v>2.92023611068726</v>
+        <v>2.92023587226868</v>
       </c>
       <c r="H153" t="n">
         <v>14357</v>
@@ -4864,7 +4864,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092648506165</v>
       </c>
       <c r="H155" t="n">
         <v>5951</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H156" t="n">
         <v>10379</v>
@@ -4922,7 +4922,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756321907043</v>
+        <v>2.89756345748901</v>
       </c>
       <c r="H157" t="n">
         <v>4634</v>
@@ -4951,7 +4951,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G158" t="n">
-        <v>2.96104693412781</v>
+        <v>2.96104669570923</v>
       </c>
       <c r="H158" t="n">
         <v>1286</v>
@@ -5038,7 +5038,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278831481934</v>
+        <v>2.99278855323792</v>
       </c>
       <c r="H161" t="n">
         <v>12598</v>
@@ -5067,7 +5067,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H162" t="n">
         <v>5456</v>
@@ -5154,7 +5154,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G165" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092648506165</v>
       </c>
       <c r="H165" t="n">
         <v>3774</v>
@@ -5328,7 +5328,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615181922913</v>
+        <v>3.10615158081055</v>
       </c>
       <c r="H171" t="n">
         <v>59616</v>
@@ -5357,7 +5357,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G172" t="n">
-        <v>3.11522078514099</v>
+        <v>3.11522054672241</v>
       </c>
       <c r="H172" t="n">
         <v>8398</v>
@@ -5386,7 +5386,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G173" t="n">
-        <v>3.16056561470032</v>
+        <v>3.1605658531189</v>
       </c>
       <c r="H173" t="n">
         <v>546</v>
@@ -5444,7 +5444,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092648506165</v>
       </c>
       <c r="H175" t="n">
         <v>7513</v>
@@ -5473,7 +5473,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.91116714477539</v>
+        <v>2.91116690635681</v>
       </c>
       <c r="H176" t="n">
         <v>13401</v>
@@ -5531,7 +5531,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.02452993392944</v>
+        <v>3.0245304107666</v>
       </c>
       <c r="H178" t="n">
         <v>1198</v>
@@ -5560,7 +5560,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G179" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H179" t="n">
         <v>2982</v>
@@ -5647,7 +5647,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G182" t="n">
-        <v>2.97918510437012</v>
+        <v>2.97918486595154</v>
       </c>
       <c r="H182" t="n">
         <v>7488</v>
@@ -5705,7 +5705,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266810417175</v>
+        <v>3.04266834259033</v>
       </c>
       <c r="H184" t="n">
         <v>656</v>
@@ -5763,7 +5763,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01092624664307</v>
+        <v>3.01092648506165</v>
       </c>
       <c r="H186" t="n">
         <v>3889</v>
@@ -5792,7 +5792,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H187" t="n">
         <v>4021</v>
@@ -5850,7 +5850,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G189" t="n">
-        <v>2.99732327461243</v>
+        <v>2.99732303619385</v>
       </c>
       <c r="H189" t="n">
         <v>14092</v>
@@ -5937,7 +5937,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627179145813</v>
+        <v>3.05627155303955</v>
       </c>
       <c r="H192" t="n">
         <v>9528</v>
@@ -6111,7 +6111,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>2.92023611068726</v>
+        <v>2.92023587226868</v>
       </c>
       <c r="H198" t="n">
         <v>8621</v>
@@ -6140,7 +6140,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>2.92023611068726</v>
+        <v>2.92023587226868</v>
       </c>
       <c r="H199" t="n">
         <v>6598</v>
@@ -6169,7 +6169,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489056587219</v>
+        <v>2.87489104270935</v>
       </c>
       <c r="H200" t="n">
         <v>7430</v>
@@ -6314,7 +6314,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011613845825</v>
+        <v>2.97011590003967</v>
       </c>
       <c r="H205" t="n">
         <v>4097</v>
@@ -6343,7 +6343,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>3.00185751914978</v>
+        <v>3.0018572807312</v>
       </c>
       <c r="H206" t="n">
         <v>581</v>
@@ -6372,7 +6372,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G207" t="n">
-        <v>2.92477035522461</v>
+        <v>2.92477059364319</v>
       </c>
       <c r="H207" t="n">
         <v>1550</v>
@@ -6401,7 +6401,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>3.00639200210571</v>
+        <v>3.00639224052429</v>
       </c>
       <c r="H208" t="n">
         <v>7842</v>
@@ -6459,7 +6459,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951484680176</v>
+        <v>3.21951460838318</v>
       </c>
       <c r="H210" t="n">
         <v>21001</v>
@@ -6488,7 +6488,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G211" t="n">
-        <v>3.34648156166077</v>
+        <v>3.34648180007935</v>
       </c>
       <c r="H211" t="n">
         <v>53801</v>
@@ -6575,7 +6575,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753304481506</v>
+        <v>3.28753280639648</v>
       </c>
       <c r="H214" t="n">
         <v>1310</v>
@@ -6604,7 +6604,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416977882385</v>
       </c>
       <c r="H215" t="n">
         <v>6340</v>
@@ -6662,7 +6662,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G217" t="n">
-        <v>3.11522078514099</v>
+        <v>3.11522054672241</v>
       </c>
       <c r="H217" t="n">
         <v>1846</v>
@@ -6691,7 +6691,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G218" t="n">
-        <v>3.16056561470032</v>
+        <v>3.1605658531189</v>
       </c>
       <c r="H218" t="n">
         <v>4799</v>
@@ -6720,7 +6720,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416954040527</v>
+        <v>3.17416977882385</v>
       </c>
       <c r="H219" t="n">
         <v>8838</v>
@@ -6749,7 +6749,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603137016296</v>
+        <v>3.15603160858154</v>
       </c>
       <c r="H220" t="n">
         <v>16930</v>
@@ -6778,7 +6778,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.9293053150177</v>
+        <v>2.92930483818054</v>
       </c>
       <c r="H221" t="n">
         <v>10002</v>
@@ -6836,7 +6836,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.97918510437012</v>
+        <v>2.97918486595154</v>
       </c>
       <c r="H223" t="n">
         <v>3005</v>
@@ -6865,7 +6865,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035608291626</v>
+        <v>2.87035584449768</v>
       </c>
       <c r="H224" t="n">
         <v>4992</v>
@@ -6981,7 +6981,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H228" t="n">
         <v>593</v>
@@ -7010,7 +7010,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489056587219</v>
+        <v>2.87489104270935</v>
       </c>
       <c r="H229" t="n">
         <v>389</v>
@@ -7039,7 +7039,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954549789429</v>
+        <v>2.82954525947571</v>
       </c>
       <c r="H230" t="n">
         <v>4733</v>
@@ -7213,7 +7213,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675239562988</v>
+        <v>2.85675263404846</v>
       </c>
       <c r="H236" t="n">
         <v>11979</v>
@@ -7271,7 +7271,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H238" t="n">
         <v>16491</v>
@@ -7300,7 +7300,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H239" t="n">
         <v>10412</v>
@@ -7445,7 +7445,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H244" t="n">
         <v>4956</v>
@@ -7532,7 +7532,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H247" t="n">
         <v>5286</v>
@@ -7561,7 +7561,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H248" t="n">
         <v>1003</v>
@@ -7590,7 +7590,7 @@
         <v>3.125</v>
       </c>
       <c r="G249" t="n">
-        <v>2.8340802192688</v>
+        <v>2.83407998085022</v>
       </c>
       <c r="H249" t="n">
         <v>625</v>
@@ -7764,7 +7764,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H255" t="n">
         <v>18878</v>
@@ -7793,7 +7793,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78420042991638</v>
       </c>
       <c r="H256" t="n">
         <v>2600</v>
@@ -7822,7 +7822,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350957870483</v>
       </c>
       <c r="H257" t="n">
         <v>8062</v>
@@ -7851,7 +7851,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071647644043</v>
+        <v>2.72071671485901</v>
       </c>
       <c r="H258" t="n">
         <v>1704</v>
@@ -7880,7 +7880,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>2.69804430007935</v>
+        <v>2.69804406166077</v>
       </c>
       <c r="H259" t="n">
         <v>16864</v>
@@ -7967,7 +7967,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G262" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H262" t="n">
         <v>5847</v>
@@ -8054,7 +8054,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G265" t="n">
-        <v>2.63456058502197</v>
+        <v>2.63456082344055</v>
       </c>
       <c r="H265" t="n">
         <v>9259</v>
@@ -8112,7 +8112,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G267" t="n">
-        <v>2.67537140846252</v>
+        <v>2.6753716468811</v>
       </c>
       <c r="H267" t="n">
         <v>735</v>
@@ -8141,7 +8141,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H268" t="n">
         <v>6031</v>
@@ -8170,7 +8170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H269" t="n">
         <v>1163</v>
@@ -8228,7 +8228,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G271" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H271" t="n">
         <v>23246</v>
@@ -8286,7 +8286,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.59828448295593</v>
+        <v>2.59828472137451</v>
       </c>
       <c r="H273" t="n">
         <v>1912</v>
@@ -8315,7 +8315,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.55293941497803</v>
+        <v>2.55293917655945</v>
       </c>
       <c r="H274" t="n">
         <v>1083</v>
@@ -8373,7 +8373,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H276" t="n">
         <v>8540</v>
@@ -8402,7 +8402,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945546150208</v>
+        <v>2.48945569992065</v>
       </c>
       <c r="H277" t="n">
         <v>995</v>
@@ -8431,7 +8431,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>2.45317935943604</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H278" t="n">
         <v>2892</v>
@@ -8489,7 +8489,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062739372253</v>
+        <v>2.38062691688538</v>
       </c>
       <c r="H280" t="n">
         <v>7350</v>
@@ -8518,7 +8518,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342001914978</v>
       </c>
       <c r="H281" t="n">
         <v>44116</v>
@@ -8576,7 +8576,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.28086757659912</v>
+        <v>2.2808678150177</v>
       </c>
       <c r="H283" t="n">
         <v>2655</v>
@@ -8663,7 +8663,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G286" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H286" t="n">
         <v>3503</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750454902649</v>
+        <v>2.16750431060791</v>
       </c>
       <c r="H290" t="n">
         <v>7059</v>
@@ -8837,7 +8837,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.13576245307922</v>
+        <v>2.1357626914978</v>
       </c>
       <c r="H292" t="n">
         <v>9540</v>
@@ -8895,7 +8895,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>2.34435105323792</v>
+        <v>2.34435081481934</v>
       </c>
       <c r="H294" t="n">
         <v>591</v>
@@ -8924,7 +8924,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>2.22645330429077</v>
+        <v>2.22645306587219</v>
       </c>
       <c r="H295" t="n">
         <v>7856</v>
@@ -8982,7 +8982,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.18564248085022</v>
+        <v>2.1856427192688</v>
       </c>
       <c r="H297" t="n">
         <v>16353</v>
@@ -9156,7 +9156,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G303" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H303" t="n">
         <v>8916</v>
@@ -9214,7 +9214,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G305" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H305" t="n">
         <v>590</v>
@@ -9301,7 +9301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H308" t="n">
         <v>371</v>
@@ -9330,7 +9330,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957614898682</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H309" t="n">
         <v>7036</v>
@@ -9359,7 +9359,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957614898682</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H312" t="n">
         <v>4369</v>
@@ -9504,7 +9504,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H315" t="n">
         <v>2887</v>
@@ -9591,7 +9591,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026628494263</v>
       </c>
       <c r="H318" t="n">
         <v>3432</v>
@@ -9707,7 +9707,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G322" t="n">
-        <v>2.46224856376648</v>
+        <v>2.46224880218506</v>
       </c>
       <c r="H322" t="n">
         <v>1662</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H326" t="n">
         <v>10875</v>
@@ -9881,7 +9881,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H328" t="n">
         <v>9578</v>
@@ -9910,7 +9910,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143774032593</v>
+        <v>2.42143821716309</v>
       </c>
       <c r="H329" t="n">
         <v>4763</v>
@@ -9939,7 +9939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.36702346801758</v>
+        <v>2.367023229599</v>
       </c>
       <c r="H330" t="n">
         <v>7415</v>
@@ -9968,7 +9968,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.3534197807312</v>
+        <v>2.35342001914978</v>
       </c>
       <c r="H331" t="n">
         <v>12852</v>
@@ -9997,7 +9997,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.31260919570923</v>
+        <v>2.31260943412781</v>
       </c>
       <c r="H332" t="n">
         <v>4605</v>
@@ -10084,7 +10084,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G335" t="n">
-        <v>2.31260919570923</v>
+        <v>2.31260943412781</v>
       </c>
       <c r="H335" t="n">
         <v>4870</v>
@@ -10171,7 +10171,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.32167816162109</v>
+        <v>2.32167840003967</v>
       </c>
       <c r="H338" t="n">
         <v>5855</v>
@@ -10200,7 +10200,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528184890747</v>
+        <v>2.33528208732605</v>
       </c>
       <c r="H339" t="n">
         <v>4539</v>
@@ -10258,7 +10258,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G341" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H341" t="n">
         <v>4266</v>
@@ -10287,7 +10287,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>2.24912595748901</v>
+        <v>2.24912571907043</v>
       </c>
       <c r="H342" t="n">
         <v>12825</v>
@@ -10316,7 +10316,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G343" t="n">
-        <v>2.27633285522461</v>
+        <v>2.27633309364319</v>
       </c>
       <c r="H343" t="n">
         <v>5900</v>
@@ -10374,7 +10374,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>2.27633285522461</v>
+        <v>2.27633309364319</v>
       </c>
       <c r="H345" t="n">
         <v>8557</v>
@@ -10403,7 +10403,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>2.31260919570923</v>
+        <v>2.31260943412781</v>
       </c>
       <c r="H346" t="n">
         <v>2050</v>
@@ -10461,7 +10461,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H348" t="n">
         <v>518</v>
@@ -10548,7 +10548,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.27179837226868</v>
+        <v>2.27179861068726</v>
       </c>
       <c r="H351" t="n">
         <v>4619</v>
@@ -10577,7 +10577,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G352" t="n">
-        <v>2.45317935943604</v>
+        <v>2.45317959785461</v>
       </c>
       <c r="H352" t="n">
         <v>4007</v>
@@ -10693,7 +10693,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G356" t="n">
-        <v>2.36702346801758</v>
+        <v>2.367023229599</v>
       </c>
       <c r="H356" t="n">
         <v>153</v>
@@ -10780,7 +10780,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G359" t="n">
-        <v>2.19017696380615</v>
+        <v>2.19017672538757</v>
       </c>
       <c r="H359" t="n">
         <v>9087</v>
@@ -10809,7 +10809,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G360" t="n">
-        <v>2.24459147453308</v>
+        <v>2.2445912361145</v>
       </c>
       <c r="H360" t="n">
         <v>1525</v>
@@ -10838,7 +10838,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G361" t="n">
-        <v>2.24459147453308</v>
+        <v>2.2445912361145</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G362" t="n">
-        <v>2.24005699157715</v>
+        <v>2.24005675315857</v>
       </c>
       <c r="H362" t="n">
         <v>1115</v>
@@ -10925,7 +10925,7 @@
         <v>2.75</v>
       </c>
       <c r="G364" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H364" t="n">
         <v>5478</v>
@@ -11012,7 +11012,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34888553619385</v>
+        <v>2.34888529777527</v>
       </c>
       <c r="H367" t="n">
         <v>3824</v>
@@ -11041,7 +11041,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G368" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H368" t="n">
         <v>2162</v>
@@ -11070,7 +11070,7 @@
         <v>2.6949999332428</v>
       </c>
       <c r="G369" t="n">
-        <v>2.44411039352417</v>
+        <v>2.44411063194275</v>
       </c>
       <c r="H369" t="n">
         <v>1383</v>
@@ -11099,7 +11099,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G370" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H370" t="n">
         <v>119311</v>
@@ -11215,7 +11215,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.3896963596344</v>
+        <v>2.38969612121582</v>
       </c>
       <c r="H374" t="n">
         <v>7617</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957614898682</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H376" t="n">
         <v>7974</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H379" t="n">
         <v>125340</v>
@@ -11389,7 +11389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H380" t="n">
         <v>15968</v>
@@ -11447,7 +11447,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G382" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H382" t="n">
         <v>4545</v>
@@ -11476,7 +11476,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G383" t="n">
-        <v>2.56200838088989</v>
+        <v>2.56200861930847</v>
       </c>
       <c r="H383" t="n">
         <v>1921</v>
@@ -11505,7 +11505,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>2.55293941497803</v>
+        <v>2.55293917655945</v>
       </c>
       <c r="H384" t="n">
         <v>7902</v>
@@ -11592,7 +11592,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H387" t="n">
         <v>400</v>
@@ -11621,7 +11621,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H388" t="n">
         <v>9739</v>
@@ -11650,7 +11650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H389" t="n">
         <v>5695</v>
@@ -11679,7 +11679,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H390" t="n">
         <v>3704</v>
@@ -11737,7 +11737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H392" t="n">
         <v>8970</v>
@@ -11853,7 +11853,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666331291199</v>
+        <v>2.51666307449341</v>
       </c>
       <c r="H396" t="n">
         <v>67390</v>
@@ -11882,7 +11882,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H397" t="n">
         <v>6517</v>
@@ -11911,7 +11911,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G398" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H398" t="n">
         <v>3914</v>
@@ -12085,7 +12085,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H404" t="n">
         <v>20579</v>
@@ -12114,7 +12114,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H405" t="n">
         <v>5957</v>
@@ -12143,7 +12143,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H406" t="n">
         <v>4040</v>
@@ -12172,7 +12172,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H407" t="n">
         <v>10856</v>
@@ -12201,7 +12201,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H408" t="n">
         <v>3770</v>
@@ -12230,7 +12230,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H409" t="n">
         <v>3350</v>
@@ -12317,7 +12317,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G412" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H412" t="n">
         <v>5700</v>
@@ -12346,7 +12346,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.46224856376648</v>
+        <v>2.46224880218506</v>
       </c>
       <c r="H413" t="n">
         <v>224</v>
@@ -12404,7 +12404,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573251724243</v>
+        <v>2.52573227882385</v>
       </c>
       <c r="H415" t="n">
         <v>8421</v>
@@ -12520,7 +12520,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G419" t="n">
-        <v>2.36702346801758</v>
+        <v>2.367023229599</v>
       </c>
       <c r="H419" t="n">
         <v>3581</v>
@@ -12549,7 +12549,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34888553619385</v>
+        <v>2.34888529777527</v>
       </c>
       <c r="H420" t="n">
         <v>3648</v>
@@ -12578,7 +12578,7 @@
         <v>2.75</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H421" t="n">
         <v>5517</v>
@@ -12607,7 +12607,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H422" t="n">
         <v>7693</v>
@@ -12636,7 +12636,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G423" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H423" t="n">
         <v>7526</v>
@@ -12694,7 +12694,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47131752967834</v>
+        <v>2.47131776809692</v>
       </c>
       <c r="H425" t="n">
         <v>642</v>
@@ -12723,7 +12723,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026676177979</v>
+        <v>2.53026628494263</v>
       </c>
       <c r="H426" t="n">
         <v>2034</v>
@@ -12781,7 +12781,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G428" t="n">
-        <v>2.56200838088989</v>
+        <v>2.56200861930847</v>
       </c>
       <c r="H428" t="n">
         <v>30098</v>
@@ -12810,7 +12810,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>2.50305938720703</v>
+        <v>2.50305962562561</v>
       </c>
       <c r="H429" t="n">
         <v>9718</v>
@@ -12868,7 +12868,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957614898682</v>
+        <v>2.43957591056824</v>
       </c>
       <c r="H431" t="n">
         <v>2176</v>
@@ -12897,7 +12897,7 @@
         <v>2.75</v>
       </c>
       <c r="G432" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H432" t="n">
         <v>6692</v>
@@ -12984,7 +12984,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G435" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H435" t="n">
         <v>2214</v>
@@ -13071,7 +13071,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G438" t="n">
-        <v>2.63002634048462</v>
+        <v>2.63002610206604</v>
       </c>
       <c r="H438" t="n">
         <v>7550</v>
@@ -13129,7 +13129,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="n">
-        <v>2.49399042129517</v>
+        <v>2.49399018287659</v>
       </c>
       <c r="H440" t="n">
         <v>1970</v>
@@ -13216,7 +13216,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H443" t="n">
         <v>905</v>
@@ -13245,7 +13245,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H444" t="n">
         <v>305</v>
@@ -13332,7 +13332,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G447" t="n">
-        <v>2.57561159133911</v>
+        <v>2.57561182975769</v>
       </c>
       <c r="H447" t="n">
         <v>1026</v>
@@ -13361,7 +13361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350957870483</v>
       </c>
       <c r="H448" t="n">
         <v>14662</v>
@@ -13390,7 +13390,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H449" t="n">
         <v>5650</v>
@@ -13448,7 +13448,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H451" t="n">
         <v>17368</v>
@@ -13506,7 +13506,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H453" t="n">
         <v>1381</v>
@@ -13622,7 +13622,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G457" t="n">
-        <v>2.71164751052856</v>
+        <v>2.71164774894714</v>
       </c>
       <c r="H457" t="n">
         <v>267</v>
@@ -13651,7 +13651,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>2.81140732765198</v>
+        <v>2.8114070892334</v>
       </c>
       <c r="H458" t="n">
         <v>2064</v>
@@ -13709,7 +13709,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G460" t="n">
-        <v>2.64816451072693</v>
+        <v>2.64816427230835</v>
       </c>
       <c r="H460" t="n">
         <v>4577</v>
@@ -13738,7 +13738,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G461" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H461" t="n">
         <v>1854</v>
@@ -13883,7 +13883,7 @@
         <v>3</v>
       </c>
       <c r="G466" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H466" t="n">
         <v>2400</v>
@@ -13912,7 +13912,7 @@
         <v>3</v>
       </c>
       <c r="G467" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H467" t="n">
         <v>897</v>
@@ -13970,7 +13970,7 @@
         <v>3</v>
       </c>
       <c r="G469" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H469" t="n">
         <v>598</v>
@@ -13999,7 +13999,7 @@
         <v>3</v>
       </c>
       <c r="G470" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -14086,7 +14086,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G473" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H473" t="n">
         <v>7200</v>
@@ -14115,7 +14115,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G474" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H474" t="n">
         <v>468</v>
@@ -14231,7 +14231,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G478" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H478" t="n">
         <v>21409</v>
@@ -14289,7 +14289,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G480" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H480" t="n">
         <v>6941</v>
@@ -14318,7 +14318,7 @@
         <v>2.75</v>
       </c>
       <c r="G481" t="n">
-        <v>2.53743982315063</v>
+        <v>2.53743958473206</v>
       </c>
       <c r="H481" t="n">
         <v>5639</v>
@@ -14376,7 +14376,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G483" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H483" t="n">
         <v>869</v>
@@ -14405,7 +14405,7 @@
         <v>2.75</v>
       </c>
       <c r="G484" t="n">
-        <v>2.53743982315063</v>
+        <v>2.53743958473206</v>
       </c>
       <c r="H484" t="n">
         <v>1915</v>
@@ -14434,7 +14434,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H485" t="n">
         <v>2516</v>
@@ -14463,7 +14463,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G486" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H486" t="n">
         <v>1200</v>
@@ -14492,7 +14492,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61125612258911</v>
+        <v>2.61125588417053</v>
       </c>
       <c r="H487" t="n">
         <v>126942</v>
@@ -14724,7 +14724,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G495" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H495" t="n">
         <v>367</v>
@@ -15014,7 +15014,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H505" t="n">
         <v>2168</v>
@@ -15043,7 +15043,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G506" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H506" t="n">
         <v>516</v>
@@ -15072,7 +15072,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H507" t="n">
         <v>4213</v>
@@ -15101,7 +15101,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H508" t="n">
         <v>1909</v>
@@ -15130,7 +15130,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G509" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H509" t="n">
         <v>2208</v>
@@ -15159,7 +15159,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G510" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H510" t="n">
         <v>2337</v>
@@ -15188,7 +15188,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G511" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H511" t="n">
         <v>123</v>
@@ -15246,7 +15246,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G513" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H513" t="n">
         <v>2999</v>
@@ -15275,7 +15275,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G514" t="n">
-        <v>2.66661858558655</v>
+        <v>2.66661882400513</v>
       </c>
       <c r="H514" t="n">
         <v>3133</v>
@@ -15304,7 +15304,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G515" t="n">
-        <v>2.66661858558655</v>
+        <v>2.66661882400513</v>
       </c>
       <c r="H515" t="n">
         <v>1609</v>
@@ -15333,7 +15333,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G516" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H516" t="n">
         <v>9199</v>
@@ -15420,7 +15420,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H519" t="n">
         <v>107</v>
@@ -15536,7 +15536,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H523" t="n">
         <v>3940</v>
@@ -15565,7 +15565,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G524" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H524" t="n">
         <v>5586</v>
@@ -15797,7 +15797,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G532" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H532" t="n">
         <v>420</v>
@@ -15826,7 +15826,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G533" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H533" t="n">
         <v>8008</v>
@@ -15855,7 +15855,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G534" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H534" t="n">
         <v>1274</v>
@@ -15884,7 +15884,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G537" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G538" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H538" t="n">
         <v>908</v>
@@ -16029,7 +16029,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H540" t="n">
         <v>14503</v>
@@ -16058,7 +16058,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G541" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H541" t="n">
         <v>300</v>
@@ -16145,7 +16145,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H544" t="n">
         <v>5816</v>
@@ -16203,7 +16203,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120808601379</v>
       </c>
       <c r="H546" t="n">
         <v>23578</v>
@@ -16232,7 +16232,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120808601379</v>
       </c>
       <c r="H547" t="n">
         <v>4925</v>
@@ -16290,7 +16290,7 @@
         <v>3</v>
       </c>
       <c r="G549" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H549" t="n">
         <v>2815</v>
@@ -16377,7 +16377,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120808601379</v>
       </c>
       <c r="H552" t="n">
         <v>22273</v>
@@ -16551,7 +16551,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H558" t="n">
         <v>8956</v>
@@ -16609,7 +16609,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734327316284</v>
+        <v>2.77734279632568</v>
       </c>
       <c r="H560" t="n">
         <v>6973</v>
@@ -16667,7 +16667,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H562" t="n">
         <v>6763</v>
@@ -16696,7 +16696,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120784759521</v>
+        <v>2.73120808601379</v>
       </c>
       <c r="H563" t="n">
         <v>1740</v>
@@ -16754,7 +16754,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H565" t="n">
         <v>27</v>
@@ -16870,7 +16870,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.55589365959167</v>
+        <v>2.55589389801025</v>
       </c>
       <c r="H569" t="n">
         <v>3153</v>
@@ -16928,7 +16928,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G571" t="n">
-        <v>2.43594217300415</v>
+        <v>2.43594193458557</v>
       </c>
       <c r="H571" t="n">
         <v>13431</v>
@@ -17044,7 +17044,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G575" t="n">
-        <v>2.43594217300415</v>
+        <v>2.43594193458557</v>
       </c>
       <c r="H575" t="n">
         <v>838</v>
@@ -17073,7 +17073,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G576" t="n">
-        <v>2.43594217300415</v>
+        <v>2.43594193458557</v>
       </c>
       <c r="H576" t="n">
         <v>24569</v>
@@ -17102,7 +17102,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>2.66661858558655</v>
+        <v>2.66661882400513</v>
       </c>
       <c r="H577" t="n">
         <v>1902</v>
@@ -17189,7 +17189,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G580" t="n">
-        <v>2.63893723487854</v>
+        <v>2.63893699645996</v>
       </c>
       <c r="H580" t="n">
         <v>596</v>
@@ -17218,7 +17218,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G581" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H581" t="n">
         <v>3015</v>
@@ -17247,7 +17247,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G582" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H582" t="n">
         <v>1550</v>
@@ -17334,7 +17334,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G585" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H585" t="n">
         <v>1960</v>
@@ -17363,7 +17363,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G586" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H586" t="n">
         <v>2846</v>
@@ -17392,7 +17392,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.61125612258911</v>
+        <v>2.61125588417053</v>
       </c>
       <c r="H587" t="n">
         <v>2540</v>
@@ -17450,7 +17450,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G589" t="n">
-        <v>2.50975871086121</v>
+        <v>2.50975847244263</v>
       </c>
       <c r="H589" t="n">
         <v>6124</v>
@@ -17508,7 +17508,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>2.65739130973816</v>
+        <v>2.65739154815674</v>
       </c>
       <c r="H591" t="n">
         <v>2840</v>
@@ -17769,7 +17769,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.52821254730225</v>
+        <v>2.52821278572083</v>
       </c>
       <c r="H600" t="n">
         <v>1222</v>
@@ -17856,7 +17856,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G603" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H603" t="n">
         <v>2226</v>
@@ -17885,7 +17885,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>2.62048292160034</v>
+        <v>2.62048316001892</v>
       </c>
       <c r="H604" t="n">
         <v>50</v>
@@ -17943,7 +17943,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>2.50975871086121</v>
+        <v>2.50975847244263</v>
       </c>
       <c r="H606" t="n">
         <v>5678</v>
@@ -17972,7 +17972,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G607" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H607" t="n">
         <v>5192</v>
@@ -18001,7 +18001,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.54666686058044</v>
+        <v>2.54666662216187</v>
       </c>
       <c r="H608" t="n">
         <v>2394</v>
@@ -18030,7 +18030,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G609" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H609" t="n">
         <v>7373</v>
@@ -18059,7 +18059,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H610" t="n">
         <v>1755</v>
@@ -18088,7 +18088,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G611" t="n">
-        <v>2.62970995903015</v>
+        <v>2.62971019744873</v>
       </c>
       <c r="H611" t="n">
         <v>3646</v>
@@ -18117,7 +18117,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H612" t="n">
         <v>1353</v>
@@ -18146,7 +18146,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>2.64816427230835</v>
+        <v>2.64816403388977</v>
       </c>
       <c r="H613" t="n">
         <v>3521</v>
@@ -18233,7 +18233,7 @@
         <v>3</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H616" t="n">
         <v>31723</v>
@@ -18349,7 +18349,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734327316284</v>
+        <v>2.77734279632568</v>
       </c>
       <c r="H620" t="n">
         <v>10213</v>
@@ -18668,7 +18668,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H631" t="n">
         <v>57880</v>
@@ -18726,7 +18726,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.11874437332153</v>
+        <v>3.11874413490295</v>
       </c>
       <c r="H633" t="n">
         <v>2929</v>
@@ -18755,7 +18755,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>3.15565228462219</v>
+        <v>3.15565252304077</v>
       </c>
       <c r="H634" t="n">
         <v>2023</v>
@@ -18784,7 +18784,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G635" t="n">
-        <v>3.11874437332153</v>
+        <v>3.11874413490295</v>
       </c>
       <c r="H635" t="n">
         <v>15459</v>
@@ -18813,7 +18813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H636" t="n">
         <v>1875</v>
@@ -18871,7 +18871,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>3.15565228462219</v>
+        <v>3.15565252304077</v>
       </c>
       <c r="H638" t="n">
         <v>17794</v>
@@ -18900,7 +18900,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>3.19256043434143</v>
+        <v>3.19256067276001</v>
       </c>
       <c r="H639" t="n">
         <v>121971</v>
@@ -19045,7 +19045,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G644" t="n">
-        <v>3.11874437332153</v>
+        <v>3.11874413490295</v>
       </c>
       <c r="H644" t="n">
         <v>1108</v>
@@ -19132,7 +19132,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G647" t="n">
-        <v>2.97111129760742</v>
+        <v>2.97111105918884</v>
       </c>
       <c r="H647" t="n">
         <v>1164</v>
@@ -19248,7 +19248,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G651" t="n">
-        <v>3.17410659790039</v>
+        <v>3.17410635948181</v>
       </c>
       <c r="H651" t="n">
         <v>7106</v>
@@ -19277,7 +19277,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H652" t="n">
         <v>8899</v>
@@ -19306,7 +19306,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>3.19256043434143</v>
+        <v>3.19256067276001</v>
       </c>
       <c r="H653" t="n">
         <v>17275</v>
@@ -19335,7 +19335,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G654" t="n">
-        <v>3.2571496963501</v>
+        <v>3.25714993476868</v>
       </c>
       <c r="H654" t="n">
         <v>1756</v>
@@ -19422,7 +19422,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>3.43246388435364</v>
+        <v>3.43246412277222</v>
       </c>
       <c r="H657" t="n">
         <v>69496</v>
@@ -19451,7 +19451,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G658" t="n">
-        <v>3.29405784606934</v>
+        <v>3.29405808448792</v>
       </c>
       <c r="H658" t="n">
         <v>44455</v>
@@ -19509,7 +19509,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>3.13719820976257</v>
+        <v>3.13719797134399</v>
       </c>
       <c r="H660" t="n">
         <v>3302</v>
@@ -19538,7 +19538,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G661" t="n">
-        <v>3.10951662063599</v>
+        <v>3.10951685905457</v>
       </c>
       <c r="H661" t="n">
         <v>7980</v>
@@ -19596,7 +19596,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>2.96188402175903</v>
+        <v>2.96188426017761</v>
       </c>
       <c r="H663" t="n">
         <v>19629</v>
@@ -19625,7 +19625,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G664" t="n">
-        <v>2.90652203559875</v>
+        <v>2.90652179718018</v>
       </c>
       <c r="H664" t="n">
         <v>78917</v>
@@ -19654,7 +19654,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.88806796073914</v>
+        <v>2.88806772232056</v>
       </c>
       <c r="H665" t="n">
         <v>1731</v>
@@ -19683,7 +19683,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G666" t="n">
-        <v>2.85115957260132</v>
+        <v>2.85115933418274</v>
       </c>
       <c r="H666" t="n">
         <v>3592</v>
@@ -19712,7 +19712,7 @@
         <v>3</v>
       </c>
       <c r="G667" t="n">
-        <v>2.76811575889587</v>
+        <v>2.76811623573303</v>
       </c>
       <c r="H667" t="n">
         <v>3857</v>
@@ -19741,7 +19741,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H668" t="n">
         <v>18109</v>
@@ -19770,7 +19770,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G669" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H669" t="n">
         <v>2510</v>
@@ -19828,7 +19828,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>2.90652203559875</v>
+        <v>2.90652179718018</v>
       </c>
       <c r="H671" t="n">
         <v>3776</v>
@@ -19886,7 +19886,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G673" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H673" t="n">
         <v>229</v>
@@ -19944,7 +19944,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>2.92497611045837</v>
+        <v>2.92497587203979</v>
       </c>
       <c r="H675" t="n">
         <v>12549</v>
@@ -20002,7 +20002,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.90652203559875</v>
+        <v>2.90652179718018</v>
       </c>
       <c r="H677" t="n">
         <v>213</v>
@@ -20060,7 +20060,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.11874437332153</v>
+        <v>3.11874413490295</v>
       </c>
       <c r="H679" t="n">
         <v>14622</v>
@@ -20234,7 +20234,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>3.05415439605713</v>
+        <v>3.05415463447571</v>
       </c>
       <c r="H685" t="n">
         <v>1682</v>
@@ -20379,7 +20379,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>2.90652203559875</v>
+        <v>2.90652179718018</v>
       </c>
       <c r="H690" t="n">
         <v>20373</v>
@@ -20582,7 +20582,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G697" t="n">
-        <v>2.96188402175903</v>
+        <v>2.96188426017761</v>
       </c>
       <c r="H697" t="n">
         <v>422</v>
@@ -20611,7 +20611,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H698" t="n">
         <v>581</v>
@@ -20640,7 +20640,7 @@
         <v>3.25</v>
       </c>
       <c r="G699" t="n">
-        <v>2.99879217147827</v>
+        <v>2.99879240989685</v>
       </c>
       <c r="H699" t="n">
         <v>620</v>
@@ -20785,7 +20785,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G704" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H704" t="n">
         <v>7911</v>
@@ -20814,7 +20814,7 @@
         <v>3.25</v>
       </c>
       <c r="G705" t="n">
-        <v>2.99879217147827</v>
+        <v>2.99879240989685</v>
       </c>
       <c r="H705" t="n">
         <v>46785</v>
@@ -20843,7 +20843,7 @@
         <v>3.25</v>
       </c>
       <c r="G706" t="n">
-        <v>2.99879217147827</v>
+        <v>2.99879240989685</v>
       </c>
       <c r="H706" t="n">
         <v>3156</v>
@@ -20872,7 +20872,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>2.98033809661865</v>
+        <v>2.98033833503723</v>
       </c>
       <c r="H707" t="n">
         <v>553</v>
@@ -20901,7 +20901,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G708" t="n">
-        <v>2.98956537246704</v>
+        <v>2.98956513404846</v>
       </c>
       <c r="H708" t="n">
         <v>10802</v>
@@ -20988,7 +20988,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>3.17410659790039</v>
+        <v>3.17410635948181</v>
       </c>
       <c r="H711" t="n">
         <v>37895</v>
@@ -21191,7 +21191,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G718" t="n">
-        <v>3.42463636398315</v>
+        <v>3.42463660240173</v>
       </c>
       <c r="H718" t="n">
         <v>19996</v>
@@ -21249,7 +21249,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G720" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H720" t="n">
         <v>26821</v>
@@ -21278,7 +21278,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G721" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H721" t="n">
         <v>22556</v>
@@ -21423,7 +21423,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>3.68734836578369</v>
+        <v>3.68734812736511</v>
       </c>
       <c r="H726" t="n">
         <v>2271</v>
@@ -21481,7 +21481,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G728" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H728" t="n">
         <v>10721</v>
@@ -21510,7 +21510,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G729" t="n">
-        <v>3.62167000770569</v>
+        <v>3.62167024612427</v>
       </c>
       <c r="H729" t="n">
         <v>4368</v>
@@ -21539,7 +21539,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G730" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H730" t="n">
         <v>12120</v>
@@ -21568,7 +21568,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G731" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H731" t="n">
         <v>10096</v>
@@ -21626,7 +21626,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G733" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H733" t="n">
         <v>8164</v>
@@ -21742,7 +21742,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G737" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H737" t="n">
         <v>2069</v>
@@ -21887,7 +21887,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>3.53722715377808</v>
+        <v>3.5372269153595</v>
       </c>
       <c r="H742" t="n">
         <v>32</v>
@@ -22177,7 +22177,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H752" t="n">
         <v>1100</v>
@@ -22206,7 +22206,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H753" t="n">
         <v>4824</v>
@@ -22235,7 +22235,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H754" t="n">
         <v>15245</v>
@@ -22322,7 +22322,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G757" t="n">
-        <v>3.66858315467834</v>
+        <v>3.66858291625977</v>
       </c>
       <c r="H757" t="n">
         <v>8377</v>
@@ -22467,7 +22467,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G762" t="n">
-        <v>3.62167000770569</v>
+        <v>3.62167024612427</v>
       </c>
       <c r="H762" t="n">
         <v>7020</v>
@@ -22612,7 +22612,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H767" t="n">
         <v>18904</v>
@@ -22641,7 +22641,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G768" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H768" t="n">
         <v>7062</v>
@@ -22728,7 +22728,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G771" t="n">
-        <v>3.64981818199158</v>
+        <v>3.649817943573</v>
       </c>
       <c r="H771" t="n">
         <v>1791</v>
@@ -22960,7 +22960,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G779" t="n">
-        <v>3.68734836578369</v>
+        <v>3.68734812736511</v>
       </c>
       <c r="H779" t="n">
         <v>1305</v>
@@ -23105,7 +23105,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G784" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H784" t="n">
         <v>297</v>
@@ -23134,7 +23134,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G785" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H785" t="n">
         <v>0</v>
@@ -23221,7 +23221,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H788" t="n">
         <v>372</v>
@@ -23308,7 +23308,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G791" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H791" t="n">
         <v>2121</v>
@@ -23395,7 +23395,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H794" t="n">
         <v>18360</v>
@@ -23424,7 +23424,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G795" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H795" t="n">
         <v>5078</v>
@@ -23511,7 +23511,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G798" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H798" t="n">
         <v>12843</v>
@@ -23569,7 +23569,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G800" t="n">
-        <v>3.8562343120575</v>
+        <v>3.85623455047607</v>
       </c>
       <c r="H800" t="n">
         <v>1776</v>
@@ -23598,7 +23598,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G801" t="n">
-        <v>3.88438200950623</v>
+        <v>3.88438177108765</v>
       </c>
       <c r="H801" t="n">
         <v>4253</v>
@@ -23627,7 +23627,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G802" t="n">
-        <v>3.88438200950623</v>
+        <v>3.88438177108765</v>
       </c>
       <c r="H802" t="n">
         <v>2408</v>
@@ -23685,7 +23685,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G804" t="n">
-        <v>3.96882510185242</v>
+        <v>3.96882486343384</v>
       </c>
       <c r="H804" t="n">
         <v>11913</v>
@@ -23743,7 +23743,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H806" t="n">
         <v>41169</v>
@@ -23888,7 +23888,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G811" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H811" t="n">
         <v>17935</v>
@@ -23917,7 +23917,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G812" t="n">
-        <v>4.10018110275269</v>
+        <v>4.10018062591553</v>
       </c>
       <c r="H812" t="n">
         <v>12249</v>
@@ -23946,7 +23946,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G813" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H813" t="n">
         <v>3381</v>
@@ -24236,7 +24236,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G823" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H823" t="n">
         <v>41614</v>
@@ -24294,7 +24294,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G825" t="n">
-        <v>4.16585874557495</v>
+        <v>4.16585922241211</v>
       </c>
       <c r="H825" t="n">
         <v>2822</v>
@@ -24323,7 +24323,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G826" t="n">
-        <v>4.15647602081299</v>
+        <v>4.15647649765015</v>
       </c>
       <c r="H826" t="n">
         <v>4126</v>
@@ -24410,7 +24410,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G829" t="n">
-        <v>3.99697303771973</v>
+        <v>3.99697279930115</v>
       </c>
       <c r="H829" t="n">
         <v>5363</v>
@@ -24439,7 +24439,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G830" t="n">
-        <v>4.30659770965576</v>
+        <v>4.3065972328186</v>
       </c>
       <c r="H830" t="n">
         <v>13944</v>
@@ -24468,7 +24468,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G831" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H831" t="n">
         <v>8663</v>
@@ -24526,7 +24526,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G833" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H833" t="n">
         <v>15658</v>
@@ -24613,7 +24613,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G836" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H836" t="n">
         <v>10141</v>
@@ -24671,7 +24671,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G838" t="n">
-        <v>3.68734836578369</v>
+        <v>3.68734812736511</v>
       </c>
       <c r="H838" t="n">
         <v>2963</v>
@@ -24700,7 +24700,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H839" t="n">
         <v>15833</v>
@@ -24758,7 +24758,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G841" t="n">
-        <v>3.86561679840088</v>
+        <v>3.8656165599823</v>
       </c>
       <c r="H841" t="n">
         <v>3553</v>
@@ -24787,7 +24787,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H842" t="n">
         <v>5470</v>
@@ -24874,7 +24874,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G845" t="n">
-        <v>3.92191219329834</v>
+        <v>3.92191243171692</v>
       </c>
       <c r="H845" t="n">
         <v>3484</v>
@@ -25019,7 +25019,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G850" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H850" t="n">
         <v>3030</v>
@@ -25106,7 +25106,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H853" t="n">
         <v>2333</v>
@@ -25164,7 +25164,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G855" t="n">
-        <v>3.81870412826538</v>
+        <v>3.81870436668396</v>
       </c>
       <c r="H855" t="n">
         <v>12319</v>
@@ -25280,7 +25280,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H859" t="n">
         <v>7062</v>
@@ -25338,7 +25338,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G861" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H861" t="n">
         <v>9293</v>
@@ -25454,7 +25454,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G865" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H865" t="n">
         <v>808</v>
@@ -25512,7 +25512,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G867" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H867" t="n">
         <v>611</v>
@@ -25570,7 +25570,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G869" t="n">
-        <v>3.92191219329834</v>
+        <v>3.92191243171692</v>
       </c>
       <c r="H869" t="n">
         <v>13902</v>
@@ -25657,7 +25657,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G872" t="n">
-        <v>3.92191219329834</v>
+        <v>3.92191243171692</v>
       </c>
       <c r="H872" t="n">
         <v>570</v>
@@ -25802,7 +25802,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H877" t="n">
         <v>5546</v>
@@ -25918,7 +25918,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G881" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H881" t="n">
         <v>10744</v>
@@ -25976,7 +25976,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G883" t="n">
-        <v>3.74364376068115</v>
+        <v>3.74364352226257</v>
       </c>
       <c r="H883" t="n">
         <v>50</v>
@@ -26005,7 +26005,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H884" t="n">
         <v>2574</v>
@@ -26034,7 +26034,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G885" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H885" t="n">
         <v>3925</v>
@@ -26063,7 +26063,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G886" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H886" t="n">
         <v>1154</v>
@@ -26092,7 +26092,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>3.56537461280823</v>
+        <v>3.56537485122681</v>
       </c>
       <c r="H887" t="n">
         <v>6727</v>
@@ -26179,7 +26179,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G890" t="n">
-        <v>3.66858315467834</v>
+        <v>3.66858291625977</v>
       </c>
       <c r="H890" t="n">
         <v>6569</v>
@@ -26208,7 +26208,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G891" t="n">
-        <v>3.65920042991638</v>
+        <v>3.65920066833496</v>
       </c>
       <c r="H891" t="n">
         <v>1081</v>
@@ -26295,7 +26295,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>3.60290503501892</v>
+        <v>3.60290479660034</v>
       </c>
       <c r="H894" t="n">
         <v>1455</v>
@@ -26353,7 +26353,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G896" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H896" t="n">
         <v>4606</v>
@@ -26440,7 +26440,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G899" t="n">
-        <v>3.99697303771973</v>
+        <v>3.99697279930115</v>
       </c>
       <c r="H899" t="n">
         <v>4331</v>
@@ -26469,7 +26469,7 @@
         <v>4.25</v>
       </c>
       <c r="G900" t="n">
-        <v>3.98759055137634</v>
+        <v>3.98759031295776</v>
       </c>
       <c r="H900" t="n">
         <v>477</v>
@@ -26498,7 +26498,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G901" t="n">
-        <v>3.97820734977722</v>
+        <v>3.9782075881958</v>
       </c>
       <c r="H901" t="n">
         <v>160</v>
@@ -26556,7 +26556,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G903" t="n">
-        <v>3.86561679840088</v>
+        <v>3.8656165599823</v>
       </c>
       <c r="H903" t="n">
         <v>7451</v>
@@ -26585,7 +26585,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G904" t="n">
-        <v>3.86561679840088</v>
+        <v>3.8656165599823</v>
       </c>
       <c r="H904" t="n">
         <v>0</v>
@@ -26643,7 +26643,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G906" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H906" t="n">
         <v>7171</v>
@@ -26846,7 +26846,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G913" t="n">
-        <v>3.84685158729553</v>
+        <v>3.84685182571411</v>
       </c>
       <c r="H913" t="n">
         <v>5572</v>
@@ -26875,7 +26875,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G914" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H914" t="n">
         <v>2431</v>
@@ -26904,7 +26904,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G915" t="n">
-        <v>3.81870412826538</v>
+        <v>3.81870436668396</v>
       </c>
       <c r="H915" t="n">
         <v>694</v>
@@ -26933,7 +26933,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G916" t="n">
-        <v>3.81870412826538</v>
+        <v>3.81870436668396</v>
       </c>
       <c r="H916" t="n">
         <v>6079</v>
@@ -26962,7 +26962,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H917" t="n">
         <v>1682</v>
@@ -27020,7 +27020,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G919" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H919" t="n">
         <v>172</v>
@@ -27078,7 +27078,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G921" t="n">
-        <v>3.76240873336792</v>
+        <v>3.7624089717865</v>
       </c>
       <c r="H921" t="n">
         <v>3356</v>
@@ -27136,7 +27136,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G923" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H923" t="n">
         <v>10267</v>
@@ -27165,7 +27165,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>3.79993891716003</v>
+        <v>3.79993915557861</v>
       </c>
       <c r="H924" t="n">
         <v>2845</v>
@@ -27194,7 +27194,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G925" t="n">
-        <v>3.8562343120575</v>
+        <v>3.85623455047607</v>
       </c>
       <c r="H925" t="n">
         <v>6744</v>
@@ -27223,7 +27223,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G926" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H926" t="n">
         <v>81918</v>
@@ -27252,7 +27252,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H927" t="n">
         <v>16501</v>
@@ -27281,7 +27281,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G928" t="n">
-        <v>4.10018110275269</v>
+        <v>4.10018062591553</v>
       </c>
       <c r="H928" t="n">
         <v>19219</v>
@@ -27310,7 +27310,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G929" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H929" t="n">
         <v>7657</v>
@@ -27339,7 +27339,7 @@
         <v>4.25</v>
       </c>
       <c r="G930" t="n">
-        <v>3.98759055137634</v>
+        <v>3.98759031295776</v>
       </c>
       <c r="H930" t="n">
         <v>18877</v>
@@ -27397,7 +27397,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G932" t="n">
-        <v>4.08141565322876</v>
+        <v>4.08141613006592</v>
       </c>
       <c r="H932" t="n">
         <v>12772</v>
@@ -27455,7 +27455,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G934" t="n">
-        <v>3.92191219329834</v>
+        <v>3.92191243171692</v>
       </c>
       <c r="H934" t="n">
         <v>1187</v>
@@ -27484,7 +27484,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G935" t="n">
-        <v>3.96882510185242</v>
+        <v>3.96882486343384</v>
       </c>
       <c r="H935" t="n">
         <v>193</v>
@@ -27513,7 +27513,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G936" t="n">
-        <v>3.87499952316284</v>
+        <v>3.87499976158142</v>
       </c>
       <c r="H936" t="n">
         <v>1816</v>
@@ -27687,7 +27687,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G942" t="n">
-        <v>3.99697303771973</v>
+        <v>3.99697279930115</v>
       </c>
       <c r="H942" t="n">
         <v>4920</v>
@@ -27774,7 +27774,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G945" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H945" t="n">
         <v>1416</v>
@@ -27803,7 +27803,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G946" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H946" t="n">
         <v>5443</v>
@@ -27832,7 +27832,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G947" t="n">
-        <v>4.13771152496338</v>
+        <v>4.13771104812622</v>
       </c>
       <c r="H947" t="n">
         <v>1999</v>
@@ -27948,7 +27948,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G951" t="n">
-        <v>4.16585874557495</v>
+        <v>4.16585922241211</v>
       </c>
       <c r="H951" t="n">
         <v>2435</v>
@@ -28093,7 +28093,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.16585874557495</v>
+        <v>4.16585922241211</v>
       </c>
       <c r="H956" t="n">
         <v>2077</v>
@@ -28122,7 +28122,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.14709424972534</v>
+        <v>4.14709377288818</v>
       </c>
       <c r="H957" t="n">
         <v>2834</v>
@@ -28151,7 +28151,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G958" t="n">
-        <v>4.15647602081299</v>
+        <v>4.15647649765015</v>
       </c>
       <c r="H958" t="n">
         <v>1651</v>
@@ -28267,7 +28267,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G962" t="n">
-        <v>4.15647602081299</v>
+        <v>4.15647649765015</v>
       </c>
       <c r="H962" t="n">
         <v>1164</v>
@@ -39003,6 +39003,35 @@
         <v>2759</v>
       </c>
       <c r="I1332" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1333" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1333" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="G1333" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="H1333" t="n">
+        <v>12223</v>
+      </c>
+      <c r="I1333" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161709785461</v>
+        <v>3.10161733627319</v>
       </c>
       <c r="H5" t="n">
         <v>23147</v>
@@ -601,7 +601,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G8" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H8" t="n">
         <v>720993</v>
@@ -775,7 +775,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H14" t="n">
         <v>18667</v>
@@ -804,7 +804,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G15" t="n">
-        <v>3.39182686805725</v>
+        <v>3.39182662963867</v>
       </c>
       <c r="H15" t="n">
         <v>33287</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H16" t="n">
         <v>44813</v>
@@ -862,7 +862,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924377441406</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H17" t="n">
         <v>150547</v>
@@ -891,7 +891,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924377441406</v>
+        <v>3.70924425125122</v>
       </c>
       <c r="H18" t="n">
         <v>290894</v>
@@ -1036,7 +1036,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H23" t="n">
         <v>29141</v>
@@ -1094,7 +1094,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.89515995979309</v>
+        <v>3.89515948295593</v>
       </c>
       <c r="H25" t="n">
         <v>186140</v>
@@ -1152,7 +1152,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>3.77726197242737</v>
+        <v>3.77726149559021</v>
       </c>
       <c r="H27" t="n">
         <v>75595</v>
@@ -1210,7 +1210,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993438720703</v>
+        <v>3.79993486404419</v>
       </c>
       <c r="H29" t="n">
         <v>38465</v>
@@ -1239,7 +1239,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G30" t="n">
-        <v>3.68657112121582</v>
+        <v>3.6865713596344</v>
       </c>
       <c r="H30" t="n">
         <v>57117</v>
@@ -1326,7 +1326,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G33" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H33" t="n">
         <v>18869</v>
@@ -1384,7 +1384,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>3.56413912773132</v>
+        <v>3.56413888931274</v>
       </c>
       <c r="H35" t="n">
         <v>54741</v>
@@ -1413,7 +1413,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G36" t="n">
-        <v>3.56413912773132</v>
+        <v>3.56413888931274</v>
       </c>
       <c r="H36" t="n">
         <v>13961</v>
@@ -1529,7 +1529,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633069992065</v>
+        <v>3.78633117675781</v>
       </c>
       <c r="H40" t="n">
         <v>4635</v>
@@ -1587,7 +1587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74552035331726</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H42" t="n">
         <v>23606</v>
@@ -1616,7 +1616,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.74552035331726</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H43" t="n">
         <v>10910</v>
@@ -1674,7 +1674,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H45" t="n">
         <v>2007</v>
@@ -1703,7 +1703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738218307495</v>
+        <v>3.72738194465637</v>
       </c>
       <c r="H46" t="n">
         <v>6914</v>
@@ -1761,7 +1761,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>3.68657112121582</v>
+        <v>3.6865713596344</v>
       </c>
       <c r="H48" t="n">
         <v>2180</v>
@@ -1877,7 +1877,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.74552035331726</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H52" t="n">
         <v>919</v>
@@ -1906,7 +1906,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.74552035331726</v>
+        <v>3.74552011489868</v>
       </c>
       <c r="H53" t="n">
         <v>5908</v>
@@ -2051,7 +2051,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G58" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H58" t="n">
         <v>4003</v>
@@ -2080,7 +2080,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G59" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H59" t="n">
         <v>6637</v>
@@ -2138,7 +2138,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G61" t="n">
-        <v>3.64576053619385</v>
+        <v>3.64576077461243</v>
       </c>
       <c r="H61" t="n">
         <v>93456</v>
@@ -2167,7 +2167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.7001748085022</v>
+        <v>3.70017504692078</v>
       </c>
       <c r="H62" t="n">
         <v>8191</v>
@@ -2225,7 +2225,7 @@
         <v>4.07499980926514</v>
       </c>
       <c r="G64" t="n">
-        <v>3.69564032554626</v>
+        <v>3.69564008712769</v>
       </c>
       <c r="H64" t="n">
         <v>5559</v>
@@ -2312,7 +2312,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H67" t="n">
         <v>3242</v>
@@ -2486,7 +2486,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69110608100891</v>
+        <v>3.69110584259033</v>
       </c>
       <c r="H73" t="n">
         <v>6007</v>
@@ -2602,7 +2602,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G77" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H77" t="n">
         <v>10457</v>
@@ -2631,7 +2631,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.7001748085022</v>
+        <v>3.70017504692078</v>
       </c>
       <c r="H78" t="n">
         <v>36913</v>
@@ -2660,7 +2660,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G79" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H79" t="n">
         <v>16654</v>
@@ -2718,7 +2718,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>3.58227682113647</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H81" t="n">
         <v>14163</v>
@@ -2747,7 +2747,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G82" t="n">
-        <v>3.57320809364319</v>
+        <v>3.57320785522461</v>
       </c>
       <c r="H82" t="n">
         <v>5877</v>
@@ -2776,7 +2776,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G83" t="n">
-        <v>3.54600071907043</v>
+        <v>3.54600095748901</v>
       </c>
       <c r="H83" t="n">
         <v>3337</v>
@@ -2805,7 +2805,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G84" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H84" t="n">
         <v>21297</v>
@@ -2863,7 +2863,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729238510132</v>
+        <v>3.38729214668274</v>
       </c>
       <c r="H86" t="n">
         <v>4796</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.44624137878418</v>
+        <v>3.4462411403656</v>
       </c>
       <c r="H89" t="n">
         <v>5063</v>
@@ -2979,7 +2979,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.46437931060791</v>
+        <v>3.46437954902649</v>
       </c>
       <c r="H90" t="n">
         <v>2965</v>
@@ -3037,7 +3037,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>3.47344851493835</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H92" t="n">
         <v>2793</v>
@@ -3095,7 +3095,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903400421143</v>
+        <v>3.41903424263</v>
       </c>
       <c r="H94" t="n">
         <v>14502</v>
@@ -3182,7 +3182,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531034469604</v>
+        <v>3.45531058311462</v>
       </c>
       <c r="H97" t="n">
         <v>13724</v>
@@ -3211,7 +3211,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>3.46891379356384</v>
+        <v>3.46891403198242</v>
       </c>
       <c r="H98" t="n">
         <v>2853</v>
@@ -3559,7 +3559,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>3.60948443412781</v>
+        <v>3.60948419570923</v>
       </c>
       <c r="H110" t="n">
         <v>33451</v>
@@ -3588,7 +3588,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>3.58227682113647</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H111" t="n">
         <v>13196</v>
@@ -3646,7 +3646,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077586174011</v>
+        <v>3.45077562332153</v>
       </c>
       <c r="H113" t="n">
         <v>3151</v>
@@ -3733,7 +3733,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>3.58227682113647</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H116" t="n">
         <v>1006</v>
@@ -3791,7 +3791,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831321716309</v>
+        <v>3.71831274032593</v>
       </c>
       <c r="H118" t="n">
         <v>29715</v>
@@ -3820,7 +3820,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G119" t="n">
-        <v>3.58227682113647</v>
+        <v>3.58227705955505</v>
       </c>
       <c r="H119" t="n">
         <v>35244</v>
@@ -3907,7 +3907,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G122" t="n">
-        <v>3.46437931060791</v>
+        <v>3.46437954902649</v>
       </c>
       <c r="H122" t="n">
         <v>1150</v>
@@ -4139,7 +4139,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>3.40543055534363</v>
+        <v>3.40543079376221</v>
       </c>
       <c r="H130" t="n">
         <v>2361</v>
@@ -4168,7 +4168,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G131" t="n">
-        <v>3.27392935752869</v>
+        <v>3.27392911911011</v>
       </c>
       <c r="H131" t="n">
         <v>8662</v>
@@ -4255,7 +4255,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G134" t="n">
-        <v>3.21951460838318</v>
+        <v>3.21951484680176</v>
       </c>
       <c r="H134" t="n">
         <v>60461</v>
@@ -4371,7 +4371,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020569801331</v>
+        <v>3.31020545959473</v>
       </c>
       <c r="H138" t="n">
         <v>2087</v>
@@ -4487,7 +4487,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>3.47344851493835</v>
+        <v>3.47344827651978</v>
       </c>
       <c r="H142" t="n">
         <v>1980</v>
@@ -4690,7 +4690,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.14696264266968</v>
+        <v>3.1469624042511</v>
       </c>
       <c r="H149" t="n">
         <v>11513</v>
@@ -4719,7 +4719,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>3.25125670433044</v>
+        <v>3.25125646591187</v>
       </c>
       <c r="H150" t="n">
         <v>5307</v>
@@ -4777,7 +4777,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.97465038299561</v>
+        <v>2.97465062141418</v>
       </c>
       <c r="H152" t="n">
         <v>14806</v>
@@ -4806,7 +4806,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G153" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H153" t="n">
         <v>14357</v>
@@ -4835,7 +4835,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570162773132</v>
       </c>
       <c r="H154" t="n">
         <v>1770</v>
@@ -4893,7 +4893,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H156" t="n">
         <v>10379</v>
@@ -4922,7 +4922,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756345748901</v>
+        <v>2.89756321907043</v>
       </c>
       <c r="H157" t="n">
         <v>4634</v>
@@ -5096,7 +5096,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G163" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H163" t="n">
         <v>1018</v>
@@ -5328,7 +5328,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615158081055</v>
+        <v>3.10615181922913</v>
       </c>
       <c r="H171" t="n">
         <v>59616</v>
@@ -5502,7 +5502,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G177" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H177" t="n">
         <v>9793</v>
@@ -5531,7 +5531,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.0245304107666</v>
+        <v>3.02453017234802</v>
       </c>
       <c r="H178" t="n">
         <v>1198</v>
@@ -5589,7 +5589,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G180" t="n">
-        <v>3.02906465530396</v>
+        <v>3.02906441688538</v>
       </c>
       <c r="H180" t="n">
         <v>998</v>
@@ -5618,7 +5618,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>2.97465038299561</v>
+        <v>2.97465062141418</v>
       </c>
       <c r="H181" t="n">
         <v>3283</v>
@@ -5705,7 +5705,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G184" t="n">
-        <v>3.04266834259033</v>
+        <v>3.04266858100891</v>
       </c>
       <c r="H184" t="n">
         <v>656</v>
@@ -5937,7 +5937,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627155303955</v>
+        <v>3.05627179145813</v>
       </c>
       <c r="H192" t="n">
         <v>9528</v>
@@ -6053,7 +6053,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H196" t="n">
         <v>9781</v>
@@ -6111,7 +6111,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G198" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H198" t="n">
         <v>8621</v>
@@ -6140,7 +6140,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G199" t="n">
-        <v>2.92023587226868</v>
+        <v>2.92023611068726</v>
       </c>
       <c r="H199" t="n">
         <v>6598</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744324684143</v>
+        <v>2.94744300842285</v>
       </c>
       <c r="H204" t="n">
         <v>41187</v>
@@ -6459,7 +6459,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G210" t="n">
-        <v>3.21951460838318</v>
+        <v>3.21951484680176</v>
       </c>
       <c r="H210" t="n">
         <v>21001</v>
@@ -6575,7 +6575,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753280639648</v>
+        <v>3.28753304481506</v>
       </c>
       <c r="H214" t="n">
         <v>1310</v>
@@ -6749,7 +6749,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603160858154</v>
+        <v>3.15603184700012</v>
       </c>
       <c r="H220" t="n">
         <v>16930</v>
@@ -6778,7 +6778,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G221" t="n">
-        <v>2.92930483818054</v>
+        <v>2.92930507659912</v>
       </c>
       <c r="H221" t="n">
         <v>10002</v>
@@ -6865,7 +6865,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035584449768</v>
+        <v>2.87035608291626</v>
       </c>
       <c r="H224" t="n">
         <v>4992</v>
@@ -6894,7 +6894,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570138931274</v>
+        <v>2.91570162773132</v>
       </c>
       <c r="H225" t="n">
         <v>3170</v>
@@ -6981,7 +6981,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H228" t="n">
         <v>593</v>
@@ -7213,7 +7213,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>2.85675263404846</v>
+        <v>2.85675287246704</v>
       </c>
       <c r="H236" t="n">
         <v>11979</v>
@@ -7300,7 +7300,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.78420042991638</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H239" t="n">
         <v>10412</v>
@@ -7445,7 +7445,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H244" t="n">
         <v>4956</v>
@@ -7503,7 +7503,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G246" t="n">
-        <v>2.8476836681366</v>
+        <v>2.84768342971802</v>
       </c>
       <c r="H246" t="n">
         <v>8994</v>
@@ -7532,7 +7532,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.78420042991638</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H247" t="n">
         <v>5286</v>
@@ -7561,7 +7561,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.78420042991638</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H248" t="n">
         <v>1003</v>
@@ -7648,7 +7648,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G251" t="n">
-        <v>2.7524585723877</v>
+        <v>2.75245881080627</v>
       </c>
       <c r="H251" t="n">
         <v>1377</v>
@@ -7677,7 +7677,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G252" t="n">
-        <v>2.7524585723877</v>
+        <v>2.75245881080627</v>
       </c>
       <c r="H252" t="n">
         <v>336</v>
@@ -7793,7 +7793,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.78420042991638</v>
+        <v>2.7842001914978</v>
       </c>
       <c r="H256" t="n">
         <v>2600</v>
@@ -7822,7 +7822,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350957870483</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H257" t="n">
         <v>8062</v>
@@ -7851,7 +7851,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071671485901</v>
+        <v>2.72071647644043</v>
       </c>
       <c r="H258" t="n">
         <v>1704</v>
@@ -8170,7 +8170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H269" t="n">
         <v>1163</v>
@@ -8286,7 +8286,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>2.59828472137451</v>
+        <v>2.59828448295593</v>
       </c>
       <c r="H273" t="n">
         <v>1912</v>
@@ -8344,7 +8344,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H275" t="n">
         <v>1505</v>
@@ -8373,7 +8373,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H276" t="n">
         <v>8540</v>
@@ -8402,7 +8402,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945569992065</v>
+        <v>2.48945546150208</v>
       </c>
       <c r="H277" t="n">
         <v>995</v>
@@ -8489,7 +8489,7 @@
         <v>2.625</v>
       </c>
       <c r="G280" t="n">
-        <v>2.38062691688538</v>
+        <v>2.38062715530396</v>
       </c>
       <c r="H280" t="n">
         <v>7350</v>
@@ -8779,7 +8779,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G290" t="n">
-        <v>2.16750431060791</v>
+        <v>2.16750454902649</v>
       </c>
       <c r="H290" t="n">
         <v>7059</v>
@@ -8895,7 +8895,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>2.34435081481934</v>
+        <v>2.34435105323792</v>
       </c>
       <c r="H294" t="n">
         <v>591</v>
@@ -8982,7 +8982,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G297" t="n">
-        <v>2.1856427192688</v>
+        <v>2.18564248085022</v>
       </c>
       <c r="H297" t="n">
         <v>16353</v>
@@ -9127,7 +9127,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>2.35795450210571</v>
+        <v>2.35795426368713</v>
       </c>
       <c r="H302" t="n">
         <v>5211</v>
@@ -9301,7 +9301,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H308" t="n">
         <v>371</v>
@@ -9330,7 +9330,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957591056824</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H309" t="n">
         <v>7036</v>
@@ -9359,7 +9359,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957591056824</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H311" t="n">
         <v>5875</v>
@@ -9533,7 +9533,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G316" t="n">
-        <v>2.50759387016296</v>
+        <v>2.50759410858154</v>
       </c>
       <c r="H316" t="n">
         <v>2151</v>
@@ -9591,7 +9591,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026628494263</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H318" t="n">
         <v>3432</v>
@@ -9620,7 +9620,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G319" t="n">
-        <v>2.55747365951538</v>
+        <v>2.55747389793396</v>
       </c>
       <c r="H319" t="n">
         <v>2553</v>
@@ -9649,7 +9649,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H320" t="n">
         <v>752</v>
@@ -9794,7 +9794,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.39876532554626</v>
+        <v>2.39876508712769</v>
       </c>
       <c r="H325" t="n">
         <v>2044</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H326" t="n">
         <v>10875</v>
@@ -9881,7 +9881,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H328" t="n">
         <v>9578</v>
@@ -9910,7 +9910,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.42143821716309</v>
+        <v>2.42143797874451</v>
       </c>
       <c r="H329" t="n">
         <v>4763</v>
@@ -9997,7 +9997,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.31260943412781</v>
+        <v>2.31260919570923</v>
       </c>
       <c r="H332" t="n">
         <v>4605</v>
@@ -10084,7 +10084,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G335" t="n">
-        <v>2.31260943412781</v>
+        <v>2.31260919570923</v>
       </c>
       <c r="H335" t="n">
         <v>4870</v>
@@ -10113,7 +10113,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.3080747127533</v>
+        <v>2.30807447433472</v>
       </c>
       <c r="H336" t="n">
         <v>989</v>
@@ -10403,7 +10403,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G346" t="n">
-        <v>2.31260943412781</v>
+        <v>2.31260919570923</v>
       </c>
       <c r="H346" t="n">
         <v>2050</v>
@@ -10461,7 +10461,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423084259033</v>
+        <v>2.39423108100891</v>
       </c>
       <c r="H348" t="n">
         <v>518</v>
@@ -10606,7 +10606,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>2.36248922348022</v>
+        <v>2.36248898506165</v>
       </c>
       <c r="H353" t="n">
         <v>4548</v>
@@ -10722,7 +10722,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.35795450210571</v>
+        <v>2.35795426368713</v>
       </c>
       <c r="H357" t="n">
         <v>1884</v>
@@ -10925,7 +10925,7 @@
         <v>2.75</v>
       </c>
       <c r="G364" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H364" t="n">
         <v>5478</v>
@@ -11215,7 +11215,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.38969612121582</v>
+        <v>2.3896963596344</v>
       </c>
       <c r="H374" t="n">
         <v>7617</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957591056824</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H376" t="n">
         <v>7974</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H379" t="n">
         <v>125340</v>
@@ -11389,7 +11389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H380" t="n">
         <v>15968</v>
@@ -11563,7 +11563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H386" t="n">
         <v>6461</v>
@@ -11592,7 +11592,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H387" t="n">
         <v>400</v>
@@ -11650,7 +11650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H389" t="n">
         <v>5695</v>
@@ -11679,7 +11679,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H390" t="n">
         <v>3704</v>
@@ -11737,7 +11737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H392" t="n">
         <v>8970</v>
@@ -11882,7 +11882,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933572769165</v>
+        <v>2.53933548927307</v>
       </c>
       <c r="H397" t="n">
         <v>6517</v>
@@ -11940,7 +11940,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.53480124473572</v>
+        <v>2.53480100631714</v>
       </c>
       <c r="H399" t="n">
         <v>73</v>
@@ -11969,7 +11969,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G400" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H400" t="n">
         <v>6772</v>
@@ -11998,7 +11998,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G401" t="n">
-        <v>2.54840469360352</v>
+        <v>2.54840445518494</v>
       </c>
       <c r="H401" t="n">
         <v>25644</v>
@@ -12085,7 +12085,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H404" t="n">
         <v>20579</v>
@@ -12230,7 +12230,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H409" t="n">
         <v>3350</v>
@@ -12578,7 +12578,7 @@
         <v>2.75</v>
       </c>
       <c r="G421" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H421" t="n">
         <v>5517</v>
@@ -12607,7 +12607,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H422" t="n">
         <v>7693</v>
@@ -12723,7 +12723,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026628494263</v>
+        <v>2.53026652336121</v>
       </c>
       <c r="H426" t="n">
         <v>2034</v>
@@ -12752,7 +12752,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H427" t="n">
         <v>4867</v>
@@ -12868,7 +12868,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957591056824</v>
+        <v>2.43957614898682</v>
       </c>
       <c r="H431" t="n">
         <v>2176</v>
@@ -12897,7 +12897,7 @@
         <v>2.75</v>
       </c>
       <c r="G432" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H432" t="n">
         <v>6692</v>
@@ -13013,7 +13013,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>2.55747365951538</v>
+        <v>2.55747389793396</v>
       </c>
       <c r="H436" t="n">
         <v>4951</v>
@@ -13042,7 +13042,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654262542725</v>
+        <v>2.56654286384583</v>
       </c>
       <c r="H437" t="n">
         <v>4459</v>
@@ -13129,7 +13129,7 @@
         <v>2.75</v>
       </c>
       <c r="G440" t="n">
-        <v>2.49399018287659</v>
+        <v>2.49399042129517</v>
       </c>
       <c r="H440" t="n">
         <v>1970</v>
@@ -13187,7 +13187,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.66630244255066</v>
+        <v>2.66630220413208</v>
       </c>
       <c r="H442" t="n">
         <v>3157</v>
@@ -13216,7 +13216,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468103408813</v>
+        <v>2.58468079566956</v>
       </c>
       <c r="H443" t="n">
         <v>905</v>
@@ -13245,7 +13245,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H444" t="n">
         <v>305</v>
@@ -13361,7 +13361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350957870483</v>
+        <v>2.69350981712341</v>
       </c>
       <c r="H448" t="n">
         <v>14662</v>
@@ -13390,7 +13390,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095737457275</v>
+        <v>2.62095713615417</v>
       </c>
       <c r="H449" t="n">
         <v>5650</v>
@@ -13448,7 +13448,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H451" t="n">
         <v>17368</v>
@@ -13506,7 +13506,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885464668274</v>
+        <v>2.73885488510132</v>
       </c>
       <c r="H453" t="n">
         <v>1381</v>
@@ -39032,6 +39032,35 @@
         <v>12223</v>
       </c>
       <c r="I1333" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1334" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="G1334" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="H1334" t="n">
+        <v>977</v>
+      </c>
+      <c r="I1334" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/OMER.MI.xlsx
+++ b/data/OMER.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H2" t="n">
         <v>561784</v>
@@ -456,7 +456,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11975526809692</v>
+        <v>3.11975502967834</v>
       </c>
       <c r="H3" t="n">
         <v>105419</v>
@@ -514,7 +514,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>3.10161733627319</v>
+        <v>3.10161709785461</v>
       </c>
       <c r="H5" t="n">
         <v>23147</v>
@@ -543,7 +543,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.13335871696472</v>
+        <v>3.1333589553833</v>
       </c>
       <c r="H6" t="n">
         <v>30898</v>
@@ -572,7 +572,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>3.29206728935242</v>
+        <v>3.292067527771</v>
       </c>
       <c r="H7" t="n">
         <v>292211</v>
@@ -659,7 +659,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H10" t="n">
         <v>160329</v>
@@ -688,7 +688,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G11" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H11" t="n">
         <v>65268</v>
@@ -717,7 +717,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>3.44170665740967</v>
+        <v>3.44170689582825</v>
       </c>
       <c r="H12" t="n">
         <v>34000</v>
@@ -775,7 +775,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H14" t="n">
         <v>18667</v>
@@ -804,7 +804,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G15" t="n">
-        <v>3.39182662963867</v>
+        <v>3.39182686805725</v>
       </c>
       <c r="H15" t="n">
         <v>33287</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H16" t="n">
         <v>44813</v>
@@ -862,7 +862,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924401283264</v>
       </c>
       <c r="H17" t="n">
         <v>150547</v>
@@ -891,7 +891,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.70924425125122</v>
+        <v>3.70924401283264</v>
       </c>
       <c r="H18" t="n">
         <v>290894</v>
@@ -920,7 +920,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H19" t="n">
         <v>61034</v>
@@ -978,7 +978,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H21" t="n">
         <v>33033</v>
@@ -1007,7 +1007,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H22" t="n">
         <v>16624</v>
@@ -1036,7 +1036,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G23" t="n">
-        <v>3.71831274032593</v>
+        <v>3.71831321716309</v>
       </c>
       <c r="H23" t="n">
         <v>29141</v>
@@ -1094,7 +1094,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.89515948295593</v>
+        <v>3.89515924453735</v>
       </c>
       <c r="H25" t="n">
         <v>186140</v>
@@ -1181,7 +1181,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H28" t="n">
         <v>90036</v>
@@ -1210,7 +1210,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G29" t="n">
-        <v>3.79993486404419</v>
+        <v>3.79993414878845</v>
       </c>
       <c r="H29" t="n">
         <v>38465</v>
@@ -1297,7 +1297,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H32" t="n">
         <v>14654</v>
@@ -1355,7 +1355,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H34" t="n">
         <v>5781</v>
@@ -1442,7 +1442,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>3.67296767234802</v>
+        <v>3.6729679107666</v>
       </c>
       <c r="H37" t="n">
         <v>85205</v>
@@ -1471,7 +1471,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>3.76365804672241</v>
+        <v>3.76365852355957</v>
       </c>
       <c r="H38" t="n">
         <v>28609</v>
@@ -1529,7 +1529,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G40" t="n">
-        <v>3.78633117675781</v>
+        <v>3.78633093833923</v>
       </c>
       <c r="H40" t="n">
         <v>4635</v>
@@ -1558,7 +1558,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>3.78179621696472</v>
+        <v>3.7817964553833</v>
       </c>
       <c r="H41" t="n">
         <v>19462</v>
@@ -1587,7 +1587,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G42" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H42" t="n">
         <v>23606</v>
@@ -1616,7 +1616,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H43" t="n">
         <v>10910</v>
@@ -1645,7 +1645,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G44" t="n">
-        <v>3.77272701263428</v>
+        <v>3.77272725105286</v>
       </c>
       <c r="H44" t="n">
         <v>34605</v>
@@ -1674,7 +1674,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G45" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H45" t="n">
         <v>2007</v>
@@ -1703,7 +1703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72738194465637</v>
+        <v>3.72738218307495</v>
       </c>
       <c r="H46" t="n">
         <v>6914</v>
@@ -1790,7 +1790,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G49" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H49" t="n">
         <v>16797</v>
@@ -1819,7 +1819,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.76365804672241</v>
+        <v>3.76365852355957</v>
       </c>
       <c r="H50" t="n">
         <v>9599</v>
@@ -1877,7 +1877,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G52" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H52" t="n">
         <v>919</v>
@@ -1906,7 +1906,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G53" t="n">
-        <v>3.74552011489868</v>
+        <v>3.74552035331726</v>
       </c>
       <c r="H53" t="n">
         <v>5908</v>
@@ -2022,7 +2022,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H57" t="n">
         <v>18537</v>
@@ -2167,7 +2167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>3.70017504692078</v>
+        <v>3.7001748085022</v>
       </c>
       <c r="H62" t="n">
         <v>8191</v>
@@ -2254,7 +2254,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G65" t="n">
-        <v>3.68203663825989</v>
+        <v>3.68203687667847</v>
       </c>
       <c r="H65" t="n">
         <v>13936</v>
@@ -2341,7 +2341,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>3.67296767234802</v>
+        <v>3.6729679107666</v>
       </c>
       <c r="H68" t="n">
         <v>56808</v>
@@ -2370,7 +2370,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>3.75458908081055</v>
+        <v>3.75458884239197</v>
       </c>
       <c r="H69" t="n">
         <v>16753</v>
@@ -2399,7 +2399,7 @@
         <v>4.08500003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>3.70470952987671</v>
+        <v>3.70470929145813</v>
       </c>
       <c r="H70" t="n">
         <v>15982</v>
@@ -2428,7 +2428,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G71" t="n">
-        <v>3.68203663825989</v>
+        <v>3.68203687667847</v>
       </c>
       <c r="H71" t="n">
         <v>9106</v>
@@ -2544,7 +2544,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H75" t="n">
         <v>10828</v>
@@ -2573,7 +2573,7 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H76" t="n">
         <v>9217</v>
@@ -2631,7 +2631,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G78" t="n">
-        <v>3.70017504692078</v>
+        <v>3.7001748085022</v>
       </c>
       <c r="H78" t="n">
         <v>36913</v>
@@ -2689,7 +2689,7 @@
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>3.62762236595154</v>
+        <v>3.62762260437012</v>
       </c>
       <c r="H80" t="n">
         <v>1294</v>
@@ -2834,7 +2834,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G85" t="n">
-        <v>3.50065541267395</v>
+        <v>3.50065565109253</v>
       </c>
       <c r="H85" t="n">
         <v>6702</v>
@@ -2863,7 +2863,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G86" t="n">
-        <v>3.38729214668274</v>
+        <v>3.38729190826416</v>
       </c>
       <c r="H86" t="n">
         <v>4796</v>
@@ -2950,7 +2950,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>3.4462411403656</v>
+        <v>3.44624137878418</v>
       </c>
       <c r="H89" t="n">
         <v>5063</v>
@@ -2979,7 +2979,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>3.46437954902649</v>
+        <v>3.46437931060791</v>
       </c>
       <c r="H90" t="n">
         <v>2965</v>
@@ -3095,7 +3095,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>3.41903424263</v>
+        <v>3.41903400421143</v>
       </c>
       <c r="H94" t="n">
         <v>14502</v>
@@ -3124,7 +3124,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555100440979</v>
       </c>
       <c r="H95" t="n">
         <v>19856</v>
@@ -3182,7 +3182,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G97" t="n">
-        <v>3.45531058311462</v>
+        <v>3.45531034469604</v>
       </c>
       <c r="H97" t="n">
         <v>13724</v>
@@ -3240,7 +3240,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>3.42356896400452</v>
+        <v>3.42356872558594</v>
       </c>
       <c r="H99" t="n">
         <v>4056</v>
@@ -3269,7 +3269,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G100" t="n">
-        <v>3.41449975967407</v>
+        <v>3.41449999809265</v>
       </c>
       <c r="H100" t="n">
         <v>2072</v>
@@ -3298,7 +3298,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>3.40996503829956</v>
+        <v>3.40996527671814</v>
       </c>
       <c r="H101" t="n">
         <v>3157</v>
@@ -3327,7 +3327,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G102" t="n">
-        <v>3.40996503829956</v>
+        <v>3.40996527671814</v>
       </c>
       <c r="H102" t="n">
         <v>340</v>
@@ -3356,7 +3356,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G103" t="n">
-        <v>3.36008524894714</v>
+        <v>3.36008501052856</v>
       </c>
       <c r="H103" t="n">
         <v>13842</v>
@@ -3385,7 +3385,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G104" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555100440979</v>
       </c>
       <c r="H104" t="n">
         <v>6856</v>
@@ -3414,7 +3414,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555100440979</v>
       </c>
       <c r="H105" t="n">
         <v>4111</v>
@@ -3443,7 +3443,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G106" t="n">
-        <v>3.50065541267395</v>
+        <v>3.50065565109253</v>
       </c>
       <c r="H106" t="n">
         <v>14793</v>
@@ -3530,7 +3530,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>3.41449975967407</v>
+        <v>3.41449999809265</v>
       </c>
       <c r="H109" t="n">
         <v>6279</v>
@@ -3646,7 +3646,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G113" t="n">
-        <v>3.45077562332153</v>
+        <v>3.45077586174011</v>
       </c>
       <c r="H113" t="n">
         <v>3151</v>
@@ -3704,7 +3704,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>3.55507016181946</v>
+        <v>3.55506992340088</v>
       </c>
       <c r="H115" t="n">
         <v>8785</v>
@@ -3791,7 +3791,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G118" t="n">
-        <v>3.71831274032593</v>
+        <v>3.71831321716309</v>
       </c>
       <c r="H118" t="n">
         <v>29715</v>
@@ -3849,7 +3849,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G120" t="n">
-        <v>3.50972461700439</v>
+        <v>3.50972437858582</v>
       </c>
       <c r="H120" t="n">
         <v>9381</v>
@@ -3907,7 +3907,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G122" t="n">
-        <v>3.46437954902649</v>
+        <v>3.46437931060791</v>
       </c>
       <c r="H122" t="n">
         <v>1150</v>
@@ -3965,7 +3965,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G124" t="n">
-        <v>3.26485991477966</v>
+        <v>3.26486015319824</v>
       </c>
       <c r="H124" t="n">
         <v>17450</v>
@@ -3994,7 +3994,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>3.32834362983704</v>
+        <v>3.32834339141846</v>
       </c>
       <c r="H125" t="n">
         <v>9558</v>
@@ -4197,7 +4197,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>3.26485991477966</v>
+        <v>3.26486015319824</v>
       </c>
       <c r="H132" t="n">
         <v>3010</v>
@@ -4284,7 +4284,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G135" t="n">
-        <v>3.30113625526428</v>
+        <v>3.30113649368286</v>
       </c>
       <c r="H135" t="n">
         <v>17559</v>
@@ -4313,7 +4313,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G136" t="n">
-        <v>3.31927442550659</v>
+        <v>3.31927466392517</v>
       </c>
       <c r="H136" t="n">
         <v>21037</v>
@@ -4371,7 +4371,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G138" t="n">
-        <v>3.31020545959473</v>
+        <v>3.31020569801331</v>
       </c>
       <c r="H138" t="n">
         <v>2087</v>
@@ -4400,7 +4400,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>3.35555076599121</v>
+        <v>3.35555100440979</v>
       </c>
       <c r="H139" t="n">
         <v>353762</v>
@@ -4429,7 +4429,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>3.55507016181946</v>
+        <v>3.55506992340088</v>
       </c>
       <c r="H140" t="n">
         <v>17360</v>
@@ -4545,7 +4545,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G144" t="n">
-        <v>3.30113625526428</v>
+        <v>3.30113649368286</v>
       </c>
       <c r="H144" t="n">
         <v>9061</v>
@@ -4574,7 +4574,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G145" t="n">
-        <v>3.31927442550659</v>
+        <v>3.31927466392517</v>
       </c>
       <c r="H145" t="n">
         <v>2079</v>
@@ -4632,7 +4632,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G147" t="n">
-        <v>3.22858381271362</v>
+        <v>3.2285840511322</v>
       </c>
       <c r="H147" t="n">
         <v>5516</v>
@@ -4690,7 +4690,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G149" t="n">
-        <v>3.1469624042511</v>
+        <v>3.14696216583252</v>
       </c>
       <c r="H149" t="n">
         <v>11513</v>
@@ -4777,7 +4777,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.97465062141418</v>
+        <v>2.97465038299561</v>
       </c>
       <c r="H152" t="n">
         <v>14806</v>
@@ -4835,7 +4835,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91570162773132</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H154" t="n">
         <v>1770</v>
@@ -4922,7 +4922,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G157" t="n">
-        <v>2.89756321907043</v>
+        <v>2.89756345748901</v>
       </c>
       <c r="H157" t="n">
         <v>4634</v>
@@ -5038,7 +5038,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G161" t="n">
-        <v>2.99278855323792</v>
+        <v>2.99278831481934</v>
       </c>
       <c r="H161" t="n">
         <v>12598</v>
@@ -5067,7 +5067,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G162" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H162" t="n">
         <v>5456</v>
@@ -5183,7 +5183,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G166" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H166" t="n">
         <v>6067</v>
@@ -5241,7 +5241,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>3.21044564247131</v>
+        <v>3.21044588088989</v>
       </c>
       <c r="H168" t="n">
         <v>11151</v>
@@ -5270,7 +5270,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G169" t="n">
-        <v>3.37368893623352</v>
+        <v>3.37368869781494</v>
       </c>
       <c r="H169" t="n">
         <v>87762</v>
@@ -5328,7 +5328,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G171" t="n">
-        <v>3.10615181922913</v>
+        <v>3.10615158081055</v>
       </c>
       <c r="H171" t="n">
         <v>59616</v>
@@ -5415,7 +5415,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H174" t="n">
         <v>4116</v>
@@ -5473,7 +5473,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>2.91116690635681</v>
+        <v>2.91116714477539</v>
       </c>
       <c r="H176" t="n">
         <v>13401</v>
@@ -5560,7 +5560,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G179" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H179" t="n">
         <v>2982</v>
@@ -5618,7 +5618,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G181" t="n">
-        <v>2.97465062141418</v>
+        <v>2.97465038299561</v>
       </c>
       <c r="H181" t="n">
         <v>3283</v>
@@ -5647,7 +5647,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G182" t="n">
-        <v>2.97918486595154</v>
+        <v>2.97918510437012</v>
       </c>
       <c r="H182" t="n">
         <v>7488</v>
@@ -5792,7 +5792,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G187" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H187" t="n">
         <v>4021</v>
@@ -5850,7 +5850,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G189" t="n">
-        <v>2.99732303619385</v>
+        <v>2.99732327461243</v>
       </c>
       <c r="H189" t="n">
         <v>14092</v>
@@ -5908,7 +5908,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>3.08347916603088</v>
+        <v>3.0834789276123</v>
       </c>
       <c r="H191" t="n">
         <v>12796</v>
@@ -5937,7 +5937,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>3.05627179145813</v>
+        <v>3.05627155303955</v>
       </c>
       <c r="H192" t="n">
         <v>9528</v>
@@ -5995,7 +5995,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>3.06534123420715</v>
+        <v>3.06534099578857</v>
       </c>
       <c r="H194" t="n">
         <v>924</v>
@@ -6053,7 +6053,7 @@
         <v>3.25</v>
       </c>
       <c r="G196" t="n">
-        <v>2.94744300842285</v>
+        <v>2.94744324684143</v>
       </c>
       <c r="H196" t="n">
         <v>9781</v>
@@ -6169,7 +6169,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G200" t="n">
-        <v>2.87489104270935</v>
+        <v>2.87489080429077</v>
       </c>
       <c r="H200" t="n">
         <v>7430</v>
@@ -6198,7 +6198,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G201" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H201" t="n">
         <v>7306</v>
@@ -6256,7 +6256,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G203" t="n">
-        <v>2.9565122127533</v>
+        <v>2.95651245117188</v>
       </c>
       <c r="H203" t="n">
         <v>1563</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.94744300842285</v>
+        <v>2.94744324684143</v>
       </c>
       <c r="H204" t="n">
         <v>41187</v>
@@ -6314,7 +6314,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G205" t="n">
-        <v>2.97011590003967</v>
+        <v>2.97011566162109</v>
       </c>
       <c r="H205" t="n">
         <v>4097</v>
@@ -6343,7 +6343,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G206" t="n">
-        <v>3.0018572807312</v>
+        <v>3.00185751914978</v>
       </c>
       <c r="H206" t="n">
         <v>581</v>
@@ -6372,7 +6372,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G207" t="n">
-        <v>2.92477059364319</v>
+        <v>2.92477035522461</v>
       </c>
       <c r="H207" t="n">
         <v>1550</v>
@@ -6401,7 +6401,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>3.00639224052429</v>
+        <v>3.00639200210571</v>
       </c>
       <c r="H208" t="n">
         <v>7842</v>
@@ -6517,7 +6517,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.36461997032166</v>
+        <v>3.36461973190308</v>
       </c>
       <c r="H212" t="n">
         <v>17177</v>
@@ -6546,7 +6546,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G213" t="n">
-        <v>3.23765301704407</v>
+        <v>3.23765277862549</v>
       </c>
       <c r="H213" t="n">
         <v>4683</v>
@@ -6575,7 +6575,7 @@
         <v>3.625</v>
       </c>
       <c r="G214" t="n">
-        <v>3.28753304481506</v>
+        <v>3.28753280639648</v>
       </c>
       <c r="H214" t="n">
         <v>1310</v>
@@ -6604,7 +6604,7 @@
         <v>3.5</v>
       </c>
       <c r="G215" t="n">
-        <v>3.17416977882385</v>
+        <v>3.17416930198669</v>
       </c>
       <c r="H215" t="n">
         <v>6340</v>
@@ -6633,7 +6633,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G216" t="n">
-        <v>3.11975526809692</v>
+        <v>3.11975502967834</v>
       </c>
       <c r="H216" t="n">
         <v>5488</v>
@@ -6720,7 +6720,7 @@
         <v>3.5</v>
       </c>
       <c r="G219" t="n">
-        <v>3.17416977882385</v>
+        <v>3.17416930198669</v>
       </c>
       <c r="H219" t="n">
         <v>8838</v>
@@ -6749,7 +6749,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>3.15603184700012</v>
+        <v>3.15603137016296</v>
       </c>
       <c r="H220" t="n">
         <v>16930</v>
@@ -6836,7 +6836,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G223" t="n">
-        <v>2.97918486595154</v>
+        <v>2.97918510437012</v>
       </c>
       <c r="H223" t="n">
         <v>3005</v>
@@ -6865,7 +6865,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.87035608291626</v>
+        <v>2.87035584449768</v>
       </c>
       <c r="H224" t="n">
         <v>4992</v>
@@ -6894,7 +6894,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G225" t="n">
-        <v>2.91570162773132</v>
+        <v>2.91570115089417</v>
       </c>
       <c r="H225" t="n">
         <v>3170</v>
@@ -6923,7 +6923,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G226" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H226" t="n">
         <v>8814</v>
@@ -7010,7 +7010,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G229" t="n">
-        <v>2.87489104270935</v>
+        <v>2.87489080429077</v>
       </c>
       <c r="H229" t="n">
         <v>389</v>
@@ -7039,7 +7039,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G230" t="n">
-        <v>2.82954525947571</v>
+        <v>2.82954549789429</v>
       </c>
       <c r="H230" t="n">
         <v>4733</v>
@@ -7068,7 +7068,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G231" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H231" t="n">
         <v>1012</v>
@@ -7242,7 +7242,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G237" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H237" t="n">
         <v>3487</v>
@@ -7300,7 +7300,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G239" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H239" t="n">
         <v>10412</v>
@@ -7329,7 +7329,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G240" t="n">
-        <v>2.88396000862122</v>
+        <v>2.88395977020264</v>
       </c>
       <c r="H240" t="n">
         <v>17990</v>
@@ -7416,7 +7416,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G243" t="n">
-        <v>2.77513098716736</v>
+        <v>2.77513122558594</v>
       </c>
       <c r="H243" t="n">
         <v>3305</v>
@@ -7445,7 +7445,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G244" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H244" t="n">
         <v>4956</v>
@@ -7503,7 +7503,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G246" t="n">
-        <v>2.84768342971802</v>
+        <v>2.8476836681366</v>
       </c>
       <c r="H246" t="n">
         <v>8994</v>
@@ -7532,7 +7532,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H247" t="n">
         <v>5286</v>
@@ -7561,7 +7561,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G248" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H248" t="n">
         <v>1003</v>
@@ -7619,7 +7619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G250" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H250" t="n">
         <v>11443</v>
@@ -7648,7 +7648,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G251" t="n">
-        <v>2.75245881080627</v>
+        <v>2.7524585723877</v>
       </c>
       <c r="H251" t="n">
         <v>1377</v>
@@ -7677,7 +7677,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G252" t="n">
-        <v>2.75245881080627</v>
+        <v>2.7524585723877</v>
       </c>
       <c r="H252" t="n">
         <v>336</v>
@@ -7706,7 +7706,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G253" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H253" t="n">
         <v>1884</v>
@@ -7735,7 +7735,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>2.70257878303528</v>
+        <v>2.7025785446167</v>
       </c>
       <c r="H254" t="n">
         <v>1758</v>
@@ -7793,7 +7793,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G256" t="n">
-        <v>2.7842001914978</v>
+        <v>2.78419995307922</v>
       </c>
       <c r="H256" t="n">
         <v>2600</v>
@@ -7822,7 +7822,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G257" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350934028625</v>
       </c>
       <c r="H257" t="n">
         <v>8062</v>
@@ -7851,7 +7851,7 @@
         <v>3</v>
       </c>
       <c r="G258" t="n">
-        <v>2.72071647644043</v>
+        <v>2.72071671485901</v>
       </c>
       <c r="H258" t="n">
         <v>1704</v>
@@ -7938,7 +7938,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>2.7161819934845</v>
+        <v>2.71618223190308</v>
       </c>
       <c r="H261" t="n">
         <v>2757</v>
@@ -8141,7 +8141,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G268" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H268" t="n">
         <v>6031</v>
@@ -8170,7 +8170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G269" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H269" t="n">
         <v>1163</v>
@@ -8199,7 +8199,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G270" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H270" t="n">
         <v>9817</v>
@@ -8257,7 +8257,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G272" t="n">
-        <v>2.58014631271362</v>
+        <v>2.5801465511322</v>
       </c>
       <c r="H272" t="n">
         <v>7178</v>
@@ -8315,7 +8315,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G274" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H274" t="n">
         <v>1083</v>
@@ -8344,7 +8344,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G275" t="n">
-        <v>2.53480100631714</v>
+        <v>2.53480124473572</v>
       </c>
       <c r="H275" t="n">
         <v>1505</v>
@@ -8402,7 +8402,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G277" t="n">
-        <v>2.48945546150208</v>
+        <v>2.48945569992065</v>
       </c>
       <c r="H277" t="n">
         <v>995</v>
@@ -8518,7 +8518,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G281" t="n">
-        <v>2.35342001914978</v>
+        <v>2.35342025756836</v>
       </c>
       <c r="H281" t="n">
         <v>44116</v>
@@ -8547,7 +8547,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H282" t="n">
         <v>4891</v>
@@ -8576,7 +8576,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G283" t="n">
-        <v>2.2808678150177</v>
+        <v>2.28086757659912</v>
       </c>
       <c r="H283" t="n">
         <v>2655</v>
@@ -8808,7 +8808,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>2.11309003829956</v>
+        <v>2.11308979988098</v>
       </c>
       <c r="H291" t="n">
         <v>2789</v>
@@ -8866,7 +8866,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.33074736595154</v>
+        <v>2.33074712753296</v>
       </c>
       <c r="H293" t="n">
         <v>4108</v>
@@ -9098,7 +9098,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G301" t="n">
-        <v>2.33074736595154</v>
+        <v>2.33074712753296</v>
       </c>
       <c r="H301" t="n">
         <v>9820</v>
@@ -9127,7 +9127,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G302" t="n">
-        <v>2.35795426368713</v>
+        <v>2.35795450210571</v>
       </c>
       <c r="H302" t="n">
         <v>5211</v>
@@ -9214,7 +9214,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G305" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H305" t="n">
         <v>590</v>
@@ -9272,7 +9272,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G307" t="n">
-        <v>2.43050694465637</v>
+        <v>2.43050718307495</v>
       </c>
       <c r="H307" t="n">
         <v>5406</v>
@@ -9330,7 +9330,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H309" t="n">
         <v>7036</v>
@@ -9359,7 +9359,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G310" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G311" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H311" t="n">
         <v>5875</v>
@@ -9417,7 +9417,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G312" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H312" t="n">
         <v>4369</v>
@@ -9475,7 +9475,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G314" t="n">
-        <v>2.48038673400879</v>
+        <v>2.48038649559021</v>
       </c>
       <c r="H314" t="n">
         <v>4439</v>
@@ -9533,7 +9533,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G316" t="n">
-        <v>2.50759410858154</v>
+        <v>2.50759387016296</v>
       </c>
       <c r="H316" t="n">
         <v>2151</v>
@@ -9591,7 +9591,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G318" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H318" t="n">
         <v>3432</v>
@@ -9620,7 +9620,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G319" t="n">
-        <v>2.55747389793396</v>
+        <v>2.55747365951538</v>
       </c>
       <c r="H319" t="n">
         <v>2553</v>
@@ -9649,7 +9649,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>2.53480100631714</v>
+        <v>2.53480124473572</v>
       </c>
       <c r="H320" t="n">
         <v>752</v>
@@ -9707,7 +9707,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G322" t="n">
-        <v>2.46224880218506</v>
+        <v>2.46224856376648</v>
       </c>
       <c r="H322" t="n">
         <v>1662</v>
@@ -9794,7 +9794,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.39876508712769</v>
+        <v>2.39876532554626</v>
       </c>
       <c r="H325" t="n">
         <v>2044</v>
@@ -9823,7 +9823,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G326" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H326" t="n">
         <v>10875</v>
@@ -9852,7 +9852,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G327" t="n">
-        <v>2.43050694465637</v>
+        <v>2.43050718307495</v>
       </c>
       <c r="H327" t="n">
         <v>902</v>
@@ -9939,7 +9939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.367023229599</v>
+        <v>2.36702346801758</v>
       </c>
       <c r="H330" t="n">
         <v>7415</v>
@@ -9968,7 +9968,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G331" t="n">
-        <v>2.35342001914978</v>
+        <v>2.35342025756836</v>
       </c>
       <c r="H331" t="n">
         <v>12852</v>
@@ -10055,7 +10055,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G334" t="n">
-        <v>2.2944712638855</v>
+        <v>2.29447102546692</v>
       </c>
       <c r="H334" t="n">
         <v>2916</v>
@@ -10113,7 +10113,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>2.30807447433472</v>
+        <v>2.30807495117188</v>
       </c>
       <c r="H336" t="n">
         <v>989</v>
@@ -10171,7 +10171,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G338" t="n">
-        <v>2.32167840003967</v>
+        <v>2.32167816162109</v>
       </c>
       <c r="H338" t="n">
         <v>5855</v>
@@ -10200,7 +10200,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G339" t="n">
-        <v>2.33528208732605</v>
+        <v>2.33528184890747</v>
       </c>
       <c r="H339" t="n">
         <v>4539</v>
@@ -10229,7 +10229,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G340" t="n">
-        <v>2.28993654251099</v>
+        <v>2.28993678092957</v>
       </c>
       <c r="H340" t="n">
         <v>31736</v>
@@ -10316,7 +10316,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G343" t="n">
-        <v>2.27633309364319</v>
+        <v>2.27633285522461</v>
       </c>
       <c r="H343" t="n">
         <v>5900</v>
@@ -10374,7 +10374,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G345" t="n">
-        <v>2.27633309364319</v>
+        <v>2.27633285522461</v>
       </c>
       <c r="H345" t="n">
         <v>8557</v>
@@ -10461,7 +10461,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G348" t="n">
-        <v>2.39423108100891</v>
+        <v>2.39423084259033</v>
       </c>
       <c r="H348" t="n">
         <v>518</v>
@@ -10490,7 +10490,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H349" t="n">
         <v>5793</v>
@@ -10519,7 +10519,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G350" t="n">
-        <v>2.32621288299561</v>
+        <v>2.32621264457703</v>
       </c>
       <c r="H350" t="n">
         <v>68</v>
@@ -10606,7 +10606,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>2.36248898506165</v>
+        <v>2.36248922348022</v>
       </c>
       <c r="H353" t="n">
         <v>4548</v>
@@ -10693,7 +10693,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G356" t="n">
-        <v>2.367023229599</v>
+        <v>2.36702346801758</v>
       </c>
       <c r="H356" t="n">
         <v>153</v>
@@ -10722,7 +10722,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G357" t="n">
-        <v>2.35795426368713</v>
+        <v>2.35795450210571</v>
       </c>
       <c r="H357" t="n">
         <v>1884</v>
@@ -10751,7 +10751,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G358" t="n">
-        <v>2.26272940635681</v>
+        <v>2.26272964477539</v>
       </c>
       <c r="H358" t="n">
         <v>5565</v>
@@ -10780,7 +10780,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G359" t="n">
-        <v>2.19017672538757</v>
+        <v>2.19017696380615</v>
       </c>
       <c r="H359" t="n">
         <v>9087</v>
@@ -11012,7 +11012,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G367" t="n">
-        <v>2.34888529777527</v>
+        <v>2.34888553619385</v>
       </c>
       <c r="H367" t="n">
         <v>3824</v>
@@ -11099,7 +11099,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G370" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H370" t="n">
         <v>119311</v>
@@ -11186,7 +11186,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>2.4032998085022</v>
+        <v>2.40330004692078</v>
       </c>
       <c r="H373" t="n">
         <v>26801</v>
@@ -11215,7 +11215,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G374" t="n">
-        <v>2.3896963596344</v>
+        <v>2.38969612121582</v>
       </c>
       <c r="H374" t="n">
         <v>7617</v>
@@ -11244,7 +11244,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.4032998085022</v>
+        <v>2.40330004692078</v>
       </c>
       <c r="H375" t="n">
         <v>8213</v>
@@ -11273,7 +11273,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H376" t="n">
         <v>7974</v>
@@ -11360,7 +11360,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G379" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H379" t="n">
         <v>125340</v>
@@ -11389,7 +11389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H380" t="n">
         <v>15968</v>
@@ -11418,7 +11418,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G381" t="n">
-        <v>2.4985249042511</v>
+        <v>2.49852514266968</v>
       </c>
       <c r="H381" t="n">
         <v>3626</v>
@@ -11505,7 +11505,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G384" t="n">
-        <v>2.55293917655945</v>
+        <v>2.55293941497803</v>
       </c>
       <c r="H384" t="n">
         <v>7902</v>
@@ -11563,7 +11563,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H386" t="n">
         <v>6461</v>
@@ -11592,7 +11592,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G387" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H387" t="n">
         <v>400</v>
@@ -11650,7 +11650,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G389" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H389" t="n">
         <v>5695</v>
@@ -11679,7 +11679,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G390" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H390" t="n">
         <v>3704</v>
@@ -11737,7 +11737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G392" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H392" t="n">
         <v>8970</v>
@@ -11766,7 +11766,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G393" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H393" t="n">
         <v>258</v>
@@ -11853,7 +11853,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G396" t="n">
-        <v>2.51666307449341</v>
+        <v>2.51666283607483</v>
       </c>
       <c r="H396" t="n">
         <v>67390</v>
@@ -11882,7 +11882,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>2.53933548927307</v>
+        <v>2.53933572769165</v>
       </c>
       <c r="H397" t="n">
         <v>6517</v>
@@ -11911,7 +11911,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G398" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H398" t="n">
         <v>3914</v>
@@ -11940,7 +11940,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>2.53480100631714</v>
+        <v>2.53480124473572</v>
       </c>
       <c r="H399" t="n">
         <v>73</v>
@@ -12027,7 +12027,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G402" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281872749329</v>
       </c>
       <c r="H402" t="n">
         <v>27847</v>
@@ -12056,7 +12056,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G403" t="n">
-        <v>2.7161819934845</v>
+        <v>2.71618223190308</v>
       </c>
       <c r="H403" t="n">
         <v>27202</v>
@@ -12085,7 +12085,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G404" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H404" t="n">
         <v>20579</v>
@@ -12114,7 +12114,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G405" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H405" t="n">
         <v>5957</v>
@@ -12143,7 +12143,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H406" t="n">
         <v>4040</v>
@@ -12172,7 +12172,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G407" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H407" t="n">
         <v>10856</v>
@@ -12201,7 +12201,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H408" t="n">
         <v>3770</v>
@@ -12230,7 +12230,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G409" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H409" t="n">
         <v>3350</v>
@@ -12259,7 +12259,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281872749329</v>
       </c>
       <c r="H410" t="n">
         <v>4500</v>
@@ -12288,7 +12288,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G411" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281872749329</v>
       </c>
       <c r="H411" t="n">
         <v>2860</v>
@@ -12317,7 +12317,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G412" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H412" t="n">
         <v>5700</v>
@@ -12346,7 +12346,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G413" t="n">
-        <v>2.46224880218506</v>
+        <v>2.46224856376648</v>
       </c>
       <c r="H413" t="n">
         <v>224</v>
@@ -12404,7 +12404,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G415" t="n">
-        <v>2.52573227882385</v>
+        <v>2.52573204040527</v>
       </c>
       <c r="H415" t="n">
         <v>8421</v>
@@ -12433,7 +12433,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H416" t="n">
         <v>1088</v>
@@ -12520,7 +12520,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G419" t="n">
-        <v>2.367023229599</v>
+        <v>2.36702346801758</v>
       </c>
       <c r="H419" t="n">
         <v>3581</v>
@@ -12549,7 +12549,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G420" t="n">
-        <v>2.34888529777527</v>
+        <v>2.34888553619385</v>
       </c>
       <c r="H420" t="n">
         <v>3648</v>
@@ -12607,7 +12607,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H422" t="n">
         <v>7693</v>
@@ -12665,7 +12665,7 @@
         <v>2.875</v>
       </c>
       <c r="G424" t="n">
-        <v>2.6073534488678</v>
+        <v>2.60735368728638</v>
       </c>
       <c r="H424" t="n">
         <v>1280</v>
@@ -12694,7 +12694,7 @@
         <v>2.72499990463257</v>
       </c>
       <c r="G425" t="n">
-        <v>2.47131776809692</v>
+        <v>2.47131752967834</v>
       </c>
       <c r="H425" t="n">
         <v>642</v>
@@ -12723,7 +12723,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>2.53026652336121</v>
+        <v>2.53026676177979</v>
       </c>
       <c r="H426" t="n">
         <v>2034</v>
@@ -12752,7 +12752,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H427" t="n">
         <v>4867</v>
@@ -12810,7 +12810,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G429" t="n">
-        <v>2.50305962562561</v>
+        <v>2.50305938720703</v>
       </c>
       <c r="H429" t="n">
         <v>9718</v>
@@ -12868,7 +12868,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43957614898682</v>
+        <v>2.4395763874054</v>
       </c>
       <c r="H431" t="n">
         <v>2176</v>
@@ -12955,7 +12955,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.51212859153748</v>
+        <v>2.5121283531189</v>
       </c>
       <c r="H434" t="n">
         <v>10353</v>
@@ -13013,7 +13013,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>2.55747389793396</v>
+        <v>2.55747365951538</v>
       </c>
       <c r="H436" t="n">
         <v>4951</v>
@@ -13042,7 +13042,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>2.56654286384583</v>
+        <v>2.56654262542725</v>
       </c>
       <c r="H437" t="n">
         <v>4459</v>
@@ -13071,7 +13071,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G438" t="n">
-        <v>2.63002610206604</v>
+        <v>2.63002634048462</v>
       </c>
       <c r="H438" t="n">
         <v>7550</v>
@@ -13158,7 +13158,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G441" t="n">
-        <v>2.60281896591187</v>
+        <v>2.60281872749329</v>
       </c>
       <c r="H441" t="n">
         <v>16239</v>
@@ -13187,7 +13187,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.66630220413208</v>
+        <v>2.66630244255066</v>
       </c>
       <c r="H442" t="n">
         <v>3157</v>
@@ -13216,7 +13216,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>2.58468079566956</v>
+        <v>2.58468103408813</v>
       </c>
       <c r="H443" t="n">
         <v>905</v>
@@ -13245,7 +13245,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G444" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H444" t="n">
         <v>305</v>
@@ -13274,7 +13274,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61188840866089</v>
+        <v>2.61188817024231</v>
       </c>
       <c r="H445" t="n">
         <v>5437</v>
@@ -13303,7 +13303,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G446" t="n">
-        <v>2.59375</v>
+        <v>2.59374976158142</v>
       </c>
       <c r="H446" t="n">
         <v>2456</v>
@@ -13361,7 +13361,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G448" t="n">
-        <v>2.69350981712341</v>
+        <v>2.69350934028625</v>
       </c>
       <c r="H448" t="n">
         <v>14662</v>
@@ -13390,7 +13390,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G449" t="n">
-        <v>2.62095713615417</v>
+        <v>2.62095737457275</v>
       </c>
       <c r="H449" t="n">
         <v>5650</v>
@@ -13448,7 +13448,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G451" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H451" t="n">
         <v>17368</v>
@@ -13477,7 +13477,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H452" t="n">
         <v>9599</v>
@@ -13506,7 +13506,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>2.73885488510132</v>
+        <v>2.73885464668274</v>
       </c>
       <c r="H453" t="n">
         <v>1381</v>
@@ -13535,7 +13535,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H454" t="n">
         <v>642</v>
@@ -13564,7 +13564,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G455" t="n">
-        <v>2.82047629356384</v>
+        <v>2.82047653198242</v>
       </c>
       <c r="H455" t="n">
         <v>22810</v>
@@ -13593,7 +13593,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G456" t="n">
-        <v>2.76606202125549</v>
+        <v>2.76606225967407</v>
       </c>
       <c r="H456" t="n">
         <v>17281</v>
@@ -13651,7 +13651,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G458" t="n">
-        <v>2.8114070892334</v>
+        <v>2.81140732765198</v>
       </c>
       <c r="H458" t="n">
         <v>2064</v>
@@ -13796,7 +13796,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G463" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H463" t="n">
         <v>1249</v>
@@ -13883,7 +13883,7 @@
         <v>3</v>
       </c>
       <c r="G466" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H466" t="n">
         <v>2400</v>
@@ -13912,7 +13912,7 @@
         <v>3</v>
       </c>
       <c r="G467" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H467" t="n">
         <v>897</v>
@@ -13970,7 +13970,7 @@
         <v>3</v>
       </c>
       <c r="G469" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H469" t="n">
         <v>598</v>
@@ -13999,7 +13999,7 @@
         <v>3</v>
       </c>
       <c r="G470" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H470" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H471" t="n">
         <v>6971</v>
@@ -14057,7 +14057,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H472" t="n">
         <v>15161</v>
@@ -14434,7 +14434,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G485" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H485" t="n">
         <v>2516</v>
@@ -14492,7 +14492,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>2.61125588417053</v>
+        <v>2.61125612258911</v>
       </c>
       <c r="H487" t="n">
         <v>126942</v>
@@ -14521,7 +14521,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G488" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H488" t="n">
         <v>4646</v>
@@ -14550,7 +14550,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G489" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H489" t="n">
         <v>1637</v>
@@ -14579,7 +14579,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G490" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H490" t="n">
         <v>62146</v>
@@ -14608,7 +14608,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G491" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H491" t="n">
         <v>146750</v>
@@ -14637,7 +14637,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H492" t="n">
         <v>9831</v>
@@ -14666,7 +14666,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G493" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G494" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H494" t="n">
         <v>4238</v>
@@ -14782,7 +14782,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G497" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H497" t="n">
         <v>1143</v>
@@ -14840,7 +14840,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G499" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H499" t="n">
         <v>146</v>
@@ -14869,7 +14869,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G500" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H500" t="n">
         <v>5010</v>
@@ -15275,7 +15275,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G514" t="n">
-        <v>2.66661882400513</v>
+        <v>2.66661858558655</v>
       </c>
       <c r="H514" t="n">
         <v>3133</v>
@@ -15304,7 +15304,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G515" t="n">
-        <v>2.66661882400513</v>
+        <v>2.66661858558655</v>
       </c>
       <c r="H515" t="n">
         <v>1609</v>
@@ -15478,7 +15478,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H521" t="n">
         <v>2000</v>
@@ -15507,7 +15507,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H522" t="n">
         <v>3105</v>
@@ -15594,7 +15594,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G525" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H525" t="n">
         <v>256</v>
@@ -15623,7 +15623,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H526" t="n">
         <v>2296</v>
@@ -15681,7 +15681,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H528" t="n">
         <v>165</v>
@@ -15710,7 +15710,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H529" t="n">
         <v>352</v>
@@ -15739,7 +15739,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H530" t="n">
         <v>1618</v>
@@ -15768,7 +15768,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G531" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H531" t="n">
         <v>5250</v>
@@ -15913,7 +15913,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G536" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H536" t="n">
         <v>553</v>
@@ -16116,7 +16116,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H543" t="n">
         <v>50</v>
@@ -16203,7 +16203,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>2.73120808601379</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H546" t="n">
         <v>23578</v>
@@ -16232,7 +16232,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>2.73120808601379</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H547" t="n">
         <v>4925</v>
@@ -16290,7 +16290,7 @@
         <v>3</v>
       </c>
       <c r="G549" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H549" t="n">
         <v>2815</v>
@@ -16348,7 +16348,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G551" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H551" t="n">
         <v>1945</v>
@@ -16377,7 +16377,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>2.73120808601379</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H552" t="n">
         <v>22273</v>
@@ -16435,7 +16435,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G554" t="n">
-        <v>2.86961340904236</v>
+        <v>2.86961364746094</v>
       </c>
       <c r="H554" t="n">
         <v>10116</v>
@@ -16580,7 +16580,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G559" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H559" t="n">
         <v>5192</v>
@@ -16609,7 +16609,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G560" t="n">
-        <v>2.77734279632568</v>
+        <v>2.77734303474426</v>
       </c>
       <c r="H560" t="n">
         <v>6973</v>
@@ -16638,7 +16638,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G561" t="n">
-        <v>2.79579734802246</v>
+        <v>2.79579710960388</v>
       </c>
       <c r="H561" t="n">
         <v>2786</v>
@@ -16667,7 +16667,7 @@
         <v>3</v>
       </c>
       <c r="G562" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H562" t="n">
         <v>6763</v>
@@ -16696,7 +16696,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>2.73120808601379</v>
+        <v>2.73120760917664</v>
       </c>
       <c r="H563" t="n">
         <v>1740</v>
@@ -16725,7 +16725,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>2.71275353431702</v>
+        <v>2.7127537727356</v>
       </c>
       <c r="H564" t="n">
         <v>33572</v>
@@ -16754,7 +16754,7 @@
         <v>3</v>
       </c>
       <c r="G565" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H565" t="n">
         <v>27</v>
@@ -16783,7 +16783,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H566" t="n">
         <v>2877</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H568" t="n">
         <v>4278</v>
@@ -16870,7 +16870,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G569" t="n">
-        <v>2.55589389801025</v>
+        <v>2.55589365959167</v>
       </c>
       <c r="H569" t="n">
         <v>3153</v>
@@ -16957,7 +16957,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G572" t="n">
-        <v>2.41748785972595</v>
+        <v>2.41748809814453</v>
       </c>
       <c r="H572" t="n">
         <v>1200</v>
@@ -17102,7 +17102,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G577" t="n">
-        <v>2.66661882400513</v>
+        <v>2.66661858558655</v>
       </c>
       <c r="H577" t="n">
         <v>1902</v>
@@ -17131,7 +17131,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G578" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H578" t="n">
         <v>8794</v>
@@ -17160,7 +17160,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G579" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H579" t="n">
         <v>17262</v>
@@ -17305,7 +17305,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.57434773445129</v>
+        <v>2.57434797286987</v>
       </c>
       <c r="H584" t="n">
         <v>8917</v>
@@ -17392,7 +17392,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>2.61125588417053</v>
+        <v>2.61125612258911</v>
       </c>
       <c r="H587" t="n">
         <v>2540</v>
@@ -17537,7 +17537,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G592" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H592" t="n">
         <v>2322</v>
@@ -17566,7 +17566,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G593" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H593" t="n">
         <v>12355</v>
@@ -17595,7 +17595,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G594" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H594" t="n">
         <v>4823</v>
@@ -17624,7 +17624,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G595" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H595" t="n">
         <v>7592</v>
@@ -17653,7 +17653,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>2.41748785972595</v>
+        <v>2.41748809814453</v>
       </c>
       <c r="H596" t="n">
         <v>13053</v>
@@ -17682,7 +17682,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G597" t="n">
-        <v>2.45439648628235</v>
+        <v>2.45439624786377</v>
       </c>
       <c r="H597" t="n">
         <v>20130</v>
@@ -17798,7 +17798,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G601" t="n">
-        <v>2.56512093544006</v>
+        <v>2.56512069702148</v>
       </c>
       <c r="H601" t="n">
         <v>1618</v>
@@ -17972,7 +17972,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G607" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H607" t="n">
         <v>5192</v>
@@ -18001,7 +18001,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G608" t="n">
-        <v>2.54666662216187</v>
+        <v>2.54666686058044</v>
       </c>
       <c r="H608" t="n">
         <v>2394</v>
@@ -18175,7 +18175,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H614" t="n">
         <v>1453</v>
@@ -18204,7 +18204,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G615" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H615" t="n">
         <v>12525</v>
@@ -18233,7 +18233,7 @@
         <v>3</v>
       </c>
       <c r="G616" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H616" t="n">
         <v>31723</v>
@@ -18291,7 +18291,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>2.67584538459778</v>
+        <v>2.67584586143494</v>
       </c>
       <c r="H618" t="n">
         <v>5256</v>
@@ -18320,7 +18320,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G619" t="n">
-        <v>2.72198081016541</v>
+        <v>2.72198104858398</v>
       </c>
       <c r="H619" t="n">
         <v>345</v>
@@ -18349,7 +18349,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G620" t="n">
-        <v>2.77734279632568</v>
+        <v>2.77734303474426</v>
       </c>
       <c r="H620" t="n">
         <v>10213</v>
@@ -18407,7 +18407,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>2.69429969787598</v>
+        <v>2.6942994594574</v>
       </c>
       <c r="H622" t="n">
         <v>2229</v>
@@ -18465,7 +18465,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G624" t="n">
-        <v>2.68507266044617</v>
+        <v>2.68507242202759</v>
       </c>
       <c r="H624" t="n">
         <v>87</v>
@@ -18668,7 +18668,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H631" t="n">
         <v>57880</v>
@@ -18755,7 +18755,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>3.15565252304077</v>
+        <v>3.15565228462219</v>
       </c>
       <c r="H634" t="n">
         <v>2023</v>
@@ -18813,7 +18813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G636" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H636" t="n">
         <v>1875</v>
@@ -18871,7 +18871,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G638" t="n">
-        <v>3.15565252304077</v>
+        <v>3.15565228462219</v>
       </c>
       <c r="H638" t="n">
         <v>17794</v>
@@ -19132,7 +19132,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G647" t="n">
-        <v>2.97111105918884</v>
+        <v>2.97111129760742</v>
       </c>
       <c r="H647" t="n">
         <v>1164</v>
@@ -19277,7 +19277,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H652" t="n">
         <v>8899</v>
@@ -19364,7 +19364,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>3.32173919677734</v>
+        <v>3.32173943519592</v>
       </c>
       <c r="H655" t="n">
         <v>35366</v>
@@ -19393,7 +19393,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>3.34019303321838</v>
+        <v>3.34019327163696</v>
       </c>
       <c r="H656" t="n">
         <v>11889</v>
@@ -19422,7 +19422,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G657" t="n">
-        <v>3.43246412277222</v>
+        <v>3.43246388435364</v>
       </c>
       <c r="H657" t="n">
         <v>69496</v>
@@ -19451,7 +19451,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G658" t="n">
-        <v>3.29405808448792</v>
+        <v>3.29405784606934</v>
       </c>
       <c r="H658" t="n">
         <v>44455</v>
@@ -19509,7 +19509,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G660" t="n">
-        <v>3.13719797134399</v>
+        <v>3.13719820976257</v>
       </c>
       <c r="H660" t="n">
         <v>3302</v>
@@ -19567,7 +19567,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G662" t="n">
-        <v>3.06338167190552</v>
+        <v>3.0633819103241</v>
       </c>
       <c r="H662" t="n">
         <v>6848</v>
@@ -19683,7 +19683,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G666" t="n">
-        <v>2.85115933418274</v>
+        <v>2.85115957260132</v>
       </c>
       <c r="H666" t="n">
         <v>3592</v>
@@ -19712,7 +19712,7 @@
         <v>3</v>
       </c>
       <c r="G667" t="n">
-        <v>2.76811623573303</v>
+        <v>2.76811599731445</v>
       </c>
       <c r="H667" t="n">
         <v>3857</v>
@@ -19741,7 +19741,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G668" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H668" t="n">
         <v>18109</v>
@@ -19944,7 +19944,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>2.92497587203979</v>
+        <v>2.92497611045837</v>
       </c>
       <c r="H675" t="n">
         <v>12549</v>
@@ -20089,7 +20089,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G680" t="n">
-        <v>3.03570055961609</v>
+        <v>3.03570032119751</v>
       </c>
       <c r="H680" t="n">
         <v>6809</v>
@@ -20437,7 +20437,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G692" t="n">
-        <v>2.8327054977417</v>
+        <v>2.83270525932312</v>
       </c>
       <c r="H692" t="n">
         <v>5417</v>
@@ -20495,7 +20495,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G694" t="n">
-        <v>2.94343018531799</v>
+        <v>2.94342994689941</v>
       </c>
       <c r="H694" t="n">
         <v>2567</v>
@@ -20611,7 +20611,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G698" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H698" t="n">
         <v>581</v>
@@ -20698,7 +20698,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G701" t="n">
-        <v>2.86961340904236</v>
+        <v>2.86961364746094</v>
       </c>
       <c r="H701" t="n">
         <v>2172</v>
@@ -20872,7 +20872,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G707" t="n">
-        <v>2.98033833503723</v>
+        <v>2.98033809661865</v>
       </c>
       <c r="H707" t="n">
         <v>553</v>
@@ -20930,7 +20930,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G709" t="n">
-        <v>3.06338167190552</v>
+        <v>3.0633819103241</v>
       </c>
       <c r="H709" t="n">
         <v>10942</v>
@@ -20959,7 +20959,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>3.03570055961609</v>
+        <v>3.03570032119751</v>
       </c>
       <c r="H710" t="n">
         <v>132393</v>
@@ -21017,7 +21017,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.32173919677734</v>
+        <v>3.32173943519592</v>
       </c>
       <c r="H712" t="n">
         <v>125810</v>
@@ -21046,7 +21046,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G713" t="n">
-        <v>3.34019303321838</v>
+        <v>3.34019327163696</v>
       </c>
       <c r="H713" t="n">
         <v>29644</v>
@@ -39061,6 +39061,35 @@
         <v>977</v>
       </c>
       <c r="I1334" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1335" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>3.47000002861023</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="H1335" t="n">
+        <v>8132</v>
+      </c>
+      <c r="I1335" t="s">
         <v>9</v>
       </c>
     </row>
